--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -17866,7 +17866,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>진행 업데이트(2026-09-07) · 사이트 완료 9/21 (43%) · 완료 25 · 작업중 32</t>
+          <t>전체 완료(2026-09-14) · 사이트 완료 21/21 (100%) · 완료 57 · 작업중 0</t>
         </is>
       </c>
     </row>
@@ -17920,16 +17920,20 @@
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="F4" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
+          <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -17946,16 +17950,20 @@
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E5" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="F5" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -17972,16 +17980,20 @@
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E6" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="F6" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
+          <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -17998,16 +18010,20 @@
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E7" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="F7" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
+          <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -18024,16 +18040,20 @@
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E8" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="F8" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규 · CMS 라이브 표기였으나 실측 404</t>
+          <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
@@ -18050,16 +18070,20 @@
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E9" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="F9" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
@@ -18076,16 +18100,20 @@
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E10" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
       <c r="F10" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규</t>
+          <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
@@ -18098,16 +18126,20 @@
       <c r="C11" s="0" t="inlineStr"/>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E11" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="F11" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규</t>
+          <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
@@ -18120,16 +18152,20 @@
       <c r="C12" s="0" t="inlineStr"/>
       <c r="D12" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E12" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="F12" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -18146,10 +18182,14 @@
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E13" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="F13" s="0" t="n">
         <v>1</v>
       </c>
@@ -18172,10 +18212,14 @@
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E14" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="F14" s="0" t="n">
         <v>1</v>
       </c>
@@ -18198,10 +18242,14 @@
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E15" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="F15" s="0" t="n">
         <v>1</v>
       </c>
@@ -18224,10 +18272,14 @@
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E16" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
       <c r="F16" s="0" t="n">
         <v>1</v>
       </c>
@@ -18250,10 +18302,14 @@
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E17" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="F17" s="0" t="n">
         <v>1</v>
       </c>
@@ -18276,10 +18332,14 @@
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E18" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="F18" s="0" t="n">
         <v>1</v>
       </c>
@@ -18302,10 +18362,14 @@
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E19" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="F19" s="0" t="n">
         <v>1</v>
       </c>
@@ -18328,10 +18392,14 @@
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E20" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="F20" s="0" t="n">
         <v>1</v>
       </c>
@@ -18384,16 +18452,20 @@
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E22" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="F22" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규 · White</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨 · 요청서 미기재 신규 · White</t>
         </is>
       </c>
     </row>
@@ -18410,16 +18482,20 @@
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E23" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="F23" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t>32U721SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규</t>
+          <t>32U721SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
@@ -18469,7 +18545,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E25" s="0" t="inlineStr"/>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
       <c r="F25" s="0" t="n">
         <v>1</v>
       </c>
@@ -18492,10 +18572,14 @@
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E26" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E26" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="F26" s="0" t="n">
         <v>1</v>
       </c>
@@ -18521,7 +18605,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E27" s="0" t="inlineStr"/>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="F27" s="0" t="n">
         <v>1</v>
       </c>
@@ -18547,7 +18635,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E28" s="0" t="inlineStr"/>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="F28" s="0" t="n">
         <v>1</v>
       </c>
@@ -18633,7 +18725,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E31" s="0" t="inlineStr"/>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="F31" s="0" t="n">
         <v>1</v>
       </c>
@@ -18659,7 +18755,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E32" s="0" t="inlineStr"/>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="F32" s="0" t="n">
         <v>1</v>
       </c>
@@ -18685,7 +18785,11 @@
           <t>완료</t>
         </is>
       </c>
-      <c r="E33" s="0" t="inlineStr"/>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="F33" s="0" t="n">
         <v>1</v>
       </c>
@@ -18888,10 +18992,14 @@
       </c>
       <c r="D40" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E40" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="F40" s="0" t="n">
         <v>1</v>
       </c>
@@ -18914,10 +19022,14 @@
       </c>
       <c r="D41" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E41" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="F41" s="0" t="n">
         <v>1</v>
       </c>
@@ -18936,16 +19048,20 @@
       <c r="C42" s="0" t="inlineStr"/>
       <c r="D42" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E42" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="F42" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="0" t="inlineStr">
         <is>
-          <t>27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -18962,10 +19078,14 @@
       </c>
       <c r="D43" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E43" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="F43" s="0" t="n">
         <v>1</v>
       </c>
@@ -18988,10 +19108,14 @@
       </c>
       <c r="D44" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E44" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="F44" s="0" t="n">
         <v>1</v>
       </c>
@@ -19014,10 +19138,14 @@
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E45" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="F45" s="0" t="n">
         <v>1</v>
       </c>
@@ -19040,10 +19168,14 @@
       </c>
       <c r="D46" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E46" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="F46" s="0" t="n">
         <v>1</v>
       </c>
@@ -19182,16 +19314,20 @@
       <c r="C51" s="0" t="inlineStr"/>
       <c r="D51" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E51" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="F51" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>34U620SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>34U620SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -19204,16 +19340,20 @@
       <c r="C52" s="0" t="inlineStr"/>
       <c r="D52" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E52" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="F52" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t>34U620SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>34U620SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -19316,16 +19456,20 @@
       <c r="C56" s="0" t="inlineStr"/>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E56" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E56" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="F56" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t>27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -19398,16 +19542,20 @@
       <c r="C59" s="0" t="inlineStr"/>
       <c r="D59" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E59" s="0" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E59" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="F59" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="0" t="inlineStr">
         <is>
-          <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
         </is>
       </c>
     </row>
@@ -19424,16 +19572,20 @@
       </c>
       <c r="D60" s="0" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E60" s="0" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E60" s="0" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
       <c r="F60" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="0" t="inlineStr">
         <is>
-          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 타겟 보강(2026-09-03) · Black</t>
+          <t>27U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨 · 타겟 보강(2026-09-03) · Black</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -17866,7 +17866,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>전체 완료(2026-09-14) · 사이트 완료 21/21 (100%) · 완료 57 · 작업중 0</t>
+          <t>전체 완료(2026-09-14) · 사이트 완료 21/21 (100%) · 완료 57 · 작업중 0 · STG 작업 7건(라이브 URL 없음)</t>
         </is>
       </c>
     </row>
@@ -18139,7 +18139,7 @@
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨 · 요청서 미기재 신규</t>
+          <t>[STG 작업] 라이브 미게시 · 32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 요청서 미기재 신규 · 사이트맵·실측 확인(2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -18165,7 +18165,7 @@
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
+          <t>[STG 작업] 라이브 미게시 · 32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 사이트맵·실측 확인(2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -19061,7 +19061,7 @@
       </c>
       <c r="G42" s="0" t="inlineStr">
         <is>
-          <t>27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
+          <t>[STG 작업] 라이브 미게시 · 27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 사이트맵·실측 확인(2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -19327,7 +19327,7 @@
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>34U620SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
+          <t>[STG 작업] 라이브 미게시 · 34U620SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 사이트맵·실측 확인(2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -19353,7 +19353,7 @@
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t>34U620SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
+          <t>[STG 작업] 라이브 미게시 · 34U620SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 사이트맵·실측 확인(2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -19469,7 +19469,7 @@
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t>27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
+          <t>[STG 작업] 라이브 미게시 · 27U731SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 사이트맵·실측 확인(2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="G59" s="0" t="inlineStr">
         <is>
-          <t>32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 라이브 게시됨</t>
+          <t>[STG 작업] 라이브 미게시 · 32U701SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · 사이트맵·실측 확인(2026-09-14)</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -40145,7 +40145,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="18.13" customWidth="1" style="203" min="1" max="1"/>
@@ -40175,8 +40175,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>IT : 작업중 → 법인리뷰
-SE : 작업중 → 법인리뷰</t>
+          <t>PTT 반영(2026-09-15) · VN 완료(09-10) · AU 취소(PTT) · HU/JP 취소(법인 요청) · BG/HR/RS 취소 신규(법인 요청)</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -40274,58 +40273,62 @@
       </c>
       <c r="D10" s="263" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="E10" s="123" t="inlineStr"/>
       <c r="F10" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>PTT 7건 전부 취소(2026-09-02)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="261" t="inlineStr">
         <is>
-          <t>BR : BR (pt)</t>
+          <t>BG : BG (bg)</t>
         </is>
       </c>
       <c r="C11" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/br</t>
+          <t>https://www.lg.com/bg</t>
         </is>
       </c>
       <c r="D11" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E11" s="123" t="inlineStr"/>
+          <t>취소</t>
+        </is>
+      </c>
+      <c r="E11" s="123" t="n"/>
       <c r="F11" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>법인 취소 요청(2026-09-15)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="261" t="inlineStr">
         <is>
-          <t>CA_EN : CA (en)</t>
+          <t>BR : BR (pt)</t>
         </is>
       </c>
       <c r="C12" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en</t>
-        </is>
-      </c>
-      <c r="D12" s="265" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E12" s="123" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
+          <t>https://www.lg.com/br</t>
+        </is>
+      </c>
+      <c r="D12" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E12" s="123" t="inlineStr"/>
       <c r="F12" s="123" t="n">
         <v>1</v>
       </c>
@@ -40334,12 +40337,12 @@
     <row r="13">
       <c r="B13" s="261" t="inlineStr">
         <is>
-          <t>CA_FR : CA (fr)</t>
+          <t>CA_EN : CA (en)</t>
         </is>
       </c>
       <c r="C13" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr</t>
+          <t>https://www.lg.com/ca_en</t>
         </is>
       </c>
       <c r="D13" s="265" t="inlineStr">
@@ -40360,20 +40363,24 @@
     <row r="14">
       <c r="B14" s="261" t="inlineStr">
         <is>
-          <t>CH_DE : CH (de)</t>
+          <t>CA_FR : CA (fr)</t>
         </is>
       </c>
       <c r="C14" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ch_de</t>
-        </is>
-      </c>
-      <c r="D14" s="262" t="inlineStr">
-        <is>
-          <t>취소</t>
-        </is>
-      </c>
-      <c r="E14" s="123" t="inlineStr"/>
+          <t>https://www.lg.com/ca_fr</t>
+        </is>
+      </c>
+      <c r="D14" s="265" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E14" s="123" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
       <c r="F14" s="123" t="n">
         <v>1</v>
       </c>
@@ -40382,17 +40389,17 @@
     <row r="15">
       <c r="B15" s="261" t="inlineStr">
         <is>
-          <t>CH_FR : CH (fr)</t>
+          <t>CH_DE : CH (de)</t>
         </is>
       </c>
       <c r="C15" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ch_fr</t>
-        </is>
-      </c>
-      <c r="D15" s="264" t="inlineStr">
-        <is>
-          <t>작업중</t>
+          <t>https://www.lg.com/ch_de</t>
+        </is>
+      </c>
+      <c r="D15" s="262" t="inlineStr">
+        <is>
+          <t>취소</t>
         </is>
       </c>
       <c r="E15" s="123" t="inlineStr"/>
@@ -40404,12 +40411,12 @@
     <row r="16">
       <c r="B16" s="261" t="inlineStr">
         <is>
-          <t>CL : CL (es)</t>
+          <t>CH_FR : CH (fr)</t>
         </is>
       </c>
       <c r="C16" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cl</t>
+          <t>https://www.lg.com/ch_fr</t>
         </is>
       </c>
       <c r="D16" s="264" t="inlineStr">
@@ -40426,12 +40433,12 @@
     <row r="17">
       <c r="B17" s="261" t="inlineStr">
         <is>
-          <t>CO : CO (es)</t>
+          <t>CL : CL (es)</t>
         </is>
       </c>
       <c r="C17" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/co</t>
+          <t>https://www.lg.com/cl</t>
         </is>
       </c>
       <c r="D17" s="264" t="inlineStr">
@@ -40448,24 +40455,20 @@
     <row r="18">
       <c r="B18" s="261" t="inlineStr">
         <is>
-          <t>CZ : CZ (cz)</t>
+          <t>CO : CO (es)</t>
         </is>
       </c>
       <c r="C18" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cz</t>
-        </is>
-      </c>
-      <c r="D18" s="265" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E18" s="123" t="inlineStr">
-        <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
+          <t>https://www.lg.com/co</t>
+        </is>
+      </c>
+      <c r="D18" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E18" s="123" t="inlineStr"/>
       <c r="F18" s="123" t="n">
         <v>1</v>
       </c>
@@ -40474,12 +40477,12 @@
     <row r="19">
       <c r="B19" s="261" t="inlineStr">
         <is>
-          <t>DE : DE (de)</t>
+          <t>CZ : CZ (cz)</t>
         </is>
       </c>
       <c r="C19" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/de</t>
+          <t>https://www.lg.com/cz</t>
         </is>
       </c>
       <c r="D19" s="265" t="inlineStr">
@@ -40489,7 +40492,7 @@
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F19" s="123" t="n">
@@ -40500,20 +40503,24 @@
     <row r="20">
       <c r="B20" s="261" t="inlineStr">
         <is>
-          <t>DK : DK (da)</t>
+          <t>DE : DE (de)</t>
         </is>
       </c>
       <c r="C20" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/dk</t>
-        </is>
-      </c>
-      <c r="D20" s="264" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E20" s="123" t="inlineStr"/>
+          <t>https://www.lg.com/de</t>
+        </is>
+      </c>
+      <c r="D20" s="265" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E20" s="123" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="F20" s="123" t="n">
         <v>1</v>
       </c>
@@ -40522,12 +40529,12 @@
     <row r="21">
       <c r="B21" s="261" t="inlineStr">
         <is>
-          <t>EG_AR : EG (ar)</t>
+          <t>DK : DK (da)</t>
         </is>
       </c>
       <c r="C21" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/eg_ar</t>
+          <t>https://www.lg.com/dk</t>
         </is>
       </c>
       <c r="D21" s="264" t="inlineStr">
@@ -40544,12 +40551,12 @@
     <row r="22">
       <c r="B22" s="261" t="inlineStr">
         <is>
-          <t>EG_EN : EG (en)</t>
+          <t>EG_AR : EG (ar)</t>
         </is>
       </c>
       <c r="C22" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/eg_en</t>
+          <t>https://www.lg.com/eg_ar</t>
         </is>
       </c>
       <c r="D22" s="264" t="inlineStr">
@@ -40566,24 +40573,20 @@
     <row r="23">
       <c r="B23" s="261" t="inlineStr">
         <is>
-          <t>ES : ES (es)</t>
+          <t>EG_EN : EG (en)</t>
         </is>
       </c>
       <c r="C23" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/es</t>
-        </is>
-      </c>
-      <c r="D23" s="265" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E23" s="123" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
+          <t>https://www.lg.com/eg_en</t>
+        </is>
+      </c>
+      <c r="D23" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E23" s="123" t="inlineStr"/>
       <c r="F23" s="123" t="n">
         <v>1</v>
       </c>
@@ -40592,12 +40595,12 @@
     <row r="24">
       <c r="B24" s="261" t="inlineStr">
         <is>
-          <t>FR : FR (fr)</t>
+          <t>ES : ES (es)</t>
         </is>
       </c>
       <c r="C24" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/fr</t>
+          <t>https://www.lg.com/es</t>
         </is>
       </c>
       <c r="D24" s="265" t="inlineStr">
@@ -40607,7 +40610,7 @@
       </c>
       <c r="E24" s="123" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F24" s="123" t="n">
@@ -40618,20 +40621,24 @@
     <row r="25">
       <c r="B25" s="261" t="inlineStr">
         <is>
-          <t>HK : HK (zh)</t>
+          <t>FR : FR (fr)</t>
         </is>
       </c>
       <c r="C25" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk</t>
-        </is>
-      </c>
-      <c r="D25" s="264" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E25" s="123" t="inlineStr"/>
+          <t>https://www.lg.com/fr</t>
+        </is>
+      </c>
+      <c r="D25" s="265" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E25" s="123" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
       <c r="F25" s="123" t="n">
         <v>1</v>
       </c>
@@ -40640,12 +40647,12 @@
     <row r="26">
       <c r="B26" s="261" t="inlineStr">
         <is>
-          <t>HK_EN : HK (en)</t>
+          <t>HK : HK (zh)</t>
         </is>
       </c>
       <c r="C26" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk_en</t>
+          <t>https://www.lg.com/hk</t>
         </is>
       </c>
       <c r="D26" s="264" t="inlineStr">
@@ -40662,12 +40669,12 @@
     <row r="27">
       <c r="B27" s="261" t="inlineStr">
         <is>
-          <t>HU : HU (hu)</t>
+          <t>HK_EN : HK (en)</t>
         </is>
       </c>
       <c r="C27" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hu</t>
+          <t>https://www.lg.com/hk_en</t>
         </is>
       </c>
       <c r="D27" s="264" t="inlineStr">
@@ -40684,65 +40691,69 @@
     <row r="28">
       <c r="B28" s="261" t="inlineStr">
         <is>
-          <t>ID : ID (id)</t>
+          <t>HR : HR (hr)</t>
         </is>
       </c>
       <c r="C28" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/id</t>
+          <t>https://www.lg.com/hr</t>
         </is>
       </c>
       <c r="D28" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E28" s="123" t="inlineStr"/>
+          <t>취소</t>
+        </is>
+      </c>
+      <c r="E28" s="123" t="n"/>
       <c r="F28" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="0" t="inlineStr"/>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>법인 취소 요청(2026-09-15)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="261" t="inlineStr">
         <is>
-          <t>IN : IN (en)</t>
+          <t>HU : HU (hu)</t>
         </is>
       </c>
       <c r="C29" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/in</t>
-        </is>
-      </c>
-      <c r="D29" s="263" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E29" s="123" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
+          <t>https://www.lg.com/hu</t>
+        </is>
+      </c>
+      <c r="D29" s="264" t="inlineStr">
+        <is>
+          <t>취소</t>
+        </is>
+      </c>
+      <c r="E29" s="123" t="inlineStr"/>
       <c r="F29" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="0" t="inlineStr"/>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>법인 취소 요청(2026-09-15)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="B30" s="261" t="inlineStr">
         <is>
-          <t>IT : IT (it)</t>
+          <t>ID : ID (id)</t>
         </is>
       </c>
       <c r="C30" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/it</t>
+          <t>https://www.lg.com/id</t>
         </is>
       </c>
       <c r="D30" s="264" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E30" s="123" t="inlineStr"/>
@@ -40754,20 +40765,24 @@
     <row r="31">
       <c r="B31" s="261" t="inlineStr">
         <is>
-          <t>JP : JP (ja)</t>
+          <t>IN : IN (en)</t>
         </is>
       </c>
       <c r="C31" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp</t>
+          <t>https://www.lg.com/in</t>
         </is>
       </c>
       <c r="D31" s="263" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E31" s="123" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E31" s="123" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
       <c r="F31" s="123" t="n">
         <v>1</v>
       </c>
@@ -40776,17 +40791,17 @@
     <row r="32">
       <c r="B32" s="261" t="inlineStr">
         <is>
-          <t>KZ : KZ (ru)</t>
+          <t>IT : IT (it)</t>
         </is>
       </c>
       <c r="C32" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/kz</t>
+          <t>https://www.lg.com/it</t>
         </is>
       </c>
       <c r="D32" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E32" s="123" t="inlineStr"/>
@@ -40798,15 +40813,15 @@
     <row r="33">
       <c r="B33" s="261" t="inlineStr">
         <is>
-          <t>MA : MA (fr)</t>
+          <t>JP : JP (ja)</t>
         </is>
       </c>
       <c r="C33" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ma</t>
-        </is>
-      </c>
-      <c r="D33" s="262" t="inlineStr">
+          <t>https://www.lg.com/jp</t>
+        </is>
+      </c>
+      <c r="D33" s="263" t="inlineStr">
         <is>
           <t>취소</t>
         </is>
@@ -40815,17 +40830,21 @@
       <c r="F33" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="0" t="inlineStr"/>
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t>법인 취소 요청(2026-09-15)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="B34" s="261" t="inlineStr">
         <is>
-          <t>MX : MX (es)</t>
+          <t>KZ : KZ (ru)</t>
         </is>
       </c>
       <c r="C34" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/mx</t>
+          <t>https://www.lg.com/kz</t>
         </is>
       </c>
       <c r="D34" s="264" t="inlineStr">
@@ -40842,17 +40861,17 @@
     <row r="35">
       <c r="B35" s="261" t="inlineStr">
         <is>
-          <t>MY : MY (en)</t>
+          <t>MA : MA (fr)</t>
         </is>
       </c>
       <c r="C35" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/my</t>
-        </is>
-      </c>
-      <c r="D35" s="264" t="inlineStr">
-        <is>
-          <t>작업중</t>
+          <t>https://www.lg.com/ma</t>
+        </is>
+      </c>
+      <c r="D35" s="262" t="inlineStr">
+        <is>
+          <t>취소</t>
         </is>
       </c>
       <c r="E35" s="123" t="inlineStr"/>
@@ -40864,24 +40883,20 @@
     <row r="36">
       <c r="B36" s="261" t="inlineStr">
         <is>
-          <t>NL : NL (nl)</t>
+          <t>MX : MX (es)</t>
         </is>
       </c>
       <c r="C36" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/nl</t>
-        </is>
-      </c>
-      <c r="D36" s="265" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E36" s="123" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
+          <t>https://www.lg.com/mx</t>
+        </is>
+      </c>
+      <c r="D36" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E36" s="123" t="inlineStr"/>
       <c r="F36" s="123" t="n">
         <v>1</v>
       </c>
@@ -40890,12 +40905,12 @@
     <row r="37">
       <c r="B37" s="261" t="inlineStr">
         <is>
-          <t>NZ : NZ (en)</t>
+          <t>MY : MY (en)</t>
         </is>
       </c>
       <c r="C37" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/nz</t>
+          <t>https://www.lg.com/my</t>
         </is>
       </c>
       <c r="D37" s="264" t="inlineStr">
@@ -40912,20 +40927,24 @@
     <row r="38">
       <c r="B38" s="261" t="inlineStr">
         <is>
-          <t>PA : PA (es)</t>
+          <t>NL : NL (nl)</t>
         </is>
       </c>
       <c r="C38" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pa</t>
-        </is>
-      </c>
-      <c r="D38" s="264" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E38" s="123" t="inlineStr"/>
+          <t>https://www.lg.com/nl</t>
+        </is>
+      </c>
+      <c r="D38" s="265" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E38" s="123" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
       <c r="F38" s="123" t="n">
         <v>1</v>
       </c>
@@ -40934,12 +40953,12 @@
     <row r="39">
       <c r="B39" s="261" t="inlineStr">
         <is>
-          <t>PE : PE (es)</t>
+          <t>NZ : NZ (en)</t>
         </is>
       </c>
       <c r="C39" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pe</t>
+          <t>https://www.lg.com/nz</t>
         </is>
       </c>
       <c r="D39" s="264" t="inlineStr">
@@ -40951,17 +40970,21 @@
       <c r="F39" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G39" s="0" t="inlineStr"/>
+      <c r="G39" s="0" t="inlineStr">
+        <is>
+          <t>PTT 7건 중 3건 취소(09-14 · Hyper/Professional/Swing PLP) · 4건 WB 신규 요청</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="B40" s="261" t="inlineStr">
         <is>
-          <t>PH : PH (en)</t>
+          <t>PA : PA (es)</t>
         </is>
       </c>
       <c r="C40" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ph</t>
+          <t>https://www.lg.com/pa</t>
         </is>
       </c>
       <c r="D40" s="264" t="inlineStr">
@@ -40978,12 +41001,12 @@
     <row r="41">
       <c r="B41" s="261" t="inlineStr">
         <is>
-          <t>PL : PL (pl)</t>
+          <t>PE : PE (es)</t>
         </is>
       </c>
       <c r="C41" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pl</t>
+          <t>https://www.lg.com/pe</t>
         </is>
       </c>
       <c r="D41" s="264" t="inlineStr">
@@ -41000,12 +41023,12 @@
     <row r="42">
       <c r="B42" s="261" t="inlineStr">
         <is>
-          <t>PT : PT (pt)</t>
+          <t>PH : PH (en)</t>
         </is>
       </c>
       <c r="C42" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pt</t>
+          <t>https://www.lg.com/ph</t>
         </is>
       </c>
       <c r="D42" s="264" t="inlineStr">
@@ -41022,22 +41045,20 @@
     <row r="43">
       <c r="B43" s="261" t="inlineStr">
         <is>
-          <t>SA_AR : SA (ar)</t>
+          <t>PL : PL (pl)</t>
         </is>
       </c>
       <c r="C43" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sa</t>
-        </is>
-      </c>
-      <c r="D43" s="263" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E43" s="200" t="n">
-        <v>46246</v>
-      </c>
+          <t>https://www.lg.com/pl</t>
+        </is>
+      </c>
+      <c r="D43" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E43" s="123" t="inlineStr"/>
       <c r="F43" s="123" t="n">
         <v>1</v>
       </c>
@@ -41046,22 +41067,20 @@
     <row r="44">
       <c r="B44" s="261" t="inlineStr">
         <is>
-          <t>SA_EN : SA (en)</t>
+          <t>PT : PT (pt)</t>
         </is>
       </c>
       <c r="C44" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sa_en</t>
-        </is>
-      </c>
-      <c r="D44" s="263" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E44" s="200" t="n">
-        <v>46246</v>
-      </c>
+          <t>https://www.lg.com/pt</t>
+        </is>
+      </c>
+      <c r="D44" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E44" s="123" t="inlineStr"/>
       <c r="F44" s="123" t="n">
         <v>1</v>
       </c>
@@ -41070,42 +41089,48 @@
     <row r="45">
       <c r="B45" s="261" t="inlineStr">
         <is>
-          <t>SE : SE (sv)</t>
+          <t>RS : RS (sr)</t>
         </is>
       </c>
       <c r="C45" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/se</t>
-        </is>
-      </c>
-      <c r="D45" s="264" t="inlineStr">
-        <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E45" s="123" t="inlineStr"/>
+          <t>https://www.lg.com/rs</t>
+        </is>
+      </c>
+      <c r="D45" s="263" t="inlineStr">
+        <is>
+          <t>취소</t>
+        </is>
+      </c>
+      <c r="E45" s="200" t="n"/>
       <c r="F45" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="0" t="inlineStr"/>
+      <c r="G45" s="0" t="inlineStr">
+        <is>
+          <t>법인 취소 요청(2026-09-15)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="B46" s="261" t="inlineStr">
         <is>
-          <t>SG : SG (en)</t>
+          <t>SA_AR : SA (ar)</t>
         </is>
       </c>
       <c r="C46" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sg</t>
-        </is>
-      </c>
-      <c r="D46" s="264" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E46" s="123" t="inlineStr"/>
+          <t>https://www.lg.com/sa</t>
+        </is>
+      </c>
+      <c r="D46" s="263" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E46" s="200" t="n">
+        <v>46246</v>
+      </c>
       <c r="F46" s="123" t="n">
         <v>1</v>
       </c>
@@ -41114,20 +41139,22 @@
     <row r="47">
       <c r="B47" s="261" t="inlineStr">
         <is>
-          <t>TH : TH (th)</t>
+          <t>SA_EN : SA (en)</t>
         </is>
       </c>
       <c r="C47" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/th</t>
-        </is>
-      </c>
-      <c r="D47" s="264" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E47" s="123" t="inlineStr"/>
+          <t>https://www.lg.com/sa_en</t>
+        </is>
+      </c>
+      <c r="D47" s="263" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E47" s="200" t="n">
+        <v>46246</v>
+      </c>
       <c r="F47" s="123" t="n">
         <v>1</v>
       </c>
@@ -41136,42 +41163,34 @@
     <row r="48">
       <c r="B48" s="261" t="inlineStr">
         <is>
-          <t>TR : TR (tr)</t>
+          <t>SE : SE (sv)</t>
         </is>
       </c>
       <c r="C48" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/tr</t>
+          <t>https://www.lg.com/se</t>
         </is>
       </c>
       <c r="D48" s="264" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E48" s="123" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
+          <t>법인리뷰</t>
+        </is>
+      </c>
+      <c r="E48" s="123" t="inlineStr"/>
       <c r="F48" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="0" t="inlineStr">
-        <is>
-          <t>7건 중 6건 게시완료 · 1건 Final Live Check 잔여</t>
-        </is>
-      </c>
+      <c r="G48" s="0" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="B49" s="261" t="inlineStr">
         <is>
-          <t>TW : TW (zh)</t>
+          <t>SG : SG (en)</t>
         </is>
       </c>
       <c r="C49" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/tw</t>
+          <t>https://www.lg.com/sg</t>
         </is>
       </c>
       <c r="D49" s="264" t="inlineStr">
@@ -41188,24 +41207,20 @@
     <row r="50">
       <c r="B50" s="261" t="inlineStr">
         <is>
-          <t>UK : GB (en)</t>
+          <t>TH : TH (th)</t>
         </is>
       </c>
       <c r="C50" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/uk</t>
-        </is>
-      </c>
-      <c r="D50" s="265" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E50" s="123" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
+          <t>https://www.lg.com/th</t>
+        </is>
+      </c>
+      <c r="D50" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E50" s="123" t="inlineStr"/>
       <c r="F50" s="123" t="n">
         <v>1</v>
       </c>
@@ -41214,34 +41229,42 @@
     <row r="51">
       <c r="B51" s="261" t="inlineStr">
         <is>
-          <t>VN : VN (vi)</t>
+          <t>TR : TR (tr)</t>
         </is>
       </c>
       <c r="C51" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/vn</t>
+          <t>https://www.lg.com/tr</t>
         </is>
       </c>
       <c r="D51" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E51" s="123" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E51" s="123" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
       <c r="F51" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G51" s="0" t="inlineStr"/>
+      <c r="G51" s="0" t="inlineStr">
+        <is>
+          <t>7건 중 6건 게시완료 · 1건 Final Live Check 잔여</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="B52" s="261" t="inlineStr">
         <is>
-          <t>ZA : ZA (en)</t>
+          <t>TW : TW (zh)</t>
         </is>
       </c>
       <c r="C52" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/za</t>
+          <t>https://www.lg.com/tw</t>
         </is>
       </c>
       <c r="D52" s="264" t="inlineStr">
@@ -41254,6 +41277,88 @@
         <v>1</v>
       </c>
       <c r="G52" s="0" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="261" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C53" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk</t>
+        </is>
+      </c>
+      <c r="D53" s="265" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E53" s="123" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F53" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="0" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="261" t="inlineStr">
+        <is>
+          <t>VN : VN (vi)</t>
+        </is>
+      </c>
+      <c r="C54" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn</t>
+        </is>
+      </c>
+      <c r="D54" s="264" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E54" s="123" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="F54" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="0" t="inlineStr">
+        <is>
+          <t>7건 중 6건 게시완료(09-10) · Hyper Mini LED PLP 1건 취소(08-31)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="261" t="inlineStr">
+        <is>
+          <t>ZA : ZA (en)</t>
+        </is>
+      </c>
+      <c r="C55" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/za</t>
+        </is>
+      </c>
+      <c r="D55" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E55" s="123" t="inlineStr"/>
+      <c r="F55" s="123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="0" t="inlineStr">
+        <is>
+          <t>7건 중 1건 게시(07-27 · GNB 수정) · UltraGear evo PLP QA 리뷰 · 5건 WB 신규</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -41301,6 +41406,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -2986,6 +2986,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -3574,6 +3575,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -5564,6 +5566,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -7493,6 +7496,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -18435,7 +18439,7 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시 · 요청서 미기재 신규</t>
+          <t>24U511SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(법인) · 라이브 미게시 · 요청서 미기재 신규</t>
         </is>
       </c>
     </row>
@@ -19499,7 +19503,7 @@
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
-          <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32U501SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -19529,7 +19533,7 @@
       </c>
       <c r="G58" s="0" t="inlineStr">
         <is>
-          <t>32U721SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32U721SB · Multi AI 컴포넌트 → AI Search 컴포넌트 교체 (PDP · Gallery Image) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -20370,7 +20374,7 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>27GX704A-B · Hexagon Lighting 삭제 에셋으로 교체 (PDP) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
+          <t>27GX704A-B · Hexagon Lighting 삭제 에셋으로 교체 (PDP) · STG 준비(법인) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
         </is>
       </c>
     </row>
@@ -21228,7 +21232,7 @@
       </c>
       <c r="G55" s="0" t="inlineStr">
         <is>
-          <t>27GX704A-B · Hexagon Lighting 삭제 에셋으로 교체 (PDP) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27GX704A-B · Hexagon Lighting 삭제 에셋으로 교체 (PDP) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -21280,7 +21284,7 @@
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
-          <t>27GX704A-B · Hexagon Lighting 삭제 에셋으로 교체 (PDP) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27GX704A-B · Hexagon Lighting 삭제 에셋으로 교체 (PDP) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -35189,7 +35193,7 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>32G620B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32G620B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -35241,7 +35245,7 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>32G620B-B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
+          <t>32G620B-B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
         </is>
       </c>
     </row>
@@ -35263,7 +35267,7 @@
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>27G64NA · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27G64NA · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -35315,7 +35319,7 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>32G403B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32G403B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -35389,7 +35393,7 @@
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>27GX790B-B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
+          <t>27GX790B-B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
         </is>
       </c>
     </row>
@@ -35411,7 +35415,7 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>32G620B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32G620B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -36013,7 +36017,7 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t>24G414B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>24G414B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -36323,7 +36327,7 @@
       </c>
       <c r="G46" s="0" t="inlineStr">
         <is>
-          <t>27GX790B-B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
+          <t>27GX790B-B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
         </is>
       </c>
     </row>
@@ -36345,7 +36349,7 @@
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
-          <t>32G620B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32G620B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -36367,7 +36371,7 @@
       </c>
       <c r="G48" s="0" t="inlineStr">
         <is>
-          <t>27GX790B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27GX790B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -36755,7 +36759,7 @@
       </c>
       <c r="G62" s="0" t="inlineStr">
         <is>
-          <t>27GX790B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27GX790B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -36777,7 +36781,7 @@
       </c>
       <c r="G63" s="0" t="inlineStr">
         <is>
-          <t>32G620B-B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
+          <t>32G620B-B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
         </is>
       </c>
     </row>
@@ -37069,7 +37073,7 @@
       </c>
       <c r="G73" s="0" t="inlineStr">
         <is>
-          <t>27GX790B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27GX790B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -37151,7 +37155,7 @@
       </c>
       <c r="G76" s="0" t="inlineStr">
         <is>
-          <t>27GX790B-B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
+          <t>27GX790B-B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
         </is>
       </c>
     </row>
@@ -37173,7 +37177,7 @@
       </c>
       <c r="G77" s="0" t="inlineStr">
         <is>
-          <t>27GX790B-B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
+          <t>27GX790B-B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
         </is>
       </c>
     </row>
@@ -37195,7 +37199,7 @@
       </c>
       <c r="G78" s="0" t="inlineStr">
         <is>
-          <t>32G620B-B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
+          <t>32G620B-B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시 · CMS 라이브 표기였으나 실측 404</t>
         </is>
       </c>
     </row>
@@ -37307,7 +37311,7 @@
       </c>
       <c r="G82" s="0" t="inlineStr">
         <is>
-          <t>27GX790B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27GX790B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -37509,7 +37513,7 @@
       </c>
       <c r="G89" s="0" t="inlineStr">
         <is>
-          <t>27GX790B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27GX790B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -37531,7 +37535,7 @@
       </c>
       <c r="G90" s="0" t="inlineStr">
         <is>
-          <t>32G620B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32G620B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -37643,7 +37647,7 @@
       </c>
       <c r="G94" s="0" t="inlineStr">
         <is>
-          <t>27GX790B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27GX790B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -37665,7 +37669,7 @@
       </c>
       <c r="G95" s="0" t="inlineStr">
         <is>
-          <t>32G620B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32G620B · 모델별 변경사항 적용 (PDP · 유첨 PPT 참조) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -37844,7 +37848,7 @@
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시(CMS 라이브 표기였으나 실측 404)</t>
+          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시(CMS 라이브 표기였으나 실측 404)</t>
         </is>
       </c>
     </row>
@@ -37866,7 +37870,7 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -37888,7 +37892,7 @@
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -37910,7 +37914,7 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -37962,7 +37966,7 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -37984,7 +37988,7 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -38182,7 +38186,7 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -38204,7 +38208,7 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시(CMS 라이브 표기였으나 실측 404)</t>
+          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시(CMS 라이브 표기였으나 실측 404)</t>
         </is>
       </c>
     </row>
@@ -38316,7 +38320,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -38338,7 +38342,7 @@
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -38420,7 +38424,7 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -38442,7 +38446,7 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -38464,7 +38468,7 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -38486,7 +38490,7 @@
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -38508,7 +38512,7 @@
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -38530,7 +38534,7 @@
       </c>
       <c r="G31" s="0" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -38552,7 +38556,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -38604,7 +38608,7 @@
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -38966,7 +38970,7 @@
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -38988,7 +38992,7 @@
       </c>
       <c r="G48" s="0" t="inlineStr">
         <is>
-          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -39010,7 +39014,7 @@
       </c>
       <c r="G49" s="0" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -39032,7 +39036,7 @@
       </c>
       <c r="G50" s="0" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -39144,7 +39148,7 @@
       </c>
       <c r="G54" s="0" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -39196,7 +39200,7 @@
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32U700B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -39248,7 +39252,7 @@
       </c>
       <c r="G58" s="0" t="inlineStr">
         <is>
-          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>32U701B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -39386,7 +39390,7 @@
       </c>
       <c r="G63" s="0" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -39408,7 +39412,7 @@
       </c>
       <c r="G64" s="0" t="inlineStr">
         <is>
-          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U711B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -39430,7 +39434,7 @@
       </c>
       <c r="G65" s="0" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -39512,7 +39516,7 @@
       </c>
       <c r="G68" s="0" t="inlineStr">
         <is>
-          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U710B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -39534,7 +39538,7 @@
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(PTT) · 라이브 미게시</t>
+          <t>27U730B · MIC 문구 삭제 (Preview / Feature Card / USP Gallery) · STG 준비(법인) · 라이브 미게시</t>
         </is>
       </c>
     </row>
@@ -39658,6 +39662,7 @@
       <c r="G5" s="127" t="n"/>
     </row>
     <row r="6" ht="40.5" customHeight="1" s="203"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="136" t="inlineStr">
         <is>
@@ -40175,7 +40180,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>PTT 반영(2026-09-15) · VN 완료(09-10) · AU 취소(PTT) · HU/JP 취소(법인 요청) · BG/HR/RS 취소 신규(법인 요청)</t>
+          <t>법인 현황 반영(2026-09-15) · VN 완료(09-10) · AU 취소(법인) · HU/JP 취소(법인 요청) · BG/HR/RS 취소 신규(법인 요청)</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -40282,7 +40287,7 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>PTT 7건 전부 취소(2026-09-02)</t>
+          <t>법인 7건 전부 취소(2026-09-02)</t>
         </is>
       </c>
     </row>
@@ -40972,7 +40977,7 @@
       </c>
       <c r="G39" s="0" t="inlineStr">
         <is>
-          <t>PTT 7건 중 3건 취소(09-14 · Hyper/Professional/Swing PLP) · 4건 WB 신규 요청</t>
+          <t>법인 7건 중 3건 취소(09-14 · Hyper/Professional/Swing PLP) · 4건 신규 요청</t>
         </is>
       </c>
     </row>
@@ -41356,7 +41361,7 @@
       </c>
       <c r="G55" s="0" t="inlineStr">
         <is>
-          <t>7건 중 1건 게시(07-27 · GNB 수정) · UltraGear evo PLP QA 리뷰 · 5건 WB 신규</t>
+          <t>7건 중 1건 게시(07-27 · GNB 수정) · UltraGear evo PLP QA 리뷰 · 5건 신규 요청</t>
         </is>
       </c>
     </row>
@@ -41466,6 +41471,10 @@
       <c r="F3" s="131" t="n"/>
       <c r="G3" s="127" t="n"/>
     </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="266" t="inlineStr">
         <is>
@@ -42920,6 +42929,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -44183,6 +44193,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -44745,6 +44756,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -2986,7 +2986,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -3575,7 +3574,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -5566,7 +5564,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -7496,7 +7493,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -39662,7 +39658,6 @@
       <c r="G5" s="127" t="n"/>
     </row>
     <row r="6" ht="40.5" customHeight="1" s="203"/>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="136" t="inlineStr">
         <is>
@@ -40287,7 +40282,7 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>법인 7건 전부 취소(2026-09-02)</t>
+          <t>법인 취소(2026-09-02)</t>
         </is>
       </c>
     </row>
@@ -40977,7 +40972,7 @@
       </c>
       <c r="G39" s="0" t="inlineStr">
         <is>
-          <t>법인 7건 중 3건 취소(09-14 · Hyper/Professional/Swing PLP) · 4건 신규 요청</t>
+          <t>Hyper/Professional/Swing PLP 취소(09-14) · 나머지 신규 요청</t>
         </is>
       </c>
     </row>
@@ -41257,7 +41252,7 @@
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>7건 중 6건 게시완료 · 1건 Final Live Check 잔여</t>
+          <t>게시완료 · Final Live Check 잔여</t>
         </is>
       </c>
     </row>
@@ -41335,7 +41330,7 @@
       </c>
       <c r="G54" s="0" t="inlineStr">
         <is>
-          <t>7건 중 6건 게시완료(09-10) · Hyper Mini LED PLP 1건 취소(08-31)</t>
+          <t>게시완료(09-10) · Hyper Mini LED PLP 취소(08-31)</t>
         </is>
       </c>
     </row>
@@ -41361,7 +41356,7 @@
       </c>
       <c r="G55" s="0" t="inlineStr">
         <is>
-          <t>7건 중 1건 게시(07-27 · GNB 수정) · UltraGear evo PLP QA 리뷰 · 5건 신규 요청</t>
+          <t>GNB 수정 게시(07-27) · UltraGear evo PLP QA 리뷰 · 나머지 신규 요청</t>
         </is>
       </c>
     </row>
@@ -41471,10 +41466,6 @@
       <c r="F3" s="131" t="n"/>
       <c r="G3" s="127" t="n"/>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="266" t="inlineStr">
         <is>
@@ -42929,7 +42920,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -44193,7 +44183,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -44756,7 +44745,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -40175,7 +40175,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>법인 현황 반영(2026-09-15) · VN 완료(09-10) · AU 취소(법인) · HU/JP 취소(법인 요청) · BG/HR/RS 취소 신규(법인 요청)</t>
+          <t>법인 현황 반영(2026-09-15) · VN 완료(09-10) · AU 취소(법인) · HU/JP 취소(법인 요청) · BG/HR/RS 취소 신규(법인 요청) · CH_FR 취소(법인 요청, 09-16)</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -40421,14 +40421,18 @@
       </c>
       <c r="D16" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E16" s="123" t="inlineStr"/>
+          <t>취소</t>
+        </is>
+      </c>
+      <c r="E16" s="123" t="n"/>
       <c r="F16" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>법인 취소 요청(2026-09-16)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="261" t="inlineStr">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -27,6 +27,7 @@
     <sheet name="W32 - Digital Trends Award 삭제" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="W32 - UltraGear PDP 5모델" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="W32 - UltraFine PDP MIC 삭제" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="W38 - gram pro gallery" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,7 +39,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="70">
+  <fonts count="72">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -405,6 +406,15 @@
       <color rgb="000563C1"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -627,7 +637,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="295">
+  <cellXfs count="297">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -1211,6 +1221,8 @@
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -39581,6 +39593,1199 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" style="203" min="1" max="1"/>
+    <col width="13" customWidth="1" style="203" min="2" max="2"/>
+    <col width="13" customWidth="1" style="203" min="3" max="3"/>
+    <col width="13" customWidth="1" style="203" min="4" max="4"/>
+    <col width="13" customWidth="1" style="203" min="5" max="5"/>
+    <col width="13" customWidth="1" style="203" min="6" max="6"/>
+    <col width="13" customWidth="1" style="203" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="295" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="295" t="inlineStr">
+        <is>
+          <t>GR26-W38-MS-IT gram pro gallery 이미지 교체</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="295" t="inlineStr">
+        <is>
+          <t>이번주 추가</t>
+        </is>
+      </c>
+      <c r="B2" s="295" t="inlineStr">
+        <is>
+          <t>금주 신규 등록 · 작업중 41건 · 4모델 × 10개국 (라이브 URL 41건 실측 200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="296" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B3" s="296" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C3" s="296" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D3" s="296" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E3" s="296" t="inlineStr">
+        <is>
+          <t>완료일</t>
+        </is>
+      </c>
+      <c r="F3" s="296" t="inlineStr">
+        <is>
+          <t>Page#</t>
+        </is>
+      </c>
+      <c r="G3" s="296" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="295" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C4" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/gram-pro/16z90u-g-au75ap/</t>
+        </is>
+      </c>
+      <c r="D4" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E4" s="295" t="n"/>
+      <c r="F4" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="295" t="inlineStr">
+        <is>
+          <t>16Z90U-G.AU75AP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="295" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C5" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/gram-pro/16z90u-g-au88ap/</t>
+        </is>
+      </c>
+      <c r="D5" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E5" s="295" t="n"/>
+      <c r="F5" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="295" t="inlineStr">
+        <is>
+          <t>16Z90U-G.AU88AP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="295" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C6" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/notebooks/lg-16z90u-gal87c</t>
+        </is>
+      </c>
+      <c r="D6" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E6" s="295" t="n"/>
+      <c r="F6" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="295" t="inlineStr">
+        <is>
+          <t>16Z90U-G.AL87C</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="295" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C7" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/notebooks/lg-16z90u-gal88c</t>
+        </is>
+      </c>
+      <c r="D7" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E7" s="295" t="n"/>
+      <c r="F7" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="295" t="inlineStr">
+        <is>
+          <t>16Z90U-G.AL88C</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="295" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C8" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/notebooks/lg-16z90u-kalb7c</t>
+        </is>
+      </c>
+      <c r="D8" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E8" s="295" t="n"/>
+      <c r="F8" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="295" t="inlineStr">
+        <is>
+          <t>16Z90U-K.ALB7C</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="295" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C9" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/notebooks/lg-16z90u-kalb8c</t>
+        </is>
+      </c>
+      <c r="D9" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E9" s="295" t="n"/>
+      <c r="F9" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="295" t="inlineStr">
+        <is>
+          <t>16Z90U-K.ALB8C</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="295" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C10" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/notebooks/lg-16z90u-kalb9c</t>
+        </is>
+      </c>
+      <c r="D10" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E10" s="295" t="n"/>
+      <c r="F10" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="295" t="inlineStr">
+        <is>
+          <t>16Z90U-K.ALB9C</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="295" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C11" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/notebooks/gram-pro/16z90u-g-au78gn/</t>
+        </is>
+      </c>
+      <c r="D11" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E11" s="295" t="n"/>
+      <c r="F11" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="295" t="inlineStr">
+        <is>
+          <t>16Z90U-G.AU78GN</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL : GLOBAL (en)</t>
+        </is>
+      </c>
+      <c r="C12" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram-pro/16z90u/</t>
+        </is>
+      </c>
+      <c r="D12" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E12" s="295" t="n"/>
+      <c r="F12" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="295" t="inlineStr">
+        <is>
+          <t>16Z90U-K.AUA8GN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="295" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C13" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram-pro/16z90u-k-aua5a3/</t>
+        </is>
+      </c>
+      <c r="D13" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E13" s="295" t="n"/>
+      <c r="F13" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="295" t="inlineStr">
+        <is>
+          <t>16Z90U-K.AUA5A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="295" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C14" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram-pro/16z90u-k-aub5a3/</t>
+        </is>
+      </c>
+      <c r="D14" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E14" s="295" t="n"/>
+      <c r="F14" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="295" t="inlineStr">
+        <is>
+          <t>16Z90U-K.AUB5A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="295" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C15" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram-pro/16z90u-k-aub9a3/</t>
+        </is>
+      </c>
+      <c r="D15" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E15" s="295" t="n"/>
+      <c r="F15" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="295" t="inlineStr">
+        <is>
+          <t>16Z90U-K.AUB9A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="295" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C16" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/business/it-products/lg-gram/16z90u-k-azb5a3/</t>
+        </is>
+      </c>
+      <c r="D16" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E16" s="295" t="n"/>
+      <c r="F16" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="295" t="inlineStr">
+        <is>
+          <t>16Z90U-K.AZB5A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="295" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C17" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/laptops/gram-pro/16z90u-h-au78an/</t>
+        </is>
+      </c>
+      <c r="D17" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E17" s="295" t="n"/>
+      <c r="F17" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="295" t="inlineStr">
+        <is>
+          <t>16Z90U-H.AU78AN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="295" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C18" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/laptops/gram-pro/16z90u-k-aub8an/</t>
+        </is>
+      </c>
+      <c r="D18" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E18" s="295" t="n"/>
+      <c r="F18" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="295" t="inlineStr">
+        <is>
+          <t>16Z90U-K.AUB8AN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="295" t="inlineStr">
+        <is>
+          <t>VN : VN (vi)</t>
+        </is>
+      </c>
+      <c r="C19" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/laptop-lg-gram/16z90u-g-16gb/</t>
+        </is>
+      </c>
+      <c r="D19" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E19" s="295" t="n"/>
+      <c r="F19" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="295" t="inlineStr">
+        <is>
+          <t>16Z90U-G.AN55A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="295" t="inlineStr">
+        <is>
+          <t>VN : VN (vi)</t>
+        </is>
+      </c>
+      <c r="C20" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/laptop-lg-gram/16z90u-g-32gb/</t>
+        </is>
+      </c>
+      <c r="D20" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E20" s="295" t="n"/>
+      <c r="F20" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="295" t="inlineStr">
+        <is>
+          <t>16Z90U-G.AV85A5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="295" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C21" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au75ap/</t>
+        </is>
+      </c>
+      <c r="D21" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E21" s="295" t="n"/>
+      <c r="F21" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="295" t="inlineStr">
+        <is>
+          <t>17Z90U-G.AU75AP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="295" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C22" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au78ap/</t>
+        </is>
+      </c>
+      <c r="D22" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E22" s="295" t="n"/>
+      <c r="F22" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="295" t="inlineStr">
+        <is>
+          <t>17Z90U-G.AU78AP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="295" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C23" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au88ap/</t>
+        </is>
+      </c>
+      <c r="D23" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E23" s="295" t="n"/>
+      <c r="F23" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="295" t="inlineStr">
+        <is>
+          <t>17Z90U-G.AU88AP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="295" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C24" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/monitors-pcs/laptops/gram-pro/17z90u-g/</t>
+        </is>
+      </c>
+      <c r="D24" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E24" s="295" t="n"/>
+      <c r="F24" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="295" t="inlineStr">
+        <is>
+          <t>17Z90U-G.AU78A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="295" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C25" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90u-g78/</t>
+        </is>
+      </c>
+      <c r="D25" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E25" s="295" t="n"/>
+      <c r="F25" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="295" t="inlineStr">
+        <is>
+          <t>17Z90U-G.AU78A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="295" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C26" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90u-g88/</t>
+        </is>
+      </c>
+      <c r="D26" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E26" s="295" t="n"/>
+      <c r="F26" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="295" t="inlineStr">
+        <is>
+          <t>17Z90U-G.AU88A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="295" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C27" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/business/moniteurs-et-pc/ordinateurs-portables/gram-pro/17z90u-g/</t>
+        </is>
+      </c>
+      <c r="D27" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E27" s="295" t="n"/>
+      <c r="F27" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="295" t="inlineStr">
+        <is>
+          <t>17Z90U-G.AU88A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="295" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C28" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17z90u-g78/</t>
+        </is>
+      </c>
+      <c r="D28" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E28" s="295" t="n"/>
+      <c r="F28" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="295" t="inlineStr">
+        <is>
+          <t>17Z90U-G.AU78A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="295" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C29" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17z90u-g88/</t>
+        </is>
+      </c>
+      <c r="D29" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E29" s="295" t="n"/>
+      <c r="F29" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="295" t="inlineStr">
+        <is>
+          <t>17Z90U-G.AU88A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="295" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C30" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/notebooks/lg-17z90u-al87c</t>
+        </is>
+      </c>
+      <c r="D30" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E30" s="295" t="n"/>
+      <c r="F30" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="295" t="inlineStr">
+        <is>
+          <t>17Z90U-G.AL87C</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="295" t="inlineStr">
+        <is>
+          <t>CN : CN (zh)</t>
+        </is>
+      </c>
+      <c r="C31" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/notebooks/lg-17z90u-gal88c</t>
+        </is>
+      </c>
+      <c r="D31" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E31" s="295" t="n"/>
+      <c r="F31" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="295" t="inlineStr">
+        <is>
+          <t>17Z90U-G.AL88C</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="295" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C32" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/notebooks/gram-pro/17z90u-g-au78gn/</t>
+        </is>
+      </c>
+      <c r="D32" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E32" s="295" t="n"/>
+      <c r="F32" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="295" t="inlineStr">
+        <is>
+          <t>17Z90U-G.AU78GN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="295" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C33" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/notebooks/gram-pro/17z90u-g-au8bgn/</t>
+        </is>
+      </c>
+      <c r="D33" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E33" s="295" t="n"/>
+      <c r="F33" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="295" t="inlineStr">
+        <is>
+          <t>17Z90U-G.AU8BGN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL : GLOBAL (en)</t>
+        </is>
+      </c>
+      <c r="C34" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram-pro/17z90u/</t>
+        </is>
+      </c>
+      <c r="D34" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E34" s="295" t="n"/>
+      <c r="F34" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="295" t="inlineStr">
+        <is>
+          <t>17Z90U-G.AU88AP</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="295" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C35" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/notebook/gram-pro/17z90u-g-au78dn/</t>
+        </is>
+      </c>
+      <c r="D35" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E35" s="295" t="n"/>
+      <c r="F35" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="295" t="inlineStr">
+        <is>
+          <t>17Z90U-G.AU78DN</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="295" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C36" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/gram/17z90u-g-au85a3/</t>
+        </is>
+      </c>
+      <c r="D36" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E36" s="295" t="n"/>
+      <c r="F36" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="295" t="inlineStr">
+        <is>
+          <t>17Z90U-G.AU85A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="295" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C37" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/laptops/gram-pro/17z90u-g-au78an/</t>
+        </is>
+      </c>
+      <c r="D37" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E37" s="295" t="n"/>
+      <c r="F37" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="295" t="inlineStr">
+        <is>
+          <t>17Z90U-G.AU78AN</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="295" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C38" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90ur-p/</t>
+        </is>
+      </c>
+      <c r="D38" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E38" s="295" t="n"/>
+      <c r="F38" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="295" t="inlineStr">
+        <is>
+          <t>17Z90UR-P.AU9CA9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="295" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C39" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17Z90ur-p/</t>
+        </is>
+      </c>
+      <c r="D39" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E39" s="295" t="n"/>
+      <c r="F39" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="295" t="inlineStr">
+        <is>
+          <t>17Z90UR-P.AU9CA9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL : GLOBAL (en)</t>
+        </is>
+      </c>
+      <c r="C40" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram-pro/17z90ur/</t>
+        </is>
+      </c>
+      <c r="D40" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E40" s="295" t="n"/>
+      <c r="F40" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="295" t="inlineStr">
+        <is>
+          <t>17Z90UR-P.AU99U3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="295" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C41" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90ub-h/</t>
+        </is>
+      </c>
+      <c r="D41" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E41" s="295" t="n"/>
+      <c r="F41" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="295" t="inlineStr">
+        <is>
+          <t>17Z90UB-H.AU89A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="295" t="inlineStr">
+        <is>
+          <t>CA_FR : CA (fr)</t>
+        </is>
+      </c>
+      <c r="C42" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17z90ub-h/</t>
+        </is>
+      </c>
+      <c r="D42" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E42" s="295" t="n"/>
+      <c r="F42" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="295" t="inlineStr">
+        <is>
+          <t>17Z90UB-H.AU89A9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL : GLOBAL (en)</t>
+        </is>
+      </c>
+      <c r="C43" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram-pro/17z90ub/</t>
+        </is>
+      </c>
+      <c r="D43" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E43" s="295" t="n"/>
+      <c r="F43" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="295" t="inlineStr">
+        <is>
+          <t>17Z90UB-H.AU99AN</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="295" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C44" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/notebook/gram-pro/17z90ub-h-au79dn/</t>
+        </is>
+      </c>
+      <c r="D44" s="295" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E44" s="295" t="n"/>
+      <c r="F44" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="295" t="inlineStr">
+        <is>
+          <t>17Z90UB-H.AU79DN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId41"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -20,7 +20,7 @@
     <sheet name="W30 - SmartMonitor ScreenShare" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="W30 - UltraGear 1000Hz FAQ" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="W31 - gram Secure Lock" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="W31 - Windows 11 Landing" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Windows 11 Landing" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="W31 - PDP Gallery Win11 Pro" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="W31 - Smart Monitor Multi AI" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="W32 - UltraGear 27GX704A" sheetId="21" state="visible" r:id="rId21"/>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>GR26-W31-MS-IT Windows 11 Home Landing Page 업데이트</t>
+          <t>GR26-MS-IT Windows 11 Home Landing Page 업데이트</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -39599,7 +39599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="203" min="1" max="1"/>
@@ -39631,7 +39631,7 @@
       </c>
       <c r="B2" s="295" t="inlineStr">
         <is>
-          <t>금주 신규 등록 · 작업중 41건 · 4모델 × 10개국 (라이브 URL 41건 실측 200)</t>
+          <t>목록 갱신 · 작업중 29건 · 4모델 × 9개국 (CN 제외) · 라이브 URL 29건 실측 200</t>
         </is>
       </c>
     </row>
@@ -39727,12 +39727,12 @@
     <row r="6">
       <c r="B6" s="295" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>DE : DE (de)</t>
         </is>
       </c>
       <c r="C6" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/notebooks/lg-16z90u-gal87c</t>
+          <t>https://www.lg.com/de/notebooks/gram-pro/16z90u-g-au78gn/</t>
         </is>
       </c>
       <c r="D6" s="295" t="inlineStr">
@@ -39746,19 +39746,19 @@
       </c>
       <c r="G6" s="295" t="inlineStr">
         <is>
-          <t>16Z90U-G.AL87C</t>
+          <t>16Z90U-G.AU78GN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="295" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>SG : SG (en)</t>
         </is>
       </c>
       <c r="C7" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/notebooks/lg-16z90u-gal88c</t>
+          <t>https://www.lg.com/sg/laptops/gram-pro/16z90u-k-aua5a3/</t>
         </is>
       </c>
       <c r="D7" s="295" t="inlineStr">
@@ -39772,19 +39772,19 @@
       </c>
       <c r="G7" s="295" t="inlineStr">
         <is>
-          <t>16Z90U-G.AL88C</t>
+          <t>16Z90U-K.AUA5A3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="295" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>SG : SG (en)</t>
         </is>
       </c>
       <c r="C8" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/notebooks/lg-16z90u-kalb7c</t>
+          <t>https://www.lg.com/sg/laptops/gram-pro/16z90u-k-aub5a3/</t>
         </is>
       </c>
       <c r="D8" s="295" t="inlineStr">
@@ -39798,19 +39798,19 @@
       </c>
       <c r="G8" s="295" t="inlineStr">
         <is>
-          <t>16Z90U-K.ALB7C</t>
+          <t>16Z90U-K.AUB5A3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="295" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>SG : SG (en)</t>
         </is>
       </c>
       <c r="C9" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/notebooks/lg-16z90u-kalb8c</t>
+          <t>https://www.lg.com/sg/laptops/gram-pro/16z90u-k-aub9a3/</t>
         </is>
       </c>
       <c r="D9" s="295" t="inlineStr">
@@ -39824,19 +39824,19 @@
       </c>
       <c r="G9" s="295" t="inlineStr">
         <is>
-          <t>16Z90U-K.ALB8C</t>
+          <t>16Z90U-K.AUB9A3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="295" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>SG : SG (en)</t>
         </is>
       </c>
       <c r="C10" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/notebooks/lg-16z90u-kalb9c</t>
+          <t>https://www.lg.com/sg/business/it-products/lg-gram/16z90u-k-azb5a3/</t>
         </is>
       </c>
       <c r="D10" s="295" t="inlineStr">
@@ -39850,19 +39850,19 @@
       </c>
       <c r="G10" s="295" t="inlineStr">
         <is>
-          <t>16Z90U-K.ALB9C</t>
+          <t>16Z90U-K.AZB5A3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="295" t="inlineStr">
         <is>
-          <t>DE : DE (de)</t>
+          <t>UK : GB (en)</t>
         </is>
       </c>
       <c r="C11" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/de/notebooks/gram-pro/16z90u-g-au78gn/</t>
+          <t>https://www.lg.com/uk/laptops/gram-pro/16z90u-h-au78an/</t>
         </is>
       </c>
       <c r="D11" s="295" t="inlineStr">
@@ -39876,19 +39876,19 @@
       </c>
       <c r="G11" s="295" t="inlineStr">
         <is>
-          <t>16Z90U-G.AU78GN</t>
+          <t>16Z90U-H.AU78AN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="295" t="inlineStr">
         <is>
-          <t>GLOBAL : GLOBAL (en)</t>
+          <t>UK : GB (en)</t>
         </is>
       </c>
       <c r="C12" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram-pro/16z90u/</t>
+          <t>https://www.lg.com/uk/laptops/gram-pro/16z90u-k-aub8an/</t>
         </is>
       </c>
       <c r="D12" s="295" t="inlineStr">
@@ -39902,19 +39902,19 @@
       </c>
       <c r="G12" s="295" t="inlineStr">
         <is>
-          <t>16Z90U-K.AUA8GN</t>
+          <t>16Z90U-K.AUB8AN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="295" t="inlineStr">
         <is>
-          <t>SG : SG (en)</t>
+          <t>VN : VN (vi)</t>
         </is>
       </c>
       <c r="C13" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sg/laptops/gram-pro/16z90u-k-aua5a3/</t>
+          <t>https://www.lg.com/vn/laptop-lg-gram/16z90u-g-16gb/</t>
         </is>
       </c>
       <c r="D13" s="295" t="inlineStr">
@@ -39928,19 +39928,19 @@
       </c>
       <c r="G13" s="295" t="inlineStr">
         <is>
-          <t>16Z90U-K.AUA5A3</t>
+          <t>16Z90U-G.AN55A5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="295" t="inlineStr">
         <is>
-          <t>SG : SG (en)</t>
+          <t>VN : VN (vi)</t>
         </is>
       </c>
       <c r="C14" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sg/laptops/gram-pro/16z90u-k-aub5a3/</t>
+          <t>https://www.lg.com/vn/laptop-lg-gram/16z90u-g-32gb/</t>
         </is>
       </c>
       <c r="D14" s="295" t="inlineStr">
@@ -39954,19 +39954,19 @@
       </c>
       <c r="G14" s="295" t="inlineStr">
         <is>
-          <t>16Z90U-K.AUB5A3</t>
+          <t>16Z90U-G.AV85A5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="295" t="inlineStr">
         <is>
-          <t>SG : SG (en)</t>
+          <t>AU : AU (en)</t>
         </is>
       </c>
       <c r="C15" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sg/laptops/gram-pro/16z90u-k-aub9a3/</t>
+          <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au75ap/</t>
         </is>
       </c>
       <c r="D15" s="295" t="inlineStr">
@@ -39980,19 +39980,19 @@
       </c>
       <c r="G15" s="295" t="inlineStr">
         <is>
-          <t>16Z90U-K.AUB9A3</t>
+          <t>17Z90U-G.AU75AP</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="295" t="inlineStr">
         <is>
-          <t>SG : SG (en)</t>
+          <t>AU : AU (en)</t>
         </is>
       </c>
       <c r="C16" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sg/business/it-products/lg-gram/16z90u-k-azb5a3/</t>
+          <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au78ap/</t>
         </is>
       </c>
       <c r="D16" s="295" t="inlineStr">
@@ -40006,19 +40006,19 @@
       </c>
       <c r="G16" s="295" t="inlineStr">
         <is>
-          <t>16Z90U-K.AZB5A3</t>
+          <t>17Z90U-G.AU78AP</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="295" t="inlineStr">
         <is>
-          <t>UK : GB (en)</t>
+          <t>AU : AU (en)</t>
         </is>
       </c>
       <c r="C17" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/uk/laptops/gram-pro/16z90u-h-au78an/</t>
+          <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au88ap/</t>
         </is>
       </c>
       <c r="D17" s="295" t="inlineStr">
@@ -40032,19 +40032,19 @@
       </c>
       <c r="G17" s="295" t="inlineStr">
         <is>
-          <t>16Z90U-H.AU78AN</t>
+          <t>17Z90U-G.AU88AP</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="295" t="inlineStr">
         <is>
-          <t>UK : GB (en)</t>
+          <t>CA_EN : CA (en)</t>
         </is>
       </c>
       <c r="C18" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/uk/laptops/gram-pro/16z90u-k-aub8an/</t>
+          <t>https://www.lg.com/ca_en/business/monitors-pcs/laptops/gram-pro/17z90u-g/</t>
         </is>
       </c>
       <c r="D18" s="295" t="inlineStr">
@@ -40058,19 +40058,19 @@
       </c>
       <c r="G18" s="295" t="inlineStr">
         <is>
-          <t>16Z90U-K.AUB8AN</t>
+          <t>17Z90U-G.AU78A9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="295" t="inlineStr">
         <is>
-          <t>VN : VN (vi)</t>
+          <t>CA_FR : CA (fr)</t>
         </is>
       </c>
       <c r="C19" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/vn/laptop-lg-gram/16z90u-g-16gb/</t>
+          <t>https://www.lg.com/ca_fr/business/moniteurs-et-pc/ordinateurs-portables/gram-pro/17z90u-g/</t>
         </is>
       </c>
       <c r="D19" s="295" t="inlineStr">
@@ -40084,19 +40084,19 @@
       </c>
       <c r="G19" s="295" t="inlineStr">
         <is>
-          <t>16Z90U-G.AN55A5</t>
+          <t>17Z90U-G.AU88A9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="295" t="inlineStr">
         <is>
-          <t>VN : VN (vi)</t>
+          <t>DE : DE (de)</t>
         </is>
       </c>
       <c r="C20" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/vn/laptop-lg-gram/16z90u-g-32gb/</t>
+          <t>https://www.lg.com/de/notebooks/gram-pro/17z90u-g-au78gn/</t>
         </is>
       </c>
       <c r="D20" s="295" t="inlineStr">
@@ -40110,19 +40110,19 @@
       </c>
       <c r="G20" s="295" t="inlineStr">
         <is>
-          <t>16Z90U-G.AV85A5</t>
+          <t>17Z90U-G.AU78GN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="295" t="inlineStr">
         <is>
-          <t>AU : AU (en)</t>
+          <t>DE : DE (de)</t>
         </is>
       </c>
       <c r="C21" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au75ap/</t>
+          <t>https://www.lg.com/de/notebooks/gram-pro/17z90u-g-au8bgn/</t>
         </is>
       </c>
       <c r="D21" s="295" t="inlineStr">
@@ -40136,19 +40136,19 @@
       </c>
       <c r="G21" s="295" t="inlineStr">
         <is>
-          <t>17Z90U-G.AU75AP</t>
+          <t>17Z90U-G.AU8BGN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="295" t="inlineStr">
         <is>
-          <t>AU : AU (en)</t>
+          <t>GLOBAL : GLOBAL (en)</t>
         </is>
       </c>
       <c r="C22" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au78ap/</t>
+          <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram-pro/17z90u/</t>
         </is>
       </c>
       <c r="D22" s="295" t="inlineStr">
@@ -40162,19 +40162,19 @@
       </c>
       <c r="G22" s="295" t="inlineStr">
         <is>
-          <t>17Z90U-G.AU78AP</t>
+          <t>17Z90U-G.AU88AP</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="295" t="inlineStr">
         <is>
-          <t>AU : AU (en)</t>
+          <t>IT : IT (it)</t>
         </is>
       </c>
       <c r="C23" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/au/laptops/gram-pro/17z90u-g-au88ap/</t>
+          <t>https://www.lg.com/it/notebook/gram-pro/17z90u-g-au78dn/</t>
         </is>
       </c>
       <c r="D23" s="295" t="inlineStr">
@@ -40188,19 +40188,19 @@
       </c>
       <c r="G23" s="295" t="inlineStr">
         <is>
-          <t>17Z90U-G.AU88AP</t>
+          <t>17Z90U-G.AU78DN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="295" t="inlineStr">
         <is>
-          <t>CA_EN : CA (en)</t>
+          <t>SG : SG (en)</t>
         </is>
       </c>
       <c r="C24" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en/business/monitors-pcs/laptops/gram-pro/17z90u-g/</t>
+          <t>https://www.lg.com/sg/laptops/gram/17z90u-g-au85a3/</t>
         </is>
       </c>
       <c r="D24" s="295" t="inlineStr">
@@ -40214,19 +40214,19 @@
       </c>
       <c r="G24" s="295" t="inlineStr">
         <is>
-          <t>17Z90U-G.AU78A9</t>
+          <t>17Z90U-G.AU85A3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="295" t="inlineStr">
         <is>
-          <t>CA_EN : CA (en)</t>
+          <t>UK : GB (en)</t>
         </is>
       </c>
       <c r="C25" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90u-g78/</t>
+          <t>https://www.lg.com/uk/laptops/gram-pro/17z90u-g-au78an/</t>
         </is>
       </c>
       <c r="D25" s="295" t="inlineStr">
@@ -40240,7 +40240,7 @@
       </c>
       <c r="G25" s="295" t="inlineStr">
         <is>
-          <t>17Z90U-G.AU78A9</t>
+          <t>17Z90U-G.AU78AN</t>
         </is>
       </c>
     </row>
@@ -40252,7 +40252,7 @@
       </c>
       <c r="C26" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90u-g88/</t>
+          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90ur-p/</t>
         </is>
       </c>
       <c r="D26" s="295" t="inlineStr">
@@ -40266,7 +40266,7 @@
       </c>
       <c r="G26" s="295" t="inlineStr">
         <is>
-          <t>17Z90U-G.AU88A9</t>
+          <t>17Z90UR-P.AU9CA9</t>
         </is>
       </c>
     </row>
@@ -40278,7 +40278,7 @@
       </c>
       <c r="C27" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/business/moniteurs-et-pc/ordinateurs-portables/gram-pro/17z90u-g/</t>
+          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17Z90ur-p/</t>
         </is>
       </c>
       <c r="D27" s="295" t="inlineStr">
@@ -40292,19 +40292,19 @@
       </c>
       <c r="G27" s="295" t="inlineStr">
         <is>
-          <t>17Z90U-G.AU88A9</t>
+          <t>17Z90UR-P.AU9CA9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="295" t="inlineStr">
         <is>
-          <t>CA_FR : CA (fr)</t>
+          <t>GLOBAL : GLOBAL (en)</t>
         </is>
       </c>
       <c r="C28" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17z90u-g78/</t>
+          <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram-pro/17z90ur/</t>
         </is>
       </c>
       <c r="D28" s="295" t="inlineStr">
@@ -40318,19 +40318,19 @@
       </c>
       <c r="G28" s="295" t="inlineStr">
         <is>
-          <t>17Z90U-G.AU78A9</t>
+          <t>17Z90UR-P.AU99U3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="295" t="inlineStr">
         <is>
-          <t>CA_FR : CA (fr)</t>
+          <t>CA_EN : CA (en)</t>
         </is>
       </c>
       <c r="C29" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17z90u-g88/</t>
+          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90ub-h/</t>
         </is>
       </c>
       <c r="D29" s="295" t="inlineStr">
@@ -40344,19 +40344,19 @@
       </c>
       <c r="G29" s="295" t="inlineStr">
         <is>
-          <t>17Z90U-G.AU88A9</t>
+          <t>17Z90UB-H.AU89A9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="295" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>CA_FR : CA (fr)</t>
         </is>
       </c>
       <c r="C30" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/notebooks/lg-17z90u-al87c</t>
+          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17z90ub-h/</t>
         </is>
       </c>
       <c r="D30" s="295" t="inlineStr">
@@ -40370,19 +40370,19 @@
       </c>
       <c r="G30" s="295" t="inlineStr">
         <is>
-          <t>17Z90U-G.AL87C</t>
+          <t>17Z90UB-H.AU89A9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="295" t="inlineStr">
         <is>
-          <t>CN : CN (zh)</t>
+          <t>GLOBAL : GLOBAL (en)</t>
         </is>
       </c>
       <c r="C31" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cn/notebooks/lg-17z90u-gal88c</t>
+          <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram-pro/17z90ub/</t>
         </is>
       </c>
       <c r="D31" s="295" t="inlineStr">
@@ -40396,19 +40396,19 @@
       </c>
       <c r="G31" s="295" t="inlineStr">
         <is>
-          <t>17Z90U-G.AL88C</t>
+          <t>17Z90UB-H.AU99AN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="295" t="inlineStr">
         <is>
-          <t>DE : DE (de)</t>
+          <t>IT : IT (it)</t>
         </is>
       </c>
       <c r="C32" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/de/notebooks/gram-pro/17z90u-g-au78gn/</t>
+          <t>https://www.lg.com/it/notebook/gram-pro/17z90ub-h-au79dn/</t>
         </is>
       </c>
       <c r="D32" s="295" t="inlineStr">
@@ -40421,318 +40421,6 @@
         <v>1</v>
       </c>
       <c r="G32" s="295" t="inlineStr">
-        <is>
-          <t>17Z90U-G.AU78GN</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="295" t="inlineStr">
-        <is>
-          <t>DE : DE (de)</t>
-        </is>
-      </c>
-      <c r="C33" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/de/notebooks/gram-pro/17z90u-g-au8bgn/</t>
-        </is>
-      </c>
-      <c r="D33" s="295" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E33" s="295" t="n"/>
-      <c r="F33" s="295" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="295" t="inlineStr">
-        <is>
-          <t>17Z90U-G.AU8BGN</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="295" t="inlineStr">
-        <is>
-          <t>GLOBAL : GLOBAL (en)</t>
-        </is>
-      </c>
-      <c r="C34" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram-pro/17z90u/</t>
-        </is>
-      </c>
-      <c r="D34" s="295" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E34" s="295" t="n"/>
-      <c r="F34" s="295" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="295" t="inlineStr">
-        <is>
-          <t>17Z90U-G.AU88AP</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="295" t="inlineStr">
-        <is>
-          <t>IT : IT (it)</t>
-        </is>
-      </c>
-      <c r="C35" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/it/notebook/gram-pro/17z90u-g-au78dn/</t>
-        </is>
-      </c>
-      <c r="D35" s="295" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E35" s="295" t="n"/>
-      <c r="F35" s="295" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="295" t="inlineStr">
-        <is>
-          <t>17Z90U-G.AU78DN</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="295" t="inlineStr">
-        <is>
-          <t>SG : SG (en)</t>
-        </is>
-      </c>
-      <c r="C36" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sg/laptops/gram/17z90u-g-au85a3/</t>
-        </is>
-      </c>
-      <c r="D36" s="295" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E36" s="295" t="n"/>
-      <c r="F36" s="295" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" s="295" t="inlineStr">
-        <is>
-          <t>17Z90U-G.AU85A3</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="295" t="inlineStr">
-        <is>
-          <t>UK : GB (en)</t>
-        </is>
-      </c>
-      <c r="C37" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/uk/laptops/gram-pro/17z90u-g-au78an/</t>
-        </is>
-      </c>
-      <c r="D37" s="295" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E37" s="295" t="n"/>
-      <c r="F37" s="295" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" s="295" t="inlineStr">
-        <is>
-          <t>17Z90U-G.AU78AN</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="295" t="inlineStr">
-        <is>
-          <t>CA_EN : CA (en)</t>
-        </is>
-      </c>
-      <c r="C38" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90ur-p/</t>
-        </is>
-      </c>
-      <c r="D38" s="295" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E38" s="295" t="n"/>
-      <c r="F38" s="295" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="295" t="inlineStr">
-        <is>
-          <t>17Z90UR-P.AU9CA9</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="295" t="inlineStr">
-        <is>
-          <t>CA_FR : CA (fr)</t>
-        </is>
-      </c>
-      <c r="C39" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17Z90ur-p/</t>
-        </is>
-      </c>
-      <c r="D39" s="295" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E39" s="295" t="n"/>
-      <c r="F39" s="295" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="295" t="inlineStr">
-        <is>
-          <t>17Z90UR-P.AU9CA9</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="295" t="inlineStr">
-        <is>
-          <t>GLOBAL : GLOBAL (en)</t>
-        </is>
-      </c>
-      <c r="C40" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram-pro/17z90ur/</t>
-        </is>
-      </c>
-      <c r="D40" s="295" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E40" s="295" t="n"/>
-      <c r="F40" s="295" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="295" t="inlineStr">
-        <is>
-          <t>17Z90UR-P.AU99U3</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="295" t="inlineStr">
-        <is>
-          <t>CA_EN : CA (en)</t>
-        </is>
-      </c>
-      <c r="C41" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ca_en/laptops/all-laptops/17z90ub-h/</t>
-        </is>
-      </c>
-      <c r="D41" s="295" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E41" s="295" t="n"/>
-      <c r="F41" s="295" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="295" t="inlineStr">
-        <is>
-          <t>17Z90UB-H.AU89A9</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="295" t="inlineStr">
-        <is>
-          <t>CA_FR : CA (fr)</t>
-        </is>
-      </c>
-      <c r="C42" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ca_fr/computing/purchase-guide/laptops/17z90ub-h/</t>
-        </is>
-      </c>
-      <c r="D42" s="295" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E42" s="295" t="n"/>
-      <c r="F42" s="295" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="295" t="inlineStr">
-        <is>
-          <t>17Z90UB-H.AU89A9</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="295" t="inlineStr">
-        <is>
-          <t>GLOBAL : GLOBAL (en)</t>
-        </is>
-      </c>
-      <c r="C43" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram-pro/17z90ub/</t>
-        </is>
-      </c>
-      <c r="D43" s="295" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E43" s="295" t="n"/>
-      <c r="F43" s="295" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="295" t="inlineStr">
-        <is>
-          <t>17Z90UB-H.AU99AN</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="295" t="inlineStr">
-        <is>
-          <t>IT : IT (it)</t>
-        </is>
-      </c>
-      <c r="C44" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/it/notebook/gram-pro/17z90ub-h-au79dn/</t>
-        </is>
-      </c>
-      <c r="D44" s="295" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E44" s="295" t="n"/>
-      <c r="F44" s="295" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="295" t="inlineStr">
         <is>
           <t>17Z90UB-H.AU79DN</t>
         </is>
@@ -40769,18 +40457,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -2998,6 +2998,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -3586,6 +3587,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -5576,6 +5578,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -7505,6 +7508,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -39631,7 +39635,7 @@
       </c>
       <c r="B2" s="295" t="inlineStr">
         <is>
-          <t>목록 갱신 · 작업중 29건 · 4모델 × 9개국 (CN 제외) · 라이브 URL 29건 실측 200</t>
+          <t>전건 완료 — gram pro gallery 이미지 교체 29건 · 4모델 × 9개국 (CN 제외)</t>
         </is>
       </c>
     </row>
@@ -39685,10 +39689,14 @@
       </c>
       <c r="D4" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E4" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E4" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F4" s="295" t="n">
         <v>1</v>
       </c>
@@ -39711,10 +39719,14 @@
       </c>
       <c r="D5" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E5" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E5" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F5" s="295" t="n">
         <v>1</v>
       </c>
@@ -39737,10 +39749,14 @@
       </c>
       <c r="D6" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E6" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E6" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F6" s="295" t="n">
         <v>1</v>
       </c>
@@ -39763,10 +39779,14 @@
       </c>
       <c r="D7" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E7" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E7" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F7" s="295" t="n">
         <v>1</v>
       </c>
@@ -39789,10 +39809,14 @@
       </c>
       <c r="D8" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E8" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E8" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F8" s="295" t="n">
         <v>1</v>
       </c>
@@ -39815,10 +39839,14 @@
       </c>
       <c r="D9" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E9" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E9" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F9" s="295" t="n">
         <v>1</v>
       </c>
@@ -39841,10 +39869,14 @@
       </c>
       <c r="D10" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E10" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E10" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F10" s="295" t="n">
         <v>1</v>
       </c>
@@ -39867,10 +39899,14 @@
       </c>
       <c r="D11" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E11" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E11" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F11" s="295" t="n">
         <v>1</v>
       </c>
@@ -39893,10 +39929,14 @@
       </c>
       <c r="D12" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E12" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E12" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F12" s="295" t="n">
         <v>1</v>
       </c>
@@ -39919,10 +39959,14 @@
       </c>
       <c r="D13" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E13" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E13" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F13" s="295" t="n">
         <v>1</v>
       </c>
@@ -39945,10 +39989,14 @@
       </c>
       <c r="D14" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E14" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E14" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F14" s="295" t="n">
         <v>1</v>
       </c>
@@ -39971,10 +40019,14 @@
       </c>
       <c r="D15" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E15" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E15" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F15" s="295" t="n">
         <v>1</v>
       </c>
@@ -39997,10 +40049,14 @@
       </c>
       <c r="D16" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E16" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E16" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F16" s="295" t="n">
         <v>1</v>
       </c>
@@ -40023,10 +40079,14 @@
       </c>
       <c r="D17" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E17" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E17" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F17" s="295" t="n">
         <v>1</v>
       </c>
@@ -40049,10 +40109,14 @@
       </c>
       <c r="D18" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E18" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E18" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F18" s="295" t="n">
         <v>1</v>
       </c>
@@ -40075,10 +40139,14 @@
       </c>
       <c r="D19" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E19" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E19" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F19" s="295" t="n">
         <v>1</v>
       </c>
@@ -40101,10 +40169,14 @@
       </c>
       <c r="D20" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E20" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E20" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F20" s="295" t="n">
         <v>1</v>
       </c>
@@ -40127,10 +40199,14 @@
       </c>
       <c r="D21" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E21" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E21" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F21" s="295" t="n">
         <v>1</v>
       </c>
@@ -40153,10 +40229,14 @@
       </c>
       <c r="D22" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E22" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E22" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F22" s="295" t="n">
         <v>1</v>
       </c>
@@ -40179,10 +40259,14 @@
       </c>
       <c r="D23" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E23" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E23" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F23" s="295" t="n">
         <v>1</v>
       </c>
@@ -40205,10 +40289,14 @@
       </c>
       <c r="D24" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E24" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E24" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F24" s="295" t="n">
         <v>1</v>
       </c>
@@ -40231,10 +40319,14 @@
       </c>
       <c r="D25" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E25" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E25" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F25" s="295" t="n">
         <v>1</v>
       </c>
@@ -40257,10 +40349,14 @@
       </c>
       <c r="D26" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E26" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E26" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F26" s="295" t="n">
         <v>1</v>
       </c>
@@ -40283,10 +40379,14 @@
       </c>
       <c r="D27" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E27" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E27" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F27" s="295" t="n">
         <v>1</v>
       </c>
@@ -40309,10 +40409,14 @@
       </c>
       <c r="D28" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E28" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E28" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F28" s="295" t="n">
         <v>1</v>
       </c>
@@ -40335,10 +40439,14 @@
       </c>
       <c r="D29" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E29" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E29" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F29" s="295" t="n">
         <v>1</v>
       </c>
@@ -40361,10 +40469,14 @@
       </c>
       <c r="D30" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E30" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E30" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F30" s="295" t="n">
         <v>1</v>
       </c>
@@ -40387,10 +40499,14 @@
       </c>
       <c r="D31" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E31" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E31" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F31" s="295" t="n">
         <v>1</v>
       </c>
@@ -40413,10 +40529,14 @@
       </c>
       <c r="D32" s="295" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E32" s="295" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E32" s="295" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="F32" s="295" t="n">
         <v>1</v>
       </c>
@@ -40539,6 +40659,7 @@
       <c r="G5" s="127" t="n"/>
     </row>
     <row r="6" ht="40.5" customHeight="1" s="203"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="136" t="inlineStr">
         <is>
@@ -42351,6 +42472,10 @@
       <c r="F3" s="131" t="n"/>
       <c r="G3" s="127" t="n"/>
     </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="266" t="inlineStr">
         <is>
@@ -43805,6 +43930,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -45068,6 +45194,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -45630,6 +45757,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="W16 - CineBeam S PDP Video Upda" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="W16 - Copilot+ Filter Creation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="W16 - Microsoft PDP Gallery Car" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="W17 - GNB Structure" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="W18 - FAQ Request (UltraGear PL" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="W18 - UltraGear OLED FAQ Update" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="W22 - UltraGear Buying Guide" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="W23 - 27GM950B-B 갤러리 이미지 교체" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="W23 - 39GX950B 이미지 수정 2차" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="W23 - 52G930B Feature 수정 건" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="W23 - UL인증 feature 삭제 1차" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="W25 - Copilot+ Hero Banner" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="W28 - AI Upscaling Disclaimer" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="W28 - UL Verified Eye Comfort" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="W30 - SmartMonitor ScreenShare" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="W30 - UltraGear 1000Hz FAQ" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="W31 - gram Secure Lock" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Windows 11 Landing" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="W31 - PDP Gallery Win11 Pro" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="W31 - Smart Monitor Multi AI" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="W32 - UltraGear 27GX704A" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="W32 - Digital Trends Award 삭제" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="W32 - UltraGear PDP 5모델" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="W32 - UltraFine PDP MIC 삭제" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="W38 - gram pro gallery" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W16 - CineBeam S PDP Video Upda" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W16 - Copilot+ Filter Creation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W16 - Microsoft PDP Gallery Car" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W17 - GNB Structure" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W18 - FAQ Request (UltraGear PL" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W18 - UltraGear OLED FAQ Update" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W22 - UltraGear Buying Guide" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - 27GM950B-B 갤러리 이미지 교체" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - 39GX950B 이미지 수정 2차" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - 52G930B Feature 수정 건" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - UL인증 feature 삭제 1차" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W25 - Copilot+ Hero Banner" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W28 - AI Upscaling Disclaimer" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W28 - UL Verified Eye Comfort" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W30 - SmartMonitor ScreenShare" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W30 - UltraGear 1000Hz FAQ" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W31 - gram Secure Lock" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Windows 11 Landing" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W31 - PDP Gallery Win11 Pro" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W31 - Smart Monitor Multi AI" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - UltraGear 27GX704A" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - Digital Trends Award 삭제" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - UltraGear PDP 5모델" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - UltraFine PDP MIC 삭제" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W38 - gram pro gallery" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2998,7 +2998,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -3587,7 +3586,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -5578,7 +5576,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -7508,7 +7505,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -40659,7 +40655,6 @@
       <c r="G5" s="127" t="n"/>
     </row>
     <row r="6" ht="40.5" customHeight="1" s="203"/>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="136" t="inlineStr">
         <is>
@@ -41177,7 +41172,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>법인 현황 반영(2026-09-15) · VN 완료(09-10) · AU 취소(법인) · HU/JP 취소(법인 요청) · BG/HR/RS 취소 신규(법인 요청) · CH_FR 취소(법인 요청, 09-16)</t>
+          <t>예상 일정(2026-09-29) · EU 10/16 · Americas 10/23 · Asia 10/09 · EG 10/02 · KZ 10/05 · 법인 현황 반영(2026-09-15) · VN 완료(09-10) · AU 취소(법인) · HU/JP 취소(법인 요청) · BG/HR/RS 취소 신규(법인 요청) · CH_FR 취소(법인 요청, 09-16)</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -41330,11 +41325,19 @@
           <t>작업중</t>
         </is>
       </c>
-      <c r="E12" s="123" t="inlineStr"/>
+      <c r="E12" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="F12" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-23 · 프로덕션 반영됨</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="261" t="inlineStr">
@@ -41452,11 +41455,19 @@
           <t>작업중</t>
         </is>
       </c>
-      <c r="E17" s="123" t="inlineStr"/>
+      <c r="E17" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="F17" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-23</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="261" t="inlineStr">
@@ -41474,11 +41485,19 @@
           <t>작업중</t>
         </is>
       </c>
-      <c r="E18" s="123" t="inlineStr"/>
+      <c r="E18" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="F18" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-23 · 프로덕션 반영됨</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="261" t="inlineStr">
@@ -41548,11 +41567,19 @@
           <t>작업중</t>
         </is>
       </c>
-      <c r="E21" s="123" t="inlineStr"/>
+      <c r="E21" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="F21" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-16</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="261" t="inlineStr">
@@ -41570,11 +41597,19 @@
           <t>작업중</t>
         </is>
       </c>
-      <c r="E22" s="123" t="inlineStr"/>
+      <c r="E22" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="F22" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="0" t="inlineStr"/>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-02 · LDM 회신 대기, 09/30 무응답 시 취소</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="261" t="inlineStr">
@@ -41592,11 +41627,19 @@
           <t>작업중</t>
         </is>
       </c>
-      <c r="E23" s="123" t="inlineStr"/>
+      <c r="E23" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="F23" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="0" t="inlineStr"/>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-02 · LDM 회신 대기, 09/30 무응답 시 취소</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="261" t="inlineStr">
@@ -41666,11 +41709,19 @@
           <t>작업중</t>
         </is>
       </c>
-      <c r="E26" s="123" t="inlineStr"/>
+      <c r="E26" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="F26" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="0" t="inlineStr"/>
+      <c r="G26" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-09 · LDM 번역 리뷰 대기</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="B27" s="261" t="inlineStr">
@@ -41688,11 +41739,19 @@
           <t>작업중</t>
         </is>
       </c>
-      <c r="E27" s="123" t="inlineStr"/>
+      <c r="E27" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="F27" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="0" t="inlineStr"/>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-09 · LDM 번역 리뷰 대기</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="261" t="inlineStr">
@@ -41810,11 +41869,19 @@
           <t>법인리뷰</t>
         </is>
       </c>
-      <c r="E32" s="123" t="inlineStr"/>
+      <c r="E32" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="F32" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="0" t="inlineStr"/>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-16</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="261" t="inlineStr">
@@ -41858,11 +41925,19 @@
           <t>작업중</t>
         </is>
       </c>
-      <c r="E34" s="123" t="inlineStr"/>
+      <c r="E34" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="F34" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G34" s="0" t="inlineStr"/>
+      <c r="G34" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-05 · LDM 9월 내 확인</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="B35" s="261" t="inlineStr">
@@ -41902,11 +41977,19 @@
           <t>작업중</t>
         </is>
       </c>
-      <c r="E36" s="123" t="inlineStr"/>
+      <c r="E36" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="F36" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="0" t="inlineStr"/>
+      <c r="G36" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-23 · 프로덕션 반영됨</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="B37" s="261" t="inlineStr">
@@ -41924,11 +42007,19 @@
           <t>작업중</t>
         </is>
       </c>
-      <c r="E37" s="123" t="inlineStr"/>
+      <c r="E37" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="F37" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G37" s="0" t="inlineStr"/>
+      <c r="G37" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-09 · LDM 9월 내 확인</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="B38" s="261" t="inlineStr">
@@ -41998,11 +42089,19 @@
           <t>작업중</t>
         </is>
       </c>
-      <c r="E40" s="123" t="inlineStr"/>
+      <c r="E40" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="F40" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G40" s="0" t="inlineStr"/>
+      <c r="G40" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-23</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="B41" s="261" t="inlineStr">
@@ -42064,11 +42163,19 @@
           <t>작업중</t>
         </is>
       </c>
-      <c r="E43" s="123" t="inlineStr"/>
+      <c r="E43" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="F43" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="0" t="inlineStr"/>
+      <c r="G43" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-16</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="B44" s="261" t="inlineStr">
@@ -42086,11 +42193,19 @@
           <t>작업중</t>
         </is>
       </c>
-      <c r="E44" s="123" t="inlineStr"/>
+      <c r="E44" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="F44" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="0" t="inlineStr"/>
+      <c r="G44" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-16 · LDM 무응답, 리마인더 발송</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="B45" s="261" t="inlineStr">
@@ -42182,11 +42297,19 @@
           <t>법인리뷰</t>
         </is>
       </c>
-      <c r="E48" s="123" t="inlineStr"/>
+      <c r="E48" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="F48" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="0" t="inlineStr"/>
+      <c r="G48" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-16</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="B49" s="261" t="inlineStr">
@@ -42204,11 +42327,19 @@
           <t>작업중</t>
         </is>
       </c>
-      <c r="E49" s="123" t="inlineStr"/>
+      <c r="E49" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="F49" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="0" t="inlineStr"/>
+      <c r="G49" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-09 · LDM 9월 내 확인</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="B50" s="261" t="inlineStr">
@@ -42472,10 +42603,6 @@
       <c r="F3" s="131" t="n"/>
       <c r="G3" s="127" t="n"/>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="266" t="inlineStr">
         <is>
@@ -43930,7 +44057,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -45194,7 +45320,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -45757,7 +45882,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -41172,7 +41172,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>예상 일정(2026-09-29) · EU 10/16 · Americas 10/23 · Asia 10/09 · EG 10/02 · KZ 10/05 · 법인 현황 반영(2026-09-15) · VN 완료(09-10) · AU 취소(법인) · HU/JP 취소(법인 요청) · BG/HR/RS 취소 신규(법인 요청) · CH_FR 취소(법인 요청, 09-16)</t>
+          <t>예상 일정(2026-09-29) · IT·SE 10/02(법인리뷰) · EU 10/16 · Americas 10/23 · Asia 10/09 · EG 10/02 · KZ 10/05 · 법인 현황 반영(2026-09-15) · VN 완료(09-10) · AU 취소(법인) · HU/JP 취소(법인 요청) · BG/HR/RS 취소 신규(법인 요청) · CH_FR 취소(법인 요청, 09-16)</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -41871,7 +41871,7 @@
       </c>
       <c r="E32" s="123" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F32" s="123" t="n">
@@ -41879,7 +41879,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-16</t>
+          <t>예상 2026-10-02 · 법인리뷰</t>
         </is>
       </c>
     </row>
@@ -42299,7 +42299,7 @@
       </c>
       <c r="E48" s="123" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F48" s="123" t="n">
@@ -42307,7 +42307,7 @@
       </c>
       <c r="G48" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-16</t>
+          <t>예상 2026-10-02 · 법인리뷰</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -41172,7 +41172,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>예상 일정(2026-09-29) · IT·SE 10/02(법인리뷰) · EU 10/16 · Americas 10/23 · Asia 10/09 · EG 10/02 · KZ 10/05 · 법인 현황 반영(2026-09-15) · VN 완료(09-10) · AU 취소(법인) · HU/JP 취소(법인 요청) · BG/HR/RS 취소 신규(법인 요청) · CH_FR 취소(법인 요청, 09-16)</t>
+          <t>예상 일정(2026-09-29) · IT·SE 10/02(법인리뷰) · PTT 0929 법인리뷰: HK·HK_EN·ID·NZ·PH·PT · EU 10/16 · Americas 10/23 · Asia 10/09 · EG 10/02 · KZ 10/05 · 법인 현황 반영(2026-09-15) · VN 완료(09-10) · AU 취소(법인) · HU/JP 취소(법인 요청) · BG/HR/RS 취소 신규(법인 요청) · CH_FR 취소(법인 요청, 09-16)</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -41706,7 +41706,7 @@
       </c>
       <c r="D26" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E26" s="123" t="inlineStr">
@@ -41736,7 +41736,7 @@
       </c>
       <c r="D27" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E27" s="123" t="inlineStr">
@@ -41818,14 +41818,18 @@
       </c>
       <c r="D30" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E30" s="123" t="inlineStr"/>
       <c r="F30" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="0" t="inlineStr"/>
+      <c r="G30" s="0" t="inlineStr">
+        <is>
+          <t>PTT 0929 · Client Review</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="B31" s="261" t="inlineStr">
@@ -42060,7 +42064,7 @@
       </c>
       <c r="D39" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E39" s="123" t="inlineStr"/>
@@ -42069,7 +42073,7 @@
       </c>
       <c r="G39" s="0" t="inlineStr">
         <is>
-          <t>Hyper/Professional/Swing PLP 취소(09-14) · 나머지 신규 요청</t>
+          <t>Hyper/Professional/Swing PLP 취소(09-14) · 나머지 Client Review (PTT 0929)</t>
         </is>
       </c>
     </row>
@@ -42138,14 +42142,18 @@
       </c>
       <c r="D42" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E42" s="123" t="inlineStr"/>
       <c r="F42" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="0" t="inlineStr"/>
+      <c r="G42" s="0" t="inlineStr">
+        <is>
+          <t>PTT 0929 · Client Review</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="B43" s="261" t="inlineStr">
@@ -42190,7 +42198,7 @@
       </c>
       <c r="D44" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E44" s="123" t="inlineStr">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -1,33 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W16 - CineBeam S PDP Video Upda" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W16 - Copilot+ Filter Creation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W16 - Microsoft PDP Gallery Car" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W17 - GNB Structure" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W18 - FAQ Request (UltraGear PL" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W18 - UltraGear OLED FAQ Update" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W22 - UltraGear Buying Guide" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - 27GM950B-B 갤러리 이미지 교체" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - 39GX950B 이미지 수정 2차" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - 52G930B Feature 수정 건" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - UL인증 feature 삭제 1차" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W25 - Copilot+ Hero Banner" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W28 - AI Upscaling Disclaimer" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W28 - UL Verified Eye Comfort" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W30 - SmartMonitor ScreenShare" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W30 - UltraGear 1000Hz FAQ" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W31 - gram Secure Lock" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Windows 11 Landing" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W31 - PDP Gallery Win11 Pro" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W31 - Smart Monitor Multi AI" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - UltraGear 27GX704A" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - Digital Trends Award 삭제" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - UltraGear PDP 5모델" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - UltraFine PDP MIC 삭제" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W38 - gram pro gallery" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="W16 - CineBeam S PDP Video Upda" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="W16 - Copilot+ Filter Creation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="W16 - Microsoft PDP Gallery Car" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="W17 - GNB Structure" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="W18 - FAQ Request (UltraGear PL" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="W18 - UltraGear OLED FAQ Update" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="W22 - UltraGear Buying Guide" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="W23 - 27GM950B-B 갤러리 이미지 교체" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="W23 - 39GX950B 이미지 수정 2차" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="W23 - 52G930B Feature 수정 건" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="W23 - UL인증 feature 삭제 1차" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="W25 - Copilot+ Hero Banner" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="W28 - AI Upscaling Disclaimer" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="W28 - UL Verified Eye Comfort" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="W30 - SmartMonitor ScreenShare" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="W30 - UltraGear 1000Hz FAQ" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="W31 - gram Secure Lock" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Windows 11 Landing" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="W31 - PDP Gallery Win11 Pro" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="W31 - Smart Monitor Multi AI" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="W32 - UltraGear 27GX704A" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="W32 - Digital Trends Award 삭제" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="W32 - UltraGear PDP 5모델" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="W32 - UltraFine PDP MIC 삭제" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="W38 - gram pro gallery" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="W41 - UltraGear Buying Guide 2차" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40578,6 +40579,1063 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G52"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="166" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="163" t="inlineStr">
+        <is>
+          <t>GR26-W41-MS-IT UltraGear Buying Guide 2차 Update</t>
+        </is>
+      </c>
+      <c r="C1" s="164" t="n"/>
+      <c r="D1" s="164" t="n"/>
+      <c r="E1" s="165" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>이번주 추가</t>
+        </is>
+      </c>
+      <c r="B2" s="163" t="inlineStr">
+        <is>
+          <t>금주 신규 등록 · 1차(W22)와 동일 44개국 대상 2차 업데이트 · 담당 정알찬 책임</t>
+        </is>
+      </c>
+      <c r="C2" s="164" t="n"/>
+      <c r="D2" s="164" t="n"/>
+      <c r="E2" s="165" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="166" t="n"/>
+      <c r="B3" s="163" t="n"/>
+      <c r="C3" s="164" t="n"/>
+      <c r="D3" s="164" t="n"/>
+      <c r="E3" s="165" t="n"/>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="127" t="n"/>
+      <c r="B5" s="127" t="n"/>
+      <c r="C5" s="127" t="n"/>
+      <c r="D5" s="127" t="n"/>
+      <c r="E5" s="127" t="n"/>
+    </row>
+    <row r="6">
+      <c r="E6" s="127" t="n"/>
+    </row>
+    <row r="7">
+      <c r="E7" s="127" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="276" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B8" s="276" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C8" s="276" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D8" s="276" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E8" s="276" t="inlineStr">
+        <is>
+          <t>완료일</t>
+        </is>
+      </c>
+      <c r="F8" s="276" t="inlineStr">
+        <is>
+          <t>Page#</t>
+        </is>
+      </c>
+      <c r="G8" s="276" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" s="203">
+      <c r="B9" s="261" t="inlineStr">
+        <is>
+          <t>AE-ar</t>
+        </is>
+      </c>
+      <c r="C9" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae_ar/it-products/ultragear-buying-guide</t>
+        </is>
+      </c>
+      <c r="D9" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E9" s="123" t="n"/>
+      <c r="F9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="0" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="261" t="inlineStr">
+        <is>
+          <t>BD-en</t>
+        </is>
+      </c>
+      <c r="C10" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/bd/ultragear-gaming-buying-guide</t>
+        </is>
+      </c>
+      <c r="D10" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E10" s="123" t="n"/>
+      <c r="F10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="0" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="261" t="inlineStr">
+        <is>
+          <t>BE-fr</t>
+        </is>
+      </c>
+      <c r="C11" s="290" t="n"/>
+      <c r="D11" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E11" s="123" t="n"/>
+      <c r="F11" s="0" t="n"/>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>1차 URL 최종 404(10/06 실측) · 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="261" t="inlineStr">
+        <is>
+          <t>BR-pt</t>
+        </is>
+      </c>
+      <c r="C12" s="277" t="inlineStr"/>
+      <c r="D12" s="264" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E12" s="123" t="n"/>
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="261" t="inlineStr">
+        <is>
+          <t>CAC-es</t>
+        </is>
+      </c>
+      <c r="C13" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cac/computacion/ultragear-buying-guide</t>
+        </is>
+      </c>
+      <c r="D13" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E13" s="123" t="n"/>
+      <c r="F13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="0" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="261" t="inlineStr">
+        <is>
+          <t>CA-en</t>
+        </is>
+      </c>
+      <c r="C14" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D14" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E14" s="123" t="n"/>
+      <c r="F14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="0" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="261" t="inlineStr">
+        <is>
+          <t>CA-fr</t>
+        </is>
+      </c>
+      <c r="C15" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D15" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E15" s="123" t="n"/>
+      <c r="F15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="0" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="261" t="inlineStr">
+        <is>
+          <t>CN-zh</t>
+        </is>
+      </c>
+      <c r="C16" s="277" t="inlineStr"/>
+      <c r="D16" s="263" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E16" s="123" t="n"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="261" t="inlineStr">
+        <is>
+          <t>CO-es</t>
+        </is>
+      </c>
+      <c r="C17" s="277" t="inlineStr"/>
+      <c r="D17" s="264" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E17" s="123" t="n"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="261" t="inlineStr">
+        <is>
+          <t>CZ-cz</t>
+        </is>
+      </c>
+      <c r="C18" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cz/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D18" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E18" s="123" t="n"/>
+      <c r="F18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="0" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="261" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C19" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D19" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E19" s="123" t="n"/>
+      <c r="F19" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="0" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="261" t="inlineStr">
+        <is>
+          <t>EC-es</t>
+        </is>
+      </c>
+      <c r="C20" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ec/computacion/ultragear-buying-guide</t>
+        </is>
+      </c>
+      <c r="D20" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E20" s="123" t="n"/>
+      <c r="F20" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="0" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="261" t="inlineStr">
+        <is>
+          <t>EE-ee</t>
+        </is>
+      </c>
+      <c r="C21" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ee/it-seadmed/buying-guide/ultragear-mangumonitorid</t>
+        </is>
+      </c>
+      <c r="D21" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E21" s="123" t="n"/>
+      <c r="F21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="0" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="261" t="inlineStr">
+        <is>
+          <t>ES-es</t>
+        </is>
+      </c>
+      <c r="C22" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D22" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E22" s="123" t="n"/>
+      <c r="F22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="0" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="261" t="inlineStr">
+        <is>
+          <t>FI-fi</t>
+        </is>
+      </c>
+      <c r="C23" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fi/it-tuotteet/ultragear-buying-guide</t>
+        </is>
+      </c>
+      <c r="D23" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E23" s="123" t="n"/>
+      <c r="F23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="0" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="261" t="inlineStr">
+        <is>
+          <t>FR-fr</t>
+        </is>
+      </c>
+      <c r="C24" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/moniteurs/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D24" s="263" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E24" s="123" t="n"/>
+      <c r="F24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="0" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="261" t="inlineStr">
+        <is>
+          <t>GR-gr</t>
+        </is>
+      </c>
+      <c r="C25" s="277" t="inlineStr"/>
+      <c r="D25" s="264" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E25" s="123" t="n"/>
+      <c r="F25" s="0" t="inlineStr"/>
+      <c r="G25" s="0" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="261" t="inlineStr">
+        <is>
+          <t>HK-zh</t>
+        </is>
+      </c>
+      <c r="C26" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D26" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E26" s="123" t="n"/>
+      <c r="F26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="0" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="261" t="inlineStr">
+        <is>
+          <t>HK-en</t>
+        </is>
+      </c>
+      <c r="C27" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hk_en/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D27" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E27" s="123" t="n"/>
+      <c r="F27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="0" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="261" t="inlineStr">
+        <is>
+          <t>HU-hu</t>
+        </is>
+      </c>
+      <c r="C28" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hu/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D28" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E28" s="123" t="n"/>
+      <c r="F28" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="0" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="261" t="inlineStr">
+        <is>
+          <t>ID-id</t>
+        </is>
+      </c>
+      <c r="C29" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/id/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D29" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E29" s="123" t="n"/>
+      <c r="F29" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="0" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="261" t="inlineStr">
+        <is>
+          <t>IL-he</t>
+        </is>
+      </c>
+      <c r="C30" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/monitors/ultragear-buying-guide</t>
+        </is>
+      </c>
+      <c r="D30" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E30" s="123" t="n"/>
+      <c r="F30" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="0" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="261" t="inlineStr">
+        <is>
+          <t>IN-en</t>
+        </is>
+      </c>
+      <c r="C31" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/in/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D31" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E31" s="123" t="n"/>
+      <c r="F31" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="0" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="261" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C32" s="277" t="inlineStr"/>
+      <c r="D32" s="264" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E32" s="123" t="n"/>
+      <c r="F32" s="0" t="inlineStr"/>
+      <c r="G32" s="0" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="261" t="inlineStr">
+        <is>
+          <t>JP-ja</t>
+        </is>
+      </c>
+      <c r="C33" s="277" t="inlineStr"/>
+      <c r="D33" s="263" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E33" s="123" t="n"/>
+      <c r="F33" s="0" t="inlineStr"/>
+      <c r="G33" s="0" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="261" t="inlineStr">
+        <is>
+          <t>KZ-ru</t>
+        </is>
+      </c>
+      <c r="C34" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/kz/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D34" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E34" s="123" t="n"/>
+      <c r="F34" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="0" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="261" t="inlineStr">
+        <is>
+          <t>LT-lt</t>
+        </is>
+      </c>
+      <c r="C35" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lt/kompiuterine-technika/buying-guide/ultragear-gaming-monitor</t>
+        </is>
+      </c>
+      <c r="D35" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E35" s="123" t="n"/>
+      <c r="F35" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="0" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="261" t="inlineStr">
+        <is>
+          <t>LV-lv</t>
+        </is>
+      </c>
+      <c r="C36" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lv/datortehnika/buying-guide/ultragear-gaming-monitor</t>
+        </is>
+      </c>
+      <c r="D36" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E36" s="123" t="n"/>
+      <c r="F36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="0" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="261" t="inlineStr">
+        <is>
+          <t>NL-nl</t>
+        </is>
+      </c>
+      <c r="C37" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D37" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E37" s="123" t="n"/>
+      <c r="F37" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="0" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="261" t="inlineStr">
+        <is>
+          <t>NO-no</t>
+        </is>
+      </c>
+      <c r="C38" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/no/it-produkter/ultragear-buying-guide</t>
+        </is>
+      </c>
+      <c r="D38" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E38" s="123" t="n"/>
+      <c r="F38" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="0" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="261" t="inlineStr">
+        <is>
+          <t>PA-es</t>
+        </is>
+      </c>
+      <c r="C39" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/pa/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D39" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E39" s="123" t="n"/>
+      <c r="F39" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="0" t="n"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="261" t="inlineStr">
+        <is>
+          <t>PE-es</t>
+        </is>
+      </c>
+      <c r="C40" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/pe/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D40" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E40" s="123" t="n"/>
+      <c r="F40" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="0" t="n"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="261" t="inlineStr">
+        <is>
+          <t>PH-en</t>
+        </is>
+      </c>
+      <c r="C41" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ph/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D41" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E41" s="123" t="n"/>
+      <c r="F41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="0" t="n"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="261" t="inlineStr">
+        <is>
+          <t>PL-pl</t>
+        </is>
+      </c>
+      <c r="C42" s="277" t="inlineStr"/>
+      <c r="D42" s="264" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E42" s="123" t="n"/>
+      <c r="F42" s="0" t="inlineStr"/>
+      <c r="G42" s="0" t="n"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="261" t="inlineStr">
+        <is>
+          <t>PT-pt</t>
+        </is>
+      </c>
+      <c r="C43" s="277" t="inlineStr"/>
+      <c r="D43" s="264" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E43" s="123" t="n"/>
+      <c r="F43" s="0" t="inlineStr"/>
+      <c r="G43" s="0" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="261" t="inlineStr">
+        <is>
+          <t>RS-rs</t>
+        </is>
+      </c>
+      <c r="C44" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/rs/it-proizvodi/ultragear-buying-guide</t>
+        </is>
+      </c>
+      <c r="D44" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E44" s="123" t="n"/>
+      <c r="F44" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="0" t="n"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="261" t="inlineStr">
+        <is>
+          <t>SA-ar</t>
+        </is>
+      </c>
+      <c r="C45" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sa/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D45" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E45" s="123" t="n"/>
+      <c r="F45" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="0" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="261" t="inlineStr">
+        <is>
+          <t>SA-en</t>
+        </is>
+      </c>
+      <c r="C46" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sa_en/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D46" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E46" s="123" t="n"/>
+      <c r="F46" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="0" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="261" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C47" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D47" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E47" s="123" t="n"/>
+      <c r="F47" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="0" t="n"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="261" t="inlineStr">
+        <is>
+          <t>TH-th</t>
+        </is>
+      </c>
+      <c r="C48" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/th/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D48" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E48" s="123" t="n"/>
+      <c r="F48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="0" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="261" t="inlineStr">
+        <is>
+          <t>TR-tr</t>
+        </is>
+      </c>
+      <c r="C49" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tr/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D49" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E49" s="123" t="n"/>
+      <c r="F49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="0" t="n"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="261" t="inlineStr">
+        <is>
+          <t>TW-zh</t>
+        </is>
+      </c>
+      <c r="C50" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D50" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E50" s="123" t="n"/>
+      <c r="F50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="0" t="n"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="261" t="inlineStr">
+        <is>
+          <t>UA-uk</t>
+        </is>
+      </c>
+      <c r="C51" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ua/it-products/ultragear-buying-guide</t>
+        </is>
+      </c>
+      <c r="D51" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E51" s="123" t="n"/>
+      <c r="F51" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="0" t="n"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="261" t="inlineStr">
+        <is>
+          <t>ZA-en</t>
+        </is>
+      </c>
+      <c r="C52" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/za/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D52" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E52" s="123" t="n"/>
+      <c r="F52" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="0" t="n"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId35"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -40625,7 +40625,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -42380,7 +42379,7 @@
       </c>
       <c r="D12" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E12" s="123" t="inlineStr">
@@ -42540,7 +42539,7 @@
       </c>
       <c r="D18" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E18" s="123" t="inlineStr">
@@ -42777,7 +42776,7 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-09 · LDM 번역 리뷰 대기</t>
+          <t>예상 2026-10-09 · PTT 1006 법인 승인 완료 · QA Final Live Check(게시 직전)</t>
         </is>
       </c>
     </row>
@@ -42807,7 +42806,7 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-09 · LDM 번역 리뷰 대기</t>
+          <t>예상 2026-10-09 · PTT 1006 법인 승인 완료 · QA Final Live Check(게시 직전)</t>
         </is>
       </c>
     </row>
@@ -42984,7 +42983,7 @@
       </c>
       <c r="D34" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E34" s="123" t="inlineStr">
@@ -43036,7 +43035,7 @@
       </c>
       <c r="D36" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E36" s="123" t="inlineStr">
@@ -43178,7 +43177,7 @@
       </c>
       <c r="D41" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E41" s="123" t="inlineStr"/>
@@ -43559,7 +43558,7 @@
       </c>
       <c r="G55" s="0" t="inlineStr">
         <is>
-          <t>GNB 수정 게시(07-27) · UltraGear evo PLP QA 리뷰 · 나머지 신규 요청</t>
+          <t>GNB 수정 게시(07-27) · PTT 1006 Closed 6 · QA Final Live Check 1(완료 임박)</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -40585,7 +40585,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -40611,7 +40611,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>금주 신규 등록 · 1차(W22)와 동일 44개국 대상 2차 업데이트 · 담당 정알찬 책임</t>
+          <t>금주 신규 등록 · 1차(W22) 44개국 + 기존 라이브 6곳(AE-en·BE-nl·DE·UK·SG·MX) = 50개 사이트 · 담당 정알찬 책임</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -40625,6 +40625,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -40700,12 +40701,12 @@
     <row r="10">
       <c r="B10" s="261" t="inlineStr">
         <is>
-          <t>BD-en</t>
+          <t>AE-en</t>
         </is>
       </c>
       <c r="C10" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/bd/ultragear-gaming-buying-guide</t>
+          <t>https://www.lg.com/ae/ultragear-buying-guide</t>
         </is>
       </c>
       <c r="D10" s="265" t="inlineStr">
@@ -40717,53 +40718,65 @@
       <c r="F10" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="0" t="n"/>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="261" t="inlineStr">
         <is>
-          <t>BE-fr</t>
-        </is>
-      </c>
-      <c r="C11" s="290" t="n"/>
+          <t>BD-en</t>
+        </is>
+      </c>
+      <c r="C11" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/bd/ultragear-gaming-buying-guide</t>
+        </is>
+      </c>
       <c r="D11" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
       <c r="E11" s="123" t="n"/>
-      <c r="F11" s="0" t="n"/>
-      <c r="G11" s="0" t="inlineStr">
-        <is>
-          <t>1차 URL 최종 404(10/06 실측) · 확인 필요</t>
-        </is>
-      </c>
+      <c r="F11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="0" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="261" t="inlineStr">
         <is>
-          <t>BR-pt</t>
-        </is>
-      </c>
-      <c r="C12" s="277" t="inlineStr"/>
-      <c r="D12" s="264" t="inlineStr">
+          <t>BE-fr</t>
+        </is>
+      </c>
+      <c r="C12" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be_fr/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D12" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
       <c r="E12" s="123" t="n"/>
-      <c r="F12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="G12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="261" t="inlineStr">
         <is>
-          <t>CAC-es</t>
+          <t>BE-nl</t>
         </is>
       </c>
       <c r="C13" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cac/computacion/ultragear-buying-guide</t>
+          <t>https://www.lg.com/be/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D13" s="265" t="inlineStr">
@@ -40775,19 +40788,19 @@
       <c r="F13" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="0" t="n"/>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="261" t="inlineStr">
         <is>
-          <t>CA-en</t>
-        </is>
-      </c>
-      <c r="C14" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ca_en/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
+          <t>BR-pt</t>
+        </is>
+      </c>
+      <c r="C14" s="290" t="n"/>
       <c r="D14" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -40797,17 +40810,21 @@
       <c r="F14" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="0" t="n"/>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>신규 제작(1차 미게시)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="261" t="inlineStr">
         <is>
-          <t>CA-fr</t>
+          <t>CA-en</t>
         </is>
       </c>
       <c r="C15" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/ca_en/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D15" s="265" t="inlineStr">
@@ -40824,46 +40841,54 @@
     <row r="16">
       <c r="B16" s="261" t="inlineStr">
         <is>
-          <t>CN-zh</t>
-        </is>
-      </c>
-      <c r="C16" s="277" t="inlineStr"/>
-      <c r="D16" s="263" t="inlineStr">
+          <t>CA-fr</t>
+        </is>
+      </c>
+      <c r="C16" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D16" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
       <c r="E16" s="123" t="n"/>
-      <c r="F16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="G16" s="0" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="261" t="inlineStr">
         <is>
-          <t>CO-es</t>
-        </is>
-      </c>
-      <c r="C17" s="277" t="inlineStr"/>
-      <c r="D17" s="264" t="inlineStr">
+          <t>CAC-es</t>
+        </is>
+      </c>
+      <c r="C17" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cac/computacion/ultragear-buying-guide</t>
+        </is>
+      </c>
+      <c r="D17" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
       <c r="E17" s="123" t="n"/>
-      <c r="F17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="G17" s="0" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="261" t="inlineStr">
         <is>
-          <t>CZ-cz</t>
-        </is>
-      </c>
-      <c r="C18" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cz/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
+          <t>CN-zh</t>
+        </is>
+      </c>
+      <c r="C18" s="290" t="n"/>
       <c r="D18" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -40873,19 +40898,19 @@
       <c r="F18" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="0" t="n"/>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>신규 제작(1차 미게시)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="261" t="inlineStr">
         <is>
-          <t>DK-da</t>
-        </is>
-      </c>
-      <c r="C19" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/dk/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
+          <t>CO-es</t>
+        </is>
+      </c>
+      <c r="C19" s="290" t="n"/>
       <c r="D19" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -40895,17 +40920,21 @@
       <c r="F19" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="0" t="n"/>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>신규 제작(1차 미게시)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="261" t="inlineStr">
         <is>
-          <t>EC-es</t>
+          <t>CZ-cz</t>
         </is>
       </c>
       <c r="C20" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ec/computacion/ultragear-buying-guide</t>
+          <t>https://www.lg.com/cz/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D20" s="265" t="inlineStr">
@@ -40922,12 +40951,12 @@
     <row r="21">
       <c r="B21" s="261" t="inlineStr">
         <is>
-          <t>EE-ee</t>
+          <t>DE-de</t>
         </is>
       </c>
       <c r="C21" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ee/it-seadmed/buying-guide/ultragear-mangumonitorid</t>
+          <t>https://www.lg.com/de/buying-guides/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D21" s="265" t="inlineStr">
@@ -40939,17 +40968,21 @@
       <c r="F21" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="0" t="n"/>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="261" t="inlineStr">
         <is>
-          <t>ES-es</t>
+          <t>DK-da</t>
         </is>
       </c>
       <c r="C22" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/es/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/dk/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D22" s="265" t="inlineStr">
@@ -40966,12 +40999,12 @@
     <row r="23">
       <c r="B23" s="261" t="inlineStr">
         <is>
-          <t>FI-fi</t>
+          <t>EC-es</t>
         </is>
       </c>
       <c r="C23" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/fi/it-tuotteet/ultragear-buying-guide</t>
+          <t>https://www.lg.com/ec/computacion/ultragear-buying-guide</t>
         </is>
       </c>
       <c r="D23" s="265" t="inlineStr">
@@ -40988,15 +41021,15 @@
     <row r="24">
       <c r="B24" s="261" t="inlineStr">
         <is>
-          <t>FR-fr</t>
+          <t>EE-ee</t>
         </is>
       </c>
       <c r="C24" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/fr/moniteurs/ultragear-buying-guide/</t>
-        </is>
-      </c>
-      <c r="D24" s="263" t="inlineStr">
+          <t>https://www.lg.com/ee/it-seadmed/buying-guide/ultragear-mangumonitorid</t>
+        </is>
+      </c>
+      <c r="D24" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
@@ -41010,28 +41043,34 @@
     <row r="25">
       <c r="B25" s="261" t="inlineStr">
         <is>
-          <t>GR-gr</t>
-        </is>
-      </c>
-      <c r="C25" s="277" t="inlineStr"/>
-      <c r="D25" s="264" t="inlineStr">
+          <t>ES-es</t>
+        </is>
+      </c>
+      <c r="C25" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D25" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
       <c r="E25" s="123" t="n"/>
-      <c r="F25" s="0" t="inlineStr"/>
+      <c r="F25" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="G25" s="0" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="261" t="inlineStr">
         <is>
-          <t>HK-zh</t>
+          <t>FI-fi</t>
         </is>
       </c>
       <c r="C26" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/fi/it-tuotteet/ultragear-buying-guide</t>
         </is>
       </c>
       <c r="D26" s="265" t="inlineStr">
@@ -41048,12 +41087,12 @@
     <row r="27">
       <c r="B27" s="261" t="inlineStr">
         <is>
-          <t>HK-en</t>
+          <t>FR-fr</t>
         </is>
       </c>
       <c r="C27" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk_en/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/fr/moniteurs/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D27" s="265" t="inlineStr">
@@ -41070,14 +41109,10 @@
     <row r="28">
       <c r="B28" s="261" t="inlineStr">
         <is>
-          <t>HU-hu</t>
-        </is>
-      </c>
-      <c r="C28" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/hu/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
+          <t>GR-gr</t>
+        </is>
+      </c>
+      <c r="C28" s="290" t="n"/>
       <c r="D28" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41087,17 +41122,21 @@
       <c r="F28" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="0" t="n"/>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>신규 제작(1차 미게시)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="261" t="inlineStr">
         <is>
-          <t>ID-id</t>
+          <t>HK-en</t>
         </is>
       </c>
       <c r="C29" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/id/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/hk_en/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D29" s="265" t="inlineStr">
@@ -41114,12 +41153,12 @@
     <row r="30">
       <c r="B30" s="261" t="inlineStr">
         <is>
-          <t>IL-he</t>
+          <t>HK-zh</t>
         </is>
       </c>
       <c r="C30" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/il/monitors/ultragear-buying-guide</t>
+          <t>https://www.lg.com/hk/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D30" s="265" t="inlineStr">
@@ -41136,12 +41175,12 @@
     <row r="31">
       <c r="B31" s="261" t="inlineStr">
         <is>
-          <t>IN-en</t>
+          <t>HU-hu</t>
         </is>
       </c>
       <c r="C31" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/in/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/hu/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D31" s="265" t="inlineStr">
@@ -41158,44 +41197,56 @@
     <row r="32">
       <c r="B32" s="261" t="inlineStr">
         <is>
-          <t>IT-it</t>
-        </is>
-      </c>
-      <c r="C32" s="277" t="inlineStr"/>
-      <c r="D32" s="264" t="inlineStr">
+          <t>ID-id</t>
+        </is>
+      </c>
+      <c r="C32" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/id/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D32" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
       <c r="E32" s="123" t="n"/>
-      <c r="F32" s="0" t="inlineStr"/>
+      <c r="F32" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="G32" s="0" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="261" t="inlineStr">
         <is>
-          <t>JP-ja</t>
-        </is>
-      </c>
-      <c r="C33" s="277" t="inlineStr"/>
-      <c r="D33" s="263" t="inlineStr">
+          <t>IL-he</t>
+        </is>
+      </c>
+      <c r="C33" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/monitors/ultragear-buying-guide</t>
+        </is>
+      </c>
+      <c r="D33" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
       <c r="E33" s="123" t="n"/>
-      <c r="F33" s="0" t="inlineStr"/>
+      <c r="F33" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="G33" s="0" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="261" t="inlineStr">
         <is>
-          <t>KZ-ru</t>
+          <t>IN-en</t>
         </is>
       </c>
       <c r="C34" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/kz/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/in/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D34" s="265" t="inlineStr">
@@ -41212,14 +41263,10 @@
     <row r="35">
       <c r="B35" s="261" t="inlineStr">
         <is>
-          <t>LT-lt</t>
-        </is>
-      </c>
-      <c r="C35" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/lt/kompiuterine-technika/buying-guide/ultragear-gaming-monitor</t>
-        </is>
-      </c>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C35" s="290" t="n"/>
       <c r="D35" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41229,19 +41276,19 @@
       <c r="F35" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G35" s="0" t="n"/>
+      <c r="G35" s="0" t="inlineStr">
+        <is>
+          <t>신규 제작(1차 미게시)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="B36" s="261" t="inlineStr">
         <is>
-          <t>LV-lv</t>
-        </is>
-      </c>
-      <c r="C36" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/lv/datortehnika/buying-guide/ultragear-gaming-monitor</t>
-        </is>
-      </c>
+          <t>JP-ja</t>
+        </is>
+      </c>
+      <c r="C36" s="290" t="n"/>
       <c r="D36" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41251,17 +41298,21 @@
       <c r="F36" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="0" t="n"/>
+      <c r="G36" s="0" t="inlineStr">
+        <is>
+          <t>신규 제작(1차 미게시)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="B37" s="261" t="inlineStr">
         <is>
-          <t>NL-nl</t>
+          <t>KZ-ru</t>
         </is>
       </c>
       <c r="C37" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/nl/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/kz/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D37" s="265" t="inlineStr">
@@ -41278,12 +41329,12 @@
     <row r="38">
       <c r="B38" s="261" t="inlineStr">
         <is>
-          <t>NO-no</t>
+          <t>LT-lt</t>
         </is>
       </c>
       <c r="C38" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/no/it-produkter/ultragear-buying-guide</t>
+          <t>https://www.lg.com/lt/kompiuterine-technika/buying-guide/ultragear-gaming-monitor</t>
         </is>
       </c>
       <c r="D38" s="265" t="inlineStr">
@@ -41300,12 +41351,12 @@
     <row r="39">
       <c r="B39" s="261" t="inlineStr">
         <is>
-          <t>PA-es</t>
+          <t>LV-lv</t>
         </is>
       </c>
       <c r="C39" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pa/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/lv/datortehnika/buying-guide/ultragear-gaming-monitor</t>
         </is>
       </c>
       <c r="D39" s="265" t="inlineStr">
@@ -41322,12 +41373,12 @@
     <row r="40">
       <c r="B40" s="261" t="inlineStr">
         <is>
-          <t>PE-es</t>
+          <t>MX-es</t>
         </is>
       </c>
       <c r="C40" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pe/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/mx/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D40" s="265" t="inlineStr">
@@ -41339,17 +41390,21 @@
       <c r="F40" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G40" s="0" t="n"/>
+      <c r="G40" s="0" t="inlineStr">
+        <is>
+          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="B41" s="261" t="inlineStr">
         <is>
-          <t>PH-en</t>
+          <t>NL-nl</t>
         </is>
       </c>
       <c r="C41" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ph/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/nl/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D41" s="265" t="inlineStr">
@@ -41366,44 +41421,56 @@
     <row r="42">
       <c r="B42" s="261" t="inlineStr">
         <is>
-          <t>PL-pl</t>
-        </is>
-      </c>
-      <c r="C42" s="277" t="inlineStr"/>
-      <c r="D42" s="264" t="inlineStr">
+          <t>NO-no</t>
+        </is>
+      </c>
+      <c r="C42" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/no/it-produkter/ultragear-buying-guide</t>
+        </is>
+      </c>
+      <c r="D42" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
       <c r="E42" s="123" t="n"/>
-      <c r="F42" s="0" t="inlineStr"/>
+      <c r="F42" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="G42" s="0" t="n"/>
     </row>
     <row r="43">
       <c r="B43" s="261" t="inlineStr">
         <is>
-          <t>PT-pt</t>
-        </is>
-      </c>
-      <c r="C43" s="277" t="inlineStr"/>
-      <c r="D43" s="264" t="inlineStr">
+          <t>PA-es</t>
+        </is>
+      </c>
+      <c r="C43" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/pa/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D43" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
         </is>
       </c>
       <c r="E43" s="123" t="n"/>
-      <c r="F43" s="0" t="inlineStr"/>
+      <c r="F43" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="G43" s="0" t="n"/>
     </row>
     <row r="44">
       <c r="B44" s="261" t="inlineStr">
         <is>
-          <t>RS-rs</t>
+          <t>PE-es</t>
         </is>
       </c>
       <c r="C44" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/rs/it-proizvodi/ultragear-buying-guide</t>
+          <t>https://www.lg.com/pe/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D44" s="265" t="inlineStr">
@@ -41420,12 +41487,12 @@
     <row r="45">
       <c r="B45" s="261" t="inlineStr">
         <is>
-          <t>SA-ar</t>
+          <t>PH-en</t>
         </is>
       </c>
       <c r="C45" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sa/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/ph/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D45" s="265" t="inlineStr">
@@ -41442,14 +41509,10 @@
     <row r="46">
       <c r="B46" s="261" t="inlineStr">
         <is>
-          <t>SA-en</t>
-        </is>
-      </c>
-      <c r="C46" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sa_en/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
+          <t>PL-pl</t>
+        </is>
+      </c>
+      <c r="C46" s="290" t="n"/>
       <c r="D46" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41459,19 +41522,19 @@
       <c r="F46" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="0" t="n"/>
+      <c r="G46" s="0" t="inlineStr">
+        <is>
+          <t>신규 제작(1차 미게시)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="B47" s="261" t="inlineStr">
         <is>
-          <t>SE-sv</t>
-        </is>
-      </c>
-      <c r="C47" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/se/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
+          <t>PT-pt</t>
+        </is>
+      </c>
+      <c r="C47" s="290" t="n"/>
       <c r="D47" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41481,17 +41544,21 @@
       <c r="F47" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="0" t="n"/>
+      <c r="G47" s="0" t="inlineStr">
+        <is>
+          <t>신규 제작(1차 미게시)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="B48" s="261" t="inlineStr">
         <is>
-          <t>TH-th</t>
+          <t>RS-rs</t>
         </is>
       </c>
       <c r="C48" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/th/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/rs/it-proizvodi/ultragear-buying-guide</t>
         </is>
       </c>
       <c r="D48" s="265" t="inlineStr">
@@ -41508,12 +41575,12 @@
     <row r="49">
       <c r="B49" s="261" t="inlineStr">
         <is>
-          <t>TR-tr</t>
+          <t>SA-ar</t>
         </is>
       </c>
       <c r="C49" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/tr/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/sa/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D49" s="265" t="inlineStr">
@@ -41530,12 +41597,12 @@
     <row r="50">
       <c r="B50" s="261" t="inlineStr">
         <is>
-          <t>TW-zh</t>
+          <t>SA-en</t>
         </is>
       </c>
       <c r="C50" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/tw/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/sa_en/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D50" s="265" t="inlineStr">
@@ -41552,12 +41619,12 @@
     <row r="51">
       <c r="B51" s="261" t="inlineStr">
         <is>
-          <t>UA-uk</t>
+          <t>SE-sv</t>
         </is>
       </c>
       <c r="C51" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ua/it-products/ultragear-buying-guide</t>
+          <t>https://www.lg.com/se/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D51" s="265" t="inlineStr">
@@ -41574,12 +41641,12 @@
     <row r="52">
       <c r="B52" s="261" t="inlineStr">
         <is>
-          <t>ZA-en</t>
+          <t>SG-en</t>
         </is>
       </c>
       <c r="C52" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/za/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/sg/consumer-monitors/featured-page/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D52" s="265" t="inlineStr">
@@ -41591,45 +41658,192 @@
       <c r="F52" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G52" s="0" t="n"/>
+      <c r="G52" s="0" t="inlineStr">
+        <is>
+          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="261" t="inlineStr">
+        <is>
+          <t>TH-th</t>
+        </is>
+      </c>
+      <c r="C53" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/th/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D53" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E53" s="123" t="n"/>
+      <c r="F53" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="0" t="n"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="261" t="inlineStr">
+        <is>
+          <t>TR-tr</t>
+        </is>
+      </c>
+      <c r="C54" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tr/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D54" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E54" s="123" t="n"/>
+      <c r="F54" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="0" t="n"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="261" t="inlineStr">
+        <is>
+          <t>TW-zh</t>
+        </is>
+      </c>
+      <c r="C55" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D55" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E55" s="123" t="n"/>
+      <c r="F55" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="0" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="261" t="inlineStr">
+        <is>
+          <t>UA-uk</t>
+        </is>
+      </c>
+      <c r="C56" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ua/it-products/ultragear-buying-guide</t>
+        </is>
+      </c>
+      <c r="D56" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E56" s="123" t="n"/>
+      <c r="F56" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="0" t="n"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="261" t="inlineStr">
+        <is>
+          <t>UK-en</t>
+        </is>
+      </c>
+      <c r="C57" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/computing/buying-guides/ultragear/</t>
+        </is>
+      </c>
+      <c r="D57" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E57" s="123" t="n"/>
+      <c r="F57" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="0" t="inlineStr">
+        <is>
+          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="261" t="inlineStr">
+        <is>
+          <t>ZA-en</t>
+        </is>
+      </c>
+      <c r="C58" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/za/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D58" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E58" s="123" t="n"/>
+      <c r="F58" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="0" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45122,6 +45336,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -45232,7 +45447,7 @@
       </c>
       <c r="C11" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/be_fr/produits-informatiques/ultragear-buying-guide</t>
+          <t>https://www.lg.com/be_fr/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D11" s="265" t="inlineStr">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -40625,7 +40625,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -42413,7 +42412,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="18.13" customWidth="1" style="203" min="1" max="1"/>
@@ -42557,68 +42556,68 @@
     <row r="11">
       <c r="B11" s="261" t="inlineStr">
         <is>
-          <t>BG : BG (bg)</t>
+          <t>BR : BR (pt)</t>
         </is>
       </c>
       <c r="C11" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/bg</t>
+          <t>https://www.lg.com/br</t>
         </is>
       </c>
       <c r="D11" s="264" t="inlineStr">
         <is>
-          <t>취소</t>
-        </is>
-      </c>
-      <c r="E11" s="123" t="n"/>
+          <t>법인리뷰</t>
+        </is>
+      </c>
+      <c r="E11" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="F11" s="123" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>법인 취소 요청(2026-09-15)</t>
+          <t>예상 2026-10-23 · 프로덕션 반영됨</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="261" t="inlineStr">
         <is>
-          <t>BR : BR (pt)</t>
+          <t>CA_EN : CA (en)</t>
         </is>
       </c>
       <c r="C12" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/br</t>
-        </is>
-      </c>
-      <c r="D12" s="264" t="inlineStr">
-        <is>
-          <t>법인리뷰</t>
+          <t>https://www.lg.com/ca_en</t>
+        </is>
+      </c>
+      <c r="D12" s="265" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="E12" s="123" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F12" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="0" t="inlineStr">
-        <is>
-          <t>예상 2026-10-23 · 프로덕션 반영됨</t>
-        </is>
-      </c>
+      <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="B13" s="261" t="inlineStr">
         <is>
-          <t>CA_EN : CA (en)</t>
+          <t>CA_FR : CA (fr)</t>
         </is>
       </c>
       <c r="C13" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_en</t>
+          <t>https://www.lg.com/ca_fr</t>
         </is>
       </c>
       <c r="D13" s="265" t="inlineStr">
@@ -42639,24 +42638,20 @@
     <row r="14">
       <c r="B14" s="261" t="inlineStr">
         <is>
-          <t>CA_FR : CA (fr)</t>
+          <t>CH_DE : CH (de)</t>
         </is>
       </c>
       <c r="C14" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ca_fr</t>
-        </is>
-      </c>
-      <c r="D14" s="265" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E14" s="123" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
+          <t>https://www.lg.com/ch_de</t>
+        </is>
+      </c>
+      <c r="D14" s="262" t="inlineStr">
+        <is>
+          <t>취소</t>
+        </is>
+      </c>
+      <c r="E14" s="123" t="inlineStr"/>
       <c r="F14" s="123" t="n">
         <v>1</v>
       </c>
@@ -42665,65 +42660,73 @@
     <row r="15">
       <c r="B15" s="261" t="inlineStr">
         <is>
-          <t>CH_DE : CH (de)</t>
+          <t>CH_FR : CH (fr)</t>
         </is>
       </c>
       <c r="C15" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ch_de</t>
-        </is>
-      </c>
-      <c r="D15" s="262" t="inlineStr">
+          <t>https://www.lg.com/ch_fr</t>
+        </is>
+      </c>
+      <c r="D15" s="264" t="inlineStr">
         <is>
           <t>취소</t>
         </is>
       </c>
-      <c r="E15" s="123" t="inlineStr"/>
+      <c r="E15" s="123" t="n"/>
       <c r="F15" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>법인 취소 요청(2026-09-16)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="261" t="inlineStr">
         <is>
-          <t>CH_FR : CH (fr)</t>
+          <t>CL : CL (es)</t>
         </is>
       </c>
       <c r="C16" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ch_fr</t>
+          <t>https://www.lg.com/cl</t>
         </is>
       </c>
       <c r="D16" s="264" t="inlineStr">
         <is>
-          <t>취소</t>
-        </is>
-      </c>
-      <c r="E16" s="123" t="n"/>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E16" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="F16" s="123" t="n">
         <v>1</v>
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>법인 취소 요청(2026-09-16)</t>
+          <t>예상 2026-10-23</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="261" t="inlineStr">
         <is>
-          <t>CL : CL (es)</t>
+          <t>CO : CO (es)</t>
         </is>
       </c>
       <c r="C17" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cl</t>
+          <t>https://www.lg.com/co</t>
         </is>
       </c>
       <c r="D17" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E17" s="123" t="inlineStr">
@@ -42736,49 +42739,45 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-23</t>
+          <t>예상 2026-10-23 · 프로덕션 반영됨</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="261" t="inlineStr">
         <is>
-          <t>CO : CO (es)</t>
+          <t>CZ : CZ (cz)</t>
         </is>
       </c>
       <c r="C18" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/co</t>
-        </is>
-      </c>
-      <c r="D18" s="264" t="inlineStr">
-        <is>
-          <t>법인리뷰</t>
+          <t>https://www.lg.com/cz</t>
+        </is>
+      </c>
+      <c r="D18" s="265" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="E18" s="123" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F18" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="0" t="inlineStr">
-        <is>
-          <t>예상 2026-10-23 · 프로덕션 반영됨</t>
-        </is>
-      </c>
+      <c r="G18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="261" t="inlineStr">
         <is>
-          <t>CZ : CZ (cz)</t>
+          <t>DE : DE (de)</t>
         </is>
       </c>
       <c r="C19" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cz</t>
+          <t>https://www.lg.com/de</t>
         </is>
       </c>
       <c r="D19" s="265" t="inlineStr">
@@ -42788,7 +42787,7 @@
       </c>
       <c r="E19" s="123" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F19" s="123" t="n">
@@ -42799,38 +42798,42 @@
     <row r="20">
       <c r="B20" s="261" t="inlineStr">
         <is>
-          <t>DE : DE (de)</t>
+          <t>DK : DK (da)</t>
         </is>
       </c>
       <c r="C20" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/de</t>
-        </is>
-      </c>
-      <c r="D20" s="265" t="inlineStr">
-        <is>
-          <t>완료</t>
+          <t>https://www.lg.com/dk</t>
+        </is>
+      </c>
+      <c r="D20" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E20" s="123" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F20" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-16</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="261" t="inlineStr">
         <is>
-          <t>DK : DK (da)</t>
+          <t>EG_AR : EG (ar)</t>
         </is>
       </c>
       <c r="C21" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/dk</t>
+          <t>https://www.lg.com/eg_ar</t>
         </is>
       </c>
       <c r="D21" s="264" t="inlineStr">
@@ -42840,7 +42843,7 @@
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="F21" s="123" t="n">
@@ -42848,19 +42851,19 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-16</t>
+          <t>예상 2026-10-02 · LDM 회신 대기, 09/30 무응답 시 취소</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="261" t="inlineStr">
         <is>
-          <t>EG_AR : EG (ar)</t>
+          <t>EG_EN : EG (en)</t>
         </is>
       </c>
       <c r="C22" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/eg_ar</t>
+          <t>https://www.lg.com/eg_en</t>
         </is>
       </c>
       <c r="D22" s="264" t="inlineStr">
@@ -42885,42 +42888,38 @@
     <row r="23">
       <c r="B23" s="261" t="inlineStr">
         <is>
-          <t>EG_EN : EG (en)</t>
+          <t>ES : ES (es)</t>
         </is>
       </c>
       <c r="C23" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/eg_en</t>
-        </is>
-      </c>
-      <c r="D23" s="264" t="inlineStr">
-        <is>
-          <t>작업중</t>
+          <t>https://www.lg.com/es</t>
+        </is>
+      </c>
+      <c r="D23" s="265" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="E23" s="123" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F23" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="0" t="inlineStr">
-        <is>
-          <t>예상 2026-10-02 · LDM 회신 대기, 09/30 무응답 시 취소</t>
-        </is>
-      </c>
+      <c r="G23" s="0" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" s="261" t="inlineStr">
         <is>
-          <t>ES : ES (es)</t>
+          <t>FR : FR (fr)</t>
         </is>
       </c>
       <c r="C24" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/es</t>
+          <t>https://www.lg.com/fr</t>
         </is>
       </c>
       <c r="D24" s="265" t="inlineStr">
@@ -42930,7 +42929,7 @@
       </c>
       <c r="E24" s="123" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F24" s="123" t="n">
@@ -42941,38 +42940,42 @@
     <row r="25">
       <c r="B25" s="261" t="inlineStr">
         <is>
-          <t>FR : FR (fr)</t>
+          <t>HK : HK (zh)</t>
         </is>
       </c>
       <c r="C25" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/fr</t>
-        </is>
-      </c>
-      <c r="D25" s="265" t="inlineStr">
-        <is>
-          <t>완료</t>
+          <t>https://www.lg.com/hk</t>
+        </is>
+      </c>
+      <c r="D25" s="264" t="inlineStr">
+        <is>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F25" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="0" t="inlineStr"/>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-09 · PTT 1006 법인 승인 완료 · QA Final Live Check(게시 직전)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="261" t="inlineStr">
         <is>
-          <t>HK : HK (zh)</t>
+          <t>HK_EN : HK (en)</t>
         </is>
       </c>
       <c r="C26" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk</t>
+          <t>https://www.lg.com/hk_en</t>
         </is>
       </c>
       <c r="D26" s="264" t="inlineStr">
@@ -42997,94 +43000,90 @@
     <row r="27">
       <c r="B27" s="261" t="inlineStr">
         <is>
-          <t>HK_EN : HK (en)</t>
+          <t>HU : HU (hu)</t>
         </is>
       </c>
       <c r="C27" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk_en</t>
+          <t>https://www.lg.com/hu</t>
         </is>
       </c>
       <c r="D27" s="264" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E27" s="123" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
+          <t>취소</t>
+        </is>
+      </c>
+      <c r="E27" s="123" t="inlineStr"/>
       <c r="F27" s="123" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-09 · PTT 1006 법인 승인 완료 · QA Final Live Check(게시 직전)</t>
+          <t>법인 취소 요청(2026-09-15)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="261" t="inlineStr">
         <is>
-          <t>HR : HR (hr)</t>
+          <t>ID : ID (id)</t>
         </is>
       </c>
       <c r="C28" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hr</t>
+          <t>https://www.lg.com/id</t>
         </is>
       </c>
       <c r="D28" s="264" t="inlineStr">
         <is>
-          <t>취소</t>
-        </is>
-      </c>
-      <c r="E28" s="123" t="n"/>
+          <t>법인리뷰</t>
+        </is>
+      </c>
+      <c r="E28" s="123" t="inlineStr"/>
       <c r="F28" s="123" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>법인 취소 요청(2026-09-15)</t>
+          <t>PTT 0929 · Client Review</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="261" t="inlineStr">
         <is>
-          <t>HU : HU (hu)</t>
+          <t>IN : IN (en)</t>
         </is>
       </c>
       <c r="C29" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hu</t>
-        </is>
-      </c>
-      <c r="D29" s="264" t="inlineStr">
-        <is>
-          <t>취소</t>
-        </is>
-      </c>
-      <c r="E29" s="123" t="inlineStr"/>
+          <t>https://www.lg.com/in</t>
+        </is>
+      </c>
+      <c r="D29" s="263" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E29" s="123" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
       <c r="F29" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="0" t="inlineStr">
-        <is>
-          <t>법인 취소 요청(2026-09-15)</t>
-        </is>
-      </c>
+      <c r="G29" s="0" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="B30" s="261" t="inlineStr">
         <is>
-          <t>ID : ID (id)</t>
+          <t>IT : IT (it)</t>
         </is>
       </c>
       <c r="C30" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/id</t>
+          <t>https://www.lg.com/it</t>
         </is>
       </c>
       <c r="D30" s="264" t="inlineStr">
@@ -43092,51 +43091,55 @@
           <t>법인리뷰</t>
         </is>
       </c>
-      <c r="E30" s="123" t="inlineStr"/>
+      <c r="E30" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="F30" s="123" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t>PTT 0929 · Client Review</t>
+          <t>예상 2026-10-02 · 법인리뷰</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="261" t="inlineStr">
         <is>
-          <t>IN : IN (en)</t>
+          <t>JP : JP (ja)</t>
         </is>
       </c>
       <c r="C31" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/in</t>
+          <t>https://www.lg.com/jp</t>
         </is>
       </c>
       <c r="D31" s="263" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E31" s="123" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
+          <t>취소</t>
+        </is>
+      </c>
+      <c r="E31" s="123" t="inlineStr"/>
       <c r="F31" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="0" t="inlineStr"/>
+      <c r="G31" s="0" t="inlineStr">
+        <is>
+          <t>법인 취소 요청(2026-09-15)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="B32" s="261" t="inlineStr">
         <is>
-          <t>IT : IT (it)</t>
+          <t>KZ : KZ (ru)</t>
         </is>
       </c>
       <c r="C32" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/it</t>
+          <t>https://www.lg.com/kz</t>
         </is>
       </c>
       <c r="D32" s="264" t="inlineStr">
@@ -43146,7 +43149,7 @@
       </c>
       <c r="E32" s="123" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="F32" s="123" t="n">
@@ -43154,22 +43157,22 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-02 · 법인리뷰</t>
+          <t>예상 2026-10-05 · LDM 9월 내 확인</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="261" t="inlineStr">
         <is>
-          <t>JP : JP (ja)</t>
+          <t>MA : MA (fr)</t>
         </is>
       </c>
       <c r="C33" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/jp</t>
-        </is>
-      </c>
-      <c r="D33" s="263" t="inlineStr">
+          <t>https://www.lg.com/ma</t>
+        </is>
+      </c>
+      <c r="D33" s="262" t="inlineStr">
         <is>
           <t>취소</t>
         </is>
@@ -43178,21 +43181,17 @@
       <c r="F33" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="0" t="inlineStr">
-        <is>
-          <t>법인 취소 요청(2026-09-15)</t>
-        </is>
-      </c>
+      <c r="G33" s="0" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="B34" s="261" t="inlineStr">
         <is>
-          <t>KZ : KZ (ru)</t>
+          <t>MX : MX (es)</t>
         </is>
       </c>
       <c r="C34" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/kz</t>
+          <t>https://www.lg.com/mx</t>
         </is>
       </c>
       <c r="D34" s="264" t="inlineStr">
@@ -43202,7 +43201,7 @@
       </c>
       <c r="E34" s="123" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F34" s="123" t="n">
@@ -43210,127 +43209,131 @@
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-05 · LDM 9월 내 확인</t>
+          <t>예상 2026-10-23 · 프로덕션 반영됨</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="261" t="inlineStr">
         <is>
-          <t>MA : MA (fr)</t>
+          <t>MY : MY (en)</t>
         </is>
       </c>
       <c r="C35" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ma</t>
-        </is>
-      </c>
-      <c r="D35" s="262" t="inlineStr">
-        <is>
-          <t>취소</t>
-        </is>
-      </c>
-      <c r="E35" s="123" t="inlineStr"/>
+          <t>https://www.lg.com/my</t>
+        </is>
+      </c>
+      <c r="D35" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E35" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="F35" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G35" s="0" t="inlineStr"/>
+      <c r="G35" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-09 · LDM 9월 내 확인</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="B36" s="261" t="inlineStr">
         <is>
-          <t>MX : MX (es)</t>
+          <t>NL : NL (nl)</t>
         </is>
       </c>
       <c r="C36" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/mx</t>
-        </is>
-      </c>
-      <c r="D36" s="264" t="inlineStr">
-        <is>
-          <t>법인리뷰</t>
+          <t>https://www.lg.com/nl</t>
+        </is>
+      </c>
+      <c r="D36" s="265" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="E36" s="123" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F36" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="0" t="inlineStr">
-        <is>
-          <t>예상 2026-10-23 · 프로덕션 반영됨</t>
-        </is>
-      </c>
+      <c r="G36" s="0" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="B37" s="261" t="inlineStr">
         <is>
-          <t>MY : MY (en)</t>
+          <t>NZ : NZ (en)</t>
         </is>
       </c>
       <c r="C37" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/my</t>
+          <t>https://www.lg.com/nz</t>
         </is>
       </c>
       <c r="D37" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E37" s="123" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
+          <t>법인리뷰</t>
+        </is>
+      </c>
+      <c r="E37" s="123" t="inlineStr"/>
       <c r="F37" s="123" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-09 · LDM 9월 내 확인</t>
+          <t>Hyper/Professional/Swing PLP 취소(09-14) · 나머지 Client Review (PTT 0929)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="261" t="inlineStr">
         <is>
-          <t>NL : NL (nl)</t>
+          <t>PA : PA (es)</t>
         </is>
       </c>
       <c r="C38" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/nl</t>
-        </is>
-      </c>
-      <c r="D38" s="265" t="inlineStr">
-        <is>
-          <t>완료</t>
+          <t>https://www.lg.com/pa</t>
+        </is>
+      </c>
+      <c r="D38" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E38" s="123" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F38" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="0" t="inlineStr"/>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-23</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="B39" s="261" t="inlineStr">
         <is>
-          <t>NZ : NZ (en)</t>
+          <t>PE : PE (es)</t>
         </is>
       </c>
       <c r="C39" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/nz</t>
+          <t>https://www.lg.com/pe</t>
         </is>
       </c>
       <c r="D39" s="264" t="inlineStr">
@@ -43342,73 +43345,73 @@
       <c r="F39" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G39" s="0" t="inlineStr">
-        <is>
-          <t>Hyper/Professional/Swing PLP 취소(09-14) · 나머지 Client Review (PTT 0929)</t>
-        </is>
-      </c>
+      <c r="G39" s="0" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="B40" s="261" t="inlineStr">
         <is>
-          <t>PA : PA (es)</t>
+          <t>PH : PH (en)</t>
         </is>
       </c>
       <c r="C40" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pa</t>
+          <t>https://www.lg.com/ph</t>
         </is>
       </c>
       <c r="D40" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E40" s="123" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
+          <t>법인리뷰</t>
+        </is>
+      </c>
+      <c r="E40" s="123" t="inlineStr"/>
       <c r="F40" s="123" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-23</t>
+          <t>PTT 0929 · Client Review</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="261" t="inlineStr">
         <is>
-          <t>PE : PE (es)</t>
+          <t>PL : PL (pl)</t>
         </is>
       </c>
       <c r="C41" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pe</t>
+          <t>https://www.lg.com/pl</t>
         </is>
       </c>
       <c r="D41" s="264" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E41" s="123" t="inlineStr"/>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E41" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="F41" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="0" t="inlineStr"/>
+      <c r="G41" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-16</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="B42" s="261" t="inlineStr">
         <is>
-          <t>PH : PH (en)</t>
+          <t>PT : PT (pt)</t>
         </is>
       </c>
       <c r="C42" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ph</t>
+          <t>https://www.lg.com/pt</t>
         </is>
       </c>
       <c r="D42" s="264" t="inlineStr">
@@ -43416,145 +43419,145 @@
           <t>법인리뷰</t>
         </is>
       </c>
-      <c r="E42" s="123" t="inlineStr"/>
+      <c r="E42" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="F42" s="123" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="0" t="inlineStr">
         <is>
-          <t>PTT 0929 · Client Review</t>
+          <t>예상 2026-10-16 · LDM 무응답, 리마인더 발송</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="261" t="inlineStr">
         <is>
-          <t>PL : PL (pl)</t>
+          <t>SA_AR : SA (ar)</t>
         </is>
       </c>
       <c r="C43" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pl</t>
-        </is>
-      </c>
-      <c r="D43" s="264" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E43" s="123" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
+          <t>https://www.lg.com/sa</t>
+        </is>
+      </c>
+      <c r="D43" s="263" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E43" s="200" t="n">
+        <v>46246</v>
       </c>
       <c r="F43" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="0" t="inlineStr">
-        <is>
-          <t>예상 2026-10-16</t>
-        </is>
-      </c>
+      <c r="G43" s="0" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="B44" s="261" t="inlineStr">
         <is>
-          <t>PT : PT (pt)</t>
+          <t>SA_EN : SA (en)</t>
         </is>
       </c>
       <c r="C44" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/pt</t>
-        </is>
-      </c>
-      <c r="D44" s="264" t="inlineStr">
-        <is>
-          <t>법인리뷰</t>
-        </is>
-      </c>
-      <c r="E44" s="123" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
+          <t>https://www.lg.com/sa_en</t>
+        </is>
+      </c>
+      <c r="D44" s="263" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E44" s="200" t="n">
+        <v>46246</v>
       </c>
       <c r="F44" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="0" t="inlineStr">
-        <is>
-          <t>예상 2026-10-16 · LDM 무응답, 리마인더 발송</t>
-        </is>
-      </c>
+      <c r="G44" s="0" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="B45" s="261" t="inlineStr">
         <is>
-          <t>RS : RS (sr)</t>
+          <t>SE : SE (sv)</t>
         </is>
       </c>
       <c r="C45" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/rs</t>
-        </is>
-      </c>
-      <c r="D45" s="263" t="inlineStr">
-        <is>
-          <t>취소</t>
-        </is>
-      </c>
-      <c r="E45" s="200" t="n"/>
+          <t>https://www.lg.com/se</t>
+        </is>
+      </c>
+      <c r="D45" s="264" t="inlineStr">
+        <is>
+          <t>법인리뷰</t>
+        </is>
+      </c>
+      <c r="E45" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="F45" s="123" t="n">
         <v>1</v>
       </c>
       <c r="G45" s="0" t="inlineStr">
         <is>
-          <t>법인 취소 요청(2026-09-15)</t>
+          <t>예상 2026-10-02 · 법인리뷰</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="261" t="inlineStr">
         <is>
-          <t>SA_AR : SA (ar)</t>
+          <t>SG : SG (en)</t>
         </is>
       </c>
       <c r="C46" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sa</t>
-        </is>
-      </c>
-      <c r="D46" s="263" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E46" s="200" t="n">
-        <v>46246</v>
+          <t>https://www.lg.com/sg</t>
+        </is>
+      </c>
+      <c r="D46" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E46" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
       </c>
       <c r="F46" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="0" t="inlineStr"/>
+      <c r="G46" s="0" t="inlineStr">
+        <is>
+          <t>예상 2026-10-09 · LDM 9월 내 확인</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="B47" s="261" t="inlineStr">
         <is>
-          <t>SA_EN : SA (en)</t>
+          <t>TH : TH (th)</t>
         </is>
       </c>
       <c r="C47" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sa_en</t>
-        </is>
-      </c>
-      <c r="D47" s="263" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E47" s="200" t="n">
-        <v>46246</v>
-      </c>
+          <t>https://www.lg.com/th</t>
+        </is>
+      </c>
+      <c r="D47" s="264" t="inlineStr">
+        <is>
+          <t>작업중</t>
+        </is>
+      </c>
+      <c r="E47" s="123" t="inlineStr"/>
       <c r="F47" s="123" t="n">
         <v>1</v>
       </c>
@@ -43563,22 +43566,22 @@
     <row r="48">
       <c r="B48" s="261" t="inlineStr">
         <is>
-          <t>SE : SE (sv)</t>
+          <t>TR : TR (tr)</t>
         </is>
       </c>
       <c r="C48" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/se</t>
+          <t>https://www.lg.com/tr</t>
         </is>
       </c>
       <c r="D48" s="264" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="E48" s="123" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="F48" s="123" t="n">
@@ -43586,19 +43589,19 @@
       </c>
       <c r="G48" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-02 · 법인리뷰</t>
+          <t>게시완료 · Final Live Check 잔여</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="261" t="inlineStr">
         <is>
-          <t>SG : SG (en)</t>
+          <t>TW : TW (zh)</t>
         </is>
       </c>
       <c r="C49" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sg</t>
+          <t>https://www.lg.com/tw</t>
         </is>
       </c>
       <c r="D49" s="264" t="inlineStr">
@@ -43606,37 +43609,33 @@
           <t>작업중</t>
         </is>
       </c>
-      <c r="E49" s="123" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
+      <c r="E49" s="123" t="inlineStr"/>
       <c r="F49" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="0" t="inlineStr">
-        <is>
-          <t>예상 2026-10-09 · LDM 9월 내 확인</t>
-        </is>
-      </c>
+      <c r="G49" s="0" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="B50" s="261" t="inlineStr">
         <is>
-          <t>TH : TH (th)</t>
+          <t>UK : GB (en)</t>
         </is>
       </c>
       <c r="C50" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/th</t>
-        </is>
-      </c>
-      <c r="D50" s="264" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E50" s="123" t="inlineStr"/>
+          <t>https://www.lg.com/uk</t>
+        </is>
+      </c>
+      <c r="D50" s="265" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E50" s="123" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="F50" s="123" t="n">
         <v>1</v>
       </c>
@@ -43645,12 +43644,12 @@
     <row r="51">
       <c r="B51" s="261" t="inlineStr">
         <is>
-          <t>TR : TR (tr)</t>
+          <t>VN : VN (vi)</t>
         </is>
       </c>
       <c r="C51" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/tr</t>
+          <t>https://www.lg.com/vn</t>
         </is>
       </c>
       <c r="D51" s="264" t="inlineStr">
@@ -43660,7 +43659,7 @@
       </c>
       <c r="E51" s="123" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F51" s="123" t="n">
@@ -43668,19 +43667,19 @@
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>게시완료 · Final Live Check 잔여</t>
+          <t>게시완료(09-10) · Hyper Mini LED PLP 취소(08-31)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="261" t="inlineStr">
         <is>
-          <t>TW : TW (zh)</t>
+          <t>ZA : ZA (en)</t>
         </is>
       </c>
       <c r="C52" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/tw</t>
+          <t>https://www.lg.com/za</t>
         </is>
       </c>
       <c r="D52" s="264" t="inlineStr">
@@ -43692,85 +43691,7 @@
       <c r="F52" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G52" s="0" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="B53" s="261" t="inlineStr">
-        <is>
-          <t>UK : GB (en)</t>
-        </is>
-      </c>
-      <c r="C53" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/uk</t>
-        </is>
-      </c>
-      <c r="D53" s="265" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E53" s="123" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="F53" s="123" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="0" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="B54" s="261" t="inlineStr">
-        <is>
-          <t>VN : VN (vi)</t>
-        </is>
-      </c>
-      <c r="C54" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/vn</t>
-        </is>
-      </c>
-      <c r="D54" s="264" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E54" s="123" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="F54" s="123" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="0" t="inlineStr">
-        <is>
-          <t>게시완료(09-10) · Hyper Mini LED PLP 취소(08-31)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="261" t="inlineStr">
-        <is>
-          <t>ZA : ZA (en)</t>
-        </is>
-      </c>
-      <c r="C55" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/za</t>
-        </is>
-      </c>
-      <c r="D55" s="264" t="inlineStr">
-        <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E55" s="123" t="inlineStr"/>
-      <c r="F55" s="123" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="0" t="inlineStr">
+      <c r="G52" s="0" t="inlineStr">
         <is>
           <t>GNB 수정 게시(07-27) · PTT 1006 Closed 6 · QA Final Live Check 1(완료 임박)</t>
         </is>
@@ -43822,9 +43743,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -45336,7 +45254,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -42843,7 +42843,7 @@
       </c>
       <c r="E21" s="123" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F21" s="123" t="n">
@@ -42851,7 +42851,7 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-02 · LDM 회신 대기, 09/30 무응답 시 취소</t>
+          <t>예상 2026-10-23 · 10/02→10/23 조정 · 9/30 무응답 시 취소 기한 경과, 취소 여부 확인 필요</t>
         </is>
       </c>
     </row>
@@ -42873,7 +42873,7 @@
       </c>
       <c r="E22" s="123" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F22" s="123" t="n">
@@ -42881,7 +42881,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-02 · LDM 회신 대기, 09/30 무응답 시 취소</t>
+          <t>예상 2026-10-23 · 10/02→10/23 조정 · 9/30 무응답 시 취소 기한 경과, 취소 여부 확인 필요</t>
         </is>
       </c>
     </row>
@@ -43093,7 +43093,7 @@
       </c>
       <c r="E30" s="123" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F30" s="123" t="n">
@@ -43101,7 +43101,7 @@
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-02 · 법인리뷰</t>
+          <t>예상 2026-10-23 · 10/02→10/23 조정(PTT 1006 Create Request)</t>
         </is>
       </c>
     </row>
@@ -43149,7 +43149,7 @@
       </c>
       <c r="E32" s="123" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F32" s="123" t="n">
@@ -43157,7 +43157,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-05 · LDM 9월 내 확인</t>
+          <t>예상 2026-10-16 · 10/05→10/16 조정(PTT 1006 Client Review)</t>
         </is>
       </c>
     </row>
@@ -43499,7 +43499,7 @@
       </c>
       <c r="E45" s="123" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="F45" s="123" t="n">
@@ -43507,7 +43507,7 @@
       </c>
       <c r="G45" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-02 · 법인리뷰</t>
+          <t>예상 2026-10-16 · 10/02→10/16 조정(PTT 1006 New Request)</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -42851,7 +42851,7 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-23 · 10/02→10/23 조정 · 9/30 무응답 시 취소 기한 경과, 취소 여부 확인 필요</t>
+          <t>예상 2026-10-23 · 10/02→10/23 조정 · PTT 1007 Create Request · 9/30 무응답 시 취소 기한 경과, 취소 여부 확인 필요</t>
         </is>
       </c>
     </row>
@@ -42881,7 +42881,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-23 · 10/02→10/23 조정 · 9/30 무응답 시 취소 기한 경과, 취소 여부 확인 필요</t>
+          <t>예상 2026-10-23 · 10/02→10/23 조정 · PTT 1007 Create Request · 9/30 무응답 시 취소 기한 경과, 취소 여부 확인 필요</t>
         </is>
       </c>
     </row>
@@ -42963,7 +42963,7 @@
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-09 · PTT 1006 법인 승인 완료 · QA Final Live Check(게시 직전)</t>
+          <t>예상 2026-10-09 · PTT 1007 Publishing Approve 1 · QA Final Live Check 6(게시 직전)</t>
         </is>
       </c>
     </row>
@@ -42993,7 +42993,7 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-09 · PTT 1006 법인 승인 완료 · QA Final Live Check(게시 직전)</t>
+          <t>예상 2026-10-09 · PTT 1007 Publishing Approve 1 · QA Final Live Check 5(게시 직전)</t>
         </is>
       </c>
     </row>
@@ -43101,7 +43101,7 @@
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-23 · 10/02→10/23 조정(PTT 1006 Create Request)</t>
+          <t>예상 2026-10-23 · 10/02→10/23 조정(PTT 1007 Create Request)</t>
         </is>
       </c>
     </row>
@@ -43157,7 +43157,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-16 · 10/05→10/16 조정(PTT 1006 Client Review)</t>
+          <t>예상 2026-10-16 · 10/05→10/16 조정(PTT 1007 Client Review)</t>
         </is>
       </c>
     </row>
@@ -43507,7 +43507,7 @@
       </c>
       <c r="G45" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-16 · 10/02→10/16 조정(PTT 1006 New Request)</t>
+          <t>예상 2026-10-16 · 10/02→10/16 조정(PTT 1007 New Request)</t>
         </is>
       </c>
     </row>
@@ -43693,7 +43693,7 @@
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t>GNB 수정 게시(07-27) · PTT 1006 Closed 6 · QA Final Live Check 1(완료 임박)</t>
+          <t>GNB 수정 게시(07-27) · PTT 1007 Closed 7 · QA Final Live Check 1(완료 임박)</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -42851,7 +42851,7 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-23 · 10/02→10/23 조정 · PTT 1007 Create Request · 9/30 무응답 시 취소 기한 경과, 취소 여부 확인 필요</t>
+          <t>예상 2026-10-23 · 10/02→10/23 조정 · 9/30 무응답 시 취소 기한 경과, 취소 여부 확인 필요</t>
         </is>
       </c>
     </row>
@@ -42881,7 +42881,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-23 · 10/02→10/23 조정 · PTT 1007 Create Request · 9/30 무응답 시 취소 기한 경과, 취소 여부 확인 필요</t>
+          <t>예상 2026-10-23 · 10/02→10/23 조정 · 9/30 무응답 시 취소 기한 경과, 취소 여부 확인 필요</t>
         </is>
       </c>
     </row>
@@ -42963,7 +42963,7 @@
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-09 · PTT 1007 Publishing Approve 1 · QA Final Live Check 6(게시 직전)</t>
+          <t>예상 2026-10-09 · 법인 승인 완료 · 게시 직전</t>
         </is>
       </c>
     </row>
@@ -42993,7 +42993,7 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-09 · PTT 1007 Publishing Approve 1 · QA Final Live Check 5(게시 직전)</t>
+          <t>예상 2026-10-09 · 법인 승인 완료 · 게시 직전</t>
         </is>
       </c>
     </row>
@@ -43045,7 +43045,7 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>PTT 0929 · Client Review</t>
+          <t>법인리뷰 진행 중</t>
         </is>
       </c>
     </row>
@@ -43101,7 +43101,7 @@
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-23 · 10/02→10/23 조정(PTT 1007 Create Request)</t>
+          <t>예상 2026-10-23 · 10/02→10/23 조정</t>
         </is>
       </c>
     </row>
@@ -43157,7 +43157,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-16 · 10/05→10/16 조정(PTT 1007 Client Review)</t>
+          <t>예상 2026-10-16 · 10/05→10/16 조정</t>
         </is>
       </c>
     </row>
@@ -43291,7 +43291,7 @@
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t>Hyper/Professional/Swing PLP 취소(09-14) · 나머지 Client Review (PTT 0929)</t>
+          <t>Hyper/Professional/Swing PLP 취소(09-14) · 나머지 법인리뷰 진행 중</t>
         </is>
       </c>
     </row>
@@ -43369,7 +43369,7 @@
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t>PTT 0929 · Client Review</t>
+          <t>법인리뷰 진행 중</t>
         </is>
       </c>
     </row>
@@ -43507,7 +43507,7 @@
       </c>
       <c r="G45" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-16 · 10/02→10/16 조정(PTT 1007 New Request)</t>
+          <t>예상 2026-10-16 · 10/02→10/16 조정</t>
         </is>
       </c>
     </row>
@@ -43693,7 +43693,7 @@
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t>GNB 수정 게시(07-27) · PTT 1007 Closed 7 · QA Final Live Check 1(완료 임박)</t>
+          <t>GNB 수정 게시(07-27) · 완료 임박(최종 게시 점검 중)</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -42838,20 +42838,16 @@
       </c>
       <c r="D21" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E21" s="123" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
+          <t>취소</t>
+        </is>
+      </c>
+      <c r="E21" s="123" t="n"/>
       <c r="F21" s="123" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-23 · 10/02→10/23 조정 · 9/30 무응답 시 취소 기한 경과, 취소 여부 확인 필요</t>
+          <t>LDM 무응답으로 법인 취소(2026-10-08)</t>
         </is>
       </c>
     </row>
@@ -42868,20 +42864,16 @@
       </c>
       <c r="D22" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E22" s="123" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
+          <t>취소</t>
+        </is>
+      </c>
+      <c r="E22" s="123" t="n"/>
       <c r="F22" s="123" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-23 · 10/02→10/23 조정 · 9/30 무응답 시 취소 기한 경과, 취소 여부 확인 필요</t>
+          <t>LDM 무응답으로 법인 취소(2026-10-08)</t>
         </is>
       </c>
     </row>
@@ -42963,7 +42955,7 @@
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-09 · 법인 승인 완료 · 게시 직전</t>
+          <t>예상 2026-10-09 · 법인 승인 완료 · 게시 진행 중</t>
         </is>
       </c>
     </row>
@@ -42993,7 +42985,7 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-09 · 법인 승인 완료 · 게시 직전</t>
+          <t>예상 2026-10-09 · 법인 승인 완료 · 게시 진행 중</t>
         </is>
       </c>
     </row>
@@ -43157,7 +43149,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-16 · 10/05→10/16 조정</t>
+          <t>예상 2026-10-16 · 10/05→10/16 조정 · 법인 승인 완료, 게시 진행 중</t>
         </is>
       </c>
     </row>
@@ -43684,16 +43676,20 @@
       </c>
       <c r="D52" s="264" t="inlineStr">
         <is>
-          <t>작업중</t>
-        </is>
-      </c>
-      <c r="E52" s="123" t="inlineStr"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E52" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="F52" s="123" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t>GNB 수정 게시(07-27) · 완료 임박(최종 게시 점검 중)</t>
+          <t>GNB 수정 게시(07-27) · 전체 게시 완료(10-07)</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -638,7 +638,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="297">
+  <cellXfs count="298">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -1224,6 +1224,7 @@
     </xf>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -40585,7 +40586,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
@@ -40611,7 +40612,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>금주 신규 등록 · 1차(W22) 44개국 + 기존 라이브 6곳(AE-en·BE-nl·DE·UK·SG·MX) = 50개 사이트 · 담당 정알찬 책임</t>
+          <t>요청서 Target List 65개 사이트 · 기존 50에 15개국 추가(AR·BG·CH-fr·CL·HR·LEVANT×2·LK·NP·RO·SK·TN·UZ×2·VN) · 담당 정알찬 책임</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -40625,6 +40626,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -40726,14 +40728,10 @@
     <row r="11">
       <c r="B11" s="261" t="inlineStr">
         <is>
-          <t>BD-en</t>
-        </is>
-      </c>
-      <c r="C11" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/bd/ultragear-gaming-buying-guide</t>
-        </is>
-      </c>
+          <t>AR-es</t>
+        </is>
+      </c>
+      <c r="C11" s="290" t="n"/>
       <c r="D11" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -40743,17 +40741,21 @@
       <c r="F11" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="0" t="n"/>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>요청서 Target List 추가</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="261" t="inlineStr">
         <is>
-          <t>BE-fr</t>
+          <t>BD-en</t>
         </is>
       </c>
       <c r="C12" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/be_fr/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/bd/ultragear-gaming-buying-guide</t>
         </is>
       </c>
       <c r="D12" s="265" t="inlineStr">
@@ -40770,12 +40772,12 @@
     <row r="13">
       <c r="B13" s="261" t="inlineStr">
         <is>
-          <t>BE-nl</t>
+          <t>BE-fr</t>
         </is>
       </c>
       <c r="C13" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/be/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/be_fr/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D13" s="265" t="inlineStr">
@@ -40787,19 +40789,19 @@
       <c r="F13" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="0" t="inlineStr">
-        <is>
-          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
-        </is>
-      </c>
+      <c r="G13" s="0" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="261" t="inlineStr">
         <is>
-          <t>BR-pt</t>
-        </is>
-      </c>
-      <c r="C14" s="290" t="n"/>
+          <t>BE-nl</t>
+        </is>
+      </c>
+      <c r="C14" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
       <c r="D14" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -40811,21 +40813,17 @@
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>신규 제작(1차 미게시)</t>
+          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="261" t="inlineStr">
         <is>
-          <t>CA-en</t>
-        </is>
-      </c>
-      <c r="C15" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ca_en/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
+          <t>BG-bg</t>
+        </is>
+      </c>
+      <c r="C15" s="290" t="n"/>
       <c r="D15" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -40835,19 +40833,19 @@
       <c r="F15" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="0" t="n"/>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>요청서 Target List 추가</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="261" t="inlineStr">
         <is>
-          <t>CA-fr</t>
-        </is>
-      </c>
-      <c r="C16" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ca_fr/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
+          <t>BR-pt</t>
+        </is>
+      </c>
+      <c r="C16" s="290" t="n"/>
       <c r="D16" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -40857,17 +40855,21 @@
       <c r="F16" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="0" t="n"/>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>신규 제작(1차 미게시)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="261" t="inlineStr">
         <is>
-          <t>CAC-es</t>
+          <t>CA-en</t>
         </is>
       </c>
       <c r="C17" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/cac/computacion/ultragear-buying-guide</t>
+          <t>https://www.lg.com/ca_en/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D17" s="265" t="inlineStr">
@@ -40884,10 +40886,14 @@
     <row r="18">
       <c r="B18" s="261" t="inlineStr">
         <is>
-          <t>CN-zh</t>
-        </is>
-      </c>
-      <c r="C18" s="290" t="n"/>
+          <t>CA-fr</t>
+        </is>
+      </c>
+      <c r="C18" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
       <c r="D18" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -40897,19 +40903,19 @@
       <c r="F18" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="0" t="inlineStr">
-        <is>
-          <t>신규 제작(1차 미게시)</t>
-        </is>
-      </c>
+      <c r="G18" s="0" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="261" t="inlineStr">
         <is>
-          <t>CO-es</t>
-        </is>
-      </c>
-      <c r="C19" s="290" t="n"/>
+          <t>CAC-es</t>
+        </is>
+      </c>
+      <c r="C19" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cac/computacion/ultragear-buying-guide</t>
+        </is>
+      </c>
       <c r="D19" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -40919,23 +40925,15 @@
       <c r="F19" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="0" t="inlineStr">
-        <is>
-          <t>신규 제작(1차 미게시)</t>
-        </is>
-      </c>
+      <c r="G19" s="0" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="261" t="inlineStr">
         <is>
-          <t>CZ-cz</t>
-        </is>
-      </c>
-      <c r="C20" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cz/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
+          <t>CH-fr</t>
+        </is>
+      </c>
+      <c r="C20" s="290" t="n"/>
       <c r="D20" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -40945,19 +40943,19 @@
       <c r="F20" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="0" t="n"/>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>요청서 Target List 추가</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="261" t="inlineStr">
         <is>
-          <t>DE-de</t>
-        </is>
-      </c>
-      <c r="C21" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/de/buying-guides/ultragear-buying-guide/</t>
-        </is>
-      </c>
+          <t>CL-es</t>
+        </is>
+      </c>
+      <c r="C21" s="290" t="n"/>
       <c r="D21" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -40969,21 +40967,17 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
+          <t>요청서 Target List 추가</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="261" t="inlineStr">
         <is>
-          <t>DK-da</t>
-        </is>
-      </c>
-      <c r="C22" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/dk/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
+          <t>CN-zh</t>
+        </is>
+      </c>
+      <c r="C22" s="290" t="n"/>
       <c r="D22" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -40993,19 +40987,19 @@
       <c r="F22" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="0" t="n"/>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>신규 제작(1차 미게시)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="261" t="inlineStr">
         <is>
-          <t>EC-es</t>
-        </is>
-      </c>
-      <c r="C23" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ec/computacion/ultragear-buying-guide</t>
-        </is>
-      </c>
+          <t>CO-es</t>
+        </is>
+      </c>
+      <c r="C23" s="290" t="n"/>
       <c r="D23" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41015,17 +41009,21 @@
       <c r="F23" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="0" t="n"/>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>신규 제작(1차 미게시)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="261" t="inlineStr">
         <is>
-          <t>EE-ee</t>
+          <t>CZ-cz</t>
         </is>
       </c>
       <c r="C24" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/ee/it-seadmed/buying-guide/ultragear-mangumonitorid</t>
+          <t>https://www.lg.com/cz/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D24" s="265" t="inlineStr">
@@ -41042,12 +41040,12 @@
     <row r="25">
       <c r="B25" s="261" t="inlineStr">
         <is>
-          <t>ES-es</t>
+          <t>DE-de</t>
         </is>
       </c>
       <c r="C25" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/es/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/de/buying-guides/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D25" s="265" t="inlineStr">
@@ -41059,17 +41057,21 @@
       <c r="F25" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="0" t="n"/>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="261" t="inlineStr">
         <is>
-          <t>FI-fi</t>
+          <t>DK-da</t>
         </is>
       </c>
       <c r="C26" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/fi/it-tuotteet/ultragear-buying-guide</t>
+          <t>https://www.lg.com/dk/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D26" s="265" t="inlineStr">
@@ -41086,12 +41088,12 @@
     <row r="27">
       <c r="B27" s="261" t="inlineStr">
         <is>
-          <t>FR-fr</t>
+          <t>EC-es</t>
         </is>
       </c>
       <c r="C27" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/fr/moniteurs/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/ec/computacion/ultragear-buying-guide</t>
         </is>
       </c>
       <c r="D27" s="265" t="inlineStr">
@@ -41108,10 +41110,14 @@
     <row r="28">
       <c r="B28" s="261" t="inlineStr">
         <is>
-          <t>GR-gr</t>
-        </is>
-      </c>
-      <c r="C28" s="290" t="n"/>
+          <t>EE-ee</t>
+        </is>
+      </c>
+      <c r="C28" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ee/it-seadmed/buying-guide/ultragear-mangumonitorid</t>
+        </is>
+      </c>
       <c r="D28" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41121,21 +41127,17 @@
       <c r="F28" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="0" t="inlineStr">
-        <is>
-          <t>신규 제작(1차 미게시)</t>
-        </is>
-      </c>
+      <c r="G28" s="0" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="261" t="inlineStr">
         <is>
-          <t>HK-en</t>
+          <t>ES-es</t>
         </is>
       </c>
       <c r="C29" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk_en/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/es/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D29" s="265" t="inlineStr">
@@ -41152,12 +41154,12 @@
     <row r="30">
       <c r="B30" s="261" t="inlineStr">
         <is>
-          <t>HK-zh</t>
+          <t>FI-fi</t>
         </is>
       </c>
       <c r="C30" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hk/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/fi/it-tuotteet/ultragear-buying-guide</t>
         </is>
       </c>
       <c r="D30" s="265" t="inlineStr">
@@ -41174,12 +41176,12 @@
     <row r="31">
       <c r="B31" s="261" t="inlineStr">
         <is>
-          <t>HU-hu</t>
+          <t>FR-fr</t>
         </is>
       </c>
       <c r="C31" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/hu/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/fr/moniteurs/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D31" s="265" t="inlineStr">
@@ -41196,14 +41198,10 @@
     <row r="32">
       <c r="B32" s="261" t="inlineStr">
         <is>
-          <t>ID-id</t>
-        </is>
-      </c>
-      <c r="C32" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/id/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
+          <t>GR-gr</t>
+        </is>
+      </c>
+      <c r="C32" s="290" t="n"/>
       <c r="D32" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41213,17 +41211,21 @@
       <c r="F32" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="0" t="n"/>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>신규 제작(1차 미게시)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="261" t="inlineStr">
         <is>
-          <t>IL-he</t>
+          <t>HK-en</t>
         </is>
       </c>
       <c r="C33" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/il/monitors/ultragear-buying-guide</t>
+          <t>https://www.lg.com/hk_en/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D33" s="265" t="inlineStr">
@@ -41240,12 +41242,12 @@
     <row r="34">
       <c r="B34" s="261" t="inlineStr">
         <is>
-          <t>IN-en</t>
+          <t>HK-zh</t>
         </is>
       </c>
       <c r="C34" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/in/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/hk/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D34" s="265" t="inlineStr">
@@ -41262,7 +41264,7 @@
     <row r="35">
       <c r="B35" s="261" t="inlineStr">
         <is>
-          <t>IT-it</t>
+          <t>HR-hr</t>
         </is>
       </c>
       <c r="C35" s="290" t="n"/>
@@ -41277,17 +41279,21 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t>신규 제작(1차 미게시)</t>
+          <t>요청서 Target List 추가</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="261" t="inlineStr">
         <is>
-          <t>JP-ja</t>
-        </is>
-      </c>
-      <c r="C36" s="290" t="n"/>
+          <t>HU-hu</t>
+        </is>
+      </c>
+      <c r="C36" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/hu/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
       <c r="D36" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41297,21 +41303,17 @@
       <c r="F36" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="0" t="inlineStr">
-        <is>
-          <t>신규 제작(1차 미게시)</t>
-        </is>
-      </c>
+      <c r="G36" s="0" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="261" t="inlineStr">
         <is>
-          <t>KZ-ru</t>
+          <t>ID-id</t>
         </is>
       </c>
       <c r="C37" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/kz/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/id/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D37" s="265" t="inlineStr">
@@ -41328,12 +41330,12 @@
     <row r="38">
       <c r="B38" s="261" t="inlineStr">
         <is>
-          <t>LT-lt</t>
+          <t>IL-he</t>
         </is>
       </c>
       <c r="C38" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/lt/kompiuterine-technika/buying-guide/ultragear-gaming-monitor</t>
+          <t>https://www.lg.com/il/monitors/ultragear-buying-guide</t>
         </is>
       </c>
       <c r="D38" s="265" t="inlineStr">
@@ -41350,12 +41352,12 @@
     <row r="39">
       <c r="B39" s="261" t="inlineStr">
         <is>
-          <t>LV-lv</t>
+          <t>IN-en</t>
         </is>
       </c>
       <c r="C39" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/lv/datortehnika/buying-guide/ultragear-gaming-monitor</t>
+          <t>https://www.lg.com/in/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D39" s="265" t="inlineStr">
@@ -41372,14 +41374,10 @@
     <row r="40">
       <c r="B40" s="261" t="inlineStr">
         <is>
-          <t>MX-es</t>
-        </is>
-      </c>
-      <c r="C40" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/mx/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C40" s="290" t="n"/>
       <c r="D40" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41391,21 +41389,17 @@
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
+          <t>신규 제작(1차 미게시)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="261" t="inlineStr">
         <is>
-          <t>NL-nl</t>
-        </is>
-      </c>
-      <c r="C41" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/nl/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
+          <t>JP-ja</t>
+        </is>
+      </c>
+      <c r="C41" s="290" t="n"/>
       <c r="D41" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41415,17 +41409,21 @@
       <c r="F41" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="0" t="n"/>
+      <c r="G41" s="0" t="inlineStr">
+        <is>
+          <t>신규 제작(1차 미게시)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="B42" s="261" t="inlineStr">
         <is>
-          <t>NO-no</t>
+          <t>KZ-ru</t>
         </is>
       </c>
       <c r="C42" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/no/it-produkter/ultragear-buying-guide</t>
+          <t>https://www.lg.com/kz/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D42" s="265" t="inlineStr">
@@ -41442,14 +41440,10 @@
     <row r="43">
       <c r="B43" s="261" t="inlineStr">
         <is>
-          <t>PA-es</t>
-        </is>
-      </c>
-      <c r="C43" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/pa/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
+          <t>LEVANT-ar</t>
+        </is>
+      </c>
+      <c r="C43" s="290" t="n"/>
       <c r="D43" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41459,19 +41453,19 @@
       <c r="F43" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="0" t="n"/>
+      <c r="G43" s="0" t="inlineStr">
+        <is>
+          <t>요청서 Target List 추가</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="B44" s="261" t="inlineStr">
         <is>
-          <t>PE-es</t>
-        </is>
-      </c>
-      <c r="C44" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/pe/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
+          <t>LEVANT-en</t>
+        </is>
+      </c>
+      <c r="C44" s="290" t="n"/>
       <c r="D44" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41481,19 +41475,19 @@
       <c r="F44" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="0" t="n"/>
+      <c r="G44" s="0" t="inlineStr">
+        <is>
+          <t>요청서 Target List 추가</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="B45" s="261" t="inlineStr">
         <is>
-          <t>PH-en</t>
-        </is>
-      </c>
-      <c r="C45" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ph/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
+          <t>LK-en</t>
+        </is>
+      </c>
+      <c r="C45" s="290" t="n"/>
       <c r="D45" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41503,15 +41497,23 @@
       <c r="F45" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="0" t="n"/>
+      <c r="G45" s="0" t="inlineStr">
+        <is>
+          <t>요청서 Target List 추가</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="B46" s="261" t="inlineStr">
         <is>
-          <t>PL-pl</t>
-        </is>
-      </c>
-      <c r="C46" s="290" t="n"/>
+          <t>LT-lt</t>
+        </is>
+      </c>
+      <c r="C46" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lt/kompiuterine-technika/buying-guide/ultragear-gaming-monitor</t>
+        </is>
+      </c>
       <c r="D46" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41521,19 +41523,19 @@
       <c r="F46" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="0" t="inlineStr">
-        <is>
-          <t>신규 제작(1차 미게시)</t>
-        </is>
-      </c>
+      <c r="G46" s="0" t="n"/>
     </row>
     <row r="47">
       <c r="B47" s="261" t="inlineStr">
         <is>
-          <t>PT-pt</t>
-        </is>
-      </c>
-      <c r="C47" s="290" t="n"/>
+          <t>LV-lv</t>
+        </is>
+      </c>
+      <c r="C47" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/lv/datortehnika/buying-guide/ultragear-gaming-monitor</t>
+        </is>
+      </c>
       <c r="D47" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41543,21 +41545,17 @@
       <c r="F47" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="0" t="inlineStr">
-        <is>
-          <t>신규 제작(1차 미게시)</t>
-        </is>
-      </c>
+      <c r="G47" s="0" t="n"/>
     </row>
     <row r="48">
       <c r="B48" s="261" t="inlineStr">
         <is>
-          <t>RS-rs</t>
+          <t>MX-es</t>
         </is>
       </c>
       <c r="C48" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/rs/it-proizvodi/ultragear-buying-guide</t>
+          <t>https://www.lg.com/mx/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D48" s="265" t="inlineStr">
@@ -41569,17 +41567,21 @@
       <c r="F48" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="0" t="n"/>
+      <c r="G48" s="0" t="inlineStr">
+        <is>
+          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="B49" s="261" t="inlineStr">
         <is>
-          <t>SA-ar</t>
+          <t>NL-nl</t>
         </is>
       </c>
       <c r="C49" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sa/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/nl/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D49" s="265" t="inlineStr">
@@ -41596,12 +41598,12 @@
     <row r="50">
       <c r="B50" s="261" t="inlineStr">
         <is>
-          <t>SA-en</t>
+          <t>NO-no</t>
         </is>
       </c>
       <c r="C50" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sa_en/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/no/it-produkter/ultragear-buying-guide</t>
         </is>
       </c>
       <c r="D50" s="265" t="inlineStr">
@@ -41618,14 +41620,10 @@
     <row r="51">
       <c r="B51" s="261" t="inlineStr">
         <is>
-          <t>SE-sv</t>
-        </is>
-      </c>
-      <c r="C51" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/se/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
+          <t>NP-en</t>
+        </is>
+      </c>
+      <c r="C51" s="290" t="n"/>
       <c r="D51" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41635,17 +41633,21 @@
       <c r="F51" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G51" s="0" t="n"/>
+      <c r="G51" s="0" t="inlineStr">
+        <is>
+          <t>요청서 Target List 추가</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="B52" s="261" t="inlineStr">
         <is>
-          <t>SG-en</t>
+          <t>PA-es</t>
         </is>
       </c>
       <c r="C52" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/sg/consumer-monitors/featured-page/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/pa/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D52" s="265" t="inlineStr">
@@ -41657,21 +41659,17 @@
       <c r="F52" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G52" s="0" t="inlineStr">
-        <is>
-          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
-        </is>
-      </c>
+      <c r="G52" s="0" t="n"/>
     </row>
     <row r="53">
       <c r="B53" s="261" t="inlineStr">
         <is>
-          <t>TH-th</t>
+          <t>PE-es</t>
         </is>
       </c>
       <c r="C53" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/th/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/pe/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D53" s="265" t="inlineStr">
@@ -41688,12 +41686,12 @@
     <row r="54">
       <c r="B54" s="261" t="inlineStr">
         <is>
-          <t>TR-tr</t>
+          <t>PH-en</t>
         </is>
       </c>
       <c r="C54" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/tr/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/ph/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
         </is>
       </c>
       <c r="D54" s="265" t="inlineStr">
@@ -41710,14 +41708,10 @@
     <row r="55">
       <c r="B55" s="261" t="inlineStr">
         <is>
-          <t>TW-zh</t>
-        </is>
-      </c>
-      <c r="C55" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/tw/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
-        </is>
-      </c>
+          <t>PL-pl</t>
+        </is>
+      </c>
+      <c r="C55" s="290" t="n"/>
       <c r="D55" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41727,19 +41721,19 @@
       <c r="F55" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G55" s="0" t="n"/>
+      <c r="G55" s="0" t="inlineStr">
+        <is>
+          <t>신규 제작(1차 미게시)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="B56" s="261" t="inlineStr">
         <is>
-          <t>UA-uk</t>
-        </is>
-      </c>
-      <c r="C56" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ua/it-products/ultragear-buying-guide</t>
-        </is>
-      </c>
+          <t>PT-pt</t>
+        </is>
+      </c>
+      <c r="C56" s="290" t="n"/>
       <c r="D56" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41749,19 +41743,19 @@
       <c r="F56" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G56" s="0" t="n"/>
+      <c r="G56" s="0" t="inlineStr">
+        <is>
+          <t>신규 제작(1차 미게시)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="B57" s="261" t="inlineStr">
         <is>
-          <t>UK-en</t>
-        </is>
-      </c>
-      <c r="C57" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/uk/computing/buying-guides/ultragear/</t>
-        </is>
-      </c>
+          <t>RO-ro</t>
+        </is>
+      </c>
+      <c r="C57" s="290" t="n"/>
       <c r="D57" s="265" t="inlineStr">
         <is>
           <t>사전검토</t>
@@ -41773,19 +41767,19 @@
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
-          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
+          <t>요청서 Target List 추가</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="261" t="inlineStr">
         <is>
-          <t>ZA-en</t>
+          <t>RS-rs</t>
         </is>
       </c>
       <c r="C58" s="290" t="inlineStr">
         <is>
-          <t>https://www.lg.com/za/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+          <t>https://www.lg.com/rs/it-proizvodi/ultragear-buying-guide</t>
         </is>
       </c>
       <c r="D58" s="265" t="inlineStr">
@@ -41798,51 +41792,389 @@
         <v>1</v>
       </c>
       <c r="G58" s="0" t="n"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="261" t="inlineStr">
+        <is>
+          <t>SA-ar</t>
+        </is>
+      </c>
+      <c r="C59" s="297" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sa/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D59" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E59" s="123" t="n"/>
+      <c r="F59" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="0" t="n"/>
+    </row>
+    <row r="60">
+      <c r="B60" s="261" t="inlineStr">
+        <is>
+          <t>SA-en</t>
+        </is>
+      </c>
+      <c r="C60" s="297" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sa_en/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D60" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E60" s="123" t="n"/>
+      <c r="F60" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="0" t="n"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="261" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C61" s="297" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D61" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E61" s="123" t="n"/>
+      <c r="F61" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="0" t="n"/>
+    </row>
+    <row r="62">
+      <c r="B62" s="261" t="inlineStr">
+        <is>
+          <t>SG-en</t>
+        </is>
+      </c>
+      <c r="C62" s="297" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/consumer-monitors/featured-page/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D62" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E62" s="123" t="n"/>
+      <c r="F62" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="0" t="inlineStr">
+        <is>
+          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="261" t="inlineStr">
+        <is>
+          <t>SK-sk</t>
+        </is>
+      </c>
+      <c r="C63" s="297" t="n"/>
+      <c r="D63" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E63" s="123" t="n"/>
+      <c r="F63" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="0" t="inlineStr">
+        <is>
+          <t>요청서 Target List 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="261" t="inlineStr">
+        <is>
+          <t>TH-th</t>
+        </is>
+      </c>
+      <c r="C64" s="297" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/th/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D64" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E64" s="123" t="n"/>
+      <c r="F64" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="0" t="n"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="261" t="inlineStr">
+        <is>
+          <t>TN-fr</t>
+        </is>
+      </c>
+      <c r="C65" s="297" t="n"/>
+      <c r="D65" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E65" s="123" t="n"/>
+      <c r="F65" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="0" t="inlineStr">
+        <is>
+          <t>요청서 Target List 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="261" t="inlineStr">
+        <is>
+          <t>TR-tr</t>
+        </is>
+      </c>
+      <c r="C66" s="297" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tr/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D66" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E66" s="123" t="n"/>
+      <c r="F66" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="0" t="n"/>
+    </row>
+    <row r="67">
+      <c r="B67" s="261" t="inlineStr">
+        <is>
+          <t>TW-zh</t>
+        </is>
+      </c>
+      <c r="C67" s="297" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D67" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E67" s="123" t="n"/>
+      <c r="F67" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="0" t="n"/>
+    </row>
+    <row r="68">
+      <c r="B68" s="261" t="inlineStr">
+        <is>
+          <t>UA-uk</t>
+        </is>
+      </c>
+      <c r="C68" s="297" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ua/it-products/ultragear-buying-guide</t>
+        </is>
+      </c>
+      <c r="D68" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E68" s="123" t="n"/>
+      <c r="F68" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="0" t="n"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="261" t="inlineStr">
+        <is>
+          <t>UK-en</t>
+        </is>
+      </c>
+      <c r="C69" s="297" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/computing/buying-guides/ultragear/</t>
+        </is>
+      </c>
+      <c r="D69" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E69" s="123" t="n"/>
+      <c r="F69" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="0" t="inlineStr">
+        <is>
+          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="261" t="inlineStr">
+        <is>
+          <t>UZ-ru</t>
+        </is>
+      </c>
+      <c r="C70" s="297" t="n"/>
+      <c r="D70" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E70" s="123" t="n"/>
+      <c r="F70" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="0" t="inlineStr">
+        <is>
+          <t>요청서 Target List 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="261" t="inlineStr">
+        <is>
+          <t>UZ-uz</t>
+        </is>
+      </c>
+      <c r="C71" s="297" t="n"/>
+      <c r="D71" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E71" s="123" t="n"/>
+      <c r="F71" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="0" t="inlineStr">
+        <is>
+          <t>요청서 Target List 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="261" t="inlineStr">
+        <is>
+          <t>VN-vi</t>
+        </is>
+      </c>
+      <c r="C72" s="297" t="n"/>
+      <c r="D72" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E72" s="123" t="n"/>
+      <c r="F72" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="0" t="inlineStr">
+        <is>
+          <t>요청서 Target List 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="261" t="inlineStr">
+        <is>
+          <t>ZA-en</t>
+        </is>
+      </c>
+      <c r="C73" s="297" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/za/microsite-article/ms/it/monitor/ultragear-buying-guide/</t>
+        </is>
+      </c>
+      <c r="D73" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E73" s="123" t="n"/>
+      <c r="F73" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="0" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -14287,7 +14287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14310,7 +14310,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>예정 · 자산 배포 2026-08-09(EN)/2026-09-11(현지화) · 구현 마감 2026-11-15(Jumpstart OEM.com 준수)</t>
+          <t>예정 · 요청서 2026-10-07 기준 15사이트(Global 포함) · Due 2026-10-31 · 담당 정의현 책임</t>
         </is>
       </c>
     </row>
@@ -14351,7 +14351,414 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="B4" s="261" t="inlineStr">
+        <is>
+          <t>GLOBAL : GLOBAL (en)</t>
+        </is>
+      </c>
+      <c r="C4" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/laptops/windows-11/</t>
+        </is>
+      </c>
+      <c r="D4" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E4" s="123" t="n"/>
+      <c r="F4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>MS 참고본(English)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="261" t="inlineStr">
+        <is>
+          <t>CA-en</t>
+        </is>
+      </c>
+      <c r="C5" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/laptops/windows-11/</t>
+        </is>
+      </c>
+      <c r="D5" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E5" s="123" t="n"/>
+      <c r="F5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t>MS 참고본(English)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="261" t="inlineStr">
+        <is>
+          <t>CA-fr</t>
+        </is>
+      </c>
+      <c r="C6" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/page-de-presentation/decouvrez-choisirmc-lg-gram/windows-11/</t>
+        </is>
+      </c>
+      <c r="D6" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E6" s="123" t="n"/>
+      <c r="F6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>Translation FR-CA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="261" t="inlineStr">
+        <is>
+          <t>ES-es</t>
+        </is>
+      </c>
+      <c r="C7" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/ordenadores/windows-11/</t>
+        </is>
+      </c>
+      <c r="D7" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E7" s="123" t="n"/>
+      <c r="F7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>Translation ES-ES</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="261" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C8" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/notebook/windows-11/</t>
+        </is>
+      </c>
+      <c r="D8" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E8" s="123" t="n"/>
+      <c r="F8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>MS 참고본(It-LT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="261" t="inlineStr">
+        <is>
+          <t>UK-en</t>
+        </is>
+      </c>
+      <c r="C9" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/laptops/windows-11/</t>
+        </is>
+      </c>
+      <c r="D9" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E9" s="123" t="n"/>
+      <c r="F9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>Translation EN-GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="261" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C10" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/notebooks/windows-11/</t>
+        </is>
+      </c>
+      <c r="D10" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E10" s="123" t="n"/>
+      <c r="F10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>Translation DE-DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="261" t="inlineStr">
+        <is>
+          <t>FR-fr</t>
+        </is>
+      </c>
+      <c r="C11" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/pc-portables/windows11/</t>
+        </is>
+      </c>
+      <c r="D11" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E11" s="123" t="n"/>
+      <c r="F11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>Translation FR-FR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="261" t="inlineStr">
+        <is>
+          <t>AU-en</t>
+        </is>
+      </c>
+      <c r="C12" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/windows-11/</t>
+        </is>
+      </c>
+      <c r="D12" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E12" s="123" t="n"/>
+      <c r="F12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>Translation EN-GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="261" t="inlineStr">
+        <is>
+          <t>IN-en</t>
+        </is>
+      </c>
+      <c r="C13" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/in/laptop/windows-11/</t>
+        </is>
+      </c>
+      <c r="D13" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E13" s="123" t="n"/>
+      <c r="F13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>MS 참고본(English)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="261" t="inlineStr">
+        <is>
+          <t>JP-ja</t>
+        </is>
+      </c>
+      <c r="C14" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/computer-pc/windows11/</t>
+        </is>
+      </c>
+      <c r="D14" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E14" s="123" t="n"/>
+      <c r="F14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>Translation JA-JP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="261" t="inlineStr">
+        <is>
+          <t>CN-zh</t>
+        </is>
+      </c>
+      <c r="C15" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/notebooks/windows11</t>
+        </is>
+      </c>
+      <c r="D15" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E15" s="123" t="n"/>
+      <c r="F15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>MS 참고본(zh-CN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="261" t="inlineStr">
+        <is>
+          <t>SG-en</t>
+        </is>
+      </c>
+      <c r="C16" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/windows-11/</t>
+        </is>
+      </c>
+      <c r="D16" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E16" s="123" t="n"/>
+      <c r="F16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>MS 참고본(English)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="261" t="inlineStr">
+        <is>
+          <t>VN-vi</t>
+        </is>
+      </c>
+      <c r="C17" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/laptop-lg-gram/windows-11/</t>
+        </is>
+      </c>
+      <c r="D17" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E17" s="123" t="n"/>
+      <c r="F17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>MS 참고본(vi-VN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="261" t="inlineStr">
+        <is>
+          <t>TW-zh</t>
+        </is>
+      </c>
+      <c r="C18" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/laptops/windows-11/</t>
+        </is>
+      </c>
+      <c r="D18" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E18" s="123" t="n"/>
+      <c r="F18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>MS 참고본(zh-TW)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -40626,7 +41033,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -20,15 +20,15 @@
     <sheet name="W30 - SmartMonitor ScreenShare" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="W30 - UltraGear 1000Hz FAQ" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="W31 - gram Secure Lock" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Windows 11 Landing" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="W31 - PDP Gallery Win11 Pro" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="W31 - Smart Monitor Multi AI" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="W32 - UltraGear 27GX704A" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="W32 - Digital Trends Award 삭제" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="W32 - UltraGear PDP 5모델" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="W32 - UltraFine PDP MIC 삭제" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="W38 - gram pro gallery" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="W41 - UltraGear Buying Guide 2차" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="W31 - PDP Gallery Win11 Pro" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="W31 - Smart Monitor Multi AI" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="W32 - UltraGear 27GX704A" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="W32 - Digital Trends Award 삭제" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="W32 - UltraGear PDP 5모델" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="W32 - UltraFine PDP MIC 삭제" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="W38 - gram pro gallery" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="W41 - UltraGear Buying Guide 2차" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="W41 - Windows 11 Landing" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14287,488 +14287,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>GR26-MS-IT Windows 11 Home Landing Page 업데이트</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="inlineStr">
-        <is>
-          <t>이번주 추가</t>
-        </is>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>예정 · 요청서 2026-10-07 기준 15사이트(Global 포함) · Due 2026-10-31 · 담당 정의현 책임</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>Head</t>
-        </is>
-      </c>
-      <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="C3" s="0" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="D3" s="0" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E3" s="0" t="inlineStr">
-        <is>
-          <t>완료일</t>
-        </is>
-      </c>
-      <c r="F3" s="0" t="inlineStr">
-        <is>
-          <t>Page#</t>
-        </is>
-      </c>
-      <c r="G3" s="0" t="inlineStr">
-        <is>
-          <t>Remark</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="261" t="inlineStr">
-        <is>
-          <t>GLOBAL : GLOBAL (en)</t>
-        </is>
-      </c>
-      <c r="C4" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/global/laptops/windows-11/</t>
-        </is>
-      </c>
-      <c r="D4" s="265" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E4" s="123" t="n"/>
-      <c r="F4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="0" t="inlineStr">
-        <is>
-          <t>MS 참고본(English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="261" t="inlineStr">
-        <is>
-          <t>CA-en</t>
-        </is>
-      </c>
-      <c r="C5" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ca_en/laptops/windows-11/</t>
-        </is>
-      </c>
-      <c r="D5" s="265" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E5" s="123" t="n"/>
-      <c r="F5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="0" t="inlineStr">
-        <is>
-          <t>MS 참고본(English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="261" t="inlineStr">
-        <is>
-          <t>CA-fr</t>
-        </is>
-      </c>
-      <c r="C6" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ca_fr/page-de-presentation/decouvrez-choisirmc-lg-gram/windows-11/</t>
-        </is>
-      </c>
-      <c r="D6" s="265" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E6" s="123" t="n"/>
-      <c r="F6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="0" t="inlineStr">
-        <is>
-          <t>Translation FR-CA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="261" t="inlineStr">
-        <is>
-          <t>ES-es</t>
-        </is>
-      </c>
-      <c r="C7" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/es/ordenadores/windows-11/</t>
-        </is>
-      </c>
-      <c r="D7" s="265" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E7" s="123" t="n"/>
-      <c r="F7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="0" t="inlineStr">
-        <is>
-          <t>Translation ES-ES</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="261" t="inlineStr">
-        <is>
-          <t>IT-it</t>
-        </is>
-      </c>
-      <c r="C8" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/it/notebook/windows-11/</t>
-        </is>
-      </c>
-      <c r="D8" s="265" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E8" s="123" t="n"/>
-      <c r="F8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="0" t="inlineStr">
-        <is>
-          <t>MS 참고본(It-LT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="261" t="inlineStr">
-        <is>
-          <t>UK-en</t>
-        </is>
-      </c>
-      <c r="C9" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/uk/laptops/windows-11/</t>
-        </is>
-      </c>
-      <c r="D9" s="265" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E9" s="123" t="n"/>
-      <c r="F9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="0" t="inlineStr">
-        <is>
-          <t>Translation EN-GB</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="261" t="inlineStr">
-        <is>
-          <t>DE-de</t>
-        </is>
-      </c>
-      <c r="C10" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/de/notebooks/windows-11/</t>
-        </is>
-      </c>
-      <c r="D10" s="265" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E10" s="123" t="n"/>
-      <c r="F10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t>Translation DE-DE</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="261" t="inlineStr">
-        <is>
-          <t>FR-fr</t>
-        </is>
-      </c>
-      <c r="C11" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/fr/pc-portables/windows11/</t>
-        </is>
-      </c>
-      <c r="D11" s="265" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E11" s="123" t="n"/>
-      <c r="F11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="0" t="inlineStr">
-        <is>
-          <t>Translation FR-FR</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="261" t="inlineStr">
-        <is>
-          <t>AU-en</t>
-        </is>
-      </c>
-      <c r="C12" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/au/laptops/windows-11/</t>
-        </is>
-      </c>
-      <c r="D12" s="265" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E12" s="123" t="n"/>
-      <c r="F12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="0" t="inlineStr">
-        <is>
-          <t>Translation EN-GB</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="261" t="inlineStr">
-        <is>
-          <t>IN-en</t>
-        </is>
-      </c>
-      <c r="C13" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/in/laptop/windows-11/</t>
-        </is>
-      </c>
-      <c r="D13" s="265" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E13" s="123" t="n"/>
-      <c r="F13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="0" t="inlineStr">
-        <is>
-          <t>MS 참고본(English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="261" t="inlineStr">
-        <is>
-          <t>JP-ja</t>
-        </is>
-      </c>
-      <c r="C14" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/jp/computer-pc/windows11/</t>
-        </is>
-      </c>
-      <c r="D14" s="265" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E14" s="123" t="n"/>
-      <c r="F14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="0" t="inlineStr">
-        <is>
-          <t>Translation JA-JP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="261" t="inlineStr">
-        <is>
-          <t>CN-zh</t>
-        </is>
-      </c>
-      <c r="C15" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/cn/notebooks/windows11</t>
-        </is>
-      </c>
-      <c r="D15" s="265" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E15" s="123" t="n"/>
-      <c r="F15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="0" t="inlineStr">
-        <is>
-          <t>MS 참고본(zh-CN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="261" t="inlineStr">
-        <is>
-          <t>SG-en</t>
-        </is>
-      </c>
-      <c r="C16" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sg/laptops/windows-11/</t>
-        </is>
-      </c>
-      <c r="D16" s="265" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E16" s="123" t="n"/>
-      <c r="F16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="0" t="inlineStr">
-        <is>
-          <t>MS 참고본(English)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="261" t="inlineStr">
-        <is>
-          <t>VN-vi</t>
-        </is>
-      </c>
-      <c r="C17" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/vn/laptop-lg-gram/windows-11/</t>
-        </is>
-      </c>
-      <c r="D17" s="265" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E17" s="123" t="n"/>
-      <c r="F17" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="0" t="inlineStr">
-        <is>
-          <t>MS 참고본(vi-VN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="261" t="inlineStr">
-        <is>
-          <t>TW-zh</t>
-        </is>
-      </c>
-      <c r="C18" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/tw/laptops/windows-11/</t>
-        </is>
-      </c>
-      <c r="D18" s="265" t="inlineStr">
-        <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E18" s="123" t="n"/>
-      <c r="F18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="0" t="inlineStr">
-        <is>
-          <t>MS 참고본(zh-TW)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId15"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -17289,967 +16807,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AP16"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col width="8.130000000000001" customWidth="1" style="203" min="1" max="1"/>
-    <col width="49.63" customWidth="1" style="203" min="4" max="4"/>
-    <col width="13" customWidth="1" style="203" min="39" max="39"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="35" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" s="36" t="inlineStr">
-        <is>
-          <t>GR26-W16-MS-IT-PC Copilot+ Filter Creation</t>
-        </is>
-      </c>
-      <c r="C1" s="37" t="n"/>
-      <c r="D1" s="37" t="n"/>
-      <c r="E1" s="37" t="n"/>
-      <c r="K1" s="37" t="n"/>
-      <c r="L1" s="37" t="n"/>
-      <c r="M1" s="37" t="n"/>
-      <c r="N1" s="37" t="n"/>
-      <c r="O1" s="37" t="n"/>
-      <c r="P1" s="37" t="n"/>
-      <c r="Q1" s="37" t="n"/>
-      <c r="R1" s="37" t="n"/>
-      <c r="S1" s="37" t="n"/>
-      <c r="T1" s="37" t="n"/>
-      <c r="U1" s="37" t="n"/>
-      <c r="V1" s="37" t="n"/>
-      <c r="W1" s="37" t="n"/>
-      <c r="X1" s="37" t="n"/>
-      <c r="Y1" s="37" t="n"/>
-      <c r="Z1" s="37" t="n"/>
-      <c r="AA1" s="37" t="n"/>
-      <c r="AB1" s="37" t="n"/>
-      <c r="AC1" s="37" t="n"/>
-      <c r="AD1" s="37" t="n"/>
-      <c r="AE1" s="37" t="n"/>
-      <c r="AF1" s="37" t="n"/>
-      <c r="AG1" s="37" t="n"/>
-      <c r="AH1" s="38" t="n"/>
-      <c r="AI1" s="38" t="n"/>
-      <c r="AJ1" s="38" t="n"/>
-      <c r="AK1" s="38" t="n"/>
-      <c r="AL1" s="38" t="n"/>
-      <c r="AM1" s="38" t="n"/>
-      <c r="AN1" s="39" t="n"/>
-      <c r="AO1" s="39" t="n"/>
-      <c r="AP1" s="39" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="40" t="inlineStr">
-        <is>
-          <t>이번주 추가</t>
-        </is>
-      </c>
-      <c r="B2" s="41" t="inlineStr">
-        <is>
-          <t>GLOBAL : 작업중 → 완료</t>
-        </is>
-      </c>
-      <c r="C2" s="37" t="n"/>
-      <c r="D2" s="37" t="n"/>
-      <c r="E2" s="37" t="n"/>
-      <c r="K2" s="37" t="n"/>
-      <c r="L2" s="37" t="n"/>
-      <c r="M2" s="37" t="n"/>
-      <c r="N2" s="37" t="n"/>
-      <c r="O2" s="37" t="n"/>
-      <c r="P2" s="37" t="n"/>
-      <c r="Q2" s="37" t="n"/>
-      <c r="R2" s="37" t="n"/>
-      <c r="S2" s="37" t="n"/>
-      <c r="T2" s="37" t="n"/>
-      <c r="U2" s="37" t="n"/>
-      <c r="V2" s="37" t="n"/>
-      <c r="W2" s="37" t="n"/>
-      <c r="X2" s="37" t="n"/>
-      <c r="Y2" s="37" t="n"/>
-      <c r="Z2" s="37" t="n"/>
-      <c r="AA2" s="37" t="n"/>
-      <c r="AB2" s="37" t="n"/>
-      <c r="AC2" s="37" t="n"/>
-      <c r="AD2" s="37" t="n"/>
-      <c r="AE2" s="37" t="n"/>
-      <c r="AF2" s="37" t="n"/>
-      <c r="AG2" s="37" t="n"/>
-      <c r="AH2" s="38" t="n"/>
-      <c r="AI2" s="38" t="n"/>
-      <c r="AJ2" s="38" t="n"/>
-      <c r="AK2" s="38" t="n"/>
-      <c r="AL2" s="38" t="n"/>
-      <c r="AM2" s="38" t="n"/>
-      <c r="AN2" s="39" t="n"/>
-      <c r="AO2" s="39" t="n"/>
-      <c r="AP2" s="39" t="n"/>
-    </row>
-    <row r="3" ht="42.75" customHeight="1" s="203">
-      <c r="D3" s="37" t="n"/>
-      <c r="E3" s="37" t="n"/>
-      <c r="K3" s="37" t="n"/>
-      <c r="L3" s="37" t="n"/>
-      <c r="M3" s="37" t="n"/>
-      <c r="N3" s="37" t="n"/>
-      <c r="O3" s="37" t="n"/>
-      <c r="P3" s="37" t="n"/>
-      <c r="Q3" s="37" t="n"/>
-      <c r="R3" s="37" t="n"/>
-      <c r="S3" s="37" t="n"/>
-      <c r="T3" s="37" t="n"/>
-      <c r="U3" s="37" t="n"/>
-      <c r="V3" s="37" t="n"/>
-      <c r="W3" s="37" t="n"/>
-      <c r="X3" s="37" t="n"/>
-      <c r="Y3" s="37" t="n"/>
-      <c r="Z3" s="37" t="n"/>
-      <c r="AA3" s="37" t="n"/>
-      <c r="AB3" s="37" t="n"/>
-      <c r="AC3" s="37" t="n"/>
-      <c r="AD3" s="37" t="n"/>
-      <c r="AE3" s="37" t="n"/>
-      <c r="AF3" s="37" t="n"/>
-      <c r="AG3" s="37" t="n"/>
-      <c r="AH3" s="38" t="n"/>
-      <c r="AI3" s="38" t="n"/>
-      <c r="AJ3" s="38" t="n"/>
-      <c r="AK3" s="38" t="n"/>
-      <c r="AL3" s="38" t="n"/>
-      <c r="AM3" s="38" t="n"/>
-      <c r="AN3" s="39" t="n"/>
-      <c r="AO3" s="39" t="n"/>
-      <c r="AP3" s="39" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="42" t="n"/>
-      <c r="B4" s="37" t="n"/>
-      <c r="C4" s="37" t="n"/>
-      <c r="D4" s="37" t="n"/>
-      <c r="E4" s="37" t="n"/>
-      <c r="F4" s="37" t="n"/>
-      <c r="G4" s="37" t="n"/>
-      <c r="H4" s="37" t="n"/>
-      <c r="I4" s="37" t="n"/>
-      <c r="J4" s="37" t="n"/>
-      <c r="K4" s="37" t="n"/>
-      <c r="L4" s="37" t="n"/>
-      <c r="M4" s="37" t="n"/>
-      <c r="N4" s="37" t="n"/>
-      <c r="O4" s="37" t="n"/>
-      <c r="P4" s="37" t="n"/>
-      <c r="Q4" s="37" t="n"/>
-      <c r="R4" s="37" t="n"/>
-      <c r="S4" s="37" t="n"/>
-      <c r="T4" s="37" t="n"/>
-      <c r="U4" s="37" t="n"/>
-      <c r="V4" s="37" t="n"/>
-      <c r="W4" s="37" t="n"/>
-      <c r="X4" s="37" t="n"/>
-      <c r="Y4" s="37" t="n"/>
-      <c r="Z4" s="37" t="n"/>
-      <c r="AA4" s="37" t="n"/>
-      <c r="AB4" s="37" t="n"/>
-      <c r="AC4" s="37" t="n"/>
-      <c r="AD4" s="37" t="n"/>
-      <c r="AE4" s="37" t="n"/>
-      <c r="AF4" s="37" t="n"/>
-      <c r="AG4" s="37" t="n"/>
-      <c r="AH4" s="38" t="n"/>
-      <c r="AI4" s="38" t="n"/>
-      <c r="AJ4" s="38" t="n"/>
-      <c r="AK4" s="38" t="n"/>
-      <c r="AL4" s="38" t="n"/>
-      <c r="AM4" s="38" t="n"/>
-      <c r="AN4" s="39" t="n"/>
-      <c r="AO4" s="39" t="n"/>
-      <c r="AP4" s="39" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="280" t="inlineStr">
-        <is>
-          <t>Head</t>
-        </is>
-      </c>
-      <c r="B5" s="219" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="C5" s="219" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="D5" s="219" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E5" s="219" t="inlineStr">
-        <is>
-          <t>완료일</t>
-        </is>
-      </c>
-      <c r="F5" s="219" t="inlineStr">
-        <is>
-          <t>Page#</t>
-        </is>
-      </c>
-      <c r="G5" s="219" t="inlineStr">
-        <is>
-          <t>Remark</t>
-        </is>
-      </c>
-      <c r="H5" s="219" t="n"/>
-      <c r="I5" s="219" t="n"/>
-      <c r="J5" s="283" t="n"/>
-      <c r="K5" s="219" t="n"/>
-      <c r="L5" s="219" t="n"/>
-      <c r="M5" s="219" t="n"/>
-      <c r="N5" s="219" t="n"/>
-      <c r="O5" s="219" t="n"/>
-      <c r="P5" s="219" t="n"/>
-      <c r="Q5" s="219" t="n"/>
-      <c r="R5" s="219" t="n"/>
-      <c r="S5" s="219" t="n"/>
-      <c r="T5" s="283" t="n"/>
-      <c r="U5" s="283" t="n"/>
-      <c r="V5" s="283" t="n"/>
-      <c r="W5" s="219" t="n"/>
-      <c r="X5" s="219" t="n"/>
-      <c r="Y5" s="219" t="n"/>
-      <c r="Z5" s="219" t="n"/>
-      <c r="AA5" s="219" t="n"/>
-      <c r="AB5" s="219" t="n"/>
-      <c r="AC5" s="283" t="n"/>
-      <c r="AD5" s="283" t="n"/>
-      <c r="AE5" s="219" t="n"/>
-      <c r="AF5" s="219" t="n"/>
-      <c r="AG5" s="219" t="n"/>
-      <c r="AH5" s="283" t="n"/>
-      <c r="AI5" s="283" t="n"/>
-      <c r="AJ5" s="283" t="n"/>
-      <c r="AK5" s="283" t="n"/>
-      <c r="AL5" s="283" t="n"/>
-      <c r="AM5" s="283" t="n"/>
-      <c r="AN5" s="55" t="n"/>
-      <c r="AO5" s="55" t="n"/>
-      <c r="AP5" s="55" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="220" t="n"/>
-      <c r="B6" s="113" t="inlineStr">
-        <is>
-          <t>AU : AU (en)</t>
-        </is>
-      </c>
-      <c r="C6" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/au/laptops/gram/16z90tl-g-au88a/</t>
-        </is>
-      </c>
-      <c r="D6" s="222" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E6" s="223" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="F6" s="224" t="n">
-        <v>4</v>
-      </c>
-      <c r="G6" s="225" t="inlineStr"/>
-      <c r="H6" s="224" t="inlineStr"/>
-      <c r="I6" s="225" t="inlineStr"/>
-      <c r="J6" s="224" t="inlineStr"/>
-      <c r="K6" s="226" t="inlineStr"/>
-      <c r="L6" s="226" t="n"/>
-      <c r="M6" s="226" t="inlineStr"/>
-      <c r="N6" s="226" t="inlineStr"/>
-      <c r="O6" s="227" t="inlineStr"/>
-      <c r="P6" s="113" t="inlineStr"/>
-      <c r="Q6" s="113" t="inlineStr"/>
-      <c r="R6" s="226" t="inlineStr"/>
-      <c r="S6" s="228" t="n"/>
-      <c r="T6" s="228" t="n"/>
-      <c r="U6" s="228" t="n"/>
-      <c r="V6" s="228" t="n"/>
-      <c r="W6" s="228" t="inlineStr"/>
-      <c r="X6" s="228" t="n"/>
-      <c r="Y6" s="228" t="n"/>
-      <c r="Z6" s="228" t="n"/>
-      <c r="AA6" s="228" t="inlineStr"/>
-      <c r="AB6" s="228" t="inlineStr"/>
-      <c r="AC6" s="228" t="inlineStr"/>
-      <c r="AD6" s="228" t="inlineStr"/>
-      <c r="AE6" s="228" t="inlineStr"/>
-      <c r="AF6" s="229" t="inlineStr"/>
-      <c r="AG6" s="230" t="inlineStr"/>
-      <c r="AH6" s="55" t="inlineStr"/>
-      <c r="AI6" s="55" t="inlineStr"/>
-      <c r="AJ6" s="55" t="inlineStr"/>
-      <c r="AK6" s="55" t="n"/>
-      <c r="AL6" s="55" t="n"/>
-      <c r="AM6" s="55" t="n"/>
-      <c r="AN6" s="55" t="inlineStr"/>
-      <c r="AO6" s="55" t="inlineStr"/>
-      <c r="AP6" s="55" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="220" t="n"/>
-      <c r="B7" s="113" t="inlineStr">
-        <is>
-          <t>CA_EN : CA (en)</t>
-        </is>
-      </c>
-      <c r="C7" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/ca_en/laptops/gram/17z90tl-g-au78a9/</t>
-        </is>
-      </c>
-      <c r="D7" s="222" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E7" s="223" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="F7" s="224" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="225" t="inlineStr"/>
-      <c r="H7" s="224" t="inlineStr"/>
-      <c r="I7" s="225" t="inlineStr"/>
-      <c r="J7" s="224" t="inlineStr"/>
-      <c r="K7" s="226" t="inlineStr"/>
-      <c r="L7" s="226" t="inlineStr"/>
-      <c r="M7" s="226" t="inlineStr"/>
-      <c r="N7" s="226" t="inlineStr"/>
-      <c r="O7" s="227" t="inlineStr"/>
-      <c r="P7" s="113" t="inlineStr"/>
-      <c r="Q7" s="113" t="inlineStr"/>
-      <c r="R7" s="226" t="inlineStr"/>
-      <c r="S7" s="228" t="inlineStr"/>
-      <c r="T7" s="228" t="inlineStr"/>
-      <c r="U7" s="228" t="inlineStr"/>
-      <c r="V7" s="228" t="inlineStr"/>
-      <c r="W7" s="228" t="inlineStr"/>
-      <c r="X7" s="228" t="inlineStr"/>
-      <c r="Y7" s="228" t="inlineStr"/>
-      <c r="Z7" s="228" t="inlineStr"/>
-      <c r="AA7" s="228" t="inlineStr"/>
-      <c r="AB7" s="228" t="inlineStr"/>
-      <c r="AC7" s="228" t="inlineStr"/>
-      <c r="AD7" s="228" t="inlineStr"/>
-      <c r="AE7" s="228" t="inlineStr"/>
-      <c r="AF7" s="229" t="inlineStr"/>
-      <c r="AG7" s="230" t="inlineStr"/>
-      <c r="AH7" s="55" t="inlineStr"/>
-      <c r="AI7" s="55" t="inlineStr"/>
-      <c r="AJ7" s="55" t="inlineStr"/>
-      <c r="AK7" s="55" t="inlineStr"/>
-      <c r="AL7" s="55" t="inlineStr"/>
-      <c r="AM7" s="55" t="inlineStr"/>
-      <c r="AN7" s="55" t="inlineStr"/>
-      <c r="AO7" s="55" t="inlineStr"/>
-      <c r="AP7" s="55" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="220" t="n"/>
-      <c r="B8" s="113" t="inlineStr">
-        <is>
-          <t>DE : DE (de)</t>
-        </is>
-      </c>
-      <c r="C8" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/de/notebooks/gram-pro/16z90ts-g-au89g/</t>
-        </is>
-      </c>
-      <c r="D8" s="222" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E8" s="231" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="F8" s="232" t="n">
-        <v>8</v>
-      </c>
-      <c r="G8" s="225" t="inlineStr"/>
-      <c r="H8" s="225" t="inlineStr"/>
-      <c r="I8" s="224" t="inlineStr"/>
-      <c r="J8" s="224" t="inlineStr"/>
-      <c r="K8" s="228" t="inlineStr"/>
-      <c r="L8" s="228" t="inlineStr"/>
-      <c r="M8" s="228" t="inlineStr"/>
-      <c r="N8" s="228" t="inlineStr"/>
-      <c r="O8" s="229" t="inlineStr"/>
-      <c r="P8" s="113" t="inlineStr"/>
-      <c r="Q8" s="113" t="inlineStr"/>
-      <c r="R8" s="226" t="inlineStr"/>
-      <c r="S8" s="228" t="inlineStr"/>
-      <c r="T8" s="228" t="inlineStr"/>
-      <c r="U8" s="228" t="inlineStr"/>
-      <c r="V8" s="228" t="inlineStr"/>
-      <c r="W8" s="228" t="inlineStr"/>
-      <c r="X8" s="228" t="inlineStr"/>
-      <c r="Y8" s="228" t="inlineStr"/>
-      <c r="Z8" s="228" t="inlineStr"/>
-      <c r="AA8" s="228" t="inlineStr"/>
-      <c r="AB8" s="228" t="inlineStr"/>
-      <c r="AC8" s="228" t="inlineStr"/>
-      <c r="AD8" s="228" t="inlineStr"/>
-      <c r="AE8" s="228" t="inlineStr"/>
-      <c r="AF8" s="229" t="inlineStr"/>
-      <c r="AG8" s="230" t="inlineStr"/>
-      <c r="AH8" s="55" t="inlineStr"/>
-      <c r="AI8" s="55" t="inlineStr"/>
-      <c r="AJ8" s="55" t="inlineStr"/>
-      <c r="AK8" s="55" t="inlineStr"/>
-      <c r="AL8" s="55" t="inlineStr"/>
-      <c r="AM8" s="55" t="inlineStr"/>
-      <c r="AN8" s="55" t="inlineStr"/>
-      <c r="AO8" s="55" t="inlineStr"/>
-      <c r="AP8" s="55" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="220" t="n"/>
-      <c r="B9" s="113" t="inlineStr">
-        <is>
-          <t>ES : ES (es)</t>
-        </is>
-      </c>
-      <c r="C9" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/es/portatiles/gram/16z90ts-g-au99b/</t>
-        </is>
-      </c>
-      <c r="D9" s="222" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E9" s="231" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="F9" s="232" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="225" t="inlineStr"/>
-      <c r="H9" s="225" t="inlineStr"/>
-      <c r="I9" s="225" t="inlineStr"/>
-      <c r="J9" s="224" t="inlineStr"/>
-      <c r="K9" s="228" t="inlineStr"/>
-      <c r="L9" s="228" t="inlineStr"/>
-      <c r="M9" s="228" t="inlineStr"/>
-      <c r="N9" s="228" t="inlineStr"/>
-      <c r="O9" s="229" t="inlineStr"/>
-      <c r="P9" s="113" t="inlineStr"/>
-      <c r="Q9" s="113" t="inlineStr"/>
-      <c r="R9" s="226" t="inlineStr"/>
-      <c r="S9" s="228" t="inlineStr"/>
-      <c r="T9" s="228" t="inlineStr"/>
-      <c r="U9" s="228" t="inlineStr"/>
-      <c r="V9" s="228" t="inlineStr"/>
-      <c r="W9" s="228" t="inlineStr"/>
-      <c r="X9" s="228" t="inlineStr"/>
-      <c r="Y9" s="228" t="inlineStr"/>
-      <c r="Z9" s="228" t="inlineStr"/>
-      <c r="AA9" s="228" t="inlineStr"/>
-      <c r="AB9" s="228" t="inlineStr"/>
-      <c r="AC9" s="228" t="inlineStr"/>
-      <c r="AD9" s="228" t="inlineStr"/>
-      <c r="AE9" s="228" t="inlineStr"/>
-      <c r="AF9" s="229" t="inlineStr"/>
-      <c r="AG9" s="230" t="inlineStr"/>
-      <c r="AH9" s="55" t="inlineStr"/>
-      <c r="AI9" s="55" t="inlineStr"/>
-      <c r="AJ9" s="55" t="inlineStr"/>
-      <c r="AK9" s="55" t="inlineStr"/>
-      <c r="AL9" s="55" t="inlineStr"/>
-      <c r="AM9" s="55" t="inlineStr"/>
-      <c r="AN9" s="55" t="inlineStr"/>
-      <c r="AO9" s="55" t="inlineStr"/>
-      <c r="AP9" s="55" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="220" t="n"/>
-      <c r="B10" s="113" t="inlineStr">
-        <is>
-          <t>FR : FR (fr)</t>
-        </is>
-      </c>
-      <c r="C10" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/fr/pc-portables/gram/lg-15z80t-g-as55f/</t>
-        </is>
-      </c>
-      <c r="D10" s="222" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E10" s="231" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="F10" s="225" t="n">
-        <v>14</v>
-      </c>
-      <c r="G10" s="225" t="inlineStr"/>
-      <c r="H10" s="225" t="inlineStr"/>
-      <c r="I10" s="225" t="inlineStr"/>
-      <c r="J10" s="224" t="inlineStr"/>
-      <c r="K10" s="228" t="inlineStr"/>
-      <c r="L10" s="228" t="inlineStr"/>
-      <c r="M10" s="228" t="inlineStr"/>
-      <c r="N10" s="228" t="inlineStr"/>
-      <c r="O10" s="229" t="inlineStr"/>
-      <c r="P10" s="113" t="inlineStr"/>
-      <c r="Q10" s="113" t="inlineStr"/>
-      <c r="R10" s="226" t="inlineStr"/>
-      <c r="S10" s="228" t="inlineStr"/>
-      <c r="T10" s="228" t="inlineStr"/>
-      <c r="U10" s="228" t="inlineStr"/>
-      <c r="V10" s="228" t="inlineStr"/>
-      <c r="W10" s="228" t="inlineStr"/>
-      <c r="X10" s="228" t="inlineStr"/>
-      <c r="Y10" s="228" t="inlineStr"/>
-      <c r="Z10" s="228" t="inlineStr"/>
-      <c r="AA10" s="228" t="inlineStr"/>
-      <c r="AB10" s="228" t="inlineStr"/>
-      <c r="AC10" s="228" t="inlineStr"/>
-      <c r="AD10" s="228" t="inlineStr"/>
-      <c r="AE10" s="228" t="inlineStr"/>
-      <c r="AF10" s="229" t="inlineStr"/>
-      <c r="AG10" s="230" t="inlineStr"/>
-      <c r="AH10" s="55" t="inlineStr"/>
-      <c r="AI10" s="55" t="inlineStr"/>
-      <c r="AJ10" s="55" t="inlineStr"/>
-      <c r="AK10" s="55" t="inlineStr"/>
-      <c r="AL10" s="55" t="inlineStr"/>
-      <c r="AM10" s="55" t="inlineStr"/>
-      <c r="AN10" s="55" t="inlineStr"/>
-      <c r="AO10" s="55" t="inlineStr"/>
-      <c r="AP10" s="55" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="220" t="n"/>
-      <c r="B11" s="113" t="inlineStr">
-        <is>
-          <t>GLOBAL : GLOBAL (en)</t>
-        </is>
-      </c>
-      <c r="C11" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram-pro/16z90ts/</t>
-        </is>
-      </c>
-      <c r="D11" s="222" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E11" s="231" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="F11" s="225" t="n">
-        <v>4</v>
-      </c>
-      <c r="G11" s="225" t="inlineStr"/>
-      <c r="H11" s="224" t="inlineStr"/>
-      <c r="I11" s="224" t="inlineStr"/>
-      <c r="J11" s="224" t="inlineStr"/>
-      <c r="K11" s="228" t="inlineStr"/>
-      <c r="L11" s="228" t="inlineStr"/>
-      <c r="M11" s="228" t="inlineStr"/>
-      <c r="N11" s="228" t="inlineStr"/>
-      <c r="O11" s="229" t="inlineStr"/>
-      <c r="P11" s="113" t="inlineStr"/>
-      <c r="Q11" s="113" t="inlineStr"/>
-      <c r="R11" s="226" t="inlineStr"/>
-      <c r="S11" s="228" t="inlineStr"/>
-      <c r="T11" s="228" t="inlineStr"/>
-      <c r="U11" s="228" t="inlineStr"/>
-      <c r="V11" s="228" t="inlineStr"/>
-      <c r="W11" s="228" t="inlineStr"/>
-      <c r="X11" s="228" t="inlineStr"/>
-      <c r="Y11" s="228" t="inlineStr"/>
-      <c r="Z11" s="228" t="inlineStr"/>
-      <c r="AA11" s="228" t="inlineStr"/>
-      <c r="AB11" s="228" t="inlineStr"/>
-      <c r="AC11" s="228" t="inlineStr"/>
-      <c r="AD11" s="228" t="inlineStr"/>
-      <c r="AE11" s="228" t="inlineStr"/>
-      <c r="AF11" s="229" t="inlineStr"/>
-      <c r="AG11" s="230" t="inlineStr"/>
-      <c r="AH11" s="55" t="inlineStr"/>
-      <c r="AI11" s="55" t="inlineStr"/>
-      <c r="AJ11" s="55" t="inlineStr"/>
-      <c r="AK11" s="55" t="inlineStr"/>
-      <c r="AL11" s="55" t="inlineStr"/>
-      <c r="AM11" s="55" t="inlineStr"/>
-      <c r="AN11" s="55" t="inlineStr"/>
-      <c r="AO11" s="55" t="inlineStr"/>
-      <c r="AP11" s="55" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="220" t="n"/>
-      <c r="B12" s="113" t="inlineStr">
-        <is>
-          <t>IT : IT (it)</t>
-        </is>
-      </c>
-      <c r="C12" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/it/notebook/gram/17z90tl-g/</t>
-        </is>
-      </c>
-      <c r="D12" s="222" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E12" s="231" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="F12" s="232" t="n">
-        <v>7</v>
-      </c>
-      <c r="G12" s="225" t="inlineStr"/>
-      <c r="H12" s="224" t="inlineStr"/>
-      <c r="I12" s="225" t="inlineStr"/>
-      <c r="J12" s="224" t="inlineStr"/>
-      <c r="K12" s="228" t="inlineStr"/>
-      <c r="L12" s="228" t="inlineStr"/>
-      <c r="M12" s="228" t="inlineStr"/>
-      <c r="N12" s="228" t="inlineStr"/>
-      <c r="O12" s="229" t="inlineStr"/>
-      <c r="P12" s="113" t="inlineStr"/>
-      <c r="Q12" s="113" t="inlineStr"/>
-      <c r="R12" s="226" t="inlineStr"/>
-      <c r="S12" s="228" t="inlineStr"/>
-      <c r="T12" s="228" t="inlineStr"/>
-      <c r="U12" s="228" t="inlineStr"/>
-      <c r="V12" s="228" t="inlineStr"/>
-      <c r="W12" s="228" t="inlineStr"/>
-      <c r="X12" s="228" t="inlineStr"/>
-      <c r="Y12" s="228" t="inlineStr"/>
-      <c r="Z12" s="228" t="inlineStr"/>
-      <c r="AA12" s="228" t="inlineStr"/>
-      <c r="AB12" s="228" t="inlineStr"/>
-      <c r="AC12" s="228" t="inlineStr"/>
-      <c r="AD12" s="228" t="inlineStr"/>
-      <c r="AE12" s="228" t="inlineStr"/>
-      <c r="AF12" s="229" t="inlineStr"/>
-      <c r="AG12" s="230" t="inlineStr"/>
-      <c r="AH12" s="55" t="inlineStr"/>
-      <c r="AI12" s="55" t="inlineStr"/>
-      <c r="AJ12" s="55" t="inlineStr"/>
-      <c r="AK12" s="55" t="inlineStr"/>
-      <c r="AL12" s="55" t="inlineStr"/>
-      <c r="AM12" s="55" t="inlineStr"/>
-      <c r="AN12" s="55" t="inlineStr"/>
-      <c r="AO12" s="55" t="inlineStr"/>
-      <c r="AP12" s="55" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="220" t="n"/>
-      <c r="B13" s="113" t="inlineStr">
-        <is>
-          <t>JP : JP (ja)</t>
-        </is>
-      </c>
-      <c r="C13" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/jp/mobile-pc/gram/16z90ts-gu86j/</t>
-        </is>
-      </c>
-      <c r="D13" s="222" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E13" s="234" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="F13" s="232" t="n">
-        <v>27</v>
-      </c>
-      <c r="G13" s="225" t="inlineStr"/>
-      <c r="H13" s="225" t="inlineStr"/>
-      <c r="I13" s="225" t="inlineStr"/>
-      <c r="J13" s="224" t="inlineStr"/>
-      <c r="K13" s="228" t="inlineStr"/>
-      <c r="L13" s="228" t="inlineStr"/>
-      <c r="M13" s="228" t="inlineStr"/>
-      <c r="N13" s="228" t="inlineStr"/>
-      <c r="O13" s="229" t="inlineStr"/>
-      <c r="P13" s="113" t="inlineStr"/>
-      <c r="Q13" s="113" t="inlineStr"/>
-      <c r="R13" s="226" t="inlineStr"/>
-      <c r="S13" s="228" t="inlineStr"/>
-      <c r="T13" s="228" t="inlineStr"/>
-      <c r="U13" s="228" t="inlineStr"/>
-      <c r="V13" s="228" t="inlineStr"/>
-      <c r="W13" s="228" t="inlineStr"/>
-      <c r="X13" s="228" t="inlineStr"/>
-      <c r="Y13" s="228" t="inlineStr"/>
-      <c r="Z13" s="228" t="inlineStr"/>
-      <c r="AA13" s="228" t="inlineStr"/>
-      <c r="AB13" s="228" t="inlineStr"/>
-      <c r="AC13" s="228" t="inlineStr"/>
-      <c r="AD13" s="228" t="inlineStr"/>
-      <c r="AE13" s="228" t="inlineStr"/>
-      <c r="AF13" s="229" t="inlineStr"/>
-      <c r="AG13" s="230" t="inlineStr"/>
-      <c r="AH13" s="55" t="inlineStr"/>
-      <c r="AI13" s="55" t="inlineStr"/>
-      <c r="AJ13" s="55" t="inlineStr"/>
-      <c r="AK13" s="55" t="inlineStr"/>
-      <c r="AL13" s="55" t="inlineStr"/>
-      <c r="AM13" s="55" t="inlineStr"/>
-      <c r="AN13" s="55" t="inlineStr"/>
-      <c r="AO13" s="55" t="inlineStr"/>
-      <c r="AP13" s="55" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="220" t="n"/>
-      <c r="B14" s="113" t="inlineStr">
-        <is>
-          <t>SG : SG (en)</t>
-        </is>
-      </c>
-      <c r="C14" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/sg/business/it-products/lg-gram/16z90tl-g-az88a3/</t>
-        </is>
-      </c>
-      <c r="D14" s="222" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E14" s="231" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="F14" s="225" t="n">
-        <v>13</v>
-      </c>
-      <c r="G14" s="225" t="inlineStr"/>
-      <c r="H14" s="225" t="inlineStr"/>
-      <c r="I14" s="225" t="inlineStr"/>
-      <c r="J14" s="224" t="inlineStr"/>
-      <c r="K14" s="228" t="inlineStr"/>
-      <c r="L14" s="228" t="inlineStr"/>
-      <c r="M14" s="228" t="inlineStr"/>
-      <c r="N14" s="228" t="inlineStr"/>
-      <c r="O14" s="229" t="inlineStr"/>
-      <c r="P14" s="113" t="inlineStr"/>
-      <c r="Q14" s="113" t="inlineStr"/>
-      <c r="R14" s="226" t="inlineStr"/>
-      <c r="S14" s="228" t="inlineStr"/>
-      <c r="T14" s="228" t="inlineStr"/>
-      <c r="U14" s="228" t="inlineStr"/>
-      <c r="V14" s="228" t="inlineStr"/>
-      <c r="W14" s="228" t="inlineStr"/>
-      <c r="X14" s="228" t="inlineStr"/>
-      <c r="Y14" s="228" t="inlineStr"/>
-      <c r="Z14" s="228" t="inlineStr"/>
-      <c r="AA14" s="228" t="inlineStr"/>
-      <c r="AB14" s="228" t="inlineStr"/>
-      <c r="AC14" s="228" t="inlineStr"/>
-      <c r="AD14" s="228" t="inlineStr"/>
-      <c r="AE14" s="228" t="inlineStr"/>
-      <c r="AF14" s="229" t="inlineStr"/>
-      <c r="AG14" s="230" t="inlineStr"/>
-      <c r="AH14" s="55" t="inlineStr"/>
-      <c r="AI14" s="55" t="inlineStr"/>
-      <c r="AJ14" s="55" t="inlineStr"/>
-      <c r="AK14" s="55" t="inlineStr"/>
-      <c r="AL14" s="55" t="inlineStr"/>
-      <c r="AM14" s="55" t="inlineStr"/>
-      <c r="AN14" s="55" t="inlineStr"/>
-      <c r="AO14" s="55" t="inlineStr"/>
-      <c r="AP14" s="55" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="220" t="n"/>
-      <c r="B15" s="113" t="inlineStr">
-        <is>
-          <t>TW : TW (zh)</t>
-        </is>
-      </c>
-      <c r="C15" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/tw/laptops/gram-pro/16z90ts-g-au79c2/</t>
-        </is>
-      </c>
-      <c r="D15" s="222" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E15" s="231" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="F15" s="232" t="n">
-        <v>18</v>
-      </c>
-      <c r="G15" s="225" t="inlineStr"/>
-      <c r="H15" s="225" t="inlineStr"/>
-      <c r="I15" s="225" t="inlineStr"/>
-      <c r="J15" s="224" t="inlineStr"/>
-      <c r="K15" s="228" t="inlineStr"/>
-      <c r="L15" s="228" t="inlineStr"/>
-      <c r="M15" s="228" t="inlineStr"/>
-      <c r="N15" s="228" t="inlineStr"/>
-      <c r="O15" s="229" t="inlineStr"/>
-      <c r="P15" s="113" t="inlineStr"/>
-      <c r="Q15" s="113" t="inlineStr"/>
-      <c r="R15" s="226" t="inlineStr"/>
-      <c r="S15" s="235" t="inlineStr"/>
-      <c r="T15" s="235" t="inlineStr"/>
-      <c r="U15" s="235" t="inlineStr"/>
-      <c r="V15" s="235" t="inlineStr"/>
-      <c r="W15" s="235" t="inlineStr"/>
-      <c r="X15" s="235" t="inlineStr"/>
-      <c r="Y15" s="235" t="inlineStr"/>
-      <c r="Z15" s="235" t="inlineStr"/>
-      <c r="AA15" s="235" t="inlineStr"/>
-      <c r="AB15" s="235" t="inlineStr"/>
-      <c r="AC15" s="235" t="inlineStr"/>
-      <c r="AD15" s="235" t="inlineStr"/>
-      <c r="AE15" s="235" t="inlineStr"/>
-      <c r="AF15" s="236" t="inlineStr"/>
-      <c r="AG15" s="230" t="inlineStr"/>
-      <c r="AH15" s="55" t="inlineStr"/>
-      <c r="AI15" s="55" t="inlineStr"/>
-      <c r="AJ15" s="55" t="inlineStr"/>
-      <c r="AK15" s="55" t="inlineStr"/>
-      <c r="AL15" s="55" t="inlineStr"/>
-      <c r="AM15" s="55" t="inlineStr"/>
-      <c r="AN15" s="55" t="inlineStr"/>
-      <c r="AO15" s="55" t="inlineStr"/>
-      <c r="AP15" s="55" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="220" t="n"/>
-      <c r="B16" s="113" t="inlineStr">
-        <is>
-          <t>UK : GB (en)</t>
-        </is>
-      </c>
-      <c r="C16" s="290" t="inlineStr">
-        <is>
-          <t>https://www.lg.com/uk/laptops/gram-pro/16z90ts-g-au89a1/</t>
-        </is>
-      </c>
-      <c r="D16" s="222" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E16" s="228" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="F16" s="225" t="n">
-        <v>8</v>
-      </c>
-      <c r="G16" s="228" t="inlineStr"/>
-      <c r="H16" s="228" t="inlineStr"/>
-      <c r="I16" s="228" t="inlineStr"/>
-      <c r="J16" s="228" t="inlineStr"/>
-      <c r="K16" s="228" t="inlineStr"/>
-      <c r="L16" s="228" t="inlineStr"/>
-      <c r="M16" s="228" t="inlineStr"/>
-      <c r="N16" s="228" t="inlineStr"/>
-      <c r="O16" s="229" t="inlineStr"/>
-      <c r="P16" s="113" t="inlineStr"/>
-      <c r="Q16" s="113" t="inlineStr"/>
-      <c r="R16" s="226" t="inlineStr"/>
-      <c r="S16" s="237" t="n"/>
-      <c r="T16" s="223" t="n"/>
-      <c r="U16" s="223" t="n"/>
-      <c r="V16" s="223" t="n"/>
-      <c r="W16" s="226" t="inlineStr"/>
-      <c r="X16" s="226" t="inlineStr"/>
-      <c r="Y16" s="226" t="inlineStr"/>
-      <c r="Z16" s="226" t="inlineStr"/>
-      <c r="AA16" s="226" t="inlineStr"/>
-      <c r="AB16" s="226" t="inlineStr"/>
-      <c r="AC16" s="226" t="inlineStr"/>
-      <c r="AD16" s="226" t="inlineStr"/>
-      <c r="AE16" s="226" t="inlineStr"/>
-      <c r="AF16" s="227" t="inlineStr"/>
-      <c r="AG16" s="230" t="inlineStr"/>
-      <c r="AH16" s="55" t="inlineStr"/>
-      <c r="AI16" s="55" t="inlineStr"/>
-      <c r="AJ16" s="55" t="inlineStr"/>
-      <c r="AK16" s="55" t="inlineStr"/>
-      <c r="AL16" s="55" t="inlineStr"/>
-      <c r="AM16" s="55" t="inlineStr"/>
-      <c r="AN16" s="55" t="inlineStr"/>
-      <c r="AO16" s="55" t="inlineStr"/>
-      <c r="AP16" s="55" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId11"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20054,7 +18612,967 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AP16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="8.130000000000001" customWidth="1" style="203" min="1" max="1"/>
+    <col width="49.63" customWidth="1" style="203" min="4" max="4"/>
+    <col width="13" customWidth="1" style="203" min="39" max="39"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="36" t="inlineStr">
+        <is>
+          <t>GR26-W16-MS-IT-PC Copilot+ Filter Creation</t>
+        </is>
+      </c>
+      <c r="C1" s="37" t="n"/>
+      <c r="D1" s="37" t="n"/>
+      <c r="E1" s="37" t="n"/>
+      <c r="K1" s="37" t="n"/>
+      <c r="L1" s="37" t="n"/>
+      <c r="M1" s="37" t="n"/>
+      <c r="N1" s="37" t="n"/>
+      <c r="O1" s="37" t="n"/>
+      <c r="P1" s="37" t="n"/>
+      <c r="Q1" s="37" t="n"/>
+      <c r="R1" s="37" t="n"/>
+      <c r="S1" s="37" t="n"/>
+      <c r="T1" s="37" t="n"/>
+      <c r="U1" s="37" t="n"/>
+      <c r="V1" s="37" t="n"/>
+      <c r="W1" s="37" t="n"/>
+      <c r="X1" s="37" t="n"/>
+      <c r="Y1" s="37" t="n"/>
+      <c r="Z1" s="37" t="n"/>
+      <c r="AA1" s="37" t="n"/>
+      <c r="AB1" s="37" t="n"/>
+      <c r="AC1" s="37" t="n"/>
+      <c r="AD1" s="37" t="n"/>
+      <c r="AE1" s="37" t="n"/>
+      <c r="AF1" s="37" t="n"/>
+      <c r="AG1" s="37" t="n"/>
+      <c r="AH1" s="38" t="n"/>
+      <c r="AI1" s="38" t="n"/>
+      <c r="AJ1" s="38" t="n"/>
+      <c r="AK1" s="38" t="n"/>
+      <c r="AL1" s="38" t="n"/>
+      <c r="AM1" s="38" t="n"/>
+      <c r="AN1" s="39" t="n"/>
+      <c r="AO1" s="39" t="n"/>
+      <c r="AP1" s="39" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="40" t="inlineStr">
+        <is>
+          <t>이번주 추가</t>
+        </is>
+      </c>
+      <c r="B2" s="41" t="inlineStr">
+        <is>
+          <t>GLOBAL : 작업중 → 완료</t>
+        </is>
+      </c>
+      <c r="C2" s="37" t="n"/>
+      <c r="D2" s="37" t="n"/>
+      <c r="E2" s="37" t="n"/>
+      <c r="K2" s="37" t="n"/>
+      <c r="L2" s="37" t="n"/>
+      <c r="M2" s="37" t="n"/>
+      <c r="N2" s="37" t="n"/>
+      <c r="O2" s="37" t="n"/>
+      <c r="P2" s="37" t="n"/>
+      <c r="Q2" s="37" t="n"/>
+      <c r="R2" s="37" t="n"/>
+      <c r="S2" s="37" t="n"/>
+      <c r="T2" s="37" t="n"/>
+      <c r="U2" s="37" t="n"/>
+      <c r="V2" s="37" t="n"/>
+      <c r="W2" s="37" t="n"/>
+      <c r="X2" s="37" t="n"/>
+      <c r="Y2" s="37" t="n"/>
+      <c r="Z2" s="37" t="n"/>
+      <c r="AA2" s="37" t="n"/>
+      <c r="AB2" s="37" t="n"/>
+      <c r="AC2" s="37" t="n"/>
+      <c r="AD2" s="37" t="n"/>
+      <c r="AE2" s="37" t="n"/>
+      <c r="AF2" s="37" t="n"/>
+      <c r="AG2" s="37" t="n"/>
+      <c r="AH2" s="38" t="n"/>
+      <c r="AI2" s="38" t="n"/>
+      <c r="AJ2" s="38" t="n"/>
+      <c r="AK2" s="38" t="n"/>
+      <c r="AL2" s="38" t="n"/>
+      <c r="AM2" s="38" t="n"/>
+      <c r="AN2" s="39" t="n"/>
+      <c r="AO2" s="39" t="n"/>
+      <c r="AP2" s="39" t="n"/>
+    </row>
+    <row r="3" ht="42.75" customHeight="1" s="203">
+      <c r="D3" s="37" t="n"/>
+      <c r="E3" s="37" t="n"/>
+      <c r="K3" s="37" t="n"/>
+      <c r="L3" s="37" t="n"/>
+      <c r="M3" s="37" t="n"/>
+      <c r="N3" s="37" t="n"/>
+      <c r="O3" s="37" t="n"/>
+      <c r="P3" s="37" t="n"/>
+      <c r="Q3" s="37" t="n"/>
+      <c r="R3" s="37" t="n"/>
+      <c r="S3" s="37" t="n"/>
+      <c r="T3" s="37" t="n"/>
+      <c r="U3" s="37" t="n"/>
+      <c r="V3" s="37" t="n"/>
+      <c r="W3" s="37" t="n"/>
+      <c r="X3" s="37" t="n"/>
+      <c r="Y3" s="37" t="n"/>
+      <c r="Z3" s="37" t="n"/>
+      <c r="AA3" s="37" t="n"/>
+      <c r="AB3" s="37" t="n"/>
+      <c r="AC3" s="37" t="n"/>
+      <c r="AD3" s="37" t="n"/>
+      <c r="AE3" s="37" t="n"/>
+      <c r="AF3" s="37" t="n"/>
+      <c r="AG3" s="37" t="n"/>
+      <c r="AH3" s="38" t="n"/>
+      <c r="AI3" s="38" t="n"/>
+      <c r="AJ3" s="38" t="n"/>
+      <c r="AK3" s="38" t="n"/>
+      <c r="AL3" s="38" t="n"/>
+      <c r="AM3" s="38" t="n"/>
+      <c r="AN3" s="39" t="n"/>
+      <c r="AO3" s="39" t="n"/>
+      <c r="AP3" s="39" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="42" t="n"/>
+      <c r="B4" s="37" t="n"/>
+      <c r="C4" s="37" t="n"/>
+      <c r="D4" s="37" t="n"/>
+      <c r="E4" s="37" t="n"/>
+      <c r="F4" s="37" t="n"/>
+      <c r="G4" s="37" t="n"/>
+      <c r="H4" s="37" t="n"/>
+      <c r="I4" s="37" t="n"/>
+      <c r="J4" s="37" t="n"/>
+      <c r="K4" s="37" t="n"/>
+      <c r="L4" s="37" t="n"/>
+      <c r="M4" s="37" t="n"/>
+      <c r="N4" s="37" t="n"/>
+      <c r="O4" s="37" t="n"/>
+      <c r="P4" s="37" t="n"/>
+      <c r="Q4" s="37" t="n"/>
+      <c r="R4" s="37" t="n"/>
+      <c r="S4" s="37" t="n"/>
+      <c r="T4" s="37" t="n"/>
+      <c r="U4" s="37" t="n"/>
+      <c r="V4" s="37" t="n"/>
+      <c r="W4" s="37" t="n"/>
+      <c r="X4" s="37" t="n"/>
+      <c r="Y4" s="37" t="n"/>
+      <c r="Z4" s="37" t="n"/>
+      <c r="AA4" s="37" t="n"/>
+      <c r="AB4" s="37" t="n"/>
+      <c r="AC4" s="37" t="n"/>
+      <c r="AD4" s="37" t="n"/>
+      <c r="AE4" s="37" t="n"/>
+      <c r="AF4" s="37" t="n"/>
+      <c r="AG4" s="37" t="n"/>
+      <c r="AH4" s="38" t="n"/>
+      <c r="AI4" s="38" t="n"/>
+      <c r="AJ4" s="38" t="n"/>
+      <c r="AK4" s="38" t="n"/>
+      <c r="AL4" s="38" t="n"/>
+      <c r="AM4" s="38" t="n"/>
+      <c r="AN4" s="39" t="n"/>
+      <c r="AO4" s="39" t="n"/>
+      <c r="AP4" s="39" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="280" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B5" s="219" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C5" s="219" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D5" s="219" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E5" s="219" t="inlineStr">
+        <is>
+          <t>완료일</t>
+        </is>
+      </c>
+      <c r="F5" s="219" t="inlineStr">
+        <is>
+          <t>Page#</t>
+        </is>
+      </c>
+      <c r="G5" s="219" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+      <c r="H5" s="219" t="n"/>
+      <c r="I5" s="219" t="n"/>
+      <c r="J5" s="283" t="n"/>
+      <c r="K5" s="219" t="n"/>
+      <c r="L5" s="219" t="n"/>
+      <c r="M5" s="219" t="n"/>
+      <c r="N5" s="219" t="n"/>
+      <c r="O5" s="219" t="n"/>
+      <c r="P5" s="219" t="n"/>
+      <c r="Q5" s="219" t="n"/>
+      <c r="R5" s="219" t="n"/>
+      <c r="S5" s="219" t="n"/>
+      <c r="T5" s="283" t="n"/>
+      <c r="U5" s="283" t="n"/>
+      <c r="V5" s="283" t="n"/>
+      <c r="W5" s="219" t="n"/>
+      <c r="X5" s="219" t="n"/>
+      <c r="Y5" s="219" t="n"/>
+      <c r="Z5" s="219" t="n"/>
+      <c r="AA5" s="219" t="n"/>
+      <c r="AB5" s="219" t="n"/>
+      <c r="AC5" s="283" t="n"/>
+      <c r="AD5" s="283" t="n"/>
+      <c r="AE5" s="219" t="n"/>
+      <c r="AF5" s="219" t="n"/>
+      <c r="AG5" s="219" t="n"/>
+      <c r="AH5" s="283" t="n"/>
+      <c r="AI5" s="283" t="n"/>
+      <c r="AJ5" s="283" t="n"/>
+      <c r="AK5" s="283" t="n"/>
+      <c r="AL5" s="283" t="n"/>
+      <c r="AM5" s="283" t="n"/>
+      <c r="AN5" s="55" t="n"/>
+      <c r="AO5" s="55" t="n"/>
+      <c r="AP5" s="55" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="220" t="n"/>
+      <c r="B6" s="113" t="inlineStr">
+        <is>
+          <t>AU : AU (en)</t>
+        </is>
+      </c>
+      <c r="C6" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/gram/16z90tl-g-au88a/</t>
+        </is>
+      </c>
+      <c r="D6" s="222" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E6" s="223" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="F6" s="224" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" s="225" t="inlineStr"/>
+      <c r="H6" s="224" t="inlineStr"/>
+      <c r="I6" s="225" t="inlineStr"/>
+      <c r="J6" s="224" t="inlineStr"/>
+      <c r="K6" s="226" t="inlineStr"/>
+      <c r="L6" s="226" t="n"/>
+      <c r="M6" s="226" t="inlineStr"/>
+      <c r="N6" s="226" t="inlineStr"/>
+      <c r="O6" s="227" t="inlineStr"/>
+      <c r="P6" s="113" t="inlineStr"/>
+      <c r="Q6" s="113" t="inlineStr"/>
+      <c r="R6" s="226" t="inlineStr"/>
+      <c r="S6" s="228" t="n"/>
+      <c r="T6" s="228" t="n"/>
+      <c r="U6" s="228" t="n"/>
+      <c r="V6" s="228" t="n"/>
+      <c r="W6" s="228" t="inlineStr"/>
+      <c r="X6" s="228" t="n"/>
+      <c r="Y6" s="228" t="n"/>
+      <c r="Z6" s="228" t="n"/>
+      <c r="AA6" s="228" t="inlineStr"/>
+      <c r="AB6" s="228" t="inlineStr"/>
+      <c r="AC6" s="228" t="inlineStr"/>
+      <c r="AD6" s="228" t="inlineStr"/>
+      <c r="AE6" s="228" t="inlineStr"/>
+      <c r="AF6" s="229" t="inlineStr"/>
+      <c r="AG6" s="230" t="inlineStr"/>
+      <c r="AH6" s="55" t="inlineStr"/>
+      <c r="AI6" s="55" t="inlineStr"/>
+      <c r="AJ6" s="55" t="inlineStr"/>
+      <c r="AK6" s="55" t="n"/>
+      <c r="AL6" s="55" t="n"/>
+      <c r="AM6" s="55" t="n"/>
+      <c r="AN6" s="55" t="inlineStr"/>
+      <c r="AO6" s="55" t="inlineStr"/>
+      <c r="AP6" s="55" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="220" t="n"/>
+      <c r="B7" s="113" t="inlineStr">
+        <is>
+          <t>CA_EN : CA (en)</t>
+        </is>
+      </c>
+      <c r="C7" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/laptops/gram/17z90tl-g-au78a9/</t>
+        </is>
+      </c>
+      <c r="D7" s="222" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E7" s="223" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="F7" s="224" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="225" t="inlineStr"/>
+      <c r="H7" s="224" t="inlineStr"/>
+      <c r="I7" s="225" t="inlineStr"/>
+      <c r="J7" s="224" t="inlineStr"/>
+      <c r="K7" s="226" t="inlineStr"/>
+      <c r="L7" s="226" t="inlineStr"/>
+      <c r="M7" s="226" t="inlineStr"/>
+      <c r="N7" s="226" t="inlineStr"/>
+      <c r="O7" s="227" t="inlineStr"/>
+      <c r="P7" s="113" t="inlineStr"/>
+      <c r="Q7" s="113" t="inlineStr"/>
+      <c r="R7" s="226" t="inlineStr"/>
+      <c r="S7" s="228" t="inlineStr"/>
+      <c r="T7" s="228" t="inlineStr"/>
+      <c r="U7" s="228" t="inlineStr"/>
+      <c r="V7" s="228" t="inlineStr"/>
+      <c r="W7" s="228" t="inlineStr"/>
+      <c r="X7" s="228" t="inlineStr"/>
+      <c r="Y7" s="228" t="inlineStr"/>
+      <c r="Z7" s="228" t="inlineStr"/>
+      <c r="AA7" s="228" t="inlineStr"/>
+      <c r="AB7" s="228" t="inlineStr"/>
+      <c r="AC7" s="228" t="inlineStr"/>
+      <c r="AD7" s="228" t="inlineStr"/>
+      <c r="AE7" s="228" t="inlineStr"/>
+      <c r="AF7" s="229" t="inlineStr"/>
+      <c r="AG7" s="230" t="inlineStr"/>
+      <c r="AH7" s="55" t="inlineStr"/>
+      <c r="AI7" s="55" t="inlineStr"/>
+      <c r="AJ7" s="55" t="inlineStr"/>
+      <c r="AK7" s="55" t="inlineStr"/>
+      <c r="AL7" s="55" t="inlineStr"/>
+      <c r="AM7" s="55" t="inlineStr"/>
+      <c r="AN7" s="55" t="inlineStr"/>
+      <c r="AO7" s="55" t="inlineStr"/>
+      <c r="AP7" s="55" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="220" t="n"/>
+      <c r="B8" s="113" t="inlineStr">
+        <is>
+          <t>DE : DE (de)</t>
+        </is>
+      </c>
+      <c r="C8" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/notebooks/gram-pro/16z90ts-g-au89g/</t>
+        </is>
+      </c>
+      <c r="D8" s="222" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E8" s="231" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="F8" s="232" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" s="225" t="inlineStr"/>
+      <c r="H8" s="225" t="inlineStr"/>
+      <c r="I8" s="224" t="inlineStr"/>
+      <c r="J8" s="224" t="inlineStr"/>
+      <c r="K8" s="228" t="inlineStr"/>
+      <c r="L8" s="228" t="inlineStr"/>
+      <c r="M8" s="228" t="inlineStr"/>
+      <c r="N8" s="228" t="inlineStr"/>
+      <c r="O8" s="229" t="inlineStr"/>
+      <c r="P8" s="113" t="inlineStr"/>
+      <c r="Q8" s="113" t="inlineStr"/>
+      <c r="R8" s="226" t="inlineStr"/>
+      <c r="S8" s="228" t="inlineStr"/>
+      <c r="T8" s="228" t="inlineStr"/>
+      <c r="U8" s="228" t="inlineStr"/>
+      <c r="V8" s="228" t="inlineStr"/>
+      <c r="W8" s="228" t="inlineStr"/>
+      <c r="X8" s="228" t="inlineStr"/>
+      <c r="Y8" s="228" t="inlineStr"/>
+      <c r="Z8" s="228" t="inlineStr"/>
+      <c r="AA8" s="228" t="inlineStr"/>
+      <c r="AB8" s="228" t="inlineStr"/>
+      <c r="AC8" s="228" t="inlineStr"/>
+      <c r="AD8" s="228" t="inlineStr"/>
+      <c r="AE8" s="228" t="inlineStr"/>
+      <c r="AF8" s="229" t="inlineStr"/>
+      <c r="AG8" s="230" t="inlineStr"/>
+      <c r="AH8" s="55" t="inlineStr"/>
+      <c r="AI8" s="55" t="inlineStr"/>
+      <c r="AJ8" s="55" t="inlineStr"/>
+      <c r="AK8" s="55" t="inlineStr"/>
+      <c r="AL8" s="55" t="inlineStr"/>
+      <c r="AM8" s="55" t="inlineStr"/>
+      <c r="AN8" s="55" t="inlineStr"/>
+      <c r="AO8" s="55" t="inlineStr"/>
+      <c r="AP8" s="55" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="220" t="n"/>
+      <c r="B9" s="113" t="inlineStr">
+        <is>
+          <t>ES : ES (es)</t>
+        </is>
+      </c>
+      <c r="C9" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/portatiles/gram/16z90ts-g-au99b/</t>
+        </is>
+      </c>
+      <c r="D9" s="222" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E9" s="231" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="F9" s="232" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="225" t="inlineStr"/>
+      <c r="H9" s="225" t="inlineStr"/>
+      <c r="I9" s="225" t="inlineStr"/>
+      <c r="J9" s="224" t="inlineStr"/>
+      <c r="K9" s="228" t="inlineStr"/>
+      <c r="L9" s="228" t="inlineStr"/>
+      <c r="M9" s="228" t="inlineStr"/>
+      <c r="N9" s="228" t="inlineStr"/>
+      <c r="O9" s="229" t="inlineStr"/>
+      <c r="P9" s="113" t="inlineStr"/>
+      <c r="Q9" s="113" t="inlineStr"/>
+      <c r="R9" s="226" t="inlineStr"/>
+      <c r="S9" s="228" t="inlineStr"/>
+      <c r="T9" s="228" t="inlineStr"/>
+      <c r="U9" s="228" t="inlineStr"/>
+      <c r="V9" s="228" t="inlineStr"/>
+      <c r="W9" s="228" t="inlineStr"/>
+      <c r="X9" s="228" t="inlineStr"/>
+      <c r="Y9" s="228" t="inlineStr"/>
+      <c r="Z9" s="228" t="inlineStr"/>
+      <c r="AA9" s="228" t="inlineStr"/>
+      <c r="AB9" s="228" t="inlineStr"/>
+      <c r="AC9" s="228" t="inlineStr"/>
+      <c r="AD9" s="228" t="inlineStr"/>
+      <c r="AE9" s="228" t="inlineStr"/>
+      <c r="AF9" s="229" t="inlineStr"/>
+      <c r="AG9" s="230" t="inlineStr"/>
+      <c r="AH9" s="55" t="inlineStr"/>
+      <c r="AI9" s="55" t="inlineStr"/>
+      <c r="AJ9" s="55" t="inlineStr"/>
+      <c r="AK9" s="55" t="inlineStr"/>
+      <c r="AL9" s="55" t="inlineStr"/>
+      <c r="AM9" s="55" t="inlineStr"/>
+      <c r="AN9" s="55" t="inlineStr"/>
+      <c r="AO9" s="55" t="inlineStr"/>
+      <c r="AP9" s="55" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="220" t="n"/>
+      <c r="B10" s="113" t="inlineStr">
+        <is>
+          <t>FR : FR (fr)</t>
+        </is>
+      </c>
+      <c r="C10" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/pc-portables/gram/lg-15z80t-g-as55f/</t>
+        </is>
+      </c>
+      <c r="D10" s="222" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E10" s="231" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="F10" s="225" t="n">
+        <v>14</v>
+      </c>
+      <c r="G10" s="225" t="inlineStr"/>
+      <c r="H10" s="225" t="inlineStr"/>
+      <c r="I10" s="225" t="inlineStr"/>
+      <c r="J10" s="224" t="inlineStr"/>
+      <c r="K10" s="228" t="inlineStr"/>
+      <c r="L10" s="228" t="inlineStr"/>
+      <c r="M10" s="228" t="inlineStr"/>
+      <c r="N10" s="228" t="inlineStr"/>
+      <c r="O10" s="229" t="inlineStr"/>
+      <c r="P10" s="113" t="inlineStr"/>
+      <c r="Q10" s="113" t="inlineStr"/>
+      <c r="R10" s="226" t="inlineStr"/>
+      <c r="S10" s="228" t="inlineStr"/>
+      <c r="T10" s="228" t="inlineStr"/>
+      <c r="U10" s="228" t="inlineStr"/>
+      <c r="V10" s="228" t="inlineStr"/>
+      <c r="W10" s="228" t="inlineStr"/>
+      <c r="X10" s="228" t="inlineStr"/>
+      <c r="Y10" s="228" t="inlineStr"/>
+      <c r="Z10" s="228" t="inlineStr"/>
+      <c r="AA10" s="228" t="inlineStr"/>
+      <c r="AB10" s="228" t="inlineStr"/>
+      <c r="AC10" s="228" t="inlineStr"/>
+      <c r="AD10" s="228" t="inlineStr"/>
+      <c r="AE10" s="228" t="inlineStr"/>
+      <c r="AF10" s="229" t="inlineStr"/>
+      <c r="AG10" s="230" t="inlineStr"/>
+      <c r="AH10" s="55" t="inlineStr"/>
+      <c r="AI10" s="55" t="inlineStr"/>
+      <c r="AJ10" s="55" t="inlineStr"/>
+      <c r="AK10" s="55" t="inlineStr"/>
+      <c r="AL10" s="55" t="inlineStr"/>
+      <c r="AM10" s="55" t="inlineStr"/>
+      <c r="AN10" s="55" t="inlineStr"/>
+      <c r="AO10" s="55" t="inlineStr"/>
+      <c r="AP10" s="55" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="220" t="n"/>
+      <c r="B11" s="113" t="inlineStr">
+        <is>
+          <t>GLOBAL : GLOBAL (en)</t>
+        </is>
+      </c>
+      <c r="C11" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/laptops/gram-pro/16z90ts/</t>
+        </is>
+      </c>
+      <c r="D11" s="222" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E11" s="231" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="F11" s="225" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="225" t="inlineStr"/>
+      <c r="H11" s="224" t="inlineStr"/>
+      <c r="I11" s="224" t="inlineStr"/>
+      <c r="J11" s="224" t="inlineStr"/>
+      <c r="K11" s="228" t="inlineStr"/>
+      <c r="L11" s="228" t="inlineStr"/>
+      <c r="M11" s="228" t="inlineStr"/>
+      <c r="N11" s="228" t="inlineStr"/>
+      <c r="O11" s="229" t="inlineStr"/>
+      <c r="P11" s="113" t="inlineStr"/>
+      <c r="Q11" s="113" t="inlineStr"/>
+      <c r="R11" s="226" t="inlineStr"/>
+      <c r="S11" s="228" t="inlineStr"/>
+      <c r="T11" s="228" t="inlineStr"/>
+      <c r="U11" s="228" t="inlineStr"/>
+      <c r="V11" s="228" t="inlineStr"/>
+      <c r="W11" s="228" t="inlineStr"/>
+      <c r="X11" s="228" t="inlineStr"/>
+      <c r="Y11" s="228" t="inlineStr"/>
+      <c r="Z11" s="228" t="inlineStr"/>
+      <c r="AA11" s="228" t="inlineStr"/>
+      <c r="AB11" s="228" t="inlineStr"/>
+      <c r="AC11" s="228" t="inlineStr"/>
+      <c r="AD11" s="228" t="inlineStr"/>
+      <c r="AE11" s="228" t="inlineStr"/>
+      <c r="AF11" s="229" t="inlineStr"/>
+      <c r="AG11" s="230" t="inlineStr"/>
+      <c r="AH11" s="55" t="inlineStr"/>
+      <c r="AI11" s="55" t="inlineStr"/>
+      <c r="AJ11" s="55" t="inlineStr"/>
+      <c r="AK11" s="55" t="inlineStr"/>
+      <c r="AL11" s="55" t="inlineStr"/>
+      <c r="AM11" s="55" t="inlineStr"/>
+      <c r="AN11" s="55" t="inlineStr"/>
+      <c r="AO11" s="55" t="inlineStr"/>
+      <c r="AP11" s="55" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="220" t="n"/>
+      <c r="B12" s="113" t="inlineStr">
+        <is>
+          <t>IT : IT (it)</t>
+        </is>
+      </c>
+      <c r="C12" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/notebook/gram/17z90tl-g/</t>
+        </is>
+      </c>
+      <c r="D12" s="222" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E12" s="231" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="F12" s="232" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" s="225" t="inlineStr"/>
+      <c r="H12" s="224" t="inlineStr"/>
+      <c r="I12" s="225" t="inlineStr"/>
+      <c r="J12" s="224" t="inlineStr"/>
+      <c r="K12" s="228" t="inlineStr"/>
+      <c r="L12" s="228" t="inlineStr"/>
+      <c r="M12" s="228" t="inlineStr"/>
+      <c r="N12" s="228" t="inlineStr"/>
+      <c r="O12" s="229" t="inlineStr"/>
+      <c r="P12" s="113" t="inlineStr"/>
+      <c r="Q12" s="113" t="inlineStr"/>
+      <c r="R12" s="226" t="inlineStr"/>
+      <c r="S12" s="228" t="inlineStr"/>
+      <c r="T12" s="228" t="inlineStr"/>
+      <c r="U12" s="228" t="inlineStr"/>
+      <c r="V12" s="228" t="inlineStr"/>
+      <c r="W12" s="228" t="inlineStr"/>
+      <c r="X12" s="228" t="inlineStr"/>
+      <c r="Y12" s="228" t="inlineStr"/>
+      <c r="Z12" s="228" t="inlineStr"/>
+      <c r="AA12" s="228" t="inlineStr"/>
+      <c r="AB12" s="228" t="inlineStr"/>
+      <c r="AC12" s="228" t="inlineStr"/>
+      <c r="AD12" s="228" t="inlineStr"/>
+      <c r="AE12" s="228" t="inlineStr"/>
+      <c r="AF12" s="229" t="inlineStr"/>
+      <c r="AG12" s="230" t="inlineStr"/>
+      <c r="AH12" s="55" t="inlineStr"/>
+      <c r="AI12" s="55" t="inlineStr"/>
+      <c r="AJ12" s="55" t="inlineStr"/>
+      <c r="AK12" s="55" t="inlineStr"/>
+      <c r="AL12" s="55" t="inlineStr"/>
+      <c r="AM12" s="55" t="inlineStr"/>
+      <c r="AN12" s="55" t="inlineStr"/>
+      <c r="AO12" s="55" t="inlineStr"/>
+      <c r="AP12" s="55" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="220" t="n"/>
+      <c r="B13" s="113" t="inlineStr">
+        <is>
+          <t>JP : JP (ja)</t>
+        </is>
+      </c>
+      <c r="C13" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/mobile-pc/gram/16z90ts-gu86j/</t>
+        </is>
+      </c>
+      <c r="D13" s="222" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E13" s="234" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="F13" s="232" t="n">
+        <v>27</v>
+      </c>
+      <c r="G13" s="225" t="inlineStr"/>
+      <c r="H13" s="225" t="inlineStr"/>
+      <c r="I13" s="225" t="inlineStr"/>
+      <c r="J13" s="224" t="inlineStr"/>
+      <c r="K13" s="228" t="inlineStr"/>
+      <c r="L13" s="228" t="inlineStr"/>
+      <c r="M13" s="228" t="inlineStr"/>
+      <c r="N13" s="228" t="inlineStr"/>
+      <c r="O13" s="229" t="inlineStr"/>
+      <c r="P13" s="113" t="inlineStr"/>
+      <c r="Q13" s="113" t="inlineStr"/>
+      <c r="R13" s="226" t="inlineStr"/>
+      <c r="S13" s="228" t="inlineStr"/>
+      <c r="T13" s="228" t="inlineStr"/>
+      <c r="U13" s="228" t="inlineStr"/>
+      <c r="V13" s="228" t="inlineStr"/>
+      <c r="W13" s="228" t="inlineStr"/>
+      <c r="X13" s="228" t="inlineStr"/>
+      <c r="Y13" s="228" t="inlineStr"/>
+      <c r="Z13" s="228" t="inlineStr"/>
+      <c r="AA13" s="228" t="inlineStr"/>
+      <c r="AB13" s="228" t="inlineStr"/>
+      <c r="AC13" s="228" t="inlineStr"/>
+      <c r="AD13" s="228" t="inlineStr"/>
+      <c r="AE13" s="228" t="inlineStr"/>
+      <c r="AF13" s="229" t="inlineStr"/>
+      <c r="AG13" s="230" t="inlineStr"/>
+      <c r="AH13" s="55" t="inlineStr"/>
+      <c r="AI13" s="55" t="inlineStr"/>
+      <c r="AJ13" s="55" t="inlineStr"/>
+      <c r="AK13" s="55" t="inlineStr"/>
+      <c r="AL13" s="55" t="inlineStr"/>
+      <c r="AM13" s="55" t="inlineStr"/>
+      <c r="AN13" s="55" t="inlineStr"/>
+      <c r="AO13" s="55" t="inlineStr"/>
+      <c r="AP13" s="55" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="220" t="n"/>
+      <c r="B14" s="113" t="inlineStr">
+        <is>
+          <t>SG : SG (en)</t>
+        </is>
+      </c>
+      <c r="C14" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/business/it-products/lg-gram/16z90tl-g-az88a3/</t>
+        </is>
+      </c>
+      <c r="D14" s="222" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E14" s="231" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="F14" s="225" t="n">
+        <v>13</v>
+      </c>
+      <c r="G14" s="225" t="inlineStr"/>
+      <c r="H14" s="225" t="inlineStr"/>
+      <c r="I14" s="225" t="inlineStr"/>
+      <c r="J14" s="224" t="inlineStr"/>
+      <c r="K14" s="228" t="inlineStr"/>
+      <c r="L14" s="228" t="inlineStr"/>
+      <c r="M14" s="228" t="inlineStr"/>
+      <c r="N14" s="228" t="inlineStr"/>
+      <c r="O14" s="229" t="inlineStr"/>
+      <c r="P14" s="113" t="inlineStr"/>
+      <c r="Q14" s="113" t="inlineStr"/>
+      <c r="R14" s="226" t="inlineStr"/>
+      <c r="S14" s="228" t="inlineStr"/>
+      <c r="T14" s="228" t="inlineStr"/>
+      <c r="U14" s="228" t="inlineStr"/>
+      <c r="V14" s="228" t="inlineStr"/>
+      <c r="W14" s="228" t="inlineStr"/>
+      <c r="X14" s="228" t="inlineStr"/>
+      <c r="Y14" s="228" t="inlineStr"/>
+      <c r="Z14" s="228" t="inlineStr"/>
+      <c r="AA14" s="228" t="inlineStr"/>
+      <c r="AB14" s="228" t="inlineStr"/>
+      <c r="AC14" s="228" t="inlineStr"/>
+      <c r="AD14" s="228" t="inlineStr"/>
+      <c r="AE14" s="228" t="inlineStr"/>
+      <c r="AF14" s="229" t="inlineStr"/>
+      <c r="AG14" s="230" t="inlineStr"/>
+      <c r="AH14" s="55" t="inlineStr"/>
+      <c r="AI14" s="55" t="inlineStr"/>
+      <c r="AJ14" s="55" t="inlineStr"/>
+      <c r="AK14" s="55" t="inlineStr"/>
+      <c r="AL14" s="55" t="inlineStr"/>
+      <c r="AM14" s="55" t="inlineStr"/>
+      <c r="AN14" s="55" t="inlineStr"/>
+      <c r="AO14" s="55" t="inlineStr"/>
+      <c r="AP14" s="55" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="220" t="n"/>
+      <c r="B15" s="113" t="inlineStr">
+        <is>
+          <t>TW : TW (zh)</t>
+        </is>
+      </c>
+      <c r="C15" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/laptops/gram-pro/16z90ts-g-au79c2/</t>
+        </is>
+      </c>
+      <c r="D15" s="222" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E15" s="231" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="F15" s="232" t="n">
+        <v>18</v>
+      </c>
+      <c r="G15" s="225" t="inlineStr"/>
+      <c r="H15" s="225" t="inlineStr"/>
+      <c r="I15" s="225" t="inlineStr"/>
+      <c r="J15" s="224" t="inlineStr"/>
+      <c r="K15" s="228" t="inlineStr"/>
+      <c r="L15" s="228" t="inlineStr"/>
+      <c r="M15" s="228" t="inlineStr"/>
+      <c r="N15" s="228" t="inlineStr"/>
+      <c r="O15" s="229" t="inlineStr"/>
+      <c r="P15" s="113" t="inlineStr"/>
+      <c r="Q15" s="113" t="inlineStr"/>
+      <c r="R15" s="226" t="inlineStr"/>
+      <c r="S15" s="235" t="inlineStr"/>
+      <c r="T15" s="235" t="inlineStr"/>
+      <c r="U15" s="235" t="inlineStr"/>
+      <c r="V15" s="235" t="inlineStr"/>
+      <c r="W15" s="235" t="inlineStr"/>
+      <c r="X15" s="235" t="inlineStr"/>
+      <c r="Y15" s="235" t="inlineStr"/>
+      <c r="Z15" s="235" t="inlineStr"/>
+      <c r="AA15" s="235" t="inlineStr"/>
+      <c r="AB15" s="235" t="inlineStr"/>
+      <c r="AC15" s="235" t="inlineStr"/>
+      <c r="AD15" s="235" t="inlineStr"/>
+      <c r="AE15" s="235" t="inlineStr"/>
+      <c r="AF15" s="236" t="inlineStr"/>
+      <c r="AG15" s="230" t="inlineStr"/>
+      <c r="AH15" s="55" t="inlineStr"/>
+      <c r="AI15" s="55" t="inlineStr"/>
+      <c r="AJ15" s="55" t="inlineStr"/>
+      <c r="AK15" s="55" t="inlineStr"/>
+      <c r="AL15" s="55" t="inlineStr"/>
+      <c r="AM15" s="55" t="inlineStr"/>
+      <c r="AN15" s="55" t="inlineStr"/>
+      <c r="AO15" s="55" t="inlineStr"/>
+      <c r="AP15" s="55" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="220" t="n"/>
+      <c r="B16" s="113" t="inlineStr">
+        <is>
+          <t>UK : GB (en)</t>
+        </is>
+      </c>
+      <c r="C16" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/laptops/gram-pro/16z90ts-g-au89a1/</t>
+        </is>
+      </c>
+      <c r="D16" s="222" t="inlineStr">
+        <is>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E16" s="228" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="F16" s="225" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" s="228" t="inlineStr"/>
+      <c r="H16" s="228" t="inlineStr"/>
+      <c r="I16" s="228" t="inlineStr"/>
+      <c r="J16" s="228" t="inlineStr"/>
+      <c r="K16" s="228" t="inlineStr"/>
+      <c r="L16" s="228" t="inlineStr"/>
+      <c r="M16" s="228" t="inlineStr"/>
+      <c r="N16" s="228" t="inlineStr"/>
+      <c r="O16" s="229" t="inlineStr"/>
+      <c r="P16" s="113" t="inlineStr"/>
+      <c r="Q16" s="113" t="inlineStr"/>
+      <c r="R16" s="226" t="inlineStr"/>
+      <c r="S16" s="237" t="n"/>
+      <c r="T16" s="223" t="n"/>
+      <c r="U16" s="223" t="n"/>
+      <c r="V16" s="223" t="n"/>
+      <c r="W16" s="226" t="inlineStr"/>
+      <c r="X16" s="226" t="inlineStr"/>
+      <c r="Y16" s="226" t="inlineStr"/>
+      <c r="Z16" s="226" t="inlineStr"/>
+      <c r="AA16" s="226" t="inlineStr"/>
+      <c r="AB16" s="226" t="inlineStr"/>
+      <c r="AC16" s="226" t="inlineStr"/>
+      <c r="AD16" s="226" t="inlineStr"/>
+      <c r="AE16" s="226" t="inlineStr"/>
+      <c r="AF16" s="227" t="inlineStr"/>
+      <c r="AG16" s="230" t="inlineStr"/>
+      <c r="AH16" s="55" t="inlineStr"/>
+      <c r="AI16" s="55" t="inlineStr"/>
+      <c r="AJ16" s="55" t="inlineStr"/>
+      <c r="AK16" s="55" t="inlineStr"/>
+      <c r="AL16" s="55" t="inlineStr"/>
+      <c r="AM16" s="55" t="inlineStr"/>
+      <c r="AN16" s="55" t="inlineStr"/>
+      <c r="AO16" s="55" t="inlineStr"/>
+      <c r="AP16" s="55" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId11"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21763,7 +21281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -35483,7 +35001,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -38168,7 +37686,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40002,7 +39520,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -40987,7 +40505,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -42581,6 +42099,489 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId42"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>GR26-W41-MS-IT Windows 11 Home Landing Page 업데이트</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>이번주 추가</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>예정 · 요청서 2026-10-07 기준 15사이트(Global 포함) · Due 2026-10-31 · 담당 정의현 책임</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>완료일</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>Page#</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="261" t="inlineStr">
+        <is>
+          <t>GLOBAL : GLOBAL (en)</t>
+        </is>
+      </c>
+      <c r="C4" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/laptops/windows-11/</t>
+        </is>
+      </c>
+      <c r="D4" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E4" s="123" t="n"/>
+      <c r="F4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>MS 참고본(English)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="261" t="inlineStr">
+        <is>
+          <t>CA-en</t>
+        </is>
+      </c>
+      <c r="C5" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/laptops/windows-11/</t>
+        </is>
+      </c>
+      <c r="D5" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E5" s="123" t="n"/>
+      <c r="F5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="0" t="inlineStr">
+        <is>
+          <t>MS 참고본(English)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="261" t="inlineStr">
+        <is>
+          <t>CA-fr</t>
+        </is>
+      </c>
+      <c r="C6" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/page-de-presentation/decouvrez-choisirmc-lg-gram/windows-11/</t>
+        </is>
+      </c>
+      <c r="D6" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E6" s="123" t="n"/>
+      <c r="F6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>Translation FR-CA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="261" t="inlineStr">
+        <is>
+          <t>ES-es</t>
+        </is>
+      </c>
+      <c r="C7" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/ordenadores/windows-11/</t>
+        </is>
+      </c>
+      <c r="D7" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E7" s="123" t="n"/>
+      <c r="F7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>Translation ES-ES</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="261" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C8" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/notebook/windows-11/</t>
+        </is>
+      </c>
+      <c r="D8" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E8" s="123" t="n"/>
+      <c r="F8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>MS 참고본(It-LT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="261" t="inlineStr">
+        <is>
+          <t>UK-en</t>
+        </is>
+      </c>
+      <c r="C9" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/laptops/windows-11/</t>
+        </is>
+      </c>
+      <c r="D9" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E9" s="123" t="n"/>
+      <c r="F9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>Translation EN-GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="261" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C10" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/notebooks/windows-11/</t>
+        </is>
+      </c>
+      <c r="D10" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E10" s="123" t="n"/>
+      <c r="F10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>Translation DE-DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="261" t="inlineStr">
+        <is>
+          <t>FR-fr</t>
+        </is>
+      </c>
+      <c r="C11" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/pc-portables/windows11/</t>
+        </is>
+      </c>
+      <c r="D11" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E11" s="123" t="n"/>
+      <c r="F11" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="0" t="inlineStr">
+        <is>
+          <t>Translation FR-FR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="261" t="inlineStr">
+        <is>
+          <t>AU-en</t>
+        </is>
+      </c>
+      <c r="C12" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/au/laptops/windows-11/</t>
+        </is>
+      </c>
+      <c r="D12" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E12" s="123" t="n"/>
+      <c r="F12" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>Translation EN-GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="261" t="inlineStr">
+        <is>
+          <t>IN-en</t>
+        </is>
+      </c>
+      <c r="C13" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/in/laptop/windows-11/</t>
+        </is>
+      </c>
+      <c r="D13" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E13" s="123" t="n"/>
+      <c r="F13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>MS 참고본(English)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="261" t="inlineStr">
+        <is>
+          <t>JP-ja</t>
+        </is>
+      </c>
+      <c r="C14" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/jp/computer-pc/windows11/</t>
+        </is>
+      </c>
+      <c r="D14" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E14" s="123" t="n"/>
+      <c r="F14" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>Translation JA-JP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="261" t="inlineStr">
+        <is>
+          <t>CN-zh</t>
+        </is>
+      </c>
+      <c r="C15" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cn/notebooks/windows11</t>
+        </is>
+      </c>
+      <c r="D15" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E15" s="123" t="n"/>
+      <c r="F15" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>MS 참고본(zh-CN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="261" t="inlineStr">
+        <is>
+          <t>SG-en</t>
+        </is>
+      </c>
+      <c r="C16" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/laptops/windows-11/</t>
+        </is>
+      </c>
+      <c r="D16" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E16" s="123" t="n"/>
+      <c r="F16" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>MS 참고본(English)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="261" t="inlineStr">
+        <is>
+          <t>VN-vi</t>
+        </is>
+      </c>
+      <c r="C17" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/vn/laptop-lg-gram/windows-11/</t>
+        </is>
+      </c>
+      <c r="D17" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E17" s="123" t="n"/>
+      <c r="F17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>MS 참고본(vi-VN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="261" t="inlineStr">
+        <is>
+          <t>TW-zh</t>
+        </is>
+      </c>
+      <c r="C18" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/tw/laptops/windows-11/</t>
+        </is>
+      </c>
+      <c r="D18" s="265" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E18" s="123" t="n"/>
+      <c r="F18" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>MS 참고본(zh-TW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -42110,7 +42110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42564,7 +42564,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
@@ -43181,7 +43180,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>예상 일정(2026-09-29) · IT·SE 10/02(법인리뷰) · PTT 0929 법인리뷰: HK·HK_EN·ID·NZ·PH·PT · EU 10/16 · Americas 10/23 · Asia 10/09 · EG 10/02 · KZ 10/05 · 법인 현황 반영(2026-09-15) · VN 완료(09-10) · AU 취소(법인) · HU/JP 취소(법인 요청) · BG/HR/RS 취소 신규(법인 요청) · CH_FR 취소(법인 요청, 09-16)</t>
+          <t>진행 중</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -43288,7 +43287,7 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>법인 취소(2026-09-02)</t>
+          <t>법인 요청으로 취소(2026-09-02)</t>
         </is>
       </c>
     </row>
@@ -43318,7 +43317,7 @@
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-23 · 프로덕션 반영됨</t>
+          <t>게시 반영됨</t>
         </is>
       </c>
     </row>
@@ -43418,7 +43417,7 @@
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>법인 취소 요청(2026-09-16)</t>
+          <t>법인 요청으로 취소(2026-09-16)</t>
         </is>
       </c>
     </row>
@@ -43446,11 +43445,7 @@
       <c r="F16" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="0" t="inlineStr">
-        <is>
-          <t>예상 2026-10-23</t>
-        </is>
-      </c>
+      <c r="G16" s="0" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="261" t="inlineStr">
@@ -43478,7 +43473,7 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-23 · 프로덕션 반영됨</t>
+          <t>게시 반영됨</t>
         </is>
       </c>
     </row>
@@ -43558,11 +43553,7 @@
       <c r="F20" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="0" t="inlineStr">
-        <is>
-          <t>예상 2026-10-16</t>
-        </is>
-      </c>
+      <c r="G20" s="0" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="261" t="inlineStr">
@@ -43586,7 +43577,7 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>LDM 무응답으로 법인 취소(2026-10-08)</t>
+          <t>LDM 무응답으로 취소(2026-10-08)</t>
         </is>
       </c>
     </row>
@@ -43612,7 +43603,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>LDM 무응답으로 법인 취소(2026-10-08)</t>
+          <t>LDM 무응답으로 취소(2026-10-08)</t>
         </is>
       </c>
     </row>
@@ -43694,7 +43685,7 @@
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-09 · 법인 승인 완료 · 게시 진행 중</t>
+          <t>승인 완료, 게시 진행</t>
         </is>
       </c>
     </row>
@@ -43724,7 +43715,7 @@
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-09 · 법인 승인 완료 · 게시 진행 중</t>
+          <t>승인 완료, 게시 진행</t>
         </is>
       </c>
     </row>
@@ -43750,7 +43741,7 @@
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t>법인 취소 요청(2026-09-15)</t>
+          <t>법인 요청으로 취소(2026-09-15)</t>
         </is>
       </c>
     </row>
@@ -43774,11 +43765,7 @@
       <c r="F28" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="0" t="inlineStr">
-        <is>
-          <t>법인리뷰 진행 중</t>
-        </is>
-      </c>
+      <c r="G28" s="0" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="261" t="inlineStr">
@@ -43830,11 +43817,7 @@
       <c r="F30" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="0" t="inlineStr">
-        <is>
-          <t>예상 2026-10-23 · 10/02→10/23 조정</t>
-        </is>
-      </c>
+      <c r="G30" s="0" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="261" t="inlineStr">
@@ -43858,7 +43841,7 @@
       </c>
       <c r="G31" s="0" t="inlineStr">
         <is>
-          <t>법인 취소 요청(2026-09-15)</t>
+          <t>법인 요청으로 취소(2026-09-15)</t>
         </is>
       </c>
     </row>
@@ -43888,7 +43871,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-16 · 10/05→10/16 조정 · 법인 승인 완료, 게시 진행 중</t>
+          <t>승인 완료, 게시 진행</t>
         </is>
       </c>
     </row>
@@ -43940,7 +43923,7 @@
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-23 · 프로덕션 반영됨</t>
+          <t>게시 반영됨</t>
         </is>
       </c>
     </row>
@@ -43968,11 +43951,7 @@
       <c r="F35" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G35" s="0" t="inlineStr">
-        <is>
-          <t>예상 2026-10-09 · LDM 9월 내 확인</t>
-        </is>
-      </c>
+      <c r="G35" s="0" t="n"/>
     </row>
     <row r="36">
       <c r="B36" s="261" t="inlineStr">
@@ -44022,7 +44001,7 @@
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t>Hyper/Professional/Swing PLP 취소(09-14) · 나머지 법인리뷰 진행 중</t>
+          <t>Hyper·Professional·Swing PLP 취소(2026-09-14)</t>
         </is>
       </c>
     </row>
@@ -44050,11 +44029,7 @@
       <c r="F38" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="0" t="inlineStr">
-        <is>
-          <t>예상 2026-10-23</t>
-        </is>
-      </c>
+      <c r="G38" s="0" t="n"/>
     </row>
     <row r="39">
       <c r="B39" s="261" t="inlineStr">
@@ -44098,11 +44073,7 @@
       <c r="F40" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G40" s="0" t="inlineStr">
-        <is>
-          <t>법인리뷰 진행 중</t>
-        </is>
-      </c>
+      <c r="G40" s="0" t="n"/>
     </row>
     <row r="41">
       <c r="B41" s="261" t="inlineStr">
@@ -44128,11 +44099,7 @@
       <c r="F41" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G41" s="0" t="inlineStr">
-        <is>
-          <t>예상 2026-10-16</t>
-        </is>
-      </c>
+      <c r="G41" s="0" t="n"/>
     </row>
     <row r="42">
       <c r="B42" s="261" t="inlineStr">
@@ -44160,7 +44127,7 @@
       </c>
       <c r="G42" s="0" t="inlineStr">
         <is>
-          <t>예상 2026-10-16 · LDM 무응답, 리마인더 발송</t>
+          <t>LDM 무응답, 리마인드 발송</t>
         </is>
       </c>
     </row>
@@ -44236,11 +44203,7 @@
       <c r="F45" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="0" t="inlineStr">
-        <is>
-          <t>예상 2026-10-16 · 10/02→10/16 조정</t>
-        </is>
-      </c>
+      <c r="G45" s="0" t="n"/>
     </row>
     <row r="46">
       <c r="B46" s="261" t="inlineStr">
@@ -44266,11 +44229,7 @@
       <c r="F46" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="0" t="inlineStr">
-        <is>
-          <t>예상 2026-10-09 · LDM 9월 내 확인</t>
-        </is>
-      </c>
+      <c r="G46" s="0" t="n"/>
     </row>
     <row r="47">
       <c r="B47" s="261" t="inlineStr">
@@ -44320,7 +44279,7 @@
       </c>
       <c r="G48" s="0" t="inlineStr">
         <is>
-          <t>게시완료 · Final Live Check 잔여</t>
+          <t>최종 확인 남음</t>
         </is>
       </c>
     </row>
@@ -44398,7 +44357,7 @@
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>게시완료(09-10) · Hyper Mini LED PLP 취소(08-31)</t>
+          <t>Hyper Mini LED PLP 취소(2026-08-31)</t>
         </is>
       </c>
     </row>
@@ -44426,11 +44385,7 @@
       <c r="F52" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G52" s="0" t="inlineStr">
-        <is>
-          <t>GNB 수정 게시(07-27) · 전체 게시 완료(10-07)</t>
-        </is>
-      </c>
+      <c r="G52" s="0" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -43263,7 +43263,11 @@
       <c r="F9" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>LDM 미진행으로 취소</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="261" t="inlineStr">
@@ -43287,7 +43291,7 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>법인 요청으로 취소(2026-09-02)</t>
+          <t>법인 요청으로 취소</t>
         </is>
       </c>
     </row>
@@ -43315,11 +43319,7 @@
       <c r="F11" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="0" t="inlineStr">
-        <is>
-          <t>게시 반영됨</t>
-        </is>
-      </c>
+      <c r="G11" s="0" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="261" t="inlineStr">
@@ -43345,7 +43345,7 @@
       <c r="F12" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="261" t="inlineStr">
@@ -43371,7 +43371,7 @@
       <c r="F13" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="261" t="inlineStr">
@@ -43393,7 +43393,7 @@
       <c r="F14" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="261" t="inlineStr">
@@ -43415,11 +43415,7 @@
       <c r="F15" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="0" t="inlineStr">
-        <is>
-          <t>법인 요청으로 취소(2026-09-16)</t>
-        </is>
-      </c>
+      <c r="G15" s="0" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="261" t="inlineStr">
@@ -43471,11 +43467,7 @@
       <c r="F17" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="0" t="inlineStr">
-        <is>
-          <t>게시 반영됨</t>
-        </is>
-      </c>
+      <c r="G17" s="0" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="261" t="inlineStr">
@@ -43501,7 +43493,7 @@
       <c r="F18" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="261" t="inlineStr">
@@ -43527,7 +43519,7 @@
       <c r="F19" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="261" t="inlineStr">
@@ -43577,7 +43569,7 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>LDM 무응답으로 취소(2026-10-08)</t>
+          <t>LDM 미진행으로 취소</t>
         </is>
       </c>
     </row>
@@ -43603,7 +43595,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>LDM 무응답으로 취소(2026-10-08)</t>
+          <t>LDM 미진행으로 취소</t>
         </is>
       </c>
     </row>
@@ -43631,7 +43623,7 @@
       <c r="F23" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="0" t="inlineStr"/>
+      <c r="G23" s="0" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="261" t="inlineStr">
@@ -43657,7 +43649,7 @@
       <c r="F24" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="0" t="inlineStr"/>
+      <c r="G24" s="0" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="261" t="inlineStr">
@@ -43683,11 +43675,7 @@
       <c r="F25" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="0" t="inlineStr">
-        <is>
-          <t>승인 완료, 게시 진행</t>
-        </is>
-      </c>
+      <c r="G25" s="0" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="261" t="inlineStr">
@@ -43713,11 +43701,7 @@
       <c r="F26" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="0" t="inlineStr">
-        <is>
-          <t>승인 완료, 게시 진행</t>
-        </is>
-      </c>
+      <c r="G26" s="0" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="261" t="inlineStr">
@@ -43739,11 +43723,7 @@
       <c r="F27" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="0" t="inlineStr">
-        <is>
-          <t>법인 요청으로 취소(2026-09-15)</t>
-        </is>
-      </c>
+      <c r="G27" s="0" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="261" t="inlineStr">
@@ -43791,7 +43771,7 @@
       <c r="F29" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="0" t="inlineStr"/>
+      <c r="G29" s="0" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="261" t="inlineStr">
@@ -43839,11 +43819,7 @@
       <c r="F31" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G31" s="0" t="inlineStr">
-        <is>
-          <t>법인 요청으로 취소(2026-09-15)</t>
-        </is>
-      </c>
+      <c r="G31" s="0" t="n"/>
     </row>
     <row r="32">
       <c r="B32" s="261" t="inlineStr">
@@ -43869,11 +43845,7 @@
       <c r="F32" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G32" s="0" t="inlineStr">
-        <is>
-          <t>승인 완료, 게시 진행</t>
-        </is>
-      </c>
+      <c r="G32" s="0" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="261" t="inlineStr">
@@ -43895,7 +43867,11 @@
       <c r="F33" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="0" t="inlineStr"/>
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t>LDM 미진행으로 취소</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="B34" s="261" t="inlineStr">
@@ -43921,11 +43897,7 @@
       <c r="F34" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G34" s="0" t="inlineStr">
-        <is>
-          <t>게시 반영됨</t>
-        </is>
-      </c>
+      <c r="G34" s="0" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="261" t="inlineStr">
@@ -43977,7 +43949,7 @@
       <c r="F36" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="0" t="inlineStr"/>
+      <c r="G36" s="0" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="261" t="inlineStr">
@@ -44001,7 +43973,7 @@
       </c>
       <c r="G37" s="0" t="inlineStr">
         <is>
-          <t>Hyper·Professional·Swing PLP 취소(2026-09-14)</t>
+          <t>일부 PLP 취소</t>
         </is>
       </c>
     </row>
@@ -44051,7 +44023,7 @@
       <c r="F39" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G39" s="0" t="inlineStr"/>
+      <c r="G39" s="0" t="n"/>
     </row>
     <row r="40">
       <c r="B40" s="261" t="inlineStr">
@@ -44125,11 +44097,7 @@
       <c r="F42" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="0" t="inlineStr">
-        <is>
-          <t>LDM 무응답, 리마인드 발송</t>
-        </is>
-      </c>
+      <c r="G42" s="0" t="n"/>
     </row>
     <row r="43">
       <c r="B43" s="261" t="inlineStr">
@@ -44153,7 +44121,7 @@
       <c r="F43" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G43" s="0" t="inlineStr"/>
+      <c r="G43" s="0" t="n"/>
     </row>
     <row r="44">
       <c r="B44" s="261" t="inlineStr">
@@ -44177,7 +44145,7 @@
       <c r="F44" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G44" s="0" t="inlineStr"/>
+      <c r="G44" s="0" t="n"/>
     </row>
     <row r="45">
       <c r="B45" s="261" t="inlineStr">
@@ -44251,7 +44219,7 @@
       <c r="F47" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="0" t="inlineStr"/>
+      <c r="G47" s="0" t="n"/>
     </row>
     <row r="48">
       <c r="B48" s="261" t="inlineStr">
@@ -44277,11 +44245,7 @@
       <c r="F48" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="0" t="inlineStr">
-        <is>
-          <t>최종 확인 남음</t>
-        </is>
-      </c>
+      <c r="G48" s="0" t="n"/>
     </row>
     <row r="49">
       <c r="B49" s="261" t="inlineStr">
@@ -44303,7 +44267,7 @@
       <c r="F49" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="0" t="inlineStr"/>
+      <c r="G49" s="0" t="n"/>
     </row>
     <row r="50">
       <c r="B50" s="261" t="inlineStr">
@@ -44329,7 +44293,7 @@
       <c r="F50" s="123" t="n">
         <v>1</v>
       </c>
-      <c r="G50" s="0" t="inlineStr"/>
+      <c r="G50" s="0" t="n"/>
     </row>
     <row r="51">
       <c r="B51" s="261" t="inlineStr">
@@ -44357,7 +44321,7 @@
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>Hyper Mini LED PLP 취소(2026-08-31)</t>
+          <t>일부 PLP 취소</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -40537,7 +40537,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>요청서 Target List 65개 사이트 · 기존 50에 15개국 추가(AR·BG·CH-fr·CL·HR·LEVANT×2·LK·NP·RO·SK·TN·UZ×2·VN) · 담당 정알찬 책임</t>
+          <t>65사이트 사전검토 · 15개국 추가</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -42133,7 +42133,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>예정 · 요청서 2026-10-07 기준 15사이트(Global 포함) · Due 2026-10-31 · 담당 정의현 책임</t>
+          <t>15사이트 사전검토 · Due 2026-10-31</t>
         </is>
       </c>
     </row>
@@ -43180,7 +43180,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>진행 중</t>
+          <t>완료 14 · 법인리뷰 13 · 작업중 8 · 취소 9</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -44439,7 +44439,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>ES 완료(2026-09-11) · 사이트 9/10 (90%) · 완료 18 · 법인리뷰 2 · 작업중 0</t>
+          <t>완료 18/20 · FR 법인리뷰 2건</t>
         </is>
       </c>
       <c r="D2" s="164" t="n"/>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="W16 - CineBeam S PDP Video Upda" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="W16 - Copilot+ Filter Creation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="W16 - Microsoft PDP Gallery Car" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="W17 - GNB Structure" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="W18 - FAQ Request (UltraGear PL" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="W18 - UltraGear OLED FAQ Update" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="W22 - UltraGear Buying Guide" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="W23 - 27GM950B-B 갤러리 이미지 교체" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="W23 - 39GX950B 이미지 수정 2차" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="W23 - 52G930B Feature 수정 건" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="W23 - UL인증 feature 삭제 1차" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="W25 - Copilot+ Hero Banner" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="W28 - AI Upscaling Disclaimer" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="W28 - UL Verified Eye Comfort" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="W30 - SmartMonitor ScreenShare" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="W30 - UltraGear 1000Hz FAQ" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="W31 - gram Secure Lock" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="W31 - PDP Gallery Win11 Pro" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="W31 - Smart Monitor Multi AI" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="W32 - UltraGear 27GX704A" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="W32 - Digital Trends Award 삭제" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="W32 - UltraGear PDP 5모델" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="W32 - UltraFine PDP MIC 삭제" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="W38 - gram pro gallery" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="W41 - UltraGear Buying Guide 2차" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="W41 - Windows 11 Landing" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W16 - CineBeam S PDP Video Upda" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W16 - Copilot+ Filter Creation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W16 - Microsoft PDP Gallery Car" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W17 - GNB Structure" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W18 - FAQ Request (UltraGear PL" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W18 - UltraGear OLED FAQ Update" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W22 - UltraGear Buying Guide" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - 27GM950B-B 갤러리 이미지 교체" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - 39GX950B 이미지 수정 2차" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - 52G930B Feature 수정 건" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - UL인증 feature 삭제 1차" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W25 - Copilot+ Hero Banner" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W28 - AI Upscaling Disclaimer" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W28 - UL Verified Eye Comfort" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W30 - SmartMonitor ScreenShare" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W30 - UltraGear 1000Hz FAQ" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W31 - gram Secure Lock" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W31 - PDP Gallery Win11 Pro" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W31 - Smart Monitor Multi AI" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - UltraGear 27GX704A" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - Digital Trends Award 삭제" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - UltraGear PDP 5모델" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - UltraFine PDP MIC 삭제" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W38 - gram pro gallery" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W41 - UltraGear Buying Guide 2차" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W41 - Windows 11 Landing" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40537,7 +40537,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>65사이트 사전검토 · 15개국 추가</t>
+          <t>사전검토 64 · 취소 1(UK, 로컬 WR2338674EL과 중복) · 15개국 추가</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -40551,6 +40551,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -40621,7 +40622,11 @@
       <c r="F9" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="0" t="n"/>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>WB 접수, 착수 전</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="261" t="inlineStr">
@@ -40645,7 +40650,7 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
+          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함 · WB 접수, 착수 전</t>
         </is>
       </c>
     </row>
@@ -40805,7 +40810,11 @@
       <c r="F17" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="0" t="n"/>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>WB 접수, 착수 전</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="261" t="inlineStr">
@@ -40827,7 +40836,11 @@
       <c r="F18" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="0" t="n"/>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>WB 접수, 착수 전</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="261" t="inlineStr">
@@ -41895,7 +41908,11 @@
       <c r="F66" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G66" s="0" t="n"/>
+      <c r="G66" s="0" t="inlineStr">
+        <is>
+          <t>WB 접수, 착수 전</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="B67" s="261" t="inlineStr">
@@ -41954,7 +41971,7 @@
       </c>
       <c r="D69" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="E69" s="123" t="n"/>
@@ -41963,7 +41980,7 @@
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
+          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함 · 로컬 WR2338674EL과 중복이라 취소</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -40537,7 +40537,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>사전검토 64 · 취소 1(UK, 로컬 WR2338674EL과 중복) · 15개국 추가</t>
+          <t>사전검토 64 · 법인리뷰 1(UK, 로컬 드리븐) · 15개국 추가</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -40551,7 +40551,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -41971,7 +41970,7 @@
       </c>
       <c r="D69" s="265" t="inlineStr">
         <is>
-          <t>취소</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E69" s="123" t="n"/>
@@ -41980,7 +41979,7 @@
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함 · 로컬 WR2338674EL과 중복이라 취소</t>
+          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함 · 로컬 드리븐 · WR2338674EL(LGCOMUK-3928)</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -40537,7 +40537,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>사전검토 64 · 법인리뷰 1(UK, 로컬 드리븐) · 15개국 추가</t>
+          <t>사전검토 59 · 작업중 2(EE·LT) · 법인리뷰 3(UK·LV·CA-fr) · 완료 1(CA-en) · 15개국 추가</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -40802,16 +40802,20 @@
       </c>
       <c r="D17" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E17" s="123" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E17" s="123" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="F17" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>WB 접수, 착수 전</t>
+          <t>로컬 드리븐 · WR2340922BH(LGCOMCI-5144)</t>
         </is>
       </c>
     </row>
@@ -40828,7 +40832,7 @@
       </c>
       <c r="D18" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E18" s="123" t="n"/>
@@ -40837,7 +40841,7 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>WB 접수, 착수 전</t>
+          <t>로컬 드리븐 · WR2340921BH(LGCOMCI-5144)</t>
         </is>
       </c>
     </row>
@@ -41056,14 +41060,18 @@
       </c>
       <c r="D28" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E28" s="123" t="n"/>
       <c r="F28" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="0" t="n"/>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>로컬 드리븐 · 허브 · WR2341063AK(LGCOMEE-557)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="261" t="inlineStr">
@@ -41452,14 +41460,18 @@
       </c>
       <c r="D46" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E46" s="123" t="n"/>
       <c r="F46" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G46" s="0" t="n"/>
+      <c r="G46" s="0" t="inlineStr">
+        <is>
+          <t>로컬 드리븐 · WR2341062AK(LGCOMLT-527)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="B47" s="261" t="inlineStr">
@@ -41474,14 +41486,18 @@
       </c>
       <c r="D47" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E47" s="123" t="n"/>
       <c r="F47" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G47" s="0" t="n"/>
+      <c r="G47" s="0" t="inlineStr">
+        <is>
+          <t>로컬 드리븐 · 허브 · WR2341048AK(LGCOMLV-634)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="B48" s="261" t="inlineStr">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -40623,7 +40623,7 @@
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>WB 접수, 착수 전</t>
+          <t>접수됨, 착수 전</t>
         </is>
       </c>
     </row>
@@ -40649,7 +40649,7 @@
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함 · WB 접수, 착수 전</t>
+          <t>접수됨, 착수 전</t>
         </is>
       </c>
     </row>
@@ -40671,7 +40671,7 @@
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>요청서 Target List 추가</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -40739,11 +40739,7 @@
       <c r="F14" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="0" t="inlineStr">
-        <is>
-          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
-        </is>
-      </c>
+      <c r="G14" s="0" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="261" t="inlineStr">
@@ -40763,7 +40759,7 @@
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>요청서 Target List 추가</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -40785,7 +40781,7 @@
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>신규 제작(1차 미게시)</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -40885,7 +40881,7 @@
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t>요청서 Target List 추가</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -40907,7 +40903,7 @@
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>요청서 Target List 추가</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -40929,7 +40925,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>신규 제작(1차 미게시)</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -40951,7 +40947,7 @@
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t>신규 제작(1차 미게시)</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -40997,11 +40993,7 @@
       <c r="F25" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="0" t="inlineStr">
-        <is>
-          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
-        </is>
-      </c>
+      <c r="G25" s="0" t="n"/>
     </row>
     <row r="26">
       <c r="B26" s="261" t="inlineStr">
@@ -41069,7 +41061,7 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>로컬 드리븐 · 허브 · WR2341063AK(LGCOMEE-557)</t>
+          <t>로컬 드리븐 · 허브만 · WR2341063AK(LGCOMEE-557)</t>
         </is>
       </c>
     </row>
@@ -41157,7 +41149,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>신규 제작(1차 미게시)</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -41223,7 +41215,7 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t>요청서 Target List 추가</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -41333,7 +41325,7 @@
       </c>
       <c r="G40" s="0" t="inlineStr">
         <is>
-          <t>신규 제작(1차 미게시)</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -41355,7 +41347,7 @@
       </c>
       <c r="G41" s="0" t="inlineStr">
         <is>
-          <t>신규 제작(1차 미게시)</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -41399,7 +41391,7 @@
       </c>
       <c r="G43" s="0" t="inlineStr">
         <is>
-          <t>요청서 Target List 추가</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -41421,7 +41413,7 @@
       </c>
       <c r="G44" s="0" t="inlineStr">
         <is>
-          <t>요청서 Target List 추가</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -41443,7 +41435,7 @@
       </c>
       <c r="G45" s="0" t="inlineStr">
         <is>
-          <t>요청서 Target List 추가</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -41495,7 +41487,7 @@
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
-          <t>로컬 드리븐 · 허브 · WR2341048AK(LGCOMLV-634)</t>
+          <t>로컬 드리븐 · 허브만 · WR2341048AK(LGCOMLV-634)</t>
         </is>
       </c>
     </row>
@@ -41519,11 +41511,7 @@
       <c r="F48" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="0" t="inlineStr">
-        <is>
-          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
-        </is>
-      </c>
+      <c r="G48" s="0" t="n"/>
     </row>
     <row r="49">
       <c r="B49" s="261" t="inlineStr">
@@ -41587,7 +41575,7 @@
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>요청서 Target List 추가</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -41675,7 +41663,7 @@
       </c>
       <c r="G55" s="0" t="inlineStr">
         <is>
-          <t>신규 제작(1차 미게시)</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -41697,7 +41685,7 @@
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t>신규 제작(1차 미게시)</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -41719,7 +41707,7 @@
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
-          <t>요청서 Target List 추가</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -41831,11 +41819,7 @@
       <c r="F62" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="0" t="inlineStr">
-        <is>
-          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함</t>
-        </is>
-      </c>
+      <c r="G62" s="0" t="n"/>
     </row>
     <row r="63">
       <c r="B63" s="261" t="inlineStr">
@@ -41855,7 +41839,7 @@
       </c>
       <c r="G63" s="0" t="inlineStr">
         <is>
-          <t>요청서 Target List 추가</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -41899,7 +41883,7 @@
       </c>
       <c r="G65" s="0" t="inlineStr">
         <is>
-          <t>요청서 Target List 추가</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -41925,7 +41909,7 @@
       </c>
       <c r="G66" s="0" t="inlineStr">
         <is>
-          <t>WB 접수, 착수 전</t>
+          <t>접수됨, 착수 전</t>
         </is>
       </c>
     </row>
@@ -41995,7 +41979,7 @@
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>1차 대상 외 기존 라이브(10/06 실측) · 2차 포함 · 로컬 드리븐 · WR2338674EL(LGCOMUK-3928)</t>
+          <t>로컬 드리븐 · WR2338674EL(LGCOMUK-3928)</t>
         </is>
       </c>
     </row>
@@ -42017,7 +42001,7 @@
       </c>
       <c r="G70" s="0" t="inlineStr">
         <is>
-          <t>요청서 Target List 추가</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -42039,7 +42023,7 @@
       </c>
       <c r="G71" s="0" t="inlineStr">
         <is>
-          <t>요청서 Target List 추가</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>
@@ -42061,7 +42045,7 @@
       </c>
       <c r="G72" s="0" t="inlineStr">
         <is>
-          <t>요청서 Target List 추가</t>
+          <t>페이지 없음</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -40537,7 +40537,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>사전검토 59 · 작업중 2(EE·LT) · 법인리뷰 3(UK·LV·CA-fr) · 완료 1(CA-en) · 15개국 추가</t>
+          <t>10/14 기준 · 사전검토 59 · 법인리뷰 5(UK·EE·LT·LV·CA-fr) · 완료 1(CA-en) · 15개국 추가</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -41052,7 +41052,7 @@
       </c>
       <c r="D28" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E28" s="123" t="n"/>
@@ -41061,7 +41061,7 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>로컬 드리븐 · 허브만 · WR2341063AK(LGCOMEE-557)</t>
+          <t>로컬 드리븐 · WR2341063AK(LGCOMEE-557)</t>
         </is>
       </c>
     </row>
@@ -41173,7 +41173,11 @@
       <c r="F33" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="0" t="n"/>
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t>접수됨, 착수 전</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="B34" s="261" t="inlineStr">
@@ -41283,7 +41287,11 @@
       <c r="F38" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="0" t="n"/>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t>접수됨, 착수 전</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="B39" s="261" t="inlineStr">
@@ -41305,7 +41313,11 @@
       <c r="F39" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G39" s="0" t="n"/>
+      <c r="G39" s="0" t="inlineStr">
+        <is>
+          <t>접수됨, 착수 전</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="B40" s="261" t="inlineStr">
@@ -41371,7 +41383,11 @@
       <c r="F42" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="0" t="n"/>
+      <c r="G42" s="0" t="inlineStr">
+        <is>
+          <t>접수됨, 착수 전</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="B43" s="261" t="inlineStr">
@@ -41452,7 +41468,7 @@
       </c>
       <c r="D46" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E46" s="123" t="n"/>
@@ -41487,7 +41503,7 @@
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
-          <t>로컬 드리븐 · 허브만 · WR2341048AK(LGCOMLV-634)</t>
+          <t>로컬 드리븐 · WR2341048AK(LGCOMLV-634)</t>
         </is>
       </c>
     </row>
@@ -41753,7 +41769,11 @@
       <c r="F59" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G59" s="0" t="n"/>
+      <c r="G59" s="0" t="inlineStr">
+        <is>
+          <t>접수됨, 착수 전</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="B60" s="261" t="inlineStr">
@@ -41775,7 +41795,11 @@
       <c r="F60" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G60" s="0" t="n"/>
+      <c r="G60" s="0" t="inlineStr">
+        <is>
+          <t>접수됨, 착수 전</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="B61" s="261" t="inlineStr">
@@ -41883,7 +41907,7 @@
       </c>
       <c r="G65" s="0" t="inlineStr">
         <is>
-          <t>페이지 없음</t>
+          <t>페이지 없음 · 접수됨, 착수 전</t>
         </is>
       </c>
     </row>
@@ -41955,7 +41979,11 @@
       <c r="F68" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G68" s="0" t="n"/>
+      <c r="G68" s="0" t="inlineStr">
+        <is>
+          <t>LDM 확인 대기</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="B69" s="261" t="inlineStr">
@@ -41979,7 +42007,7 @@
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>로컬 드리븐 · WR2338674EL(LGCOMUK-3928)</t>
+          <t>로컬 드리븐 · WR2338674EL(LGCOMUK-3928) · 글로벌 건 취소</t>
         </is>
       </c>
     </row>
@@ -42001,7 +42029,7 @@
       </c>
       <c r="G70" s="0" t="inlineStr">
         <is>
-          <t>페이지 없음</t>
+          <t>페이지 없음 · 접수됨, 착수 전</t>
         </is>
       </c>
     </row>
@@ -42023,7 +42051,7 @@
       </c>
       <c r="G71" s="0" t="inlineStr">
         <is>
-          <t>페이지 없음</t>
+          <t>페이지 없음 · 접수됨, 착수 전</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -1,36 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W16 - CineBeam S PDP Video Upda" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W16 - Copilot+ Filter Creation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W16 - Microsoft PDP Gallery Car" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W17 - GNB Structure" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W18 - FAQ Request (UltraGear PL" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W18 - UltraGear OLED FAQ Update" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W22 - UltraGear Buying Guide" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - 27GM950B-B 갤러리 이미지 교체" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - 39GX950B 이미지 수정 2차" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - 52G930B Feature 수정 건" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - UL인증 feature 삭제 1차" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W25 - Copilot+ Hero Banner" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W28 - AI Upscaling Disclaimer" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W28 - UL Verified Eye Comfort" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W30 - SmartMonitor ScreenShare" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W30 - UltraGear 1000Hz FAQ" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W31 - gram Secure Lock" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W31 - PDP Gallery Win11 Pro" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W31 - Smart Monitor Multi AI" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - UltraGear 27GX704A" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - Digital Trends Award 삭제" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - UltraGear PDP 5모델" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - UltraFine PDP MIC 삭제" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W38 - gram pro gallery" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W41 - UltraGear Buying Guide 2차" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W41 - Windows 11 Landing" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="W16 - CineBeam S PDP Video Upda" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="W16 - Copilot+ Filter Creation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="W16 - Microsoft PDP Gallery Car" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="W17 - GNB Structure" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="W18 - FAQ Request (UltraGear PL" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="W18 - UltraGear OLED FAQ Update" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="W22 - UltraGear Buying Guide" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="W23 - 27GM950B-B 갤러리 이미지 교체" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="W23 - 39GX950B 이미지 수정 2차" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="W23 - 52G930B Feature 수정 건" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="W23 - UL인증 feature 삭제 1차" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="W25 - Copilot+ Hero Banner" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="W28 - AI Upscaling Disclaimer" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="W28 - UL Verified Eye Comfort" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="W30 - SmartMonitor ScreenShare" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="W30 - UltraGear 1000Hz FAQ" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="W31 - gram Secure Lock" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="W31 - PDP Gallery Win11 Pro" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="W31 - Smart Monitor Multi AI" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="W32 - UltraGear 27GX704A" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="W32 - Digital Trends Award 삭제" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="W32 - UltraGear PDP 5모델" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="W32 - UltraFine PDP MIC 삭제" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="W38 - gram pro gallery" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="W41 - UltraGear Buying Guide 2차" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="W41 - Windows 11 Landing" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="W41 - IT B2B TCO Mark" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'W41 - IT B2B TCO Mark'!$A$3:$G$232</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -40,7 +43,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="73">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -416,6 +419,11 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -638,7 +646,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="16"/>
   </cellStyleXfs>
-  <cellXfs count="298">
+  <cellXfs count="299">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -1225,6 +1233,7 @@
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -42630,6 +42639,6047 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G232"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="203" min="1" max="1"/>
+    <col width="14" customWidth="1" style="203" min="2" max="2"/>
+    <col width="78" customWidth="1" style="203" min="3" max="3"/>
+    <col width="12" customWidth="1" style="203" min="4" max="4"/>
+    <col width="14" customWidth="1" style="203" min="5" max="5"/>
+    <col width="10" customWidth="1" style="203" min="6" max="6"/>
+    <col width="42" customWidth="1" style="203" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="298" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="298" t="inlineStr">
+        <is>
+          <t>GR26-W41-MS-IT-B2B-MNT-TCO Mark &amp; Spec Modification-1008</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="295" t="inlineStr">
+        <is>
+          <t>이번주 추가</t>
+        </is>
+      </c>
+      <c r="B2" s="295" t="inlineStr">
+        <is>
+          <t>10/14 등록 · 요청자 Suan Kim · Due 2026-10-30 · 23개국 · 229 PDP · 40모델 · 사전검토</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="296" t="inlineStr">
+        <is>
+          <t>Head</t>
+        </is>
+      </c>
+      <c r="B3" s="296" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="C3" s="296" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D3" s="296" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E3" s="296" t="inlineStr">
+        <is>
+          <t>완료일</t>
+        </is>
+      </c>
+      <c r="F3" s="296" t="inlineStr">
+        <is>
+          <t>Page#</t>
+        </is>
+      </c>
+      <c r="G3" s="296" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="295" t="inlineStr">
+        <is>
+          <t>BE-nl</t>
+        </is>
+      </c>
+      <c r="C4" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be/business/computer-producten/monitoren/fhd-qhd/24ba450-b</t>
+        </is>
+      </c>
+      <c r="D4" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F4" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="295" t="inlineStr">
+        <is>
+          <t>24BA450-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="295" t="inlineStr">
+        <is>
+          <t>BE-fr</t>
+        </is>
+      </c>
+      <c r="C5" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be_fr/business/computer-producten/monitoren/fhd-qhd/24ba450-b</t>
+        </is>
+      </c>
+      <c r="D5" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F5" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="295" t="inlineStr">
+        <is>
+          <t>24BA450-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C6" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/business-monitore/24ba450-b</t>
+        </is>
+      </c>
+      <c r="D6" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F6" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="295" t="inlineStr">
+        <is>
+          <t>24BA450-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C7" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/24ba450-b</t>
+        </is>
+      </c>
+      <c r="D7" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F7" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="295" t="inlineStr">
+        <is>
+          <t>24BA450-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C8" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-monitor/24ba450</t>
+        </is>
+      </c>
+      <c r="D8" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F8" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="295" t="inlineStr">
+        <is>
+          <t>24BA450-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="295" t="inlineStr">
+        <is>
+          <t>IN-en</t>
+        </is>
+      </c>
+      <c r="C9" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/in/business/computers/monitors/ultragear-monitors/24ba450-b</t>
+        </is>
+      </c>
+      <c r="D9" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F9" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="295" t="inlineStr">
+        <is>
+          <t>24BA450-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="295" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C10" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/business/24ba450-b</t>
+        </is>
+      </c>
+      <c r="D10" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F10" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="295" t="inlineStr">
+        <is>
+          <t>24BA450-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="295" t="inlineStr">
+        <is>
+          <t>NL-nl</t>
+        </is>
+      </c>
+      <c r="C11" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/business/computer-producten/monitoren/fhd-qhd/24ba450-b</t>
+        </is>
+      </c>
+      <c r="D11" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F11" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="295" t="inlineStr">
+        <is>
+          <t>24BA450-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="295" t="inlineStr">
+        <is>
+          <t>RU-ru</t>
+        </is>
+      </c>
+      <c r="C12" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ru/business/monitors/lg-24ba450-b</t>
+        </is>
+      </c>
+      <c r="D12" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F12" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="295" t="inlineStr">
+        <is>
+          <t>24BA450-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C13" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/24ba450-b</t>
+        </is>
+      </c>
+      <c r="D13" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F13" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="295" t="inlineStr">
+        <is>
+          <t>24BA450-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="295" t="inlineStr">
+        <is>
+          <t>UK-en</t>
+        </is>
+      </c>
+      <c r="C14" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/business/monitors-pcs/monitors/lg-monitor/24ba450-b</t>
+        </is>
+      </c>
+      <c r="D14" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F14" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="295" t="inlineStr">
+        <is>
+          <t>24BA450-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="295" t="inlineStr">
+        <is>
+          <t>BE-nl</t>
+        </is>
+      </c>
+      <c r="C15" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be/business/computer-producten/monitoren/fhd-qhd/24ba550-b</t>
+        </is>
+      </c>
+      <c r="D15" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F15" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="295" t="inlineStr">
+        <is>
+          <t>24BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="295" t="inlineStr">
+        <is>
+          <t>BE-fr</t>
+        </is>
+      </c>
+      <c r="C16" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be_fr/business/computer-producten/monitoren/fhd-qhd/24ba550-b</t>
+        </is>
+      </c>
+      <c r="D16" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F16" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="295" t="inlineStr">
+        <is>
+          <t>24BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="295" t="inlineStr">
+        <is>
+          <t>CZ-cz</t>
+        </is>
+      </c>
+      <c r="C17" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cz/business/byznys/komercni-monitory/24ba550-b</t>
+        </is>
+      </c>
+      <c r="D17" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F17" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="295" t="inlineStr">
+        <is>
+          <t>24BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C18" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/24ba550-b</t>
+        </is>
+      </c>
+      <c r="D18" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F18" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="295" t="inlineStr">
+        <is>
+          <t>24BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C19" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/24ba550-b</t>
+        </is>
+      </c>
+      <c r="D19" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F19" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="295" t="inlineStr">
+        <is>
+          <t>24BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C20" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-monitor/24ba550</t>
+        </is>
+      </c>
+      <c r="D20" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F20" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="295" t="inlineStr">
+        <is>
+          <t>24BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="295" t="inlineStr">
+        <is>
+          <t>IL-he</t>
+        </is>
+      </c>
+      <c r="C21" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/business/b2b/lg-24ba550-b</t>
+        </is>
+      </c>
+      <c r="D21" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F21" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="295" t="inlineStr">
+        <is>
+          <t>24BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="295" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C22" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/business/24ba550-b</t>
+        </is>
+      </c>
+      <c r="D22" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F22" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="295" t="inlineStr">
+        <is>
+          <t>24BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="295" t="inlineStr">
+        <is>
+          <t>NL-nl</t>
+        </is>
+      </c>
+      <c r="C23" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/business/computer-producten/monitoren/fhd-qhd/24ba550-b</t>
+        </is>
+      </c>
+      <c r="D23" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F23" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="295" t="inlineStr">
+        <is>
+          <t>24BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="295" t="inlineStr">
+        <is>
+          <t>PL-pl</t>
+        </is>
+      </c>
+      <c r="C24" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/pl/business/monitory-biznesowe/monitory/lg-monitors/24ba550-b</t>
+        </is>
+      </c>
+      <c r="D24" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F24" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="295" t="inlineStr">
+        <is>
+          <t>24BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="295" t="inlineStr">
+        <is>
+          <t>RU-ru</t>
+        </is>
+      </c>
+      <c r="C25" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ru/business/monitors/lg-24ba550-b</t>
+        </is>
+      </c>
+      <c r="D25" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F25" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="295" t="inlineStr">
+        <is>
+          <t>24BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C26" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/24ba550-b</t>
+        </is>
+      </c>
+      <c r="D26" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F26" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="295" t="inlineStr">
+        <is>
+          <t>24BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="295" t="inlineStr">
+        <is>
+          <t>UK-en</t>
+        </is>
+      </c>
+      <c r="C27" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/business/monitors-pcs/monitors/lg-monitor/24ba550-b</t>
+        </is>
+      </c>
+      <c r="D27" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F27" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="295" t="inlineStr">
+        <is>
+          <t>24BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C28" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/monitore/alle-monitore/business-monitore/24ba55w-b</t>
+        </is>
+      </c>
+      <c r="D28" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F28" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="295" t="inlineStr">
+        <is>
+          <t>24BA55W-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C29" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-monitor/24ba55w</t>
+        </is>
+      </c>
+      <c r="D29" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F29" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="295" t="inlineStr">
+        <is>
+          <t>24BA55W-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="295" t="inlineStr">
+        <is>
+          <t>BE-nl</t>
+        </is>
+      </c>
+      <c r="C30" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be/business/computer-producten/monitoren/fhd-qhd/24ba560-b</t>
+        </is>
+      </c>
+      <c r="D30" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F30" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="295" t="inlineStr">
+        <is>
+          <t>24BA560-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="295" t="inlineStr">
+        <is>
+          <t>BE-fr</t>
+        </is>
+      </c>
+      <c r="C31" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be_fr/business/computer-producten/monitoren/fhd-qhd/24ba560-b</t>
+        </is>
+      </c>
+      <c r="D31" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F31" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="295" t="inlineStr">
+        <is>
+          <t>24BA560-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="295" t="inlineStr">
+        <is>
+          <t>CA-en</t>
+        </is>
+      </c>
+      <c r="C32" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/monitors-pcs/monitors/lg-monitor/24ba560-b</t>
+        </is>
+      </c>
+      <c r="D32" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F32" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="295" t="inlineStr">
+        <is>
+          <t>24BA560-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="295" t="inlineStr">
+        <is>
+          <t>CA-fr</t>
+        </is>
+      </c>
+      <c r="C33" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/business/moniteurs-et-pc/moniteurs/moniteur-lg/24ba560-b</t>
+        </is>
+      </c>
+      <c r="D33" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F33" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="295" t="inlineStr">
+        <is>
+          <t>24BA560-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C34" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/monitore/alle-monitore/business-monitore/24ba560-b</t>
+        </is>
+      </c>
+      <c r="D34" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F34" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="295" t="inlineStr">
+        <is>
+          <t>24BA560-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C35" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/24ba560-b</t>
+        </is>
+      </c>
+      <c r="D35" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F35" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="295" t="inlineStr">
+        <is>
+          <t>24BA560-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="295" t="inlineStr">
+        <is>
+          <t>ES-es</t>
+        </is>
+      </c>
+      <c r="C36" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/business/informatica/monitores/monitores-ips/24ba560-b</t>
+        </is>
+      </c>
+      <c r="D36" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F36" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="295" t="inlineStr">
+        <is>
+          <t>24BA560-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C37" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-monitor/24ba560</t>
+        </is>
+      </c>
+      <c r="D37" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F37" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="295" t="inlineStr">
+        <is>
+          <t>24BA560-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="295" t="inlineStr">
+        <is>
+          <t>NL-nl</t>
+        </is>
+      </c>
+      <c r="C38" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/business/computer-producten/monitoren/fhd-qhd/24ba560-b</t>
+        </is>
+      </c>
+      <c r="D38" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F38" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="295" t="inlineStr">
+        <is>
+          <t>24BA560-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C39" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/24ba560-b</t>
+        </is>
+      </c>
+      <c r="D39" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F39" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="295" t="inlineStr">
+        <is>
+          <t>24BA560-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C40" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/24ba560-t</t>
+        </is>
+      </c>
+      <c r="D40" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F40" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="295" t="inlineStr">
+        <is>
+          <t>24BA560-T · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="295" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C41" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/business/24ba560-t</t>
+        </is>
+      </c>
+      <c r="D41" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F41" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="295" t="inlineStr">
+        <is>
+          <t>24BA560-T · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="295" t="inlineStr">
+        <is>
+          <t>AE-en</t>
+        </is>
+      </c>
+      <c r="C42" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae/business/monitors/lg-24ba650-b</t>
+        </is>
+      </c>
+      <c r="D42" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F42" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="295" t="inlineStr">
+        <is>
+          <t>24BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="295" t="inlineStr">
+        <is>
+          <t>AE-ar</t>
+        </is>
+      </c>
+      <c r="C43" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae_ar/business/monitors/lg-24ba650-b</t>
+        </is>
+      </c>
+      <c r="D43" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F43" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="295" t="inlineStr">
+        <is>
+          <t>24BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="295" t="inlineStr">
+        <is>
+          <t>BE-nl</t>
+        </is>
+      </c>
+      <c r="C44" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be/business/computer-producten/monitoren/fhd-qhd/24ba650-b</t>
+        </is>
+      </c>
+      <c r="D44" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F44" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="295" t="inlineStr">
+        <is>
+          <t>24BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="295" t="inlineStr">
+        <is>
+          <t>BE-fr</t>
+        </is>
+      </c>
+      <c r="C45" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be_fr/business/computer-producten/monitoren/fhd-qhd/24ba650-b</t>
+        </is>
+      </c>
+      <c r="D45" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F45" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="295" t="inlineStr">
+        <is>
+          <t>24BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="295" t="inlineStr">
+        <is>
+          <t>CA-en</t>
+        </is>
+      </c>
+      <c r="C46" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/monitors-pcs/monitors/lg-monitor/24ba650-b</t>
+        </is>
+      </c>
+      <c r="D46" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F46" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="295" t="inlineStr">
+        <is>
+          <t>24BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="295" t="inlineStr">
+        <is>
+          <t>CA-fr</t>
+        </is>
+      </c>
+      <c r="C47" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/business/moniteurs-et-pc/moniteurs/moniteur-lg/24ba650-b</t>
+        </is>
+      </c>
+      <c r="D47" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F47" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="295" t="inlineStr">
+        <is>
+          <t>24BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C48" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/business-monitore/24ba650-b</t>
+        </is>
+      </c>
+      <c r="D48" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F48" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="295" t="inlineStr">
+        <is>
+          <t>24BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C49" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/24ba650-b</t>
+        </is>
+      </c>
+      <c r="D49" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F49" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="295" t="inlineStr">
+        <is>
+          <t>24BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="295" t="inlineStr">
+        <is>
+          <t>ES-es</t>
+        </is>
+      </c>
+      <c r="C50" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/business/informatica/monitores/monitores-ips/24ba650-b</t>
+        </is>
+      </c>
+      <c r="D50" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F50" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="295" t="inlineStr">
+        <is>
+          <t>24BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C51" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-monitor/24ba650</t>
+        </is>
+      </c>
+      <c r="D51" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F51" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="295" t="inlineStr">
+        <is>
+          <t>24BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="295" t="inlineStr">
+        <is>
+          <t>IL-he</t>
+        </is>
+      </c>
+      <c r="C52" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/business/b2b/lg-24ba650-b</t>
+        </is>
+      </c>
+      <c r="D52" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F52" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="295" t="inlineStr">
+        <is>
+          <t>24BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="295" t="inlineStr">
+        <is>
+          <t>IN-en</t>
+        </is>
+      </c>
+      <c r="C53" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/in/business/computers/monitors/ips-monitors/24ba650-b</t>
+        </is>
+      </c>
+      <c r="D53" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F53" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="295" t="inlineStr">
+        <is>
+          <t>24BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="295" t="inlineStr">
+        <is>
+          <t>MX-es</t>
+        </is>
+      </c>
+      <c r="C54" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/mx/business/monitores-pcs/cloud-computing/thin-client/24ba650-b</t>
+        </is>
+      </c>
+      <c r="D54" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F54" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="295" t="inlineStr">
+        <is>
+          <t>24BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="295" t="inlineStr">
+        <is>
+          <t>NL-nl</t>
+        </is>
+      </c>
+      <c r="C55" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/business/computer-producten/monitoren/fhd-qhd/24ba650-b</t>
+        </is>
+      </c>
+      <c r="D55" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F55" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="295" t="inlineStr">
+        <is>
+          <t>24BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="295" t="inlineStr">
+        <is>
+          <t>RU-ru</t>
+        </is>
+      </c>
+      <c r="C56" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ru/business/monitors/lg-24ba650-b</t>
+        </is>
+      </c>
+      <c r="D56" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F56" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="295" t="inlineStr">
+        <is>
+          <t>24BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C57" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/24ba650-b</t>
+        </is>
+      </c>
+      <c r="D57" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F57" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="295" t="inlineStr">
+        <is>
+          <t>24BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="295" t="inlineStr">
+        <is>
+          <t>UK-en</t>
+        </is>
+      </c>
+      <c r="C58" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/business/monitors-pcs/monitors/lg-monitor/24ba650-b</t>
+        </is>
+      </c>
+      <c r="D58" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F58" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="295" t="inlineStr">
+        <is>
+          <t>24BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C59" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/24ba650-t</t>
+        </is>
+      </c>
+      <c r="D59" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F59" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="295" t="inlineStr">
+        <is>
+          <t>24BA650-T · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C60" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/24ba650-t</t>
+        </is>
+      </c>
+      <c r="D60" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F60" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="295" t="inlineStr">
+        <is>
+          <t>24BA650-T · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="295" t="inlineStr">
+        <is>
+          <t>BE-nl</t>
+        </is>
+      </c>
+      <c r="C61" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be/business/computer-producten/monitoren/fhd-qhd/24ba750-b</t>
+        </is>
+      </c>
+      <c r="D61" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F61" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="295" t="inlineStr">
+        <is>
+          <t>24BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="295" t="inlineStr">
+        <is>
+          <t>BE-fr</t>
+        </is>
+      </c>
+      <c r="C62" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be_fr/business/computer-producten/monitoren/fhd-qhd/24ba750-b</t>
+        </is>
+      </c>
+      <c r="D62" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F62" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="295" t="inlineStr">
+        <is>
+          <t>24BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="295" t="inlineStr">
+        <is>
+          <t>CA-en</t>
+        </is>
+      </c>
+      <c r="C63" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/monitors-pcs/monitors/lg-monitor/24ba750-b</t>
+        </is>
+      </c>
+      <c r="D63" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F63" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="295" t="inlineStr">
+        <is>
+          <t>24BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="295" t="inlineStr">
+        <is>
+          <t>CA-fr</t>
+        </is>
+      </c>
+      <c r="C64" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/business/moniteurs-et-pc/moniteurs/moniteur-lg/24ba750-b</t>
+        </is>
+      </c>
+      <c r="D64" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F64" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="295" t="inlineStr">
+        <is>
+          <t>24BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C65" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/business-monitore/24ba750-b</t>
+        </is>
+      </c>
+      <c r="D65" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F65" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="295" t="inlineStr">
+        <is>
+          <t>24BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C66" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/24ba750-b</t>
+        </is>
+      </c>
+      <c r="D66" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F66" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="295" t="inlineStr">
+        <is>
+          <t>24BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="295" t="inlineStr">
+        <is>
+          <t>ES-es</t>
+        </is>
+      </c>
+      <c r="C67" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/business/informatica/monitores/monitores-ips/24ba750-b</t>
+        </is>
+      </c>
+      <c r="D67" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F67" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="295" t="inlineStr">
+        <is>
+          <t>24BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C68" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-monitor/24ba750</t>
+        </is>
+      </c>
+      <c r="D68" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F68" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="295" t="inlineStr">
+        <is>
+          <t>24BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="295" t="inlineStr">
+        <is>
+          <t>MX-es</t>
+        </is>
+      </c>
+      <c r="C69" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/mx/business/monitores-pcs/cloud-computing/thin-client/24ba750-b</t>
+        </is>
+      </c>
+      <c r="D69" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F69" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="295" t="inlineStr">
+        <is>
+          <t>24BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="295" t="inlineStr">
+        <is>
+          <t>NL-nl</t>
+        </is>
+      </c>
+      <c r="C70" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/business/computer-producten/monitoren/fhd-qhd/24ba750-b</t>
+        </is>
+      </c>
+      <c r="D70" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F70" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="295" t="inlineStr">
+        <is>
+          <t>24BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C71" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/24ba750-b</t>
+        </is>
+      </c>
+      <c r="D71" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F71" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="295" t="inlineStr">
+        <is>
+          <t>24BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="295" t="inlineStr">
+        <is>
+          <t>UK-en</t>
+        </is>
+      </c>
+      <c r="C72" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/business/monitors-pcs/monitors/lg-monitor/24ba750-b</t>
+        </is>
+      </c>
+      <c r="D72" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F72" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="295" t="inlineStr">
+        <is>
+          <t>24BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="295" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C73" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/business/24ba750-t-aeu</t>
+        </is>
+      </c>
+      <c r="D73" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F73" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="295" t="inlineStr">
+        <is>
+          <t>24BA750-T · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C74" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/24ba750-t</t>
+        </is>
+      </c>
+      <c r="D74" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F74" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="295" t="inlineStr">
+        <is>
+          <t>24BA750-T · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="295" t="inlineStr">
+        <is>
+          <t>BE-nl</t>
+        </is>
+      </c>
+      <c r="C75" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be/business/computer-producten/monitoren/fhd-qhd/24ba850-b</t>
+        </is>
+      </c>
+      <c r="D75" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F75" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="295" t="inlineStr">
+        <is>
+          <t>24BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="295" t="inlineStr">
+        <is>
+          <t>BE-fr</t>
+        </is>
+      </c>
+      <c r="C76" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be_fr/business/computer-producten/monitoren/fhd-qhd/24ba850-b</t>
+        </is>
+      </c>
+      <c r="D76" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F76" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="295" t="inlineStr">
+        <is>
+          <t>24BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="295" t="inlineStr">
+        <is>
+          <t>BR-pt</t>
+        </is>
+      </c>
+      <c r="C77" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/br/business/monitores/monitores-produtos/monitores-full-hd-qhd/24ba850-b</t>
+        </is>
+      </c>
+      <c r="D77" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F77" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="295" t="inlineStr">
+        <is>
+          <t>24BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="295" t="inlineStr">
+        <is>
+          <t>CA-en</t>
+        </is>
+      </c>
+      <c r="C78" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/monitors-pcs/monitors/lg-monitor/24ba850-b</t>
+        </is>
+      </c>
+      <c r="D78" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F78" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="295" t="inlineStr">
+        <is>
+          <t>24BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="295" t="inlineStr">
+        <is>
+          <t>CA-fr</t>
+        </is>
+      </c>
+      <c r="C79" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/business/moniteurs-et-pc/moniteurs/moniteur-lg/24ba850-b</t>
+        </is>
+      </c>
+      <c r="D79" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F79" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="295" t="inlineStr">
+        <is>
+          <t>24BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C80" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/business-monitore/24ba850-b</t>
+        </is>
+      </c>
+      <c r="D80" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F80" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="295" t="inlineStr">
+        <is>
+          <t>24BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C81" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/24ba850-b</t>
+        </is>
+      </c>
+      <c r="D81" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F81" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="295" t="inlineStr">
+        <is>
+          <t>24BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="295" t="inlineStr">
+        <is>
+          <t>ES-es</t>
+        </is>
+      </c>
+      <c r="C82" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/business/informatica/monitores/monitores-ips/24ba850-b</t>
+        </is>
+      </c>
+      <c r="D82" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F82" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="295" t="inlineStr">
+        <is>
+          <t>24BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="295" t="inlineStr">
+        <is>
+          <t>FR-fr</t>
+        </is>
+      </c>
+      <c r="C83" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/fr/business/moniteurs-pcs/moniteurs/lg-monitor/lg-24ba850-b-moniteur-bureautique</t>
+        </is>
+      </c>
+      <c r="D83" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F83" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="295" t="inlineStr">
+        <is>
+          <t>24BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C84" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-monitor/24ba850</t>
+        </is>
+      </c>
+      <c r="D84" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F84" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="295" t="inlineStr">
+        <is>
+          <t>24BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="295" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C85" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/business/24ba850-b</t>
+        </is>
+      </c>
+      <c r="D85" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F85" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="295" t="inlineStr">
+        <is>
+          <t>24BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="295" t="inlineStr">
+        <is>
+          <t>NL-nl</t>
+        </is>
+      </c>
+      <c r="C86" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/business/computer-producten/monitoren/fhd-qhd/24ba850-b</t>
+        </is>
+      </c>
+      <c r="D86" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F86" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="295" t="inlineStr">
+        <is>
+          <t>24BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C87" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/24ba850-b</t>
+        </is>
+      </c>
+      <c r="D87" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F87" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="295" t="inlineStr">
+        <is>
+          <t>24BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="295" t="inlineStr">
+        <is>
+          <t>UK-en</t>
+        </is>
+      </c>
+      <c r="C88" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/business/monitors-pcs/monitors/lg-monitor/24ba850-b</t>
+        </is>
+      </c>
+      <c r="D88" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F88" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="295" t="inlineStr">
+        <is>
+          <t>24BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C89" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/24ba850-t</t>
+        </is>
+      </c>
+      <c r="D89" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F89" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="295" t="inlineStr">
+        <is>
+          <t>24BA850-T · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" s="295" t="inlineStr">
+        <is>
+          <t>BR-pt</t>
+        </is>
+      </c>
+      <c r="C90" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/br/business/monitores/monitores-produtos/monitores-full-hd-qhd/24bl550j-b</t>
+        </is>
+      </c>
+      <c r="D90" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F90" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="295" t="inlineStr">
+        <is>
+          <t>24BL550J-B · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C91" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/business-monitore/24bp450s-b</t>
+        </is>
+      </c>
+      <c r="D91" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F91" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="295" t="inlineStr">
+        <is>
+          <t>24BP450S-B · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C92" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/24bp450y-b</t>
+        </is>
+      </c>
+      <c r="D92" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F92" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="295" t="inlineStr">
+        <is>
+          <t>24BP450Y-B · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C93" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/business-monitore/24bp45sp-b</t>
+        </is>
+      </c>
+      <c r="D93" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F93" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="295" t="inlineStr">
+        <is>
+          <t>24BP45SP-B · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="295" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C94" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/business/24bp45sp-b</t>
+        </is>
+      </c>
+      <c r="D94" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F94" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="295" t="inlineStr">
+        <is>
+          <t>24BP45SP-B · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C95" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/24br550y-c</t>
+        </is>
+      </c>
+      <c r="D95" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F95" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="295" t="inlineStr">
+        <is>
+          <t>24BR550Y-C · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="295" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C96" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/business/24br750c-c</t>
+        </is>
+      </c>
+      <c r="D96" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F96" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="295" t="inlineStr">
+        <is>
+          <t>24BR750C-C · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="295" t="inlineStr">
+        <is>
+          <t>CA-en</t>
+        </is>
+      </c>
+      <c r="C97" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/monitors-pcs/monitors/lg-monitor/27ba400-b</t>
+        </is>
+      </c>
+      <c r="D97" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F97" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="295" t="inlineStr">
+        <is>
+          <t>27BA400-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" s="295" t="inlineStr">
+        <is>
+          <t>CA-fr</t>
+        </is>
+      </c>
+      <c r="C98" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/business/moniteurs-et-pc/moniteurs/moniteur-lg/27ba400-b</t>
+        </is>
+      </c>
+      <c r="D98" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F98" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="295" t="inlineStr">
+        <is>
+          <t>27BA400-B · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C99" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/monitore/alle-monitore/business-monitore/27ba400-b</t>
+        </is>
+      </c>
+      <c r="D99" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F99" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="295" t="inlineStr">
+        <is>
+          <t>27BA400-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C100" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/27ba400-b</t>
+        </is>
+      </c>
+      <c r="D100" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F100" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="295" t="inlineStr">
+        <is>
+          <t>27BA400-B · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C101" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-monitor/27ba400</t>
+        </is>
+      </c>
+      <c r="D101" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F101" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="295" t="inlineStr">
+        <is>
+          <t>27BA400-B · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="295" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C102" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/business/27ba400-b</t>
+        </is>
+      </c>
+      <c r="D102" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F102" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="295" t="inlineStr">
+        <is>
+          <t>27BA400-B · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C103" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/27ba400-b</t>
+        </is>
+      </c>
+      <c r="D103" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F103" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="295" t="inlineStr">
+        <is>
+          <t>27BA400-B · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="295" t="inlineStr">
+        <is>
+          <t>BE-nl</t>
+        </is>
+      </c>
+      <c r="C104" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be/business/computer-producten/monitoren/fhd-qhd/27ba450-b</t>
+        </is>
+      </c>
+      <c r="D104" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F104" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="295" t="inlineStr">
+        <is>
+          <t>27BA450-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="295" t="inlineStr">
+        <is>
+          <t>BE-fr</t>
+        </is>
+      </c>
+      <c r="C105" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be_fr/business/computer-producten/monitoren/fhd-qhd/27ba450-b</t>
+        </is>
+      </c>
+      <c r="D105" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F105" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="295" t="inlineStr">
+        <is>
+          <t>27BA450-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C106" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/business-monitore/27ba450-b</t>
+        </is>
+      </c>
+      <c r="D106" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F106" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="295" t="inlineStr">
+        <is>
+          <t>27BA450-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C107" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/27ba450-b</t>
+        </is>
+      </c>
+      <c r="D107" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F107" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="295" t="inlineStr">
+        <is>
+          <t>27BA450-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C108" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-monitor/27ba450</t>
+        </is>
+      </c>
+      <c r="D108" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F108" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="295" t="inlineStr">
+        <is>
+          <t>27BA450-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="295" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C109" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/business/27ba450-b</t>
+        </is>
+      </c>
+      <c r="D109" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F109" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="295" t="inlineStr">
+        <is>
+          <t>27BA450-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="295" t="inlineStr">
+        <is>
+          <t>NL-nl</t>
+        </is>
+      </c>
+      <c r="C110" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/business/computer-producten/monitoren/fhd-qhd/27ba450-b</t>
+        </is>
+      </c>
+      <c r="D110" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F110" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="295" t="inlineStr">
+        <is>
+          <t>27BA450-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="295" t="inlineStr">
+        <is>
+          <t>UK-en</t>
+        </is>
+      </c>
+      <c r="C111" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/business/monitors-pcs/monitors/lg-monitor/27ba450-b</t>
+        </is>
+      </c>
+      <c r="D111" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F111" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="295" t="inlineStr">
+        <is>
+          <t>27BA450-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C112" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/4k-monitore/27ba45qb-b</t>
+        </is>
+      </c>
+      <c r="D112" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F112" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="295" t="inlineStr">
+        <is>
+          <t>27BA45QB-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C113" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/27ba45qb-b</t>
+        </is>
+      </c>
+      <c r="D113" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F113" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="295" t="inlineStr">
+        <is>
+          <t>27BA45QB-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C114" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-monitor/27ba45qb</t>
+        </is>
+      </c>
+      <c r="D114" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F114" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="295" t="inlineStr">
+        <is>
+          <t>27BA45QB-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="295" t="inlineStr">
+        <is>
+          <t>RU-ru</t>
+        </is>
+      </c>
+      <c r="C115" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ru/business/monitors/lg-27ba45qb-b</t>
+        </is>
+      </c>
+      <c r="D115" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F115" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="295" t="inlineStr">
+        <is>
+          <t>27BA45QB-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C116" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/27ba45qb-b</t>
+        </is>
+      </c>
+      <c r="D116" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F116" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="295" t="inlineStr">
+        <is>
+          <t>27BA45QB-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C117" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/monitore/alle-monitore/ultrawide-monitore/27ba54qb-b</t>
+        </is>
+      </c>
+      <c r="D117" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F117" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="295" t="inlineStr">
+        <is>
+          <t>27BA54QB-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C118" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/27ba54qb-b</t>
+        </is>
+      </c>
+      <c r="D118" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F118" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="295" t="inlineStr">
+        <is>
+          <t>27BA54QB-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C119" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-monitor/27ba54qb</t>
+        </is>
+      </c>
+      <c r="D119" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F119" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="295" t="inlineStr">
+        <is>
+          <t>27BA54QB-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="295" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C120" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/business/27ba54qb-b</t>
+        </is>
+      </c>
+      <c r="D120" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F120" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="295" t="inlineStr">
+        <is>
+          <t>27BA54QB-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C121" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/27ba54qb-b</t>
+        </is>
+      </c>
+      <c r="D121" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F121" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="295" t="inlineStr">
+        <is>
+          <t>27BA54QB-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C122" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/27ba54qb-t</t>
+        </is>
+      </c>
+      <c r="D122" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F122" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" s="295" t="inlineStr">
+        <is>
+          <t>27BA54QB-T · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C123" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/27ba54qb-t</t>
+        </is>
+      </c>
+      <c r="D123" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F123" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="295" t="inlineStr">
+        <is>
+          <t>27BA54QB-T · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="295" t="inlineStr">
+        <is>
+          <t>BE-nl</t>
+        </is>
+      </c>
+      <c r="C124" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be/business/computer-producten/monitoren/fhd-qhd/27ba550-b</t>
+        </is>
+      </c>
+      <c r="D124" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F124" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="295" t="inlineStr">
+        <is>
+          <t>27BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="295" t="inlineStr">
+        <is>
+          <t>BE-fr</t>
+        </is>
+      </c>
+      <c r="C125" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be_fr/business/computer-producten/monitoren/fhd-qhd/27ba550-b</t>
+        </is>
+      </c>
+      <c r="D125" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F125" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="295" t="inlineStr">
+        <is>
+          <t>27BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="295" t="inlineStr">
+        <is>
+          <t>CZ-cz</t>
+        </is>
+      </c>
+      <c r="C126" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/cz/business/byznys/komercni-monitory/27ba550-b</t>
+        </is>
+      </c>
+      <c r="D126" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F126" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="295" t="inlineStr">
+        <is>
+          <t>27BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C127" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/27ba550-b</t>
+        </is>
+      </c>
+      <c r="D127" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F127" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="295" t="inlineStr">
+        <is>
+          <t>27BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C128" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/27ba550-b</t>
+        </is>
+      </c>
+      <c r="D128" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F128" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" s="295" t="inlineStr">
+        <is>
+          <t>27BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C129" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-monitor/27ba550</t>
+        </is>
+      </c>
+      <c r="D129" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F129" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="295" t="inlineStr">
+        <is>
+          <t>27BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="295" t="inlineStr">
+        <is>
+          <t>IL-he</t>
+        </is>
+      </c>
+      <c r="C130" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/business/b2b/lg-27ba550-b</t>
+        </is>
+      </c>
+      <c r="D130" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F130" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" s="295" t="inlineStr">
+        <is>
+          <t>27BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="295" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C131" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/business/27ba550-b</t>
+        </is>
+      </c>
+      <c r="D131" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F131" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" s="295" t="inlineStr">
+        <is>
+          <t>27BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="295" t="inlineStr">
+        <is>
+          <t>NL-nl</t>
+        </is>
+      </c>
+      <c r="C132" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/business/computer-producten/monitoren/fhd-qhd/27ba550-b</t>
+        </is>
+      </c>
+      <c r="D132" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F132" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="295" t="inlineStr">
+        <is>
+          <t>27BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C133" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/27ba550-b</t>
+        </is>
+      </c>
+      <c r="D133" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F133" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="295" t="inlineStr">
+        <is>
+          <t>27BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="295" t="inlineStr">
+        <is>
+          <t>UK-en</t>
+        </is>
+      </c>
+      <c r="C134" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/business/monitors-pcs/monitors/lg-monitor/27ba550-b</t>
+        </is>
+      </c>
+      <c r="D134" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F134" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="295" t="inlineStr">
+        <is>
+          <t>27BA550-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="295" t="inlineStr">
+        <is>
+          <t>BE-nl</t>
+        </is>
+      </c>
+      <c r="C135" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be/business/computer-producten/monitoren/fhd-qhd/27ba560-b</t>
+        </is>
+      </c>
+      <c r="D135" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F135" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" s="295" t="inlineStr">
+        <is>
+          <t>27BA560-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="295" t="inlineStr">
+        <is>
+          <t>BE-fr</t>
+        </is>
+      </c>
+      <c r="C136" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be_fr/business/computer-producten/monitoren/fhd-qhd/27ba560-b</t>
+        </is>
+      </c>
+      <c r="D136" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F136" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="295" t="inlineStr">
+        <is>
+          <t>27BA560-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" s="295" t="inlineStr">
+        <is>
+          <t>CA-en</t>
+        </is>
+      </c>
+      <c r="C137" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/monitors-pcs/monitors/lg-monitor/27ba560-b</t>
+        </is>
+      </c>
+      <c r="D137" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F137" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="295" t="inlineStr">
+        <is>
+          <t>27BA560-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="295" t="inlineStr">
+        <is>
+          <t>CA-fr</t>
+        </is>
+      </c>
+      <c r="C138" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/business/moniteurs-et-pc/moniteurs/moniteur-lg/27ba560-b</t>
+        </is>
+      </c>
+      <c r="D138" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F138" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="295" t="inlineStr">
+        <is>
+          <t>27BA560-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C139" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/27ba560-b</t>
+        </is>
+      </c>
+      <c r="D139" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F139" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" s="295" t="inlineStr">
+        <is>
+          <t>27BA560-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C140" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/27ba560-b</t>
+        </is>
+      </c>
+      <c r="D140" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F140" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="295" t="inlineStr">
+        <is>
+          <t>27BA560-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C141" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-monitor/27ba560</t>
+        </is>
+      </c>
+      <c r="D141" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F141" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" s="295" t="inlineStr">
+        <is>
+          <t>27BA560-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" s="295" t="inlineStr">
+        <is>
+          <t>NL-nl</t>
+        </is>
+      </c>
+      <c r="C142" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/business/computer-producten/monitoren/fhd-qhd/27ba560-b</t>
+        </is>
+      </c>
+      <c r="D142" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F142" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="295" t="inlineStr">
+        <is>
+          <t>27BA560-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C143" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/27ba560-b</t>
+        </is>
+      </c>
+      <c r="D143" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F143" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="295" t="inlineStr">
+        <is>
+          <t>27BA560-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" s="295" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C144" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/business/27ba560-t</t>
+        </is>
+      </c>
+      <c r="D144" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F144" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" s="295" t="inlineStr">
+        <is>
+          <t>27BA560-T · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C145" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/27ba560-t</t>
+        </is>
+      </c>
+      <c r="D145" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F145" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="295" t="inlineStr">
+        <is>
+          <t>27BA560-T · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" s="295" t="inlineStr">
+        <is>
+          <t>AE-en</t>
+        </is>
+      </c>
+      <c r="C146" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae/business/monitors/lg-27ba650-b</t>
+        </is>
+      </c>
+      <c r="D146" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F146" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" s="295" t="inlineStr">
+        <is>
+          <t>27BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" s="295" t="inlineStr">
+        <is>
+          <t>AE-ar</t>
+        </is>
+      </c>
+      <c r="C147" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae_ar/business/monitors/lg-27ba650-b</t>
+        </is>
+      </c>
+      <c r="D147" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F147" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="295" t="inlineStr">
+        <is>
+          <t>27BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" s="295" t="inlineStr">
+        <is>
+          <t>BE-nl</t>
+        </is>
+      </c>
+      <c r="C148" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be/business/computer-producten/monitoren/fhd-qhd/27ba650-b</t>
+        </is>
+      </c>
+      <c r="D148" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F148" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="295" t="inlineStr">
+        <is>
+          <t>27BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" s="295" t="inlineStr">
+        <is>
+          <t>BE-fr</t>
+        </is>
+      </c>
+      <c r="C149" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be_fr/business/computer-producten/monitoren/fhd-qhd/27ba650-b</t>
+        </is>
+      </c>
+      <c r="D149" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F149" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" s="295" t="inlineStr">
+        <is>
+          <t>27BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" s="295" t="inlineStr">
+        <is>
+          <t>CA-en</t>
+        </is>
+      </c>
+      <c r="C150" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/monitors-pcs/monitors/lg-monitor/27ba650-b</t>
+        </is>
+      </c>
+      <c r="D150" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F150" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="295" t="inlineStr">
+        <is>
+          <t>27BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C151" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/27ba650-b</t>
+        </is>
+      </c>
+      <c r="D151" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F151" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="295" t="inlineStr">
+        <is>
+          <t>27BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" s="295" t="inlineStr">
+        <is>
+          <t>ES-es</t>
+        </is>
+      </c>
+      <c r="C152" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/business/informatica/monitores/monitores-ips/27ba650-b</t>
+        </is>
+      </c>
+      <c r="D152" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F152" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" s="295" t="inlineStr">
+        <is>
+          <t>27BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C153" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-monitor/27ba650</t>
+        </is>
+      </c>
+      <c r="D153" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F153" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" s="295" t="inlineStr">
+        <is>
+          <t>27BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="295" t="inlineStr">
+        <is>
+          <t>IL-he</t>
+        </is>
+      </c>
+      <c r="C154" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/il/business/ultrafine-uhd-monitors/lg-27ba650-b</t>
+        </is>
+      </c>
+      <c r="D154" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F154" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" s="295" t="inlineStr">
+        <is>
+          <t>27BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" s="295" t="inlineStr">
+        <is>
+          <t>NL-nl</t>
+        </is>
+      </c>
+      <c r="C155" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/business/computer-producten/monitoren/fhd-qhd/27ba650-b</t>
+        </is>
+      </c>
+      <c r="D155" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F155" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="295" t="inlineStr">
+        <is>
+          <t>27BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C156" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/27ba650-b</t>
+        </is>
+      </c>
+      <c r="D156" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F156" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" s="295" t="inlineStr">
+        <is>
+          <t>27BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" s="295" t="inlineStr">
+        <is>
+          <t>UK-en</t>
+        </is>
+      </c>
+      <c r="C157" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/business/monitors-pcs/monitors/lg-monitor/27ba650-b</t>
+        </is>
+      </c>
+      <c r="D157" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F157" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" s="295" t="inlineStr">
+        <is>
+          <t>27BA650-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" s="295" t="inlineStr">
+        <is>
+          <t>BE-nl</t>
+        </is>
+      </c>
+      <c r="C158" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be/business/computer-producten/monitoren/fhd-qhd/27ba65qb-b</t>
+        </is>
+      </c>
+      <c r="D158" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F158" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" s="295" t="inlineStr">
+        <is>
+          <t>27BA65QB-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" s="295" t="inlineStr">
+        <is>
+          <t>BE-fr</t>
+        </is>
+      </c>
+      <c r="C159" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be_fr/business/computer-producten/monitoren/fhd-qhd/27ba65qb-b</t>
+        </is>
+      </c>
+      <c r="D159" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F159" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" s="295" t="inlineStr">
+        <is>
+          <t>27BA65QB-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C160" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/monitore/alle-monitore/business-monitore/27ba65qb-b</t>
+        </is>
+      </c>
+      <c r="D160" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F160" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" s="295" t="inlineStr">
+        <is>
+          <t>27BA65QB-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C161" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/27ba65qb-b</t>
+        </is>
+      </c>
+      <c r="D161" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F161" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" s="295" t="inlineStr">
+        <is>
+          <t>27BA65QB-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C162" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-monitor/27ba65qb</t>
+        </is>
+      </c>
+      <c r="D162" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F162" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G162" s="295" t="inlineStr">
+        <is>
+          <t>27BA65QB-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" s="295" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C163" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/business/27ba65qb-b</t>
+        </is>
+      </c>
+      <c r="D163" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F163" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" s="295" t="inlineStr">
+        <is>
+          <t>27BA65QB-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" s="295" t="inlineStr">
+        <is>
+          <t>NL-nl</t>
+        </is>
+      </c>
+      <c r="C164" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/business/computer-producten/monitoren/fhd-qhd/27ba65qb-b</t>
+        </is>
+      </c>
+      <c r="D164" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F164" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" s="295" t="inlineStr">
+        <is>
+          <t>27BA65QB-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" s="295" t="inlineStr">
+        <is>
+          <t>RU-ru</t>
+        </is>
+      </c>
+      <c r="C165" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ru/business/monitors/lg-27ba65qb-b</t>
+        </is>
+      </c>
+      <c r="D165" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F165" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" s="295" t="inlineStr">
+        <is>
+          <t>27BA65QB-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C166" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/27ba65qb-t</t>
+        </is>
+      </c>
+      <c r="D166" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F166" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" s="295" t="inlineStr">
+        <is>
+          <t>27BA65QB-T · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C167" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/27ba65qb-t</t>
+        </is>
+      </c>
+      <c r="D167" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F167" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G167" s="295" t="inlineStr">
+        <is>
+          <t>27BA65QB-T · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" s="295" t="inlineStr">
+        <is>
+          <t>BE-nl</t>
+        </is>
+      </c>
+      <c r="C168" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be/business/computer-producten/monitoren/fhd-qhd/27ba750-b</t>
+        </is>
+      </c>
+      <c r="D168" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F168" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G168" s="295" t="inlineStr">
+        <is>
+          <t>27BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" s="295" t="inlineStr">
+        <is>
+          <t>BE-fr</t>
+        </is>
+      </c>
+      <c r="C169" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be_fr/business/computer-producten/monitoren/fhd-qhd/27ba750-b</t>
+        </is>
+      </c>
+      <c r="D169" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F169" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G169" s="295" t="inlineStr">
+        <is>
+          <t>27BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" s="295" t="inlineStr">
+        <is>
+          <t>CA-en</t>
+        </is>
+      </c>
+      <c r="C170" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/monitors-pcs/monitors/lg-monitor/27ba750-b</t>
+        </is>
+      </c>
+      <c r="D170" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F170" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" s="295" t="inlineStr">
+        <is>
+          <t>27BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" s="295" t="inlineStr">
+        <is>
+          <t>CA-fr</t>
+        </is>
+      </c>
+      <c r="C171" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/business/moniteurs-et-pc/moniteurs/moniteur-lg/27ba750-b</t>
+        </is>
+      </c>
+      <c r="D171" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F171" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" s="295" t="inlineStr">
+        <is>
+          <t>27BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C172" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/business-monitore/27ba750-b</t>
+        </is>
+      </c>
+      <c r="D172" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F172" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" s="295" t="inlineStr">
+        <is>
+          <t>27BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C173" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/27ba750-b</t>
+        </is>
+      </c>
+      <c r="D173" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F173" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G173" s="295" t="inlineStr">
+        <is>
+          <t>27BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" s="295" t="inlineStr">
+        <is>
+          <t>ES-es</t>
+        </is>
+      </c>
+      <c r="C174" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/business/informatica/monitores/monitores-ips/27ba750-b</t>
+        </is>
+      </c>
+      <c r="D174" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F174" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" s="295" t="inlineStr">
+        <is>
+          <t>27BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C175" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-monitor/27ba750</t>
+        </is>
+      </c>
+      <c r="D175" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F175" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" s="295" t="inlineStr">
+        <is>
+          <t>27BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" s="295" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C176" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/business/27ba750-b-aeu</t>
+        </is>
+      </c>
+      <c r="D176" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F176" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" s="295" t="inlineStr">
+        <is>
+          <t>27BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" s="295" t="inlineStr">
+        <is>
+          <t>NL-nl</t>
+        </is>
+      </c>
+      <c r="C177" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/business/computer-producten/monitoren/fhd-qhd/27ba750-b</t>
+        </is>
+      </c>
+      <c r="D177" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F177" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" s="295" t="inlineStr">
+        <is>
+          <t>27BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C178" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/27ba750-b</t>
+        </is>
+      </c>
+      <c r="D178" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F178" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" s="295" t="inlineStr">
+        <is>
+          <t>27BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" s="295" t="inlineStr">
+        <is>
+          <t>UK-en</t>
+        </is>
+      </c>
+      <c r="C179" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/business/monitors-pcs/monitors/lg-monitor/27ba750-b</t>
+        </is>
+      </c>
+      <c r="D179" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F179" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" s="295" t="inlineStr">
+        <is>
+          <t>27BA750-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" s="295" t="inlineStr">
+        <is>
+          <t>CA-en</t>
+        </is>
+      </c>
+      <c r="C180" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/monitors-pcs/monitors/lg-monitor/27ba75qb-b</t>
+        </is>
+      </c>
+      <c r="D180" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F180" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G180" s="295" t="inlineStr">
+        <is>
+          <t>27BA75QB-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" s="295" t="inlineStr">
+        <is>
+          <t>CA-fr</t>
+        </is>
+      </c>
+      <c r="C181" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/business/moniteurs-et-pc/moniteurs/moniteur-lg/27ba75qb-b</t>
+        </is>
+      </c>
+      <c r="D181" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F181" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G181" s="295" t="inlineStr">
+        <is>
+          <t>27BA75QB-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C182" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/monitore/alle-monitore/business-monitore/27ba75qb-b</t>
+        </is>
+      </c>
+      <c r="D182" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F182" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" s="295" t="inlineStr">
+        <is>
+          <t>27BA75QB-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C183" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/27ba75qb-b</t>
+        </is>
+      </c>
+      <c r="D183" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F183" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" s="295" t="inlineStr">
+        <is>
+          <t>27BA75QB-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" s="295" t="inlineStr">
+        <is>
+          <t>ES-es</t>
+        </is>
+      </c>
+      <c r="C184" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/business/informatica/monitores/monitores-ips/27ba75qb-b</t>
+        </is>
+      </c>
+      <c r="D184" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F184" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" s="295" t="inlineStr">
+        <is>
+          <t>27BA75QB-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C185" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-monitor/27ba75qb</t>
+        </is>
+      </c>
+      <c r="D185" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F185" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G185" s="295" t="inlineStr">
+        <is>
+          <t>27BA75QB-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" s="295" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C186" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/business/27ba75qb-b</t>
+        </is>
+      </c>
+      <c r="D186" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F186" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G186" s="295" t="inlineStr">
+        <is>
+          <t>27BA75QB-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C187" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/27ba75qb-b</t>
+        </is>
+      </c>
+      <c r="D187" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F187" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G187" s="295" t="inlineStr">
+        <is>
+          <t>27BA75QB-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" s="295" t="inlineStr">
+        <is>
+          <t>SG-en</t>
+        </is>
+      </c>
+      <c r="C188" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/business/it-products/commercial-monitors/fhd-qhd/27ba75qb-b</t>
+        </is>
+      </c>
+      <c r="D188" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F188" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" s="295" t="inlineStr">
+        <is>
+          <t>27BA75QB-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C189" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/27ba75qb-t</t>
+        </is>
+      </c>
+      <c r="D189" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F189" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" s="295" t="inlineStr">
+        <is>
+          <t>27BA75QB-T · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C190" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/27ba75qb-t</t>
+        </is>
+      </c>
+      <c r="D190" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F190" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" s="295" t="inlineStr">
+        <is>
+          <t>27BA75QB-T · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" s="295" t="inlineStr">
+        <is>
+          <t>AE-en</t>
+        </is>
+      </c>
+      <c r="C191" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ae/business/monitors/lg-27ba850-b</t>
+        </is>
+      </c>
+      <c r="D191" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F191" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" s="295" t="inlineStr">
+        <is>
+          <t>27BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" s="295" t="inlineStr">
+        <is>
+          <t>BE-nl</t>
+        </is>
+      </c>
+      <c r="C192" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be/business/computer-producten/monitoren/fhd-qhd/27ba850-b</t>
+        </is>
+      </c>
+      <c r="D192" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F192" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" s="295" t="inlineStr">
+        <is>
+          <t>27BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" s="295" t="inlineStr">
+        <is>
+          <t>BE-fr</t>
+        </is>
+      </c>
+      <c r="C193" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be_fr/business/computer-producten/monitoren/fhd-qhd/27ba850-b</t>
+        </is>
+      </c>
+      <c r="D193" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F193" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" s="295" t="inlineStr">
+        <is>
+          <t>27BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" s="295" t="inlineStr">
+        <is>
+          <t>CA-en</t>
+        </is>
+      </c>
+      <c r="C194" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/monitors-pcs/monitors/lg-monitor/27ba850-b</t>
+        </is>
+      </c>
+      <c r="D194" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F194" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" s="295" t="inlineStr">
+        <is>
+          <t>27BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" s="295" t="inlineStr">
+        <is>
+          <t>CA-fr</t>
+        </is>
+      </c>
+      <c r="C195" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/business/moniteurs-et-pc/moniteurs/moniteur-lg/27ba850-b</t>
+        </is>
+      </c>
+      <c r="D195" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F195" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" s="295" t="inlineStr">
+        <is>
+          <t>27BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C196" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/monitore/alle-monitore/business-monitore/27ba850-b</t>
+        </is>
+      </c>
+      <c r="D196" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F196" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" s="295" t="inlineStr">
+        <is>
+          <t>27BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C197" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/27ba850-b</t>
+        </is>
+      </c>
+      <c r="D197" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F197" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" s="295" t="inlineStr">
+        <is>
+          <t>27BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" s="295" t="inlineStr">
+        <is>
+          <t>ES-es</t>
+        </is>
+      </c>
+      <c r="C198" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/business/informatica/monitores/monitores-ips/27ba850-b</t>
+        </is>
+      </c>
+      <c r="D198" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F198" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" s="295" t="inlineStr">
+        <is>
+          <t>27BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C199" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-monitor/27ba850</t>
+        </is>
+      </c>
+      <c r="D199" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F199" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" s="295" t="inlineStr">
+        <is>
+          <t>27BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" s="295" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C200" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/business/27ba850-b</t>
+        </is>
+      </c>
+      <c r="D200" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F200" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" s="295" t="inlineStr">
+        <is>
+          <t>27BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" s="295" t="inlineStr">
+        <is>
+          <t>NL-nl</t>
+        </is>
+      </c>
+      <c r="C201" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/business/computer-producten/monitoren/fhd-qhd/27ba850-b</t>
+        </is>
+      </c>
+      <c r="D201" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F201" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" s="295" t="inlineStr">
+        <is>
+          <t>27BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C202" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/27ba850-b</t>
+        </is>
+      </c>
+      <c r="D202" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F202" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" s="295" t="inlineStr">
+        <is>
+          <t>27BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" s="295" t="inlineStr">
+        <is>
+          <t>UK-en</t>
+        </is>
+      </c>
+      <c r="C203" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/business/monitors-pcs/monitors/lg-monitor/27ba850-b</t>
+        </is>
+      </c>
+      <c r="D203" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F203" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" s="295" t="inlineStr">
+        <is>
+          <t>27BA850-B · TCO 배지·면책·스펙, PCF 배지 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C204" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/27bp450y-b</t>
+        </is>
+      </c>
+      <c r="D204" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F204" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" s="295" t="inlineStr">
+        <is>
+          <t>27BP450Y-B · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C205" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/4k-monitore/32bn67u-b</t>
+        </is>
+      </c>
+      <c r="D205" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F205" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" s="295" t="inlineStr">
+        <is>
+          <t>32BN67U-B · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C206" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/4k-monitore/32bn67u-w</t>
+        </is>
+      </c>
+      <c r="D206" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F206" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" s="295" t="inlineStr">
+        <is>
+          <t>32BN67U-W · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" s="295" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C207" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/business/32bn67up-b</t>
+        </is>
+      </c>
+      <c r="D207" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F207" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" s="295" t="inlineStr">
+        <is>
+          <t>32BN67UP-B · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C208" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/4k-monitore/32bn67up-w</t>
+        </is>
+      </c>
+      <c r="D208" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F208" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" s="295" t="inlineStr">
+        <is>
+          <t>32BN67UP-W · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" s="295" t="inlineStr">
+        <is>
+          <t>BE-nl</t>
+        </is>
+      </c>
+      <c r="C209" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be/business/computer-producten/monitoren/ultrawide/34ba75qe-b</t>
+        </is>
+      </c>
+      <c r="D209" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F209" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G209" s="295" t="inlineStr">
+        <is>
+          <t>34BA75QE-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" s="295" t="inlineStr">
+        <is>
+          <t>BE-fr</t>
+        </is>
+      </c>
+      <c r="C210" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/be_fr/business/computer-producten/monitoren/ultrawide/34ba75qe-b</t>
+        </is>
+      </c>
+      <c r="D210" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F210" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G210" s="295" t="inlineStr">
+        <is>
+          <t>34BA75QE-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" s="295" t="inlineStr">
+        <is>
+          <t>CA-en</t>
+        </is>
+      </c>
+      <c r="C211" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/monitors-pcs/monitors/lg-ultrawide/34ba75qe-b</t>
+        </is>
+      </c>
+      <c r="D211" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F211" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G211" s="295" t="inlineStr">
+        <is>
+          <t>34BA75QE-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" s="295" t="inlineStr">
+        <is>
+          <t>CA-fr</t>
+        </is>
+      </c>
+      <c r="C212" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/business/moniteurs-et-pc/moniteurs/lg-ultrawide/34ba75qe-b</t>
+        </is>
+      </c>
+      <c r="D212" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F212" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" s="295" t="inlineStr">
+        <is>
+          <t>34BA75QE-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C213" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/ultrawide-monitore/34ba75qe-b_aeu</t>
+        </is>
+      </c>
+      <c r="D213" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F213" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" s="295" t="inlineStr">
+        <is>
+          <t>34BA75QE-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C214" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/34ba75qe-b</t>
+        </is>
+      </c>
+      <c r="D214" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F214" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" s="295" t="inlineStr">
+        <is>
+          <t>34BA75QE-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" s="295" t="inlineStr">
+        <is>
+          <t>ES-es</t>
+        </is>
+      </c>
+      <c r="C215" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/business/informatica/monitores/monitores-ultrawide/34ba75qe-b</t>
+        </is>
+      </c>
+      <c r="D215" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F215" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" s="295" t="inlineStr">
+        <is>
+          <t>34BA75QE-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="B216" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C216" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-ultrawide/34ba75qe</t>
+        </is>
+      </c>
+      <c r="D216" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F216" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G216" s="295" t="inlineStr">
+        <is>
+          <t>34BA75QE-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="B217" s="295" t="inlineStr">
+        <is>
+          <t>MX-es</t>
+        </is>
+      </c>
+      <c r="C217" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/mx/business/monitores-pcs/cloud-computing/thin-client/34ba75qe-b</t>
+        </is>
+      </c>
+      <c r="D217" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F217" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G217" s="295" t="inlineStr">
+        <is>
+          <t>34BA75QE-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="B218" s="295" t="inlineStr">
+        <is>
+          <t>NL-nl</t>
+        </is>
+      </c>
+      <c r="C218" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/nl/business/computer-producten/monitoren/ultrawide/34ba75qe-b</t>
+        </is>
+      </c>
+      <c r="D218" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F218" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G218" s="295" t="inlineStr">
+        <is>
+          <t>34BA75QE-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="B219" s="295" t="inlineStr">
+        <is>
+          <t>SE-sv</t>
+        </is>
+      </c>
+      <c r="C219" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/se/foretagsskarmar/alla-foretagsskarmar/34ba75qe-b</t>
+        </is>
+      </c>
+      <c r="D219" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F219" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G219" s="295" t="inlineStr">
+        <is>
+          <t>34BA75QE-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220" s="295" t="inlineStr">
+        <is>
+          <t>UK-en</t>
+        </is>
+      </c>
+      <c r="C220" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/uk/business/monitors-pcs/monitors/lg-ultrawide/34ba75qe-b</t>
+        </is>
+      </c>
+      <c r="D220" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F220" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G220" s="295" t="inlineStr">
+        <is>
+          <t>34BA75QE-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="B221" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C221" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/ultrawide-monitore/34ba85qe-b</t>
+        </is>
+      </c>
+      <c r="D221" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F221" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G221" s="295" t="inlineStr">
+        <is>
+          <t>34BA85QE-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="B222" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C222" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/34ba85qe-b</t>
+        </is>
+      </c>
+      <c r="D222" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F222" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G222" s="295" t="inlineStr">
+        <is>
+          <t>34BA85QE-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="B223" s="295" t="inlineStr">
+        <is>
+          <t>ES-es</t>
+        </is>
+      </c>
+      <c r="C223" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/business/informatica/monitores/monitores-ultrawide/34ba85qe-b</t>
+        </is>
+      </c>
+      <c r="D223" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F223" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G223" s="295" t="inlineStr">
+        <is>
+          <t>34BA85QE-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="B224" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C224" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-ultrawide/34ba85qe</t>
+        </is>
+      </c>
+      <c r="D224" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F224" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G224" s="295" t="inlineStr">
+        <is>
+          <t>34BA85QE-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="B225" s="295" t="inlineStr">
+        <is>
+          <t>IT-it</t>
+        </is>
+      </c>
+      <c r="C225" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/it/monitor/business/34ba85qe-b</t>
+        </is>
+      </c>
+      <c r="D225" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F225" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G225" s="295" t="inlineStr">
+        <is>
+          <t>34BA85QE-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="B226" s="295" t="inlineStr">
+        <is>
+          <t>SG-en</t>
+        </is>
+      </c>
+      <c r="C226" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/sg/business/it-products/commercial-monitors/ultrawide/34ba85qe-b</t>
+        </is>
+      </c>
+      <c r="D226" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F226" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G226" s="295" t="inlineStr">
+        <is>
+          <t>34BA85QE-B · TCO 배지·면책·스펙 삭제</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="B227" s="295" t="inlineStr">
+        <is>
+          <t>CA-en</t>
+        </is>
+      </c>
+      <c r="C227" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_en/business/monitors-pcs/monitors/lg-ultrawide/38br85qc-w</t>
+        </is>
+      </c>
+      <c r="D227" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F227" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G227" s="295" t="inlineStr">
+        <is>
+          <t>38BR85QC-W · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="B228" s="295" t="inlineStr">
+        <is>
+          <t>CA-fr</t>
+        </is>
+      </c>
+      <c r="C228" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/ca_fr/business/moniteurs-et-pc/moniteurs/lg-ultrawide/38br85qc-w</t>
+        </is>
+      </c>
+      <c r="D228" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F228" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G228" s="295" t="inlineStr">
+        <is>
+          <t>38BR85QC-W · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="B229" s="295" t="inlineStr">
+        <is>
+          <t>DE-de</t>
+        </is>
+      </c>
+      <c r="C229" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/de/business/alle-monitore/ultrawide-monitore/38br85qc-w</t>
+        </is>
+      </c>
+      <c r="D229" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F229" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G229" s="295" t="inlineStr">
+        <is>
+          <t>38BR85QC-W · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="B230" s="295" t="inlineStr">
+        <is>
+          <t>DK-da</t>
+        </is>
+      </c>
+      <c r="C230" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/dk/virksomhedsskaerme/alle-virksomhedsskaerme/38br85qc-w</t>
+        </is>
+      </c>
+      <c r="D230" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F230" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G230" s="295" t="inlineStr">
+        <is>
+          <t>38BR85QC-W · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="B231" s="295" t="inlineStr">
+        <is>
+          <t>ES-es</t>
+        </is>
+      </c>
+      <c r="C231" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/es/business/informatica/monitores/monitores-ultrawide/38br85qc-w</t>
+        </is>
+      </c>
+      <c r="D231" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F231" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G231" s="295" t="inlineStr">
+        <is>
+          <t>38BR85QC-W · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="B232" s="295" t="inlineStr">
+        <is>
+          <t>GLOBAL</t>
+        </is>
+      </c>
+      <c r="C232" s="290" t="inlineStr">
+        <is>
+          <t>https://www.lg.com/global/business/monitors-pcs/monitors/lg-ultrawide/38br85qc</t>
+        </is>
+      </c>
+      <c r="D232" s="295" t="inlineStr">
+        <is>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="F232" s="295" t="n">
+        <v>1</v>
+      </c>
+      <c r="G232" s="295" t="inlineStr">
+        <is>
+          <t>38BR85QC-W · TCO·PCF 삭제 표기 없음</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:G232"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C53" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C54" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C56" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C58" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C67" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C68" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C69" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C70" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C71" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C72" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C73" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C74" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C75" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C76" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C77" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C78" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C79" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C80" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C81" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C82" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C83" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C84" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C85" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C86" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C87" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C88" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C89" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C90" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C91" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C92" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C93" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C94" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C95" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C96" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C97" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C100" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C101" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C102" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C103" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C104" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C105" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C106" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C107" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C108" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C109" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C110" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C111" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C112" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C113" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C114" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C115" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C116" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C117" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C118" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C119" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C120" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C121" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C122" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C123" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C124" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C125" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C126" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C127" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C128" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C129" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C130" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C131" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C132" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C133" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C134" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C135" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C136" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C137" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C138" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C139" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C140" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C141" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C142" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C143" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C144" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C145" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C146" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C147" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C148" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C149" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C150" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C151" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C152" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C153" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C154" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C155" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C156" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C157" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C158" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C159" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C160" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C161" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C162" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C163" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C164" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C165" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C166" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C167" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C168" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C169" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C170" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C171" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C172" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C173" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C174" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C175" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C176" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C177" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C178" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C179" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C180" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C181" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C182" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C183" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C184" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C185" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C186" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C187" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C188" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C189" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C190" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C191" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C192" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C193" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C194" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C195" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C196" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C197" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C198" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C199" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C200" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C201" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C202" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C203" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C204" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C205" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C206" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C207" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C208" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C209" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C210" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C211" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C212" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C213" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C214" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C215" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C216" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C217" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C218" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C219" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C220" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C221" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C222" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C223" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C224" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C225" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C226" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C227" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C228" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C229" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C230" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C231" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C232" r:id="rId229"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -40546,7 +40546,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>10/14 기준 · 사전검토 59 · 법인리뷰 5(UK·EE·LT·LV·CA-fr) · 완료 1(CA-en) · 15개국 추가</t>
+          <t>10/15 기준 · 사전검토 59 · 법인리뷰 5(UK·EE·LT·LV·CA-fr) · 완료 1(CA-en) · 15개국 추가</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -40934,7 +40934,7 @@
       </c>
       <c r="G22" s="0" t="inlineStr">
         <is>
-          <t>페이지 없음</t>
+          <t>페이지 없음 · 접수됨, 착수 전</t>
         </is>
       </c>
     </row>
@@ -40980,7 +40980,11 @@
       <c r="F24" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="0" t="n"/>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>접수됨, 착수 전</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="261" t="inlineStr">
@@ -41368,7 +41372,7 @@
       </c>
       <c r="G41" s="0" t="inlineStr">
         <is>
-          <t>페이지 없음</t>
+          <t>페이지 없음 · 접수됨, 착수 전</t>
         </is>
       </c>
     </row>
@@ -41460,7 +41464,7 @@
       </c>
       <c r="G45" s="0" t="inlineStr">
         <is>
-          <t>페이지 없음</t>
+          <t>페이지 없음 · 접수됨, 착수 전</t>
         </is>
       </c>
     </row>
@@ -41852,7 +41856,11 @@
       <c r="F62" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G62" s="0" t="n"/>
+      <c r="G62" s="0" t="inlineStr">
+        <is>
+          <t>접수됨, 착수 전</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="B63" s="261" t="inlineStr">
@@ -41872,7 +41880,7 @@
       </c>
       <c r="G63" s="0" t="inlineStr">
         <is>
-          <t>페이지 없음</t>
+          <t>페이지 없음 · 접수됨, 착수 전</t>
         </is>
       </c>
     </row>
@@ -41896,7 +41904,11 @@
       <c r="F64" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G64" s="0" t="n"/>
+      <c r="G64" s="0" t="inlineStr">
+        <is>
+          <t>접수됨, 착수 전</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="B65" s="261" t="inlineStr">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -42689,7 +42689,7 @@
       </c>
       <c r="B2" s="295" t="inlineStr">
         <is>
-          <t>10/14 등록 · 요청자 Suan Kim · Due 2026-10-30 · 23개국 · 229 PDP · 40모델 · 사전검토</t>
+          <t>10/14 등록 · 담당 김수안 선임 · Due 2026-10-30 · 23개국 · 229 PDP · 40모델 · 사전검토</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -1,35 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="W16 - CineBeam S PDP Video Upda" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="W16 - Copilot+ Filter Creation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="W16 - Microsoft PDP Gallery Car" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="W17 - GNB Structure" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="W18 - FAQ Request (UltraGear PL" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="W18 - UltraGear OLED FAQ Update" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="W22 - UltraGear Buying Guide" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="W23 - 27GM950B-B 갤러리 이미지 교체" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="W23 - 39GX950B 이미지 수정 2차" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="W23 - 52G930B Feature 수정 건" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="W23 - UL인증 feature 삭제 1차" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="W25 - Copilot+ Hero Banner" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="W28 - AI Upscaling Disclaimer" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="W28 - UL Verified Eye Comfort" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="W30 - SmartMonitor ScreenShare" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="W30 - UltraGear 1000Hz FAQ" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="W31 - gram Secure Lock" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="W31 - PDP Gallery Win11 Pro" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="W31 - Smart Monitor Multi AI" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="W32 - UltraGear 27GX704A" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="W32 - Digital Trends Award 삭제" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="W32 - UltraGear PDP 5모델" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="W32 - UltraFine PDP MIC 삭제" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="W38 - gram pro gallery" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="W41 - UltraGear Buying Guide 2차" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="W41 - Windows 11 Landing" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="W41 - IT B2B TCO Mark" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W16 - CineBeam S PDP Video Upda" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W16 - Copilot+ Filter Creation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W16 - Microsoft PDP Gallery Car" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W17 - GNB Structure" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W18 - FAQ Request (UltraGear PL" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W18 - UltraGear OLED FAQ Update" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W22 - UltraGear Buying Guide" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - 27GM950B-B 갤러리 이미지 교체" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - 39GX950B 이미지 수정 2차" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - 52G930B Feature 수정 건" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - UL인증 feature 삭제 1차" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W25 - Copilot+ Hero Banner" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W28 - AI Upscaling Disclaimer" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W28 - UL Verified Eye Comfort" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W30 - SmartMonitor ScreenShare" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W30 - UltraGear 1000Hz FAQ" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W31 - gram Secure Lock" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W31 - PDP Gallery Win11 Pro" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W31 - Smart Monitor Multi AI" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - UltraGear 27GX704A" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - Digital Trends Award 삭제" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - UltraGear PDP 5모델" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - UltraFine PDP MIC 삭제" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W38 - gram pro gallery" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W41 - UltraGear Buying Guide 2차" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W41 - Windows 11 Landing" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W41 - IT B2B TCO Mark" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'W41 - IT B2B TCO Mark'!$A$3:$G$232</definedName>
@@ -40546,7 +40546,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>10/15 기준 · 사전검토 59 · 법인리뷰 5(UK·EE·LT·LV·CA-fr) · 완료 1(CA-en) · 15개국 추가</t>
+          <t>10/20 기준 · 10/12 법인 LDM 승인 요청 → 16건 승인 회신(CZ·RO·HU·HR·RS·BG·TR·DE·UK·ES·CA·PA/CAC/EC·BR·GR·VN·ZA) · 작업중 16 · 사전검토 43 · 법인리뷰 5(UK·EE·LT·LV·CA-fr) · 완료 1(CA-en)</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -40759,7 +40759,7 @@
       <c r="C15" s="290" t="n"/>
       <c r="D15" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E15" s="123" t="n"/>
@@ -40768,7 +40768,7 @@
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>페이지 없음</t>
+          <t>10/12 LDM 승인 · 페이지 없음</t>
         </is>
       </c>
     </row>
@@ -40781,7 +40781,7 @@
       <c r="C16" s="290" t="n"/>
       <c r="D16" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E16" s="123" t="n"/>
@@ -40790,7 +40790,7 @@
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>페이지 없음</t>
+          <t>10/12 LDM 승인 · 페이지 없음</t>
         </is>
       </c>
     </row>
@@ -40820,7 +40820,7 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>로컬 드리븐 · WR2340922BH(LGCOMCI-5144)</t>
+          <t>10/12 LDM 승인 · 로컬 드리븐 · WR2340922BH(LGCOMCI-5144)</t>
         </is>
       </c>
     </row>
@@ -40846,7 +40846,7 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>로컬 드리븐 · WR2340921BH(LGCOMCI-5144)</t>
+          <t>10/12 LDM 승인 · 로컬 드리븐 · WR2340921BH(LGCOMCI-5144)</t>
         </is>
       </c>
     </row>
@@ -40863,14 +40863,18 @@
       </c>
       <c r="D19" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E19" s="123" t="n"/>
       <c r="F19" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="0" t="n"/>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>10/12 LDM 승인</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="261" t="inlineStr">
@@ -40973,7 +40977,7 @@
       </c>
       <c r="D24" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E24" s="123" t="n"/>
@@ -40982,7 +40986,7 @@
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t>접수됨, 착수 전</t>
+          <t>10/12 LDM 승인</t>
         </is>
       </c>
     </row>
@@ -40999,14 +41003,18 @@
       </c>
       <c r="D25" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E25" s="123" t="n"/>
       <c r="F25" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="0" t="n"/>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>10/12 LDM 승인</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="261" t="inlineStr">
@@ -41043,14 +41051,18 @@
       </c>
       <c r="D27" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E27" s="123" t="n"/>
       <c r="F27" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="0" t="n"/>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t>10/12 LDM 승인</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="261" t="inlineStr">
@@ -41091,14 +41103,18 @@
       </c>
       <c r="D29" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E29" s="123" t="n"/>
       <c r="F29" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="0" t="n"/>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>10/12 LDM 승인</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="B30" s="261" t="inlineStr">
@@ -41153,7 +41169,7 @@
       <c r="C32" s="290" t="n"/>
       <c r="D32" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E32" s="123" t="n"/>
@@ -41162,7 +41178,7 @@
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>페이지 없음</t>
+          <t>10/12 LDM 승인 · 페이지 없음</t>
         </is>
       </c>
     </row>
@@ -41223,7 +41239,7 @@
       <c r="C35" s="290" t="n"/>
       <c r="D35" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E35" s="123" t="n"/>
@@ -41232,7 +41248,7 @@
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t>페이지 없음</t>
+          <t>10/12 LDM 승인 · 페이지 없음</t>
         </is>
       </c>
     </row>
@@ -41249,14 +41265,18 @@
       </c>
       <c r="D36" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E36" s="123" t="n"/>
       <c r="F36" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="0" t="n"/>
+      <c r="G36" s="0" t="inlineStr">
+        <is>
+          <t>10/12 LDM 승인</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="B37" s="261" t="inlineStr">
@@ -41621,14 +41641,18 @@
       </c>
       <c r="D52" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E52" s="123" t="n"/>
       <c r="F52" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G52" s="0" t="n"/>
+      <c r="G52" s="0" t="inlineStr">
+        <is>
+          <t>10/12 LDM 승인</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="B53" s="261" t="inlineStr">
@@ -41727,7 +41751,7 @@
       <c r="C57" s="290" t="n"/>
       <c r="D57" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E57" s="123" t="n"/>
@@ -41736,7 +41760,7 @@
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
-          <t>페이지 없음</t>
+          <t>10/12 LDM 승인 · 페이지 없음</t>
         </is>
       </c>
     </row>
@@ -41753,14 +41777,18 @@
       </c>
       <c r="D58" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E58" s="123" t="n"/>
       <c r="F58" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G58" s="0" t="n"/>
+      <c r="G58" s="0" t="inlineStr">
+        <is>
+          <t>10/12 LDM 승인</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="B59" s="261" t="inlineStr">
@@ -41945,7 +41973,7 @@
       </c>
       <c r="D66" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E66" s="123" t="n"/>
@@ -41954,7 +41982,7 @@
       </c>
       <c r="G66" s="0" t="inlineStr">
         <is>
-          <t>접수됨, 착수 전</t>
+          <t>10/12 LDM 승인</t>
         </is>
       </c>
     </row>
@@ -42028,7 +42056,7 @@
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>로컬 드리븐 · WR2338674EL(LGCOMUK-3928) · 글로벌 건 취소</t>
+          <t>10/12 LDM 승인 · 로컬 드리븐 · WR2338674EL(LGCOMUK-3928) · 글로벌 건 취소</t>
         </is>
       </c>
     </row>
@@ -42085,7 +42113,7 @@
       <c r="C72" s="297" t="n"/>
       <c r="D72" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E72" s="123" t="n"/>
@@ -42094,7 +42122,7 @@
       </c>
       <c r="G72" s="0" t="inlineStr">
         <is>
-          <t>페이지 없음</t>
+          <t>10/12 LDM 승인 · 페이지 없음</t>
         </is>
       </c>
     </row>
@@ -42111,14 +42139,18 @@
       </c>
       <c r="D73" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E73" s="123" t="n"/>
       <c r="F73" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G73" s="0" t="n"/>
+      <c r="G73" s="0" t="inlineStr">
+        <is>
+          <t>10/12 LDM 승인</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -42056,7 +42056,7 @@
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>10/12 LDM 승인 · 로컬 드리븐 · WR2338674EL(LGCOMUK-3928) · 글로벌 건 취소</t>
+          <t>10/12 LDM 승인 · 로컬 드리븐 · WR2338674EL(LGCOMUK-3928)</t>
         </is>
       </c>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -3009,6 +3009,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -3597,6 +3598,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -5587,6 +5589,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -7516,6 +7519,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -40560,6 +40564,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -40820,7 +40825,7 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>10/12 LDM 승인 · 로컬 드리븐 · WR2340922BH(LGCOMCI-5144)</t>
+          <t>10/12 LDM 승인 · 로컬 드리븐</t>
         </is>
       </c>
     </row>
@@ -40846,7 +40851,7 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>10/12 LDM 승인 · 로컬 드리븐 · WR2340921BH(LGCOMCI-5144)</t>
+          <t>10/12 LDM 승인 · 로컬 드리븐</t>
         </is>
       </c>
     </row>
@@ -41086,7 +41091,7 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>로컬 드리븐 · WR2341063AK(LGCOMEE-557)</t>
+          <t>로컬 드리븐</t>
         </is>
       </c>
     </row>
@@ -41510,7 +41515,7 @@
       </c>
       <c r="G46" s="0" t="inlineStr">
         <is>
-          <t>로컬 드리븐 · WR2341062AK(LGCOMLT-527)</t>
+          <t>로컬 드리븐</t>
         </is>
       </c>
     </row>
@@ -41536,7 +41541,7 @@
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
-          <t>로컬 드리븐 · WR2341048AK(LGCOMLV-634)</t>
+          <t>로컬 드리븐</t>
         </is>
       </c>
     </row>
@@ -42056,7 +42061,7 @@
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>10/12 LDM 승인 · 로컬 드리븐 · WR2338674EL(LGCOMUK-3928)</t>
+          <t>10/12 LDM 승인 · 로컬 드리븐</t>
         </is>
       </c>
     </row>
@@ -48801,6 +48806,7 @@
       <c r="G5" s="127" t="n"/>
     </row>
     <row r="6" ht="40.5" customHeight="1" s="203"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="136" t="inlineStr">
         <is>
@@ -50592,6 +50598,10 @@
       <c r="F3" s="131" t="n"/>
       <c r="G3" s="127" t="n"/>
     </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="266" t="inlineStr">
         <is>
@@ -52046,6 +52056,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -53309,6 +53320,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -53871,6 +53883,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -3009,7 +3009,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -3598,7 +3597,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -5589,7 +5587,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -7519,7 +7516,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>
@@ -40564,7 +40560,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -48806,7 +48801,6 @@
       <c r="G5" s="127" t="n"/>
     </row>
     <row r="6" ht="40.5" customHeight="1" s="203"/>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="136" t="inlineStr">
         <is>
@@ -49683,7 +49677,7 @@
       </c>
       <c r="E20" s="123" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F20" s="123" t="n">
@@ -49813,7 +49807,7 @@
       </c>
       <c r="E25" s="123" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F25" s="123" t="n">
@@ -49839,7 +49833,7 @@
       </c>
       <c r="E26" s="123" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F26" s="123" t="n">
@@ -49983,7 +49977,7 @@
       </c>
       <c r="E32" s="123" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F32" s="123" t="n">
@@ -50061,7 +50055,7 @@
       </c>
       <c r="E35" s="123" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F35" s="123" t="n">
@@ -50209,7 +50203,7 @@
       </c>
       <c r="E41" s="123" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F41" s="123" t="n">
@@ -50235,7 +50229,7 @@
       </c>
       <c r="E42" s="123" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F42" s="123" t="n">
@@ -50309,7 +50303,7 @@
       </c>
       <c r="E45" s="123" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F45" s="123" t="n">
@@ -50335,7 +50329,7 @@
       </c>
       <c r="E46" s="123" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F46" s="123" t="n">
@@ -50598,10 +50592,6 @@
       <c r="F3" s="131" t="n"/>
       <c r="G3" s="127" t="n"/>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="266" t="inlineStr">
         <is>
@@ -52027,7 +52017,7 @@
       </c>
       <c r="B1" s="163" t="inlineStr">
         <is>
-          <t>GR26-W22-MS-IT UltraGear Bying Guide</t>
+          <t>GR26-W22-MS-IT UltraGear Buying Guide</t>
         </is>
       </c>
       <c r="C1" s="164" t="n"/>
@@ -52056,7 +52046,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -53320,7 +53309,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -53883,7 +53871,6 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="E5" s="127" t="n"/>
     </row>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -1,35 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W16 - CineBeam S PDP Video Upda" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W16 - Copilot+ Filter Creation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W16 - Microsoft PDP Gallery Car" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W17 - GNB Structure" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W18 - FAQ Request (UltraGear PL" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W18 - UltraGear OLED FAQ Update" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W22 - UltraGear Buying Guide" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - 27GM950B-B 갤러리 이미지 교체" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - 39GX950B 이미지 수정 2차" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - 52G930B Feature 수정 건" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W23 - UL인증 feature 삭제 1차" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W25 - Copilot+ Hero Banner" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W28 - AI Upscaling Disclaimer" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W28 - UL Verified Eye Comfort" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W30 - SmartMonitor ScreenShare" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W30 - UltraGear 1000Hz FAQ" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W31 - gram Secure Lock" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W31 - PDP Gallery Win11 Pro" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W31 - Smart Monitor Multi AI" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - UltraGear 27GX704A" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - Digital Trends Award 삭제" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - UltraGear PDP 5모델" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W32 - UltraFine PDP MIC 삭제" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W38 - gram pro gallery" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W41 - UltraGear Buying Guide 2차" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W41 - Windows 11 Landing" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="W41 - IT B2B TCO Mark" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="W16 - CineBeam S PDP Video Upda" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="W16 - Copilot+ Filter Creation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="W16 - Microsoft PDP Gallery Car" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="W17 - GNB Structure" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="W18 - FAQ Request (UltraGear PL" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="W18 - UltraGear OLED FAQ Update" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="W22 - UltraGear Buying Guide" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="W23 - 27GM950B-B 갤러리 이미지 교체" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="W23 - 39GX950B 이미지 수정 2차" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="W23 - 52G930B Feature 수정 건" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="W23 - UL인증 feature 삭제 1차" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="W25 - Copilot+ Hero Banner" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="W28 - AI Upscaling Disclaimer" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="W28 - UL Verified Eye Comfort" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="W30 - SmartMonitor ScreenShare" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="W30 - UltraGear 1000Hz FAQ" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="W31 - gram Secure Lock" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="W31 - PDP Gallery Win11 Pro" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="W31 - Smart Monitor Multi AI" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="W32 - UltraGear 27GX704A" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="W32 - Digital Trends Award 삭제" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="W32 - UltraGear PDP 5모델" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="W32 - UltraFine PDP MIC 삭제" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="W38 - gram pro gallery" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="W41 - UltraGear Buying Guide 2차" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="W41 - Windows 11 Landing" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="W41 - IT B2B TCO Mark" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'W41 - IT B2B TCO Mark'!$A$3:$G$232</definedName>
@@ -40546,7 +40546,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>10/20 기준 · 10/12 법인 LDM 승인 요청 → 16건 승인 회신(CZ·RO·HU·HR·RS·BG·TR·DE·UK·ES·CA·PA/CAC/EC·BR·GR·VN·ZA) · 작업중 16 · 사전검토 43 · 법인리뷰 5(UK·EE·LT·LV·CA-fr) · 완료 1(CA-en)</t>
+          <t>10/22 PTT · 사전검토 64 · 취소 1</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -40560,6 +40560,7 @@
       <c r="D3" s="164" t="n"/>
       <c r="E3" s="165" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="127" t="n"/>
       <c r="B5" s="127" t="n"/>
@@ -40759,7 +40760,7 @@
       <c r="C15" s="290" t="n"/>
       <c r="D15" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E15" s="123" t="n"/>
@@ -40781,7 +40782,7 @@
       <c r="C16" s="290" t="n"/>
       <c r="D16" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E16" s="123" t="n"/>
@@ -40807,14 +40808,10 @@
       </c>
       <c r="D17" s="265" t="inlineStr">
         <is>
-          <t>완료</t>
-        </is>
-      </c>
-      <c r="E17" s="123" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
+          <t>사전검토</t>
+        </is>
+      </c>
+      <c r="E17" s="123" t="n"/>
       <c r="F17" s="0" t="n">
         <v>1</v>
       </c>
@@ -40837,7 +40834,7 @@
       </c>
       <c r="D18" s="265" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E18" s="123" t="n"/>
@@ -40863,7 +40860,7 @@
       </c>
       <c r="D19" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E19" s="123" t="n"/>
@@ -40977,7 +40974,7 @@
       </c>
       <c r="D24" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E24" s="123" t="n"/>
@@ -41003,7 +41000,7 @@
       </c>
       <c r="D25" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E25" s="123" t="n"/>
@@ -41051,7 +41048,7 @@
       </c>
       <c r="D27" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E27" s="123" t="n"/>
@@ -41077,7 +41074,7 @@
       </c>
       <c r="D28" s="265" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E28" s="123" t="n"/>
@@ -41103,7 +41100,7 @@
       </c>
       <c r="D29" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E29" s="123" t="n"/>
@@ -41169,7 +41166,7 @@
       <c r="C32" s="290" t="n"/>
       <c r="D32" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E32" s="123" t="n"/>
@@ -41239,7 +41236,7 @@
       <c r="C35" s="290" t="n"/>
       <c r="D35" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E35" s="123" t="n"/>
@@ -41265,7 +41262,7 @@
       </c>
       <c r="D36" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E36" s="123" t="n"/>
@@ -41501,7 +41498,7 @@
       </c>
       <c r="D46" s="265" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E46" s="123" t="n"/>
@@ -41527,7 +41524,7 @@
       </c>
       <c r="D47" s="265" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E47" s="123" t="n"/>
@@ -41641,7 +41638,7 @@
       </c>
       <c r="D52" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E52" s="123" t="n"/>
@@ -41751,7 +41748,7 @@
       <c r="C57" s="290" t="n"/>
       <c r="D57" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E57" s="123" t="n"/>
@@ -41777,7 +41774,7 @@
       </c>
       <c r="D58" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E58" s="123" t="n"/>
@@ -41973,7 +41970,7 @@
       </c>
       <c r="D66" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E66" s="123" t="n"/>
@@ -42047,7 +42044,7 @@
       </c>
       <c r="D69" s="265" t="inlineStr">
         <is>
-          <t>법인리뷰</t>
+          <t>취소</t>
         </is>
       </c>
       <c r="E69" s="123" t="n"/>
@@ -42113,7 +42110,7 @@
       <c r="C72" s="297" t="n"/>
       <c r="D72" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E72" s="123" t="n"/>
@@ -42139,7 +42136,7 @@
       </c>
       <c r="D73" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E73" s="123" t="n"/>
@@ -42230,7 +42227,7 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>15사이트 사전검토 · Due 2026-10-31</t>
+          <t>10/22 PTT · 작업중 15 · Due 2026-10-31</t>
         </is>
       </c>
     </row>
@@ -42284,7 +42281,7 @@
       </c>
       <c r="D4" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E4" s="123" t="n"/>
@@ -42310,7 +42307,7 @@
       </c>
       <c r="D5" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E5" s="123" t="n"/>
@@ -42336,7 +42333,7 @@
       </c>
       <c r="D6" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E6" s="123" t="n"/>
@@ -42362,7 +42359,7 @@
       </c>
       <c r="D7" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E7" s="123" t="n"/>
@@ -42388,7 +42385,7 @@
       </c>
       <c r="D8" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E8" s="123" t="n"/>
@@ -42414,7 +42411,7 @@
       </c>
       <c r="D9" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E9" s="123" t="n"/>
@@ -42440,7 +42437,7 @@
       </c>
       <c r="D10" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E10" s="123" t="n"/>
@@ -42466,7 +42463,7 @@
       </c>
       <c r="D11" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E11" s="123" t="n"/>
@@ -42492,7 +42489,7 @@
       </c>
       <c r="D12" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E12" s="123" t="n"/>
@@ -42518,7 +42515,7 @@
       </c>
       <c r="D13" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E13" s="123" t="n"/>
@@ -42544,7 +42541,7 @@
       </c>
       <c r="D14" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E14" s="123" t="n"/>
@@ -42570,7 +42567,7 @@
       </c>
       <c r="D15" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E15" s="123" t="n"/>
@@ -42596,7 +42593,7 @@
       </c>
       <c r="D16" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E16" s="123" t="n"/>
@@ -42622,7 +42619,7 @@
       </c>
       <c r="D17" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E17" s="123" t="n"/>
@@ -42648,7 +42645,7 @@
       </c>
       <c r="D18" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E18" s="123" t="n"/>
@@ -42721,7 +42718,7 @@
       </c>
       <c r="B2" s="295" t="inlineStr">
         <is>
-          <t>10/14 등록 · 담당 김수안 선임 · Due 2026-10-30 · 23개국 · 229 PDP · 40모델 · 사전검토</t>
+          <t>10/22 PTT · QA review 21개국 · Request Clarification ae-en,ae-ar · 작업중 229 · Due 2026-10-30</t>
         </is>
       </c>
     </row>
@@ -42775,7 +42772,7 @@
       </c>
       <c r="D4" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F4" s="295" t="n">
@@ -42800,7 +42797,7 @@
       </c>
       <c r="D5" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F5" s="295" t="n">
@@ -42825,7 +42822,7 @@
       </c>
       <c r="D6" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F6" s="295" t="n">
@@ -42850,7 +42847,7 @@
       </c>
       <c r="D7" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F7" s="295" t="n">
@@ -42875,7 +42872,7 @@
       </c>
       <c r="D8" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F8" s="295" t="n">
@@ -42900,7 +42897,7 @@
       </c>
       <c r="D9" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F9" s="295" t="n">
@@ -42925,7 +42922,7 @@
       </c>
       <c r="D10" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F10" s="295" t="n">
@@ -42950,7 +42947,7 @@
       </c>
       <c r="D11" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F11" s="295" t="n">
@@ -42975,7 +42972,7 @@
       </c>
       <c r="D12" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F12" s="295" t="n">
@@ -43000,7 +42997,7 @@
       </c>
       <c r="D13" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F13" s="295" t="n">
@@ -43025,7 +43022,7 @@
       </c>
       <c r="D14" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F14" s="295" t="n">
@@ -43050,7 +43047,7 @@
       </c>
       <c r="D15" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F15" s="295" t="n">
@@ -43075,7 +43072,7 @@
       </c>
       <c r="D16" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F16" s="295" t="n">
@@ -43100,7 +43097,7 @@
       </c>
       <c r="D17" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F17" s="295" t="n">
@@ -43125,7 +43122,7 @@
       </c>
       <c r="D18" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F18" s="295" t="n">
@@ -43150,7 +43147,7 @@
       </c>
       <c r="D19" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F19" s="295" t="n">
@@ -43175,7 +43172,7 @@
       </c>
       <c r="D20" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F20" s="295" t="n">
@@ -43200,7 +43197,7 @@
       </c>
       <c r="D21" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F21" s="295" t="n">
@@ -43225,7 +43222,7 @@
       </c>
       <c r="D22" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F22" s="295" t="n">
@@ -43250,7 +43247,7 @@
       </c>
       <c r="D23" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F23" s="295" t="n">
@@ -43275,7 +43272,7 @@
       </c>
       <c r="D24" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F24" s="295" t="n">
@@ -43300,7 +43297,7 @@
       </c>
       <c r="D25" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F25" s="295" t="n">
@@ -43325,7 +43322,7 @@
       </c>
       <c r="D26" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F26" s="295" t="n">
@@ -43350,7 +43347,7 @@
       </c>
       <c r="D27" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F27" s="295" t="n">
@@ -43375,7 +43372,7 @@
       </c>
       <c r="D28" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F28" s="295" t="n">
@@ -43400,7 +43397,7 @@
       </c>
       <c r="D29" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F29" s="295" t="n">
@@ -43425,7 +43422,7 @@
       </c>
       <c r="D30" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F30" s="295" t="n">
@@ -43450,7 +43447,7 @@
       </c>
       <c r="D31" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F31" s="295" t="n">
@@ -43475,7 +43472,7 @@
       </c>
       <c r="D32" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F32" s="295" t="n">
@@ -43500,7 +43497,7 @@
       </c>
       <c r="D33" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F33" s="295" t="n">
@@ -43525,7 +43522,7 @@
       </c>
       <c r="D34" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F34" s="295" t="n">
@@ -43550,7 +43547,7 @@
       </c>
       <c r="D35" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F35" s="295" t="n">
@@ -43575,7 +43572,7 @@
       </c>
       <c r="D36" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F36" s="295" t="n">
@@ -43600,7 +43597,7 @@
       </c>
       <c r="D37" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F37" s="295" t="n">
@@ -43625,7 +43622,7 @@
       </c>
       <c r="D38" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F38" s="295" t="n">
@@ -43650,7 +43647,7 @@
       </c>
       <c r="D39" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F39" s="295" t="n">
@@ -43675,7 +43672,7 @@
       </c>
       <c r="D40" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F40" s="295" t="n">
@@ -43700,7 +43697,7 @@
       </c>
       <c r="D41" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F41" s="295" t="n">
@@ -43725,7 +43722,7 @@
       </c>
       <c r="D42" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F42" s="295" t="n">
@@ -43750,7 +43747,7 @@
       </c>
       <c r="D43" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F43" s="295" t="n">
@@ -43775,7 +43772,7 @@
       </c>
       <c r="D44" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F44" s="295" t="n">
@@ -43800,7 +43797,7 @@
       </c>
       <c r="D45" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F45" s="295" t="n">
@@ -43825,7 +43822,7 @@
       </c>
       <c r="D46" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F46" s="295" t="n">
@@ -43850,7 +43847,7 @@
       </c>
       <c r="D47" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F47" s="295" t="n">
@@ -43875,7 +43872,7 @@
       </c>
       <c r="D48" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F48" s="295" t="n">
@@ -43900,7 +43897,7 @@
       </c>
       <c r="D49" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F49" s="295" t="n">
@@ -43925,7 +43922,7 @@
       </c>
       <c r="D50" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F50" s="295" t="n">
@@ -43950,7 +43947,7 @@
       </c>
       <c r="D51" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F51" s="295" t="n">
@@ -43975,7 +43972,7 @@
       </c>
       <c r="D52" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F52" s="295" t="n">
@@ -44000,7 +43997,7 @@
       </c>
       <c r="D53" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F53" s="295" t="n">
@@ -44025,7 +44022,7 @@
       </c>
       <c r="D54" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F54" s="295" t="n">
@@ -44050,7 +44047,7 @@
       </c>
       <c r="D55" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F55" s="295" t="n">
@@ -44075,7 +44072,7 @@
       </c>
       <c r="D56" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F56" s="295" t="n">
@@ -44100,7 +44097,7 @@
       </c>
       <c r="D57" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F57" s="295" t="n">
@@ -44125,7 +44122,7 @@
       </c>
       <c r="D58" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F58" s="295" t="n">
@@ -44150,7 +44147,7 @@
       </c>
       <c r="D59" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F59" s="295" t="n">
@@ -44175,7 +44172,7 @@
       </c>
       <c r="D60" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F60" s="295" t="n">
@@ -44200,7 +44197,7 @@
       </c>
       <c r="D61" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F61" s="295" t="n">
@@ -44225,7 +44222,7 @@
       </c>
       <c r="D62" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F62" s="295" t="n">
@@ -44250,7 +44247,7 @@
       </c>
       <c r="D63" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F63" s="295" t="n">
@@ -44275,7 +44272,7 @@
       </c>
       <c r="D64" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F64" s="295" t="n">
@@ -44300,7 +44297,7 @@
       </c>
       <c r="D65" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F65" s="295" t="n">
@@ -44325,7 +44322,7 @@
       </c>
       <c r="D66" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F66" s="295" t="n">
@@ -44350,7 +44347,7 @@
       </c>
       <c r="D67" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F67" s="295" t="n">
@@ -44375,7 +44372,7 @@
       </c>
       <c r="D68" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F68" s="295" t="n">
@@ -44400,7 +44397,7 @@
       </c>
       <c r="D69" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F69" s="295" t="n">
@@ -44425,7 +44422,7 @@
       </c>
       <c r="D70" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F70" s="295" t="n">
@@ -44450,7 +44447,7 @@
       </c>
       <c r="D71" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F71" s="295" t="n">
@@ -44475,7 +44472,7 @@
       </c>
       <c r="D72" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F72" s="295" t="n">
@@ -44500,7 +44497,7 @@
       </c>
       <c r="D73" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F73" s="295" t="n">
@@ -44525,7 +44522,7 @@
       </c>
       <c r="D74" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F74" s="295" t="n">
@@ -44550,7 +44547,7 @@
       </c>
       <c r="D75" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F75" s="295" t="n">
@@ -44575,7 +44572,7 @@
       </c>
       <c r="D76" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F76" s="295" t="n">
@@ -44600,7 +44597,7 @@
       </c>
       <c r="D77" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F77" s="295" t="n">
@@ -44625,7 +44622,7 @@
       </c>
       <c r="D78" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F78" s="295" t="n">
@@ -44650,7 +44647,7 @@
       </c>
       <c r="D79" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F79" s="295" t="n">
@@ -44675,7 +44672,7 @@
       </c>
       <c r="D80" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F80" s="295" t="n">
@@ -44700,7 +44697,7 @@
       </c>
       <c r="D81" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F81" s="295" t="n">
@@ -44725,7 +44722,7 @@
       </c>
       <c r="D82" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F82" s="295" t="n">
@@ -44750,7 +44747,7 @@
       </c>
       <c r="D83" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F83" s="295" t="n">
@@ -44775,7 +44772,7 @@
       </c>
       <c r="D84" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F84" s="295" t="n">
@@ -44800,7 +44797,7 @@
       </c>
       <c r="D85" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F85" s="295" t="n">
@@ -44825,7 +44822,7 @@
       </c>
       <c r="D86" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F86" s="295" t="n">
@@ -44850,7 +44847,7 @@
       </c>
       <c r="D87" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F87" s="295" t="n">
@@ -44875,7 +44872,7 @@
       </c>
       <c r="D88" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F88" s="295" t="n">
@@ -44900,7 +44897,7 @@
       </c>
       <c r="D89" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F89" s="295" t="n">
@@ -44925,7 +44922,7 @@
       </c>
       <c r="D90" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F90" s="295" t="n">
@@ -44950,7 +44947,7 @@
       </c>
       <c r="D91" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F91" s="295" t="n">
@@ -44975,7 +44972,7 @@
       </c>
       <c r="D92" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F92" s="295" t="n">
@@ -45000,7 +44997,7 @@
       </c>
       <c r="D93" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F93" s="295" t="n">
@@ -45025,7 +45022,7 @@
       </c>
       <c r="D94" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F94" s="295" t="n">
@@ -45050,7 +45047,7 @@
       </c>
       <c r="D95" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F95" s="295" t="n">
@@ -45075,7 +45072,7 @@
       </c>
       <c r="D96" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F96" s="295" t="n">
@@ -45100,7 +45097,7 @@
       </c>
       <c r="D97" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F97" s="295" t="n">
@@ -45125,7 +45122,7 @@
       </c>
       <c r="D98" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F98" s="295" t="n">
@@ -45150,7 +45147,7 @@
       </c>
       <c r="D99" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F99" s="295" t="n">
@@ -45175,7 +45172,7 @@
       </c>
       <c r="D100" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F100" s="295" t="n">
@@ -45200,7 +45197,7 @@
       </c>
       <c r="D101" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F101" s="295" t="n">
@@ -45225,7 +45222,7 @@
       </c>
       <c r="D102" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F102" s="295" t="n">
@@ -45250,7 +45247,7 @@
       </c>
       <c r="D103" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F103" s="295" t="n">
@@ -45275,7 +45272,7 @@
       </c>
       <c r="D104" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F104" s="295" t="n">
@@ -45300,7 +45297,7 @@
       </c>
       <c r="D105" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F105" s="295" t="n">
@@ -45325,7 +45322,7 @@
       </c>
       <c r="D106" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F106" s="295" t="n">
@@ -45350,7 +45347,7 @@
       </c>
       <c r="D107" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F107" s="295" t="n">
@@ -45375,7 +45372,7 @@
       </c>
       <c r="D108" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F108" s="295" t="n">
@@ -45400,7 +45397,7 @@
       </c>
       <c r="D109" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F109" s="295" t="n">
@@ -45425,7 +45422,7 @@
       </c>
       <c r="D110" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F110" s="295" t="n">
@@ -45450,7 +45447,7 @@
       </c>
       <c r="D111" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F111" s="295" t="n">
@@ -45475,7 +45472,7 @@
       </c>
       <c r="D112" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F112" s="295" t="n">
@@ -45500,7 +45497,7 @@
       </c>
       <c r="D113" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F113" s="295" t="n">
@@ -45525,7 +45522,7 @@
       </c>
       <c r="D114" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F114" s="295" t="n">
@@ -45550,7 +45547,7 @@
       </c>
       <c r="D115" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F115" s="295" t="n">
@@ -45575,7 +45572,7 @@
       </c>
       <c r="D116" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F116" s="295" t="n">
@@ -45600,7 +45597,7 @@
       </c>
       <c r="D117" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F117" s="295" t="n">
@@ -45625,7 +45622,7 @@
       </c>
       <c r="D118" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F118" s="295" t="n">
@@ -45650,7 +45647,7 @@
       </c>
       <c r="D119" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F119" s="295" t="n">
@@ -45675,7 +45672,7 @@
       </c>
       <c r="D120" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F120" s="295" t="n">
@@ -45700,7 +45697,7 @@
       </c>
       <c r="D121" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F121" s="295" t="n">
@@ -45725,7 +45722,7 @@
       </c>
       <c r="D122" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F122" s="295" t="n">
@@ -45750,7 +45747,7 @@
       </c>
       <c r="D123" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F123" s="295" t="n">
@@ -45775,7 +45772,7 @@
       </c>
       <c r="D124" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F124" s="295" t="n">
@@ -45800,7 +45797,7 @@
       </c>
       <c r="D125" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F125" s="295" t="n">
@@ -45825,7 +45822,7 @@
       </c>
       <c r="D126" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F126" s="295" t="n">
@@ -45850,7 +45847,7 @@
       </c>
       <c r="D127" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F127" s="295" t="n">
@@ -45875,7 +45872,7 @@
       </c>
       <c r="D128" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F128" s="295" t="n">
@@ -45900,7 +45897,7 @@
       </c>
       <c r="D129" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F129" s="295" t="n">
@@ -45925,7 +45922,7 @@
       </c>
       <c r="D130" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F130" s="295" t="n">
@@ -45950,7 +45947,7 @@
       </c>
       <c r="D131" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F131" s="295" t="n">
@@ -45975,7 +45972,7 @@
       </c>
       <c r="D132" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F132" s="295" t="n">
@@ -46000,7 +45997,7 @@
       </c>
       <c r="D133" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F133" s="295" t="n">
@@ -46025,7 +46022,7 @@
       </c>
       <c r="D134" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F134" s="295" t="n">
@@ -46050,7 +46047,7 @@
       </c>
       <c r="D135" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F135" s="295" t="n">
@@ -46075,7 +46072,7 @@
       </c>
       <c r="D136" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F136" s="295" t="n">
@@ -46100,7 +46097,7 @@
       </c>
       <c r="D137" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F137" s="295" t="n">
@@ -46125,7 +46122,7 @@
       </c>
       <c r="D138" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F138" s="295" t="n">
@@ -46150,7 +46147,7 @@
       </c>
       <c r="D139" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F139" s="295" t="n">
@@ -46175,7 +46172,7 @@
       </c>
       <c r="D140" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F140" s="295" t="n">
@@ -46200,7 +46197,7 @@
       </c>
       <c r="D141" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F141" s="295" t="n">
@@ -46225,7 +46222,7 @@
       </c>
       <c r="D142" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F142" s="295" t="n">
@@ -46250,7 +46247,7 @@
       </c>
       <c r="D143" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F143" s="295" t="n">
@@ -46275,7 +46272,7 @@
       </c>
       <c r="D144" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F144" s="295" t="n">
@@ -46300,7 +46297,7 @@
       </c>
       <c r="D145" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F145" s="295" t="n">
@@ -46325,7 +46322,7 @@
       </c>
       <c r="D146" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F146" s="295" t="n">
@@ -46350,7 +46347,7 @@
       </c>
       <c r="D147" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F147" s="295" t="n">
@@ -46375,7 +46372,7 @@
       </c>
       <c r="D148" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F148" s="295" t="n">
@@ -46400,7 +46397,7 @@
       </c>
       <c r="D149" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F149" s="295" t="n">
@@ -46425,7 +46422,7 @@
       </c>
       <c r="D150" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F150" s="295" t="n">
@@ -46450,7 +46447,7 @@
       </c>
       <c r="D151" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F151" s="295" t="n">
@@ -46475,7 +46472,7 @@
       </c>
       <c r="D152" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F152" s="295" t="n">
@@ -46500,7 +46497,7 @@
       </c>
       <c r="D153" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F153" s="295" t="n">
@@ -46525,7 +46522,7 @@
       </c>
       <c r="D154" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F154" s="295" t="n">
@@ -46550,7 +46547,7 @@
       </c>
       <c r="D155" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F155" s="295" t="n">
@@ -46575,7 +46572,7 @@
       </c>
       <c r="D156" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F156" s="295" t="n">
@@ -46600,7 +46597,7 @@
       </c>
       <c r="D157" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F157" s="295" t="n">
@@ -46625,7 +46622,7 @@
       </c>
       <c r="D158" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F158" s="295" t="n">
@@ -46650,7 +46647,7 @@
       </c>
       <c r="D159" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F159" s="295" t="n">
@@ -46675,7 +46672,7 @@
       </c>
       <c r="D160" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F160" s="295" t="n">
@@ -46700,7 +46697,7 @@
       </c>
       <c r="D161" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F161" s="295" t="n">
@@ -46725,7 +46722,7 @@
       </c>
       <c r="D162" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F162" s="295" t="n">
@@ -46750,7 +46747,7 @@
       </c>
       <c r="D163" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F163" s="295" t="n">
@@ -46775,7 +46772,7 @@
       </c>
       <c r="D164" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F164" s="295" t="n">
@@ -46800,7 +46797,7 @@
       </c>
       <c r="D165" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F165" s="295" t="n">
@@ -46825,7 +46822,7 @@
       </c>
       <c r="D166" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F166" s="295" t="n">
@@ -46850,7 +46847,7 @@
       </c>
       <c r="D167" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F167" s="295" t="n">
@@ -46875,7 +46872,7 @@
       </c>
       <c r="D168" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F168" s="295" t="n">
@@ -46900,7 +46897,7 @@
       </c>
       <c r="D169" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F169" s="295" t="n">
@@ -46925,7 +46922,7 @@
       </c>
       <c r="D170" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F170" s="295" t="n">
@@ -46950,7 +46947,7 @@
       </c>
       <c r="D171" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F171" s="295" t="n">
@@ -46975,7 +46972,7 @@
       </c>
       <c r="D172" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F172" s="295" t="n">
@@ -47000,7 +46997,7 @@
       </c>
       <c r="D173" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F173" s="295" t="n">
@@ -47025,7 +47022,7 @@
       </c>
       <c r="D174" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F174" s="295" t="n">
@@ -47050,7 +47047,7 @@
       </c>
       <c r="D175" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F175" s="295" t="n">
@@ -47075,7 +47072,7 @@
       </c>
       <c r="D176" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F176" s="295" t="n">
@@ -47100,7 +47097,7 @@
       </c>
       <c r="D177" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F177" s="295" t="n">
@@ -47125,7 +47122,7 @@
       </c>
       <c r="D178" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F178" s="295" t="n">
@@ -47150,7 +47147,7 @@
       </c>
       <c r="D179" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F179" s="295" t="n">
@@ -47175,7 +47172,7 @@
       </c>
       <c r="D180" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F180" s="295" t="n">
@@ -47200,7 +47197,7 @@
       </c>
       <c r="D181" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F181" s="295" t="n">
@@ -47225,7 +47222,7 @@
       </c>
       <c r="D182" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F182" s="295" t="n">
@@ -47250,7 +47247,7 @@
       </c>
       <c r="D183" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F183" s="295" t="n">
@@ -47275,7 +47272,7 @@
       </c>
       <c r="D184" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F184" s="295" t="n">
@@ -47300,7 +47297,7 @@
       </c>
       <c r="D185" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F185" s="295" t="n">
@@ -47325,7 +47322,7 @@
       </c>
       <c r="D186" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F186" s="295" t="n">
@@ -47350,7 +47347,7 @@
       </c>
       <c r="D187" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F187" s="295" t="n">
@@ -47375,7 +47372,7 @@
       </c>
       <c r="D188" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F188" s="295" t="n">
@@ -47400,7 +47397,7 @@
       </c>
       <c r="D189" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F189" s="295" t="n">
@@ -47425,7 +47422,7 @@
       </c>
       <c r="D190" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F190" s="295" t="n">
@@ -47450,7 +47447,7 @@
       </c>
       <c r="D191" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F191" s="295" t="n">
@@ -47475,7 +47472,7 @@
       </c>
       <c r="D192" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F192" s="295" t="n">
@@ -47500,7 +47497,7 @@
       </c>
       <c r="D193" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F193" s="295" t="n">
@@ -47525,7 +47522,7 @@
       </c>
       <c r="D194" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F194" s="295" t="n">
@@ -47550,7 +47547,7 @@
       </c>
       <c r="D195" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F195" s="295" t="n">
@@ -47575,7 +47572,7 @@
       </c>
       <c r="D196" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F196" s="295" t="n">
@@ -47600,7 +47597,7 @@
       </c>
       <c r="D197" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F197" s="295" t="n">
@@ -47625,7 +47622,7 @@
       </c>
       <c r="D198" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F198" s="295" t="n">
@@ -47650,7 +47647,7 @@
       </c>
       <c r="D199" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F199" s="295" t="n">
@@ -47675,7 +47672,7 @@
       </c>
       <c r="D200" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F200" s="295" t="n">
@@ -47700,7 +47697,7 @@
       </c>
       <c r="D201" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F201" s="295" t="n">
@@ -47725,7 +47722,7 @@
       </c>
       <c r="D202" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F202" s="295" t="n">
@@ -47750,7 +47747,7 @@
       </c>
       <c r="D203" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F203" s="295" t="n">
@@ -47775,7 +47772,7 @@
       </c>
       <c r="D204" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F204" s="295" t="n">
@@ -47800,7 +47797,7 @@
       </c>
       <c r="D205" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F205" s="295" t="n">
@@ -47825,7 +47822,7 @@
       </c>
       <c r="D206" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F206" s="295" t="n">
@@ -47850,7 +47847,7 @@
       </c>
       <c r="D207" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F207" s="295" t="n">
@@ -47875,7 +47872,7 @@
       </c>
       <c r="D208" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F208" s="295" t="n">
@@ -47900,7 +47897,7 @@
       </c>
       <c r="D209" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F209" s="295" t="n">
@@ -47925,7 +47922,7 @@
       </c>
       <c r="D210" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F210" s="295" t="n">
@@ -47950,7 +47947,7 @@
       </c>
       <c r="D211" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F211" s="295" t="n">
@@ -47975,7 +47972,7 @@
       </c>
       <c r="D212" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F212" s="295" t="n">
@@ -48000,7 +47997,7 @@
       </c>
       <c r="D213" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F213" s="295" t="n">
@@ -48025,7 +48022,7 @@
       </c>
       <c r="D214" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F214" s="295" t="n">
@@ -48050,7 +48047,7 @@
       </c>
       <c r="D215" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F215" s="295" t="n">
@@ -48075,7 +48072,7 @@
       </c>
       <c r="D216" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F216" s="295" t="n">
@@ -48100,7 +48097,7 @@
       </c>
       <c r="D217" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F217" s="295" t="n">
@@ -48125,7 +48122,7 @@
       </c>
       <c r="D218" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F218" s="295" t="n">
@@ -48150,7 +48147,7 @@
       </c>
       <c r="D219" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F219" s="295" t="n">
@@ -48175,7 +48172,7 @@
       </c>
       <c r="D220" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F220" s="295" t="n">
@@ -48200,7 +48197,7 @@
       </c>
       <c r="D221" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F221" s="295" t="n">
@@ -48225,7 +48222,7 @@
       </c>
       <c r="D222" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F222" s="295" t="n">
@@ -48250,7 +48247,7 @@
       </c>
       <c r="D223" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F223" s="295" t="n">
@@ -48275,7 +48272,7 @@
       </c>
       <c r="D224" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F224" s="295" t="n">
@@ -48300,7 +48297,7 @@
       </c>
       <c r="D225" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F225" s="295" t="n">
@@ -48325,7 +48322,7 @@
       </c>
       <c r="D226" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F226" s="295" t="n">
@@ -48350,7 +48347,7 @@
       </c>
       <c r="D227" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F227" s="295" t="n">
@@ -48375,7 +48372,7 @@
       </c>
       <c r="D228" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F228" s="295" t="n">
@@ -48400,7 +48397,7 @@
       </c>
       <c r="D229" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F229" s="295" t="n">
@@ -48425,7 +48422,7 @@
       </c>
       <c r="D230" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F230" s="295" t="n">
@@ -48450,7 +48447,7 @@
       </c>
       <c r="D231" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F231" s="295" t="n">
@@ -48475,7 +48472,7 @@
       </c>
       <c r="D232" s="295" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="F232" s="295" t="n">

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -40546,7 +40546,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>10/22 PTT · 사전검토 64 · 취소 1</t>
+          <t>10/22 법인 PTT 반영 · 완료 1 · 법인리뷰 1 · 작업중 21 · 사전검토 42 · 법인 PTT 없는 국가는 GR PTT(사전검토)와 10/12 LDM 승인 작업중을 유지</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -40760,7 +40760,7 @@
       <c r="C15" s="290" t="n"/>
       <c r="D15" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E15" s="123" t="n"/>
@@ -40782,7 +40782,7 @@
       <c r="C16" s="290" t="n"/>
       <c r="D16" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E16" s="123" t="n"/>
@@ -40808,16 +40808,20 @@
       </c>
       <c r="D17" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
-        </is>
-      </c>
-      <c r="E17" s="123" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="E17" s="123" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="F17" s="0" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>10/12 LDM 승인 · 로컬 드리븐</t>
+          <t>10/12 LDM 승인 · 로컬 드리븐 · 법인 PTT WR2340922BH Closed · LGCOMCI-5144</t>
         </is>
       </c>
     </row>
@@ -40834,7 +40838,7 @@
       </c>
       <c r="D18" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E18" s="123" t="n"/>
@@ -40843,7 +40847,7 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>10/12 LDM 승인 · 로컬 드리븐</t>
+          <t>10/12 LDM 승인 · 로컬 드리븐 · 법인 PTT WR2340921BH Final Live Check · LGCOMCI-5144</t>
         </is>
       </c>
     </row>
@@ -40860,7 +40864,7 @@
       </c>
       <c r="D19" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E19" s="123" t="n"/>
@@ -40974,7 +40978,7 @@
       </c>
       <c r="D24" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E24" s="123" t="n"/>
@@ -41000,7 +41004,7 @@
       </c>
       <c r="D25" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E25" s="123" t="n"/>
@@ -41048,7 +41052,7 @@
       </c>
       <c r="D27" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E27" s="123" t="n"/>
@@ -41074,7 +41078,7 @@
       </c>
       <c r="D28" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E28" s="123" t="n"/>
@@ -41083,7 +41087,7 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>로컬 드리븐</t>
+          <t>로컬 드리븐 · 법인 PTT WR2348552AK Publishing · LGCOMEE-557</t>
         </is>
       </c>
     </row>
@@ -41100,7 +41104,7 @@
       </c>
       <c r="D29" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E29" s="123" t="n"/>
@@ -41166,7 +41170,7 @@
       <c r="C32" s="290" t="n"/>
       <c r="D32" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E32" s="123" t="n"/>
@@ -41236,7 +41240,7 @@
       <c r="C35" s="290" t="n"/>
       <c r="D35" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E35" s="123" t="n"/>
@@ -41262,7 +41266,7 @@
       </c>
       <c r="D36" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E36" s="123" t="n"/>
@@ -41498,7 +41502,7 @@
       </c>
       <c r="D46" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E46" s="123" t="n"/>
@@ -41507,7 +41511,7 @@
       </c>
       <c r="G46" s="0" t="inlineStr">
         <is>
-          <t>로컬 드리븐</t>
+          <t>로컬 드리븐 · 법인 PTT WR2348544AK Publishing · LGCOMLT-527</t>
         </is>
       </c>
     </row>
@@ -41524,7 +41528,7 @@
       </c>
       <c r="D47" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E47" s="123" t="n"/>
@@ -41533,7 +41537,7 @@
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
-          <t>로컬 드리븐</t>
+          <t>로컬 드리븐 · 법인 PTT WR2346436AK Final Live Check · LGCOMLV-634</t>
         </is>
       </c>
     </row>
@@ -41550,14 +41554,18 @@
       </c>
       <c r="D48" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E48" s="123" t="n"/>
       <c r="F48" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="0" t="n"/>
+      <c r="G48" s="0" t="inlineStr">
+        <is>
+          <t>법인 PTT WR2341989SA Publishing · LGCOMMS-2686</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="B49" s="261" t="inlineStr">
@@ -41638,7 +41646,7 @@
       </c>
       <c r="D52" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E52" s="123" t="n"/>
@@ -41748,7 +41756,7 @@
       <c r="C57" s="290" t="n"/>
       <c r="D57" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E57" s="123" t="n"/>
@@ -41774,7 +41782,7 @@
       </c>
       <c r="D58" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E58" s="123" t="n"/>
@@ -41970,7 +41978,7 @@
       </c>
       <c r="D66" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E66" s="123" t="n"/>
@@ -42044,7 +42052,7 @@
       </c>
       <c r="D69" s="265" t="inlineStr">
         <is>
-          <t>취소</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E69" s="123" t="n"/>
@@ -42053,7 +42061,7 @@
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>10/12 LDM 승인 · 로컬 드리븐</t>
+          <t>10/12 LDM 승인 · 로컬 드리븐 · 법인 PTT WR2338674EL Client Review · LGCOMUK-3928</t>
         </is>
       </c>
     </row>
@@ -42110,7 +42118,7 @@
       <c r="C72" s="297" t="n"/>
       <c r="D72" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E72" s="123" t="n"/>
@@ -42136,7 +42144,7 @@
       </c>
       <c r="D73" s="265" t="inlineStr">
         <is>
-          <t>사전검토</t>
+          <t>작업중</t>
         </is>
       </c>
       <c r="E73" s="123" t="n"/>

--- a/it/Global Request.xlsx
+++ b/it/Global Request.xlsx
@@ -40546,7 +40546,7 @@
       </c>
       <c r="B2" s="163" t="inlineStr">
         <is>
-          <t>10/22 법인 PTT 반영 · 완료 1 · 법인리뷰 1 · 작업중 21 · 사전검토 42 · 법인 PTT 없는 국가는 GR PTT(사전검토)와 10/12 LDM 승인 작업중을 유지</t>
+          <t>10/20 기준 · 10/12 법인 LDM 승인 요청 → 16건 승인 회신(CZ·RO·HU·HR·RS·BG·TR·DE·UK·ES·CA·PA/CAC/EC·BR·GR·VN·ZA) · 작업중 16 · 사전검토 43 · 법인리뷰 5(UK·EE·LT·LV·CA-fr) · 완료 1(CA-en)</t>
         </is>
       </c>
       <c r="C2" s="164" t="n"/>
@@ -40813,7 +40813,7 @@
       </c>
       <c r="E17" s="123" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="F17" s="0" t="n">
@@ -40821,7 +40821,7 @@
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>10/12 LDM 승인 · 로컬 드리븐 · 법인 PTT WR2340922BH Closed · LGCOMCI-5144</t>
+          <t>10/12 LDM 승인 · 로컬 드리븐</t>
         </is>
       </c>
     </row>
@@ -40838,7 +40838,7 @@
       </c>
       <c r="D18" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E18" s="123" t="n"/>
@@ -40847,7 +40847,7 @@
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>10/12 LDM 승인 · 로컬 드리븐 · 법인 PTT WR2340921BH Final Live Check · LGCOMCI-5144</t>
+          <t>10/12 LDM 승인 · 로컬 드리븐</t>
         </is>
       </c>
     </row>
@@ -41078,7 +41078,7 @@
       </c>
       <c r="D28" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E28" s="123" t="n"/>
@@ -41087,7 +41087,7 @@
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>로컬 드리븐 · 법인 PTT WR2348552AK Publishing · LGCOMEE-557</t>
+          <t>로컬 드리븐</t>
         </is>
       </c>
     </row>
@@ -41502,7 +41502,7 @@
       </c>
       <c r="D46" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E46" s="123" t="n"/>
@@ -41511,7 +41511,7 @@
       </c>
       <c r="G46" s="0" t="inlineStr">
         <is>
-          <t>로컬 드리븐 · 법인 PTT WR2348544AK Publishing · LGCOMLT-527</t>
+          <t>로컬 드리븐</t>
         </is>
       </c>
     </row>
@@ -41528,7 +41528,7 @@
       </c>
       <c r="D47" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>법인리뷰</t>
         </is>
       </c>
       <c r="E47" s="123" t="n"/>
@@ -41537,7 +41537,7 @@
       </c>
       <c r="G47" s="0" t="inlineStr">
         <is>
-          <t>로컬 드리븐 · 법인 PTT WR2346436AK Final Live Check · LGCOMLV-634</t>
+          <t>로컬 드리븐</t>
         </is>
       </c>
     </row>
@@ -41554,18 +41554,14 @@
       </c>
       <c r="D48" s="265" t="inlineStr">
         <is>
-          <t>작업중</t>
+          <t>사전검토</t>
         </is>
       </c>
       <c r="E48" s="123" t="n"/>
       <c r="F48" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="G48" s="0" t="inlineStr">
-        <is>
-          <t>법인 PTT WR2341989SA Publishing · LGCOMMS-2686</t>
-        </is>
-      </c>
+      <c r="G48" s="0" t="n"/>
     </row>
     <row r="49">
       <c r="B49" s="261" t="inlineStr">
@@ -42061,7 +42057,7 @@
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>10/12 LDM 승인 · 로컬 드리븐 · 법인 PTT WR2338674EL Client Review · LGCOMUK-3928</t>
+          <t>10/12 LDM 승인 · 로컬 드리븐</t>
         </is>
       </c>
     </row>
